--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27886ABA-68E9-49D1-AF46-95EFEBFB5B31}"/>
+  <xr:revisionPtr revIDLastSave="211" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41C159C7-022A-4D9B-BF8C-A1276A60C35F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$2:$F$4164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$2:$G$4190</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8330" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8431" uniqueCount="155">
   <si>
     <t>Custo</t>
   </si>
@@ -475,6 +475,36 @@
   <si>
     <t>TURBOESTE</t>
   </si>
+  <si>
+    <t>VEMINAS CAMINHÕES</t>
+  </si>
+  <si>
+    <t>AUTO ALINHAMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CT DIESEL </t>
+  </si>
+  <si>
+    <t>vex</t>
+  </si>
+  <si>
+    <t>PEDÁGIO</t>
+  </si>
+  <si>
+    <t>GUILHERME RIBEIRO</t>
+  </si>
+  <si>
+    <t>LEONARDO OESTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS VINICIUS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS MEIRELES </t>
+  </si>
+  <si>
+    <t>LUAN FELIPE</t>
+  </si>
 </sst>
 </file>
 
@@ -483,7 +513,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -502,6 +532,12 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -695,7 +731,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -790,6 +826,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1127,16 +1166,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
-  <dimension ref="B2:F4245"/>
+  <dimension ref="B2:G4245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" style="35" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" style="35" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.85546875" style="35" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>61</v>
       </c>
@@ -1150,8 +1190,11 @@
       <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="36" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>63</v>
       </c>
@@ -1166,7 +1209,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
         <v>63</v>
       </c>
@@ -1181,7 +1224,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="s">
         <v>63</v>
       </c>
@@ -1196,7 +1239,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>63</v>
       </c>
@@ -1211,7 +1254,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>63</v>
       </c>
@@ -1226,7 +1269,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
         <v>63</v>
       </c>
@@ -1241,7 +1284,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
         <v>63</v>
       </c>
@@ -1256,7 +1299,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>63</v>
       </c>
@@ -1271,7 +1314,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>63</v>
       </c>
@@ -1286,7 +1329,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
         <v>63</v>
       </c>
@@ -1301,7 +1344,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
         <v>63</v>
       </c>
@@ -1316,7 +1359,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
         <v>63</v>
       </c>
@@ -1331,7 +1374,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
         <v>63</v>
       </c>
@@ -1346,7 +1389,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="11" t="s">
         <v>63</v>
       </c>
@@ -32321,7 +32364,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2081" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2081" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2081" s="15" t="s">
         <v>75</v>
       </c>
@@ -32336,7 +32379,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2082" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2082" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2082" s="15" t="s">
         <v>69</v>
       </c>
@@ -32351,7 +32394,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2083" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2083" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2083" s="15" t="s">
         <v>6</v>
       </c>
@@ -32366,7 +32409,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2084" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2084" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2084" s="15" t="s">
         <v>37</v>
       </c>
@@ -32381,7 +32424,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2085" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2085" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2085" s="15" t="s">
         <v>46</v>
       </c>
@@ -32396,7 +32439,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2086" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2086" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2086" s="15" t="s">
         <v>20</v>
       </c>
@@ -32411,7 +32454,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2087" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2087" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2087" s="15" t="s">
         <v>16</v>
       </c>
@@ -32426,7 +32469,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2088" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2088" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2088" s="15" t="s">
         <v>43</v>
       </c>
@@ -32441,7 +32484,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2089" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2089" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2089" s="15" t="s">
         <v>8</v>
       </c>
@@ -32456,7 +32499,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2090" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2090" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2090" s="15" t="s">
         <v>26</v>
       </c>
@@ -32471,7 +32514,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2091" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2091" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2091" s="15" t="s">
         <v>35</v>
       </c>
@@ -32486,7 +32529,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2092" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2092" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2092" s="15" t="s">
         <v>30</v>
       </c>
@@ -32501,7 +32544,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2093" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2093" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2093" s="15" t="s">
         <v>24</v>
       </c>
@@ -32516,7 +32559,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2094" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2094" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2094" s="15" t="s">
         <v>19</v>
       </c>
@@ -32531,13 +32574,13 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2095" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2095" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2095" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2095" s="6"/>
       <c r="D2095" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2095" s="29">
         <v>0.56000000000000005</v>
@@ -32545,14 +32588,17 @@
       <c r="F2095" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2096" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2095" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2096" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2096" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C2096" s="6"/>
       <c r="D2096" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2096" s="29">
         <v>0.56000000000000005</v>
@@ -32560,14 +32606,17 @@
       <c r="F2096" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2097" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2096" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2097" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2097" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2097" s="6"/>
       <c r="D2097" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2097" s="29">
         <v>0</v>
@@ -32575,14 +32624,17 @@
       <c r="F2097" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2098" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2097" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2098" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2098" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C2098" s="6"/>
       <c r="D2098" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2098" s="29">
         <v>0</v>
@@ -32590,14 +32642,17 @@
       <c r="F2098" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2099" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2098" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2099" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2099" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C2099" s="6"/>
       <c r="D2099" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2099" s="29">
         <v>0</v>
@@ -32605,14 +32660,17 @@
       <c r="F2099" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2100" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2099" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2100" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2100" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2100" s="6"/>
       <c r="D2100" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2100" s="29">
         <v>0</v>
@@ -32620,8 +32678,11 @@
       <c r="F2100" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2101" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2100" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2101" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2101" s="15" t="s">
         <v>5</v>
       </c>
@@ -32636,7 +32697,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2102" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2102" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2102" s="15" t="s">
         <v>5</v>
       </c>
@@ -32651,7 +32712,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2103" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2103" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2103" s="15" t="s">
         <v>5</v>
       </c>
@@ -32666,7 +32727,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2104" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2104" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2104" s="15" t="s">
         <v>76</v>
       </c>
@@ -32681,7 +32742,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2105" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2105" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2105" s="15" t="s">
         <v>3</v>
       </c>
@@ -32696,13 +32757,13 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2106" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2106" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2106" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C2106" s="6"/>
       <c r="D2106" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2106" s="29">
         <v>8.1999999999999993</v>
@@ -32710,8 +32771,11 @@
       <c r="F2106" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2107" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2106" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2107" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2107" s="15" t="s">
         <v>5</v>
       </c>
@@ -32726,7 +32790,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2108" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2108" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2108" s="15" t="s">
         <v>49</v>
       </c>
@@ -32741,7 +32805,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2109" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2109" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2109" s="15" t="s">
         <v>4</v>
       </c>
@@ -32756,7 +32820,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2110" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2110" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2110" s="15" t="s">
         <v>5</v>
       </c>
@@ -32771,7 +32835,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2111" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2111" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2111" s="15" t="s">
         <v>5</v>
       </c>
@@ -32786,7 +32850,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2112" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2112" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2112" s="15" t="s">
         <v>40</v>
       </c>
@@ -32801,7 +32865,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2113" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2113" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2113" s="15" t="s">
         <v>23</v>
       </c>
@@ -32816,7 +32880,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2114" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2114" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2114" s="15" t="s">
         <v>77</v>
       </c>
@@ -32831,7 +32895,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2115" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2115" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2115" s="15" t="s">
         <v>5</v>
       </c>
@@ -32846,7 +32910,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2116" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2116" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2116" s="15" t="s">
         <v>5</v>
       </c>
@@ -32861,7 +32925,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2117" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2117" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2117" s="15" t="s">
         <v>5</v>
       </c>
@@ -32876,7 +32940,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2118" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2118" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2118" s="15" t="s">
         <v>40</v>
       </c>
@@ -32891,7 +32955,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2119" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2119" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2119" s="15" t="s">
         <v>2</v>
       </c>
@@ -32906,13 +32970,13 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2120" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2120" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2120" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2120" s="6"/>
       <c r="D2120" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2120" s="29">
         <v>0</v>
@@ -32920,14 +32984,17 @@
       <c r="F2120" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2121" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2120" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2121" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2121" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C2121" s="6"/>
       <c r="D2121" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2121" s="29">
         <v>0</v>
@@ -32935,8 +33002,11 @@
       <c r="F2121" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2122" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2121" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2122" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2122" s="15" t="s">
         <v>4</v>
       </c>
@@ -32951,7 +33021,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2123" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2123" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2123" s="15" t="s">
         <v>77</v>
       </c>
@@ -32966,7 +33036,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2124" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2124" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2124" s="15" t="s">
         <v>40</v>
       </c>
@@ -32981,7 +33051,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2125" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2125" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2125" s="15" t="s">
         <v>5</v>
       </c>
@@ -32996,7 +33066,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2126" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2126" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2126" s="15" t="s">
         <v>5</v>
       </c>
@@ -33011,7 +33081,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2127" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2127" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2127" s="15" t="s">
         <v>12</v>
       </c>
@@ -33026,7 +33096,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2128" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2128" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2128" s="15" t="s">
         <v>37</v>
       </c>
@@ -33281,7 +33351,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2145" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2145" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2145" s="15" t="s">
         <v>11</v>
       </c>
@@ -33296,7 +33366,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2146" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2146" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2146" s="15" t="s">
         <v>39</v>
       </c>
@@ -33311,7 +33381,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2147" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2147" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2147" s="15" t="s">
         <v>13</v>
       </c>
@@ -33326,13 +33396,13 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2148" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2148" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2148" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C2148" s="6"/>
       <c r="D2148" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2148" s="29">
         <v>8.1999999999999993</v>
@@ -33340,8 +33410,11 @@
       <c r="F2148" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2149" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2148" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2149" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2149" s="15" t="s">
         <v>49</v>
       </c>
@@ -33356,7 +33429,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2150" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2150" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2150" s="15" t="s">
         <v>12</v>
       </c>
@@ -33371,7 +33444,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2151" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2151" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2151" s="15" t="s">
         <v>39</v>
       </c>
@@ -33386,7 +33459,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2152" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2152" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2152" s="15" t="s">
         <v>37</v>
       </c>
@@ -33401,7 +33474,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2153" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2153" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2153" s="15" t="s">
         <v>2</v>
       </c>
@@ -33416,7 +33489,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2154" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2154" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2154" s="15" t="s">
         <v>4</v>
       </c>
@@ -33431,7 +33504,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2155" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2155" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2155" s="15" t="s">
         <v>37</v>
       </c>
@@ -33446,7 +33519,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2156" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2156" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2156" s="15" t="s">
         <v>14</v>
       </c>
@@ -33461,7 +33534,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2157" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2157" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2157" s="15" t="s">
         <v>76</v>
       </c>
@@ -33476,7 +33549,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2158" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2158" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2158" s="15" t="s">
         <v>11</v>
       </c>
@@ -33491,7 +33564,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2159" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2159" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2159" s="15" t="s">
         <v>6</v>
       </c>
@@ -33506,7 +33579,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2160" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2160" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2160" s="15" t="s">
         <v>3</v>
       </c>
@@ -34001,7 +34074,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2193" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2193" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2193" s="15" t="s">
         <v>40</v>
       </c>
@@ -34016,13 +34089,13 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2194" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2194" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2194" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C2194" s="6"/>
       <c r="D2194" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2194" s="29">
         <v>3.94</v>
@@ -34030,14 +34103,17 @@
       <c r="F2194" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2195" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2194" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2195" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2195" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C2195" s="6"/>
       <c r="D2195" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2195" s="29">
         <v>0</v>
@@ -34045,14 +34121,17 @@
       <c r="F2195" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2196" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2195" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2196" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2196" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C2196" s="6"/>
       <c r="D2196" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2196" s="29">
         <v>0</v>
@@ -34060,8 +34139,11 @@
       <c r="F2196" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2197" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2196" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2197" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2197" s="15" t="s">
         <v>14</v>
       </c>
@@ -34076,7 +34158,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2198" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2198" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2198" s="15" t="s">
         <v>14</v>
       </c>
@@ -34091,7 +34173,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2199" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2199" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2199" s="15" t="s">
         <v>14</v>
       </c>
@@ -34106,7 +34188,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2200" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2200" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2200" s="15" t="s">
         <v>30</v>
       </c>
@@ -34121,7 +34203,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2201" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2201" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2201" s="15" t="s">
         <v>14</v>
       </c>
@@ -34136,7 +34218,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2202" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2202" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2202" s="15" t="s">
         <v>34</v>
       </c>
@@ -34151,7 +34233,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2203" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2203" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2203" s="15" t="s">
         <v>14</v>
       </c>
@@ -34166,7 +34248,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2204" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2204" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2204" s="15" t="s">
         <v>20</v>
       </c>
@@ -34181,7 +34263,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2205" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2205" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2205" s="15" t="s">
         <v>14</v>
       </c>
@@ -34196,7 +34278,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2206" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2206" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2206" s="15" t="s">
         <v>49</v>
       </c>
@@ -34211,7 +34293,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2207" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2207" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2207" s="15" t="s">
         <v>14</v>
       </c>
@@ -34226,7 +34308,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2208" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2208" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2208" s="15" t="s">
         <v>14</v>
       </c>
@@ -34241,7 +34323,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2209" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2209" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2209" s="15" t="s">
         <v>14</v>
       </c>
@@ -34256,7 +34338,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2210" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2210" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2210" s="15" t="s">
         <v>37</v>
       </c>
@@ -34271,7 +34353,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2211" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2211" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2211" s="15" t="s">
         <v>53</v>
       </c>
@@ -34286,7 +34368,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2212" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2212" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2212" s="15" t="s">
         <v>20</v>
       </c>
@@ -34301,7 +34383,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2213" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2213" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2213" s="15" t="s">
         <v>14</v>
       </c>
@@ -34316,7 +34398,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2214" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2214" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2214" s="15" t="s">
         <v>46</v>
       </c>
@@ -34331,7 +34413,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2215" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2215" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2215" s="15" t="s">
         <v>14</v>
       </c>
@@ -34346,7 +34428,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2216" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2216" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2216" s="15" t="s">
         <v>4</v>
       </c>
@@ -34361,7 +34443,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2217" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2217" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2217" s="15" t="s">
         <v>18</v>
       </c>
@@ -34376,7 +34458,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2218" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2218" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2218" s="15" t="s">
         <v>4</v>
       </c>
@@ -34391,13 +34473,13 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2219" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2219" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2219" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C2219" s="6"/>
       <c r="D2219" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2219" s="29">
         <v>0</v>
@@ -34405,8 +34487,11 @@
       <c r="F2219" s="8">
         <v>45748</v>
       </c>
-    </row>
-    <row r="2220" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2219" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2220" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2220" s="15" t="s">
         <v>14</v>
       </c>
@@ -34421,7 +34506,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2221" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2221" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2221" s="15" t="s">
         <v>14</v>
       </c>
@@ -34436,7 +34521,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2222" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2222" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2222" s="15" t="s">
         <v>22</v>
       </c>
@@ -34451,7 +34536,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2223" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2223" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2223" s="15" t="s">
         <v>18</v>
       </c>
@@ -34466,7 +34551,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="2224" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2224" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2224" s="15" t="s">
         <v>14</v>
       </c>
@@ -42641,7 +42726,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2769" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2769" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2769" s="15" t="s">
         <v>11</v>
       </c>
@@ -42656,7 +42741,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2770" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2770" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2770" s="15" t="s">
         <v>37</v>
       </c>
@@ -42671,7 +42756,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2771" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2771" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2771" s="15" t="s">
         <v>37</v>
       </c>
@@ -42686,7 +42771,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2772" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2772" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2772" s="15" t="s">
         <v>39</v>
       </c>
@@ -42701,7 +42786,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2773" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2773" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2773" s="15" t="s">
         <v>14</v>
       </c>
@@ -42716,7 +42801,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2774" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2774" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2774" s="15" t="s">
         <v>14</v>
       </c>
@@ -42731,7 +42816,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2775" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2775" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2775" s="15" t="s">
         <v>14</v>
       </c>
@@ -42746,7 +42831,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2776" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2776" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2776" s="15" t="s">
         <v>14</v>
       </c>
@@ -42761,13 +42846,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2777" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2777" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2777" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C2777" s="6"/>
       <c r="D2777" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2777" s="29">
         <v>8.1999999999999993</v>
@@ -42775,8 +42860,11 @@
       <c r="F2777" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2778" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2777" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2778" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2778" s="15" t="s">
         <v>14</v>
       </c>
@@ -42791,7 +42879,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2779" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2779" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2779" s="15" t="s">
         <v>14</v>
       </c>
@@ -42806,7 +42894,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2780" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2780" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2780" s="15" t="s">
         <v>14</v>
       </c>
@@ -42821,7 +42909,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2781" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2781" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2781" s="15" t="s">
         <v>14</v>
       </c>
@@ -42836,13 +42924,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2782" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2782" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2782" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C2782" s="6"/>
       <c r="D2782" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2782" s="29">
         <v>12.07</v>
@@ -42850,8 +42938,11 @@
       <c r="F2782" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2783" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2782" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2783" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2783" s="15" t="s">
         <v>8</v>
       </c>
@@ -42866,7 +42957,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2784" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2784" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2784" s="15" t="s">
         <v>14</v>
       </c>
@@ -42881,13 +42972,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2785" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2785" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2785" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C2785" s="6"/>
       <c r="D2785" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2785" s="29">
         <v>8.1999999999999993</v>
@@ -42895,8 +42986,11 @@
       <c r="F2785" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2786" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2785" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2786" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2786" s="15" t="s">
         <v>34</v>
       </c>
@@ -42911,7 +43005,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2787" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2787" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2787" s="15" t="s">
         <v>40</v>
       </c>
@@ -42926,7 +43020,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2788" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2788" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2788" s="15" t="s">
         <v>2</v>
       </c>
@@ -42941,7 +43035,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2789" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2789" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2789" s="15" t="s">
         <v>14</v>
       </c>
@@ -42956,7 +43050,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2790" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2790" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2790" s="15" t="s">
         <v>20</v>
       </c>
@@ -42971,7 +43065,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2791" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2791" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2791" s="15" t="s">
         <v>14</v>
       </c>
@@ -42986,13 +43080,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2792" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2792" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2792" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2792" s="6"/>
       <c r="D2792" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2792" s="29">
         <v>8.1999999999999993</v>
@@ -43000,8 +43094,11 @@
       <c r="F2792" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2793" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2792" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2793" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2793" s="15" t="s">
         <v>34</v>
       </c>
@@ -43016,7 +43113,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2794" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2794" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2794" s="15" t="s">
         <v>14</v>
       </c>
@@ -43031,13 +43128,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2795" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2795" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2795" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2795" s="6"/>
       <c r="D2795" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2795" s="29">
         <v>8.1999999999999993</v>
@@ -43045,8 +43142,11 @@
       <c r="F2795" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2796" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2795" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2796" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2796" s="15" t="s">
         <v>14</v>
       </c>
@@ -43061,7 +43161,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2797" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2797" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2797" s="15" t="s">
         <v>14</v>
       </c>
@@ -43076,7 +43176,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2798" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2798" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2798" s="15" t="s">
         <v>14</v>
       </c>
@@ -43091,7 +43191,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2799" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2799" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2799" s="15" t="s">
         <v>14</v>
       </c>
@@ -43106,7 +43206,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2800" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2800" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2800" s="15" t="s">
         <v>12</v>
       </c>
@@ -43361,7 +43461,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2817" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2817" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2817" s="15" t="s">
         <v>12</v>
       </c>
@@ -43376,7 +43476,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2818" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2818" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2818" s="15" t="s">
         <v>13</v>
       </c>
@@ -43391,7 +43491,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2819" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2819" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2819" s="15" t="s">
         <v>2</v>
       </c>
@@ -43406,7 +43506,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2820" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2820" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2820" s="15" t="s">
         <v>40</v>
       </c>
@@ -43421,7 +43521,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2821" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2821" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2821" s="15" t="s">
         <v>11</v>
       </c>
@@ -43436,7 +43536,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2822" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2822" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2822" s="15" t="s">
         <v>4</v>
       </c>
@@ -43451,7 +43551,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2823" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2823" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2823" s="15" t="s">
         <v>5</v>
       </c>
@@ -43466,7 +43566,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2824" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2824" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2824" s="15" t="s">
         <v>31</v>
       </c>
@@ -43481,7 +43581,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2825" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2825" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2825" s="15" t="s">
         <v>38</v>
       </c>
@@ -43496,7 +43596,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2826" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2826" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2826" s="15" t="s">
         <v>13</v>
       </c>
@@ -43511,13 +43611,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2827" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2827" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2827" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2827" s="6"/>
       <c r="D2827" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2827" s="29">
         <v>8.1999999999999993</v>
@@ -43525,8 +43625,11 @@
       <c r="F2827" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2828" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2827" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2828" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2828" s="15" t="s">
         <v>38</v>
       </c>
@@ -43541,7 +43644,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2829" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2829" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2829" s="15" t="s">
         <v>41</v>
       </c>
@@ -43556,7 +43659,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2830" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2830" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2830" s="15" t="s">
         <v>8</v>
       </c>
@@ -43571,7 +43674,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2831" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2831" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2831" s="15" t="s">
         <v>37</v>
       </c>
@@ -43586,7 +43689,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2832" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2832" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2832" s="15" t="s">
         <v>14</v>
       </c>
@@ -43601,7 +43704,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2833" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2833" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2833" s="15" t="s">
         <v>3</v>
       </c>
@@ -43616,7 +43719,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2834" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2834" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2834" s="15" t="s">
         <v>12</v>
       </c>
@@ -43631,13 +43734,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2835" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2835" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2835" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2835" s="6"/>
       <c r="D2835" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2835" s="29">
         <v>8.1999999999999993</v>
@@ -43645,8 +43748,11 @@
       <c r="F2835" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2836" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2835" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2836" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2836" s="15" t="s">
         <v>13</v>
       </c>
@@ -43661,7 +43767,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2837" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2837" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2837" s="15" t="s">
         <v>38</v>
       </c>
@@ -43676,7 +43782,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2838" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2838" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2838" s="15" t="s">
         <v>6</v>
       </c>
@@ -43691,7 +43797,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2839" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2839" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2839" s="15" t="s">
         <v>37</v>
       </c>
@@ -43706,7 +43812,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2840" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2840" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2840" s="15" t="s">
         <v>76</v>
       </c>
@@ -43721,7 +43827,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2841" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2841" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2841" s="15" t="s">
         <v>37</v>
       </c>
@@ -43736,7 +43842,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2842" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2842" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2842" s="15" t="s">
         <v>4</v>
       </c>
@@ -43751,7 +43857,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2843" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2843" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2843" s="15" t="s">
         <v>14</v>
       </c>
@@ -43766,7 +43872,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2844" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2844" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2844" s="15" t="s">
         <v>12</v>
       </c>
@@ -43781,7 +43887,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2845" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2845" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2845" s="15" t="s">
         <v>4</v>
       </c>
@@ -43796,7 +43902,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2846" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2846" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2846" s="15" t="s">
         <v>13</v>
       </c>
@@ -43811,13 +43917,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2847" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2847" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2847" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C2847" s="6"/>
       <c r="D2847" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2847" s="29">
         <v>8.1999999999999993</v>
@@ -43825,8 +43931,11 @@
       <c r="F2847" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2848" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2847" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2848" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2848" s="15" t="s">
         <v>20</v>
       </c>
@@ -43841,7 +43950,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2849" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2849" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2849" s="15" t="s">
         <v>20</v>
       </c>
@@ -43856,7 +43965,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2850" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2850" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2850" s="15" t="s">
         <v>20</v>
       </c>
@@ -43871,13 +43980,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2851" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2851" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2851" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C2851" s="6"/>
       <c r="D2851" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2851" s="29">
         <v>8.1999999999999993</v>
@@ -43885,8 +43994,11 @@
       <c r="F2851" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2852" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2851" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2852" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2852" s="15" t="s">
         <v>8</v>
       </c>
@@ -43901,7 +44013,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2853" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2853" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2853" s="15" t="s">
         <v>37</v>
       </c>
@@ -43916,7 +44028,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2854" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2854" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2854" s="15" t="s">
         <v>76</v>
       </c>
@@ -43931,7 +44043,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2855" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2855" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2855" s="15" t="s">
         <v>49</v>
       </c>
@@ -43946,7 +44058,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2856" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2856" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2856" s="15" t="s">
         <v>76</v>
       </c>
@@ -43961,7 +44073,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2857" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2857" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2857" s="15" t="s">
         <v>43</v>
       </c>
@@ -43976,7 +44088,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2858" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2858" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2858" s="15" t="s">
         <v>37</v>
       </c>
@@ -43991,7 +44103,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2859" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2859" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2859" s="15" t="s">
         <v>14</v>
       </c>
@@ -44006,7 +44118,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2860" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2860" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2860" s="15" t="s">
         <v>31</v>
       </c>
@@ -44021,13 +44133,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2861" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2861" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2861" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C2861" s="6"/>
       <c r="D2861" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2861" s="29">
         <v>8.1999999999999993</v>
@@ -44035,8 +44147,11 @@
       <c r="F2861" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2862" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2861" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2862" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2862" s="15" t="s">
         <v>37</v>
       </c>
@@ -44051,7 +44166,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2863" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2863" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2863" s="15" t="s">
         <v>6</v>
       </c>
@@ -44066,7 +44181,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2864" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2864" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2864" s="15" t="s">
         <v>37</v>
       </c>
@@ -44321,7 +44436,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2881" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2881" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2881" s="15" t="s">
         <v>35</v>
       </c>
@@ -44336,7 +44451,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2882" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2882" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2882" s="15" t="s">
         <v>35</v>
       </c>
@@ -44351,7 +44466,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2883" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2883" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2883" s="15" t="s">
         <v>16</v>
       </c>
@@ -44366,7 +44481,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2884" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2884" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2884" s="15" t="s">
         <v>23</v>
       </c>
@@ -44381,7 +44496,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2885" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2885" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2885" s="15" t="s">
         <v>23</v>
       </c>
@@ -44396,7 +44511,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2886" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2886" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2886" s="15" t="s">
         <v>35</v>
       </c>
@@ -44411,7 +44526,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2887" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2887" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2887" s="15" t="s">
         <v>35</v>
       </c>
@@ -44426,13 +44541,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2888" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2888" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2888" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2888" s="6"/>
       <c r="D2888" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2888" s="29">
         <v>8.1999999999999993</v>
@@ -44440,8 +44555,11 @@
       <c r="F2888" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2889" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2888" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2889" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2889" s="15" t="s">
         <v>35</v>
       </c>
@@ -44456,7 +44574,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2890" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2890" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2890" s="15" t="s">
         <v>25</v>
       </c>
@@ -44471,7 +44589,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2891" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2891" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2891" s="15" t="s">
         <v>35</v>
       </c>
@@ -44486,7 +44604,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2892" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2892" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2892" s="15" t="s">
         <v>20</v>
       </c>
@@ -44501,7 +44619,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2893" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2893" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2893" s="15" t="s">
         <v>23</v>
       </c>
@@ -44516,7 +44634,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2894" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2894" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2894" s="15" t="s">
         <v>35</v>
       </c>
@@ -44531,7 +44649,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2895" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2895" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2895" s="15" t="s">
         <v>39</v>
       </c>
@@ -44546,7 +44664,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2896" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2896" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2896" s="15" t="s">
         <v>12</v>
       </c>
@@ -44801,7 +44919,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2913" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2913" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2913" s="15" t="s">
         <v>39</v>
       </c>
@@ -44816,7 +44934,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2914" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2914" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2914" s="15" t="s">
         <v>12</v>
       </c>
@@ -44831,7 +44949,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2915" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2915" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2915" s="15" t="s">
         <v>13</v>
       </c>
@@ -44846,7 +44964,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2916" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2916" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2916" s="15" t="s">
         <v>20</v>
       </c>
@@ -44861,13 +44979,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2917" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2917" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2917" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C2917" s="6"/>
       <c r="D2917" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2917" s="29">
         <v>8.1999999999999993</v>
@@ -44875,8 +44993,11 @@
       <c r="F2917" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2918" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2917" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2918" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2918" s="15" t="s">
         <v>37</v>
       </c>
@@ -44891,7 +45012,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2919" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2919" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2919" s="15" t="s">
         <v>39</v>
       </c>
@@ -44906,7 +45027,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2920" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2920" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2920" s="15" t="s">
         <v>4</v>
       </c>
@@ -44921,7 +45042,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2921" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2921" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2921" s="15" t="s">
         <v>13</v>
       </c>
@@ -44936,7 +45057,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2922" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2922" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2922" s="15" t="s">
         <v>39</v>
       </c>
@@ -44951,7 +45072,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2923" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2923" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2923" s="15" t="s">
         <v>14</v>
       </c>
@@ -44966,7 +45087,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2924" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2924" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2924" s="15" t="s">
         <v>11</v>
       </c>
@@ -44981,7 +45102,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2925" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2925" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2925" s="15" t="s">
         <v>31</v>
       </c>
@@ -44996,7 +45117,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2926" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2926" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2926" s="15" t="s">
         <v>37</v>
       </c>
@@ -45011,7 +45132,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2927" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2927" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2927" s="15" t="s">
         <v>8</v>
       </c>
@@ -45026,7 +45147,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2928" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2928" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2928" s="15" t="s">
         <v>41</v>
       </c>
@@ -45041,7 +45162,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2929" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2929" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2929" s="15" t="s">
         <v>40</v>
       </c>
@@ -45056,13 +45177,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2930" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2930" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2930" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2930" s="6"/>
       <c r="D2930" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2930" s="29">
         <v>8.1999999999999993</v>
@@ -45070,8 +45191,11 @@
       <c r="F2930" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2931" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2930" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2931" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2931" s="15" t="s">
         <v>13</v>
       </c>
@@ -45086,7 +45210,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2932" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2932" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2932" s="15" t="s">
         <v>11</v>
       </c>
@@ -45101,13 +45225,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2933" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2933" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2933" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2933" s="6"/>
       <c r="D2933" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2933" s="29">
         <v>8.1999999999999993</v>
@@ -45115,8 +45239,11 @@
       <c r="F2933" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2934" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2933" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2934" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2934" s="15" t="s">
         <v>8</v>
       </c>
@@ -45131,7 +45258,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2935" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2935" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2935" s="15" t="s">
         <v>4</v>
       </c>
@@ -45146,7 +45273,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2936" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2936" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2936" s="15" t="s">
         <v>11</v>
       </c>
@@ -45161,7 +45288,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2937" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2937" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2937" s="15" t="s">
         <v>34</v>
       </c>
@@ -45176,7 +45303,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2938" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2938" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2938" s="15" t="s">
         <v>12</v>
       </c>
@@ -45191,7 +45318,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2939" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2939" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2939" s="15" t="s">
         <v>37</v>
       </c>
@@ -45206,7 +45333,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2940" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2940" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2940" s="15" t="s">
         <v>34</v>
       </c>
@@ -45221,7 +45348,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2941" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2941" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2941" s="15" t="s">
         <v>13</v>
       </c>
@@ -45236,7 +45363,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2942" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2942" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2942" s="15" t="s">
         <v>23</v>
       </c>
@@ -45251,7 +45378,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2943" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2943" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2943" s="15" t="s">
         <v>37</v>
       </c>
@@ -45266,7 +45393,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2944" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2944" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2944" s="15" t="s">
         <v>6</v>
       </c>
@@ -45281,13 +45408,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2945" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2945" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2945" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2945" s="6"/>
       <c r="D2945" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2945" s="29">
         <v>8.1999999999999993</v>
@@ -45295,8 +45422,11 @@
       <c r="F2945" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2946" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2945" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2946" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2946" s="15" t="s">
         <v>3</v>
       </c>
@@ -45311,7 +45441,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2947" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2947" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2947" s="15" t="s">
         <v>37</v>
       </c>
@@ -45326,7 +45456,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2948" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2948" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2948" s="15" t="s">
         <v>12</v>
       </c>
@@ -45341,7 +45471,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2949" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2949" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2949" s="15" t="s">
         <v>37</v>
       </c>
@@ -45356,7 +45486,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2950" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2950" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2950" s="15" t="s">
         <v>49</v>
       </c>
@@ -45371,7 +45501,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2951" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2951" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2951" s="15" t="s">
         <v>23</v>
       </c>
@@ -45386,7 +45516,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2952" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2952" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2952" s="15" t="s">
         <v>5</v>
       </c>
@@ -45401,7 +45531,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2953" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2953" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2953" s="15" t="s">
         <v>39</v>
       </c>
@@ -45416,7 +45546,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2954" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2954" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2954" s="15" t="s">
         <v>25</v>
       </c>
@@ -45431,7 +45561,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2955" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2955" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2955" s="15" t="s">
         <v>2</v>
       </c>
@@ -45446,7 +45576,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2956" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2956" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2956" s="15" t="s">
         <v>13</v>
       </c>
@@ -45461,7 +45591,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2957" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2957" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2957" s="15" t="s">
         <v>23</v>
       </c>
@@ -45476,7 +45606,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2958" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2958" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2958" s="15" t="s">
         <v>2</v>
       </c>
@@ -45491,7 +45621,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2959" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2959" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2959" s="15" t="s">
         <v>39</v>
       </c>
@@ -45506,7 +45636,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2960" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2960" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2960" s="15" t="s">
         <v>11</v>
       </c>
@@ -45761,7 +45891,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2977" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2977" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2977" s="15" t="s">
         <v>6</v>
       </c>
@@ -45776,7 +45906,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2978" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2978" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2978" s="15" t="s">
         <v>37</v>
       </c>
@@ -45791,7 +45921,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2979" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2979" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2979" s="15" t="s">
         <v>4</v>
       </c>
@@ -45806,7 +45936,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2980" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2980" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2980" s="15" t="s">
         <v>37</v>
       </c>
@@ -45821,7 +45951,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2981" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2981" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2981" s="15" t="s">
         <v>53</v>
       </c>
@@ -45836,13 +45966,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2982" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2982" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2982" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C2982" s="6"/>
       <c r="D2982" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2982" s="29">
         <v>8.1999999999999993</v>
@@ -45850,8 +45980,11 @@
       <c r="F2982" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2983" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2982" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2983" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2983" s="15" t="s">
         <v>30</v>
       </c>
@@ -45866,7 +45999,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2984" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2984" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2984" s="15" t="s">
         <v>35</v>
       </c>
@@ -45881,7 +46014,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2985" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2985" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2985" s="15" t="s">
         <v>35</v>
       </c>
@@ -45896,7 +46029,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2986" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2986" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2986" s="15" t="s">
         <v>35</v>
       </c>
@@ -45911,7 +46044,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2987" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2987" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2987" s="15" t="s">
         <v>8</v>
       </c>
@@ -45926,7 +46059,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2988" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2988" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2988" s="15" t="s">
         <v>35</v>
       </c>
@@ -45941,7 +46074,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2989" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2989" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2989" s="15" t="s">
         <v>35</v>
       </c>
@@ -45956,7 +46089,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2990" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2990" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2990" s="15" t="s">
         <v>35</v>
       </c>
@@ -45971,7 +46104,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2991" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2991" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2991" s="15" t="s">
         <v>35</v>
       </c>
@@ -45986,7 +46119,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2992" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2992" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2992" s="15" t="s">
         <v>5</v>
       </c>
@@ -46001,7 +46134,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2993" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2993" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2993" s="15" t="s">
         <v>35</v>
       </c>
@@ -46016,7 +46149,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2994" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2994" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2994" s="15" t="s">
         <v>35</v>
       </c>
@@ -46031,13 +46164,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2995" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2995" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2995" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C2995" s="6"/>
       <c r="D2995" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2995" s="29">
         <v>8.1999999999999993</v>
@@ -46045,8 +46178,11 @@
       <c r="F2995" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2996" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2995" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2996" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2996" s="15" t="s">
         <v>20</v>
       </c>
@@ -46061,7 +46197,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2997" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2997" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2997" s="15" t="s">
         <v>3</v>
       </c>
@@ -46076,13 +46212,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="2998" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2998" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2998" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C2998" s="6"/>
       <c r="D2998" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E2998" s="29">
         <v>8.1999999999999993</v>
@@ -46090,8 +46226,11 @@
       <c r="F2998" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="2999" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2998" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2999" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2999" s="15" t="s">
         <v>20</v>
       </c>
@@ -46106,7 +46245,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3000" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3000" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3000" s="15" t="s">
         <v>20</v>
       </c>
@@ -46121,7 +46260,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3001" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3001" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3001" s="15" t="s">
         <v>31</v>
       </c>
@@ -46136,7 +46275,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3002" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3002" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3002" s="15" t="s">
         <v>35</v>
       </c>
@@ -46151,7 +46290,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3003" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3003" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3003" s="15" t="s">
         <v>35</v>
       </c>
@@ -46166,7 +46305,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3004" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3004" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3004" s="15" t="s">
         <v>35</v>
       </c>
@@ -46181,7 +46320,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3005" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3005" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3005" s="15" t="s">
         <v>12</v>
       </c>
@@ -46196,7 +46335,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3006" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3006" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3006" s="15" t="s">
         <v>35</v>
       </c>
@@ -46211,7 +46350,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3007" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3007" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3007" s="15" t="s">
         <v>53</v>
       </c>
@@ -46226,7 +46365,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3008" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3008" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3008" s="15" t="s">
         <v>76</v>
       </c>
@@ -46481,7 +46620,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3025" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3025" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3025" s="15" t="s">
         <v>49</v>
       </c>
@@ -46496,7 +46635,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3026" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3026" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3026" s="15" t="s">
         <v>37</v>
       </c>
@@ -46511,7 +46650,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3027" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3027" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3027" s="15" t="s">
         <v>5</v>
       </c>
@@ -46526,7 +46665,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3028" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3028" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3028" s="15" t="s">
         <v>31</v>
       </c>
@@ -46541,7 +46680,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3029" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3029" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3029" s="15" t="s">
         <v>34</v>
       </c>
@@ -46556,7 +46695,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3030" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3030" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3030" s="15" t="s">
         <v>37</v>
       </c>
@@ -46571,7 +46710,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3031" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3031" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3031" s="15" t="s">
         <v>34</v>
       </c>
@@ -46586,7 +46725,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3032" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3032" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3032" s="15" t="s">
         <v>8</v>
       </c>
@@ -46601,7 +46740,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3033" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3033" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3033" s="15" t="s">
         <v>37</v>
       </c>
@@ -46616,7 +46755,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3034" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3034" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3034" s="15" t="s">
         <v>14</v>
       </c>
@@ -46631,7 +46770,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3035" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3035" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3035" s="15" t="s">
         <v>40</v>
       </c>
@@ -46646,7 +46785,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3036" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3036" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3036" s="15" t="s">
         <v>19</v>
       </c>
@@ -46661,7 +46800,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3037" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3037" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3037" s="15" t="s">
         <v>49</v>
       </c>
@@ -46676,7 +46815,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3038" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3038" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3038" s="15" t="s">
         <v>13</v>
       </c>
@@ -46691,7 +46830,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3039" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3039" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3039" s="15" t="s">
         <v>12</v>
       </c>
@@ -46706,13 +46845,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3040" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3040" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3040" s="15" t="s">
         <v>57</v>
       </c>
       <c r="C3040" s="6"/>
       <c r="D3040" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3040" s="29">
         <v>0</v>
@@ -46720,14 +46859,17 @@
       <c r="F3040" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3041" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3040" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3041" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3041" s="15" t="s">
         <v>55</v>
       </c>
       <c r="C3041" s="6"/>
       <c r="D3041" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3041" s="29">
         <v>0</v>
@@ -46735,8 +46877,11 @@
       <c r="F3041" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3042" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3041" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3042" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3042" s="15" t="s">
         <v>14</v>
       </c>
@@ -46751,7 +46896,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3043" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3043" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3043" s="15" t="s">
         <v>19</v>
       </c>
@@ -46766,7 +46911,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3044" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3044" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3044" s="15" t="s">
         <v>37</v>
       </c>
@@ -46781,13 +46926,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3045" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3045" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3045" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C3045" s="6"/>
       <c r="D3045" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3045" s="29">
         <v>8.1999999999999993</v>
@@ -46795,8 +46940,11 @@
       <c r="F3045" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3046" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3045" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3046" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3046" s="15" t="s">
         <v>13</v>
       </c>
@@ -46811,7 +46959,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3047" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3047" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3047" s="15" t="s">
         <v>39</v>
       </c>
@@ -46826,7 +46974,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3048" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3048" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3048" s="15" t="s">
         <v>76</v>
       </c>
@@ -46841,7 +46989,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3049" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3049" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3049" s="15" t="s">
         <v>76</v>
       </c>
@@ -46856,13 +47004,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3050" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3050" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3050" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C3050" s="6"/>
       <c r="D3050" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3050" s="29">
         <v>8.1999999999999993</v>
@@ -46870,14 +47018,17 @@
       <c r="F3050" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3051" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3050" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3051" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3051" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C3051" s="6"/>
       <c r="D3051" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3051" s="29">
         <v>8.1999999999999993</v>
@@ -46885,8 +47036,11 @@
       <c r="F3051" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3052" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3051" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3052" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3052" s="15" t="s">
         <v>37</v>
       </c>
@@ -46901,13 +47055,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3053" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3053" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3053" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C3053" s="6"/>
       <c r="D3053" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3053" s="29">
         <v>8.1999999999999993</v>
@@ -46915,8 +47069,11 @@
       <c r="F3053" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3054" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3053" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3054" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3054" s="15" t="s">
         <v>6</v>
       </c>
@@ -46931,7 +47088,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3055" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3055" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3055" s="15" t="s">
         <v>37</v>
       </c>
@@ -46946,7 +47103,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3056" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3056" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3056" s="15" t="s">
         <v>3</v>
       </c>
@@ -46961,7 +47118,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3057" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3057" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3057" s="15" t="s">
         <v>8</v>
       </c>
@@ -46976,7 +47133,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3058" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3058" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3058" s="15" t="s">
         <v>37</v>
       </c>
@@ -46991,7 +47148,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3059" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3059" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3059" s="15" t="s">
         <v>12</v>
       </c>
@@ -47006,7 +47163,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3060" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3060" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3060" s="15" t="s">
         <v>13</v>
       </c>
@@ -47021,7 +47178,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3061" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3061" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3061" s="15" t="s">
         <v>5</v>
       </c>
@@ -47036,7 +47193,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3062" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3062" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3062" s="15" t="s">
         <v>20</v>
       </c>
@@ -47051,7 +47208,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3063" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3063" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3063" s="15" t="s">
         <v>20</v>
       </c>
@@ -47066,7 +47223,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3064" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3064" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3064" s="15" t="s">
         <v>43</v>
       </c>
@@ -47081,13 +47238,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3065" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3065" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3065" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C3065" s="6"/>
       <c r="D3065" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3065" s="29">
         <v>8.1999999999999993</v>
@@ -47095,8 +47252,11 @@
       <c r="F3065" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3066" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3065" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3066" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3066" s="15" t="s">
         <v>20</v>
       </c>
@@ -47111,7 +47271,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3067" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3067" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3067" s="15" t="s">
         <v>13</v>
       </c>
@@ -47126,7 +47286,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3068" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3068" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3068" s="15" t="s">
         <v>31</v>
       </c>
@@ -47141,7 +47301,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3069" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3069" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3069" s="15" t="s">
         <v>30</v>
       </c>
@@ -47156,7 +47316,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3070" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3070" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3070" s="15" t="s">
         <v>37</v>
       </c>
@@ -47171,7 +47331,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3071" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3071" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3071" s="15" t="s">
         <v>31</v>
       </c>
@@ -47186,7 +47346,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3072" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3072" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3072" s="15" t="s">
         <v>43</v>
       </c>
@@ -49361,7 +49521,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3217" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3217" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3217" s="15" t="s">
         <v>41</v>
       </c>
@@ -49376,7 +49536,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3218" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3218" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3218" s="15" t="s">
         <v>11</v>
       </c>
@@ -49391,7 +49551,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3219" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3219" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3219" s="15" t="s">
         <v>8</v>
       </c>
@@ -49406,7 +49566,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3220" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3220" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3220" s="15" t="s">
         <v>14</v>
       </c>
@@ -49421,13 +49581,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3221" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3221" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3221" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C3221" s="6"/>
       <c r="D3221" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3221" s="29">
         <v>0</v>
@@ -49435,8 +49595,11 @@
       <c r="F3221" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3222" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3221" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3222" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3222" s="15" t="s">
         <v>30</v>
       </c>
@@ -49451,7 +49614,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3223" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3223" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3223" s="15" t="s">
         <v>71</v>
       </c>
@@ -49466,7 +49629,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3224" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3224" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3224" s="15" t="s">
         <v>28</v>
       </c>
@@ -49481,7 +49644,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3225" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3225" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3225" s="15" t="s">
         <v>27</v>
       </c>
@@ -49496,7 +49659,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3226" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3226" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3226" s="15" t="s">
         <v>21</v>
       </c>
@@ -49511,7 +49674,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3227" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3227" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3227" s="15" t="s">
         <v>13</v>
       </c>
@@ -49526,7 +49689,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3228" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3228" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3228" s="15" t="s">
         <v>37</v>
       </c>
@@ -49541,7 +49704,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3229" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3229" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3229" s="15" t="s">
         <v>7</v>
       </c>
@@ -49556,7 +49719,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3230" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3230" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3230" s="15" t="s">
         <v>36</v>
       </c>
@@ -49571,7 +49734,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3231" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3231" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3231" s="15" t="s">
         <v>48</v>
       </c>
@@ -49586,7 +49749,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3232" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3232" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3232" s="15" t="s">
         <v>34</v>
       </c>
@@ -49601,7 +49764,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3233" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3233" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3233" s="15" t="s">
         <v>4</v>
       </c>
@@ -49616,7 +49779,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3234" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3234" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3234" s="15" t="s">
         <v>22</v>
       </c>
@@ -49631,7 +49794,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3235" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3235" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3235" s="15" t="s">
         <v>44</v>
       </c>
@@ -49646,7 +49809,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3236" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3236" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3236" s="15" t="s">
         <v>20</v>
       </c>
@@ -49661,7 +49824,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3237" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3237" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3237" s="15" t="s">
         <v>26</v>
       </c>
@@ -49676,13 +49839,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3238" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3238" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3238" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C3238" s="6"/>
       <c r="D3238" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3238" s="29">
         <v>0</v>
@@ -49690,14 +49853,17 @@
       <c r="F3238" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3239" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3238" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3239" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3239" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C3239" s="6"/>
       <c r="D3239" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3239" s="29">
         <v>0</v>
@@ -49705,8 +49871,11 @@
       <c r="F3239" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3240" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3239" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3240" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3240" s="15" t="s">
         <v>43</v>
       </c>
@@ -49721,7 +49890,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3241" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3241" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3241" s="15" t="s">
         <v>70</v>
       </c>
@@ -49736,7 +49905,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3242" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3242" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3242" s="15" t="s">
         <v>49</v>
       </c>
@@ -49751,7 +49920,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3243" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3243" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3243" s="15" t="s">
         <v>73</v>
       </c>
@@ -49766,7 +49935,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3244" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3244" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3244" s="15" t="s">
         <v>17</v>
       </c>
@@ -49781,7 +49950,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3245" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3245" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3245" s="15" t="s">
         <v>33</v>
       </c>
@@ -49796,7 +49965,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3246" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3246" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3246" s="15" t="s">
         <v>15</v>
       </c>
@@ -49811,7 +49980,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3247" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3247" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3247" s="15" t="s">
         <v>19</v>
       </c>
@@ -49826,7 +49995,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3248" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3248" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3248" s="15" t="s">
         <v>9</v>
       </c>
@@ -50321,7 +50490,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3281" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3281" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3281" s="15" t="s">
         <v>70</v>
       </c>
@@ -50336,13 +50505,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3282" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3282" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3282" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C3282" s="6"/>
       <c r="D3282" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3282" s="29">
         <v>0</v>
@@ -50350,8 +50519,11 @@
       <c r="F3282" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3283" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3282" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3283" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3283" s="15" t="s">
         <v>9</v>
       </c>
@@ -50366,7 +50538,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3284" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3284" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3284" s="15" t="s">
         <v>67</v>
       </c>
@@ -50381,7 +50553,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3285" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3285" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3285" s="15" t="s">
         <v>24</v>
       </c>
@@ -50396,7 +50568,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3286" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3286" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3286" s="15" t="s">
         <v>27</v>
       </c>
@@ -50411,7 +50583,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3287" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3287" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3287" s="15" t="s">
         <v>26</v>
       </c>
@@ -50426,7 +50598,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3288" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3288" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3288" s="15" t="s">
         <v>20</v>
       </c>
@@ -50441,7 +50613,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3289" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3289" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3289" s="15" t="s">
         <v>43</v>
       </c>
@@ -50456,7 +50628,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3290" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3290" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3290" s="15" t="s">
         <v>77</v>
       </c>
@@ -50471,13 +50643,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3291" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3291" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3291" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C3291" s="6"/>
       <c r="D3291" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3291" s="29">
         <v>0</v>
@@ -50485,8 +50657,11 @@
       <c r="F3291" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3292" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3291" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3292" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3292" s="15" t="s">
         <v>11</v>
       </c>
@@ -50501,7 +50676,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3293" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3293" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3293" s="15" t="s">
         <v>15</v>
       </c>
@@ -50516,7 +50691,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3294" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3294" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3294" s="15" t="s">
         <v>19</v>
       </c>
@@ -50531,7 +50706,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3295" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3295" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3295" s="15" t="s">
         <v>33</v>
       </c>
@@ -50546,7 +50721,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3296" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3296" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3296" s="15" t="s">
         <v>8</v>
       </c>
@@ -50561,7 +50736,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3297" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3297" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3297" s="15" t="s">
         <v>14</v>
       </c>
@@ -50576,13 +50751,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3298" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3298" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3298" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C3298" s="6"/>
       <c r="D3298" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3298" s="29">
         <v>0</v>
@@ -50590,8 +50765,11 @@
       <c r="F3298" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3299" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3298" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3299" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3299" s="15" t="s">
         <v>28</v>
       </c>
@@ -50606,7 +50784,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3300" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3300" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3300" s="15" t="s">
         <v>38</v>
       </c>
@@ -50621,7 +50799,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3301" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3301" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3301" s="15" t="s">
         <v>2</v>
       </c>
@@ -50636,7 +50814,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3302" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3302" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3302" s="15" t="s">
         <v>18</v>
       </c>
@@ -50651,7 +50829,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3303" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3303" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3303" s="15" t="s">
         <v>35</v>
       </c>
@@ -50666,7 +50844,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3304" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3304" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3304" s="15" t="s">
         <v>3</v>
       </c>
@@ -50681,7 +50859,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3305" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3305" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3305" s="15" t="s">
         <v>32</v>
       </c>
@@ -50696,7 +50874,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3306" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3306" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3306" s="15" t="s">
         <v>30</v>
       </c>
@@ -50711,7 +50889,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3307" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3307" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3307" s="15" t="s">
         <v>45</v>
       </c>
@@ -50726,7 +50904,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3308" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3308" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3308" s="15" t="s">
         <v>21</v>
       </c>
@@ -50741,7 +50919,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3309" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3309" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3309" s="15" t="s">
         <v>38</v>
       </c>
@@ -50756,7 +50934,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3310" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3310" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3310" s="15" t="s">
         <v>69</v>
       </c>
@@ -50771,7 +50949,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3311" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3311" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3311" s="15" t="s">
         <v>30</v>
       </c>
@@ -50786,7 +50964,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3312" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3312" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3312" s="15" t="s">
         <v>6</v>
       </c>
@@ -50801,7 +50979,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3313" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3313" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3313" s="15" t="s">
         <v>40</v>
       </c>
@@ -50816,7 +50994,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3314" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3314" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3314" s="15" t="s">
         <v>51</v>
       </c>
@@ -50831,7 +51009,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3315" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3315" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3315" s="15" t="s">
         <v>74</v>
       </c>
@@ -50846,13 +51024,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3316" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3316" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3316" s="15" t="s">
         <v>59</v>
       </c>
       <c r="C3316" s="6"/>
       <c r="D3316" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3316" s="29">
         <v>16.899999999999999</v>
@@ -50860,8 +51038,11 @@
       <c r="F3316" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3317" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3316" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3317" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3317" s="15" t="s">
         <v>9</v>
       </c>
@@ -50876,7 +51057,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3318" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3318" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3318" s="15" t="s">
         <v>48</v>
       </c>
@@ -50891,7 +51072,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3319" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3319" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3319" s="15" t="s">
         <v>26</v>
       </c>
@@ -50906,7 +51087,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3320" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3320" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3320" s="15" t="s">
         <v>20</v>
       </c>
@@ -50921,7 +51102,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3321" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3321" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3321" s="15" t="s">
         <v>39</v>
       </c>
@@ -50936,13 +51117,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3322" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3322" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3322" s="15" t="s">
         <v>58</v>
       </c>
       <c r="C3322" s="6"/>
       <c r="D3322" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3322" s="29">
         <v>16.899999999999999</v>
@@ -50950,8 +51131,11 @@
       <c r="F3322" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3323" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3322" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3323" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3323" s="15" t="s">
         <v>43</v>
       </c>
@@ -50966,7 +51150,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3324" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3324" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3324" s="15" t="s">
         <v>27</v>
       </c>
@@ -50981,7 +51165,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3325" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3325" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3325" s="15" t="s">
         <v>22</v>
       </c>
@@ -50996,7 +51180,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3326" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3326" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3326" s="15" t="s">
         <v>31</v>
       </c>
@@ -51011,7 +51195,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3327" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3327" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3327" s="15" t="s">
         <v>6</v>
       </c>
@@ -51026,7 +51210,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3328" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3328" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3328" s="15" t="s">
         <v>32</v>
       </c>
@@ -51521,7 +51705,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3361" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3361" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3361" s="15" t="s">
         <v>8</v>
       </c>
@@ -51536,7 +51720,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3362" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3362" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3362" s="15" t="s">
         <v>14</v>
       </c>
@@ -51551,7 +51735,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3363" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3363" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3363" s="15" t="s">
         <v>17</v>
       </c>
@@ -51566,7 +51750,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3364" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3364" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3364" s="15" t="s">
         <v>30</v>
       </c>
@@ -51581,13 +51765,13 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3365" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3365" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3365" s="15" t="s">
         <v>56</v>
       </c>
       <c r="C3365" s="6"/>
       <c r="D3365" s="4" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="E3365" s="29">
         <v>16.899999999999999</v>
@@ -51595,8 +51779,11 @@
       <c r="F3365" s="8">
         <v>45778</v>
       </c>
-    </row>
-    <row r="3366" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G3365" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3366" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3366" s="15" t="s">
         <v>21</v>
       </c>
@@ -51611,7 +51798,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3367" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3367" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3367" s="15" t="s">
         <v>44</v>
       </c>
@@ -51626,7 +51813,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3368" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3368" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3368" s="15" t="s">
         <v>34</v>
       </c>
@@ -51641,7 +51828,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3369" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3369" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3369" s="15" t="s">
         <v>4</v>
       </c>
@@ -51656,7 +51843,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3370" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3370" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3370" s="15" t="s">
         <v>13</v>
       </c>
@@ -51671,7 +51858,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3371" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3371" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3371" s="15" t="s">
         <v>37</v>
       </c>
@@ -51686,7 +51873,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3372" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3372" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3372" s="15" t="s">
         <v>36</v>
       </c>
@@ -51701,7 +51888,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3373" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3373" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3373" s="15" t="s">
         <v>7</v>
       </c>
@@ -51716,7 +51903,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3374" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3374" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3374" s="15" t="s">
         <v>46</v>
       </c>
@@ -51731,7 +51918,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3375" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3375" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3375" s="15" t="s">
         <v>23</v>
       </c>
@@ -51746,7 +51933,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="3376" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3376" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3376" s="15" t="s">
         <v>47</v>
       </c>
@@ -63580,186 +63767,394 @@
       </c>
     </row>
     <row r="4165" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4165" s="34"/>
+      <c r="B4165" s="34" t="s">
+        <v>50</v>
+      </c>
       <c r="C4165" s="34"/>
-      <c r="D4165" s="34"/>
-      <c r="E4165" s="31"/>
-      <c r="F4165" s="23"/>
+      <c r="D4165" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4165" s="31">
+        <v>32</v>
+      </c>
+      <c r="F4165" s="24">
+        <v>45870</v>
+      </c>
     </row>
     <row r="4166" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4166" s="34"/>
+      <c r="B4166" s="34" t="s">
+        <v>43</v>
+      </c>
       <c r="C4166" s="34"/>
-      <c r="D4166" s="34"/>
-      <c r="E4166" s="31"/>
-      <c r="F4166" s="23"/>
+      <c r="D4166" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4166" s="31">
+        <v>32</v>
+      </c>
+      <c r="F4166" s="24">
+        <v>45870</v>
+      </c>
     </row>
     <row r="4167" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4167" s="34"/>
+      <c r="B4167" s="34" t="s">
+        <v>38</v>
+      </c>
       <c r="C4167" s="34"/>
-      <c r="D4167" s="34"/>
-      <c r="E4167" s="31"/>
-      <c r="F4167" s="23"/>
+      <c r="D4167" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4167" s="31">
+        <v>70</v>
+      </c>
+      <c r="F4167" s="24">
+        <v>45901</v>
+      </c>
     </row>
     <row r="4168" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4168" s="34"/>
+      <c r="B4168" s="34" t="s">
+        <v>31</v>
+      </c>
       <c r="C4168" s="34"/>
-      <c r="D4168" s="34"/>
-      <c r="E4168" s="31"/>
-      <c r="F4168" s="23"/>
+      <c r="D4168" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4168" s="31">
+        <v>1005</v>
+      </c>
+      <c r="F4168" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4169" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4169" s="34"/>
+      <c r="B4169" s="34" t="s">
+        <v>37</v>
+      </c>
       <c r="C4169" s="34"/>
-      <c r="D4169" s="34"/>
-      <c r="E4169" s="31"/>
-      <c r="F4169" s="23"/>
+      <c r="D4169" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4169" s="31">
+        <v>195</v>
+      </c>
+      <c r="F4169" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4170" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4170" s="34"/>
+      <c r="B4170" s="34" t="s">
+        <v>41</v>
+      </c>
       <c r="C4170" s="34"/>
-      <c r="D4170" s="34"/>
-      <c r="E4170" s="31"/>
-      <c r="F4170" s="23"/>
+      <c r="D4170" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4170" s="31">
+        <v>1676.55</v>
+      </c>
+      <c r="F4170" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4171" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4171" s="34"/>
+      <c r="B4171" s="34" t="s">
+        <v>3</v>
+      </c>
       <c r="C4171" s="34"/>
-      <c r="D4171" s="34"/>
-      <c r="E4171" s="31"/>
-      <c r="F4171" s="23"/>
+      <c r="D4171" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4171" s="31">
+        <v>109</v>
+      </c>
+      <c r="F4171" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4172" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4172" s="34"/>
+      <c r="B4172" s="34" t="s">
+        <v>39</v>
+      </c>
       <c r="C4172" s="34"/>
-      <c r="D4172" s="34"/>
-      <c r="E4172" s="31"/>
-      <c r="F4172" s="23"/>
+      <c r="D4172" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4172" s="31">
+        <v>250</v>
+      </c>
+      <c r="F4172" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4173" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4173" s="34"/>
+      <c r="B4173" s="34" t="s">
+        <v>39</v>
+      </c>
       <c r="C4173" s="34"/>
-      <c r="D4173" s="34"/>
-      <c r="E4173" s="31"/>
-      <c r="F4173" s="23"/>
+      <c r="D4173" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4173" s="31">
+        <v>1161</v>
+      </c>
+      <c r="F4173" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4174" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4174" s="34"/>
+      <c r="B4174" s="34" t="s">
+        <v>25</v>
+      </c>
       <c r="C4174" s="34"/>
-      <c r="D4174" s="34"/>
-      <c r="E4174" s="31"/>
-      <c r="F4174" s="23"/>
+      <c r="D4174" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4174" s="31">
+        <v>160</v>
+      </c>
+      <c r="F4174" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4175" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4175" s="34"/>
+      <c r="B4175" s="34" t="s">
+        <v>46</v>
+      </c>
       <c r="C4175" s="34"/>
-      <c r="D4175" s="34"/>
-      <c r="E4175" s="31"/>
-      <c r="F4175" s="23"/>
+      <c r="D4175" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4175" s="31">
+        <v>10800</v>
+      </c>
+      <c r="F4175" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4176" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4176" s="34"/>
+      <c r="B4176" s="34" t="s">
+        <v>34</v>
+      </c>
       <c r="C4176" s="34"/>
-      <c r="D4176" s="34"/>
-      <c r="E4176" s="31"/>
-      <c r="F4176" s="23"/>
+      <c r="D4176" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4176" s="31">
+        <v>180</v>
+      </c>
+      <c r="F4176" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4177" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4177" s="34"/>
+      <c r="B4177" s="34" t="s">
+        <v>138</v>
+      </c>
       <c r="C4177" s="34"/>
-      <c r="D4177" s="34"/>
-      <c r="E4177" s="31"/>
-      <c r="F4177" s="23"/>
+      <c r="D4177" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4177" s="31">
+        <v>410.5</v>
+      </c>
+      <c r="F4177" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4178" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4178" s="34"/>
+      <c r="B4178" s="34" t="s">
+        <v>34</v>
+      </c>
       <c r="C4178" s="34"/>
-      <c r="D4178" s="34"/>
-      <c r="E4178" s="31"/>
-      <c r="F4178" s="23"/>
+      <c r="D4178" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4178" s="31">
+        <v>35</v>
+      </c>
+      <c r="F4178" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4179" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4179" s="34"/>
+      <c r="B4179" s="34" t="s">
+        <v>31</v>
+      </c>
       <c r="C4179" s="34"/>
-      <c r="D4179" s="34"/>
-      <c r="E4179" s="31"/>
-      <c r="F4179" s="23"/>
+      <c r="D4179" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4179" s="31">
+        <v>105</v>
+      </c>
+      <c r="F4179" s="24">
+        <v>45901</v>
+      </c>
     </row>
     <row r="4180" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4180" s="34"/>
+      <c r="B4180" s="34" t="s">
+        <v>38</v>
+      </c>
       <c r="C4180" s="34"/>
-      <c r="D4180" s="34"/>
-      <c r="E4180" s="31"/>
-      <c r="F4180" s="23"/>
+      <c r="D4180" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4180" s="31">
+        <v>70</v>
+      </c>
+      <c r="F4180" s="24">
+        <v>45901</v>
+      </c>
     </row>
     <row r="4181" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4181" s="34"/>
+      <c r="B4181" s="34" t="s">
+        <v>34</v>
+      </c>
       <c r="C4181" s="34"/>
-      <c r="D4181" s="34"/>
-      <c r="E4181" s="31"/>
-      <c r="F4181" s="23"/>
+      <c r="D4181" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4181" s="31">
+        <v>35</v>
+      </c>
+      <c r="F4181" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4182" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4182" s="34"/>
+      <c r="B4182" s="34" t="s">
+        <v>37</v>
+      </c>
       <c r="C4182" s="34"/>
-      <c r="D4182" s="34"/>
-      <c r="E4182" s="31"/>
-      <c r="F4182" s="23"/>
+      <c r="D4182" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4182" s="31">
+        <v>10</v>
+      </c>
+      <c r="F4182" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4183" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4183" s="34"/>
+      <c r="B4183" s="34" t="s">
+        <v>23</v>
+      </c>
       <c r="C4183" s="34"/>
-      <c r="D4183" s="34"/>
-      <c r="E4183" s="31"/>
-      <c r="F4183" s="23"/>
+      <c r="D4183" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4183" s="31">
+        <v>5200</v>
+      </c>
+      <c r="F4183" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4184" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4184" s="34"/>
+      <c r="B4184" s="34" t="s">
+        <v>25</v>
+      </c>
       <c r="C4184" s="34"/>
-      <c r="D4184" s="34"/>
-      <c r="E4184" s="31"/>
-      <c r="F4184" s="23"/>
+      <c r="D4184" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4184" s="31">
+        <v>60</v>
+      </c>
+      <c r="F4184" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4185" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4185" s="34"/>
+      <c r="B4185" s="34" t="s">
+        <v>6</v>
+      </c>
       <c r="C4185" s="34"/>
-      <c r="D4185" s="34"/>
-      <c r="E4185" s="31"/>
-      <c r="F4185" s="23"/>
+      <c r="D4185" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4185" s="31">
+        <v>168.5</v>
+      </c>
+      <c r="F4185" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4186" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4186" s="34"/>
+      <c r="B4186" s="34" t="s">
+        <v>6</v>
+      </c>
       <c r="C4186" s="34"/>
-      <c r="D4186" s="34"/>
-      <c r="E4186" s="31"/>
-      <c r="F4186" s="23"/>
+      <c r="D4186" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4186" s="31">
+        <v>250</v>
+      </c>
+      <c r="F4186" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4187" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4187" s="34"/>
+      <c r="B4187" s="34" t="s">
+        <v>46</v>
+      </c>
       <c r="C4187" s="34"/>
-      <c r="D4187" s="34"/>
-      <c r="E4187" s="31"/>
-      <c r="F4187" s="23"/>
+      <c r="D4187" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4187" s="31">
+        <v>116</v>
+      </c>
+      <c r="F4187" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4188" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4188" s="34"/>
+      <c r="B4188" s="34" t="s">
+        <v>30</v>
+      </c>
       <c r="C4188" s="34"/>
-      <c r="D4188" s="34"/>
-      <c r="E4188" s="31"/>
-      <c r="F4188" s="23"/>
+      <c r="D4188" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4188" s="31">
+        <v>180</v>
+      </c>
+      <c r="F4188" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4189" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4189" s="34"/>
+      <c r="B4189" s="34" t="s">
+        <v>4</v>
+      </c>
       <c r="C4189" s="34"/>
-      <c r="D4189" s="34"/>
-      <c r="E4189" s="31"/>
-      <c r="F4189" s="23"/>
+      <c r="D4189" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4189" s="31">
+        <v>159.5</v>
+      </c>
+      <c r="F4189" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4190" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4190" s="34"/>
+      <c r="B4190" s="34" t="s">
+        <v>41</v>
+      </c>
       <c r="C4190" s="34"/>
-      <c r="D4190" s="34"/>
-      <c r="E4190" s="31"/>
-      <c r="F4190" s="23"/>
+      <c r="D4190" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4190" s="31">
+        <v>580</v>
+      </c>
+      <c r="F4190" s="24">
+        <v>45931</v>
+      </c>
     </row>
     <row r="4191" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4191" s="34"/>
@@ -64147,7 +64542,8 @@
       <c r="F4245" s="23"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:F4164" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
+  <autoFilter ref="B2:G4190" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="289" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E42DE2A-A550-4A36-9234-25E01B1F72F5}"/>
+  <xr:revisionPtr revIDLastSave="303" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6F3F9AB-7DA2-41FA-886D-5DE20A353326}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="113">
   <si>
     <t>Custo</t>
   </si>
@@ -14196,25 +14196,49 @@
       </c>
     </row>
     <row r="878" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B878" s="11"/>
+      <c r="B878" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C878" s="5"/>
-      <c r="D878" s="3"/>
-      <c r="E878" s="19"/>
-      <c r="F878" s="7"/>
+      <c r="D878" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E878" s="19">
+        <v>802.61</v>
+      </c>
+      <c r="F878" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="879" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B879" s="11"/>
+      <c r="B879" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C879" s="5"/>
-      <c r="D879" s="3"/>
-      <c r="E879" s="19"/>
-      <c r="F879" s="7"/>
+      <c r="D879" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E879" s="19">
+        <v>229.89</v>
+      </c>
+      <c r="F879" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="880" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B880" s="11"/>
+      <c r="B880" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C880" s="5"/>
-      <c r="D880" s="3"/>
-      <c r="E880" s="19"/>
-      <c r="F880" s="7"/>
+      <c r="D880" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E880" s="19">
+        <v>1558.88</v>
+      </c>
+      <c r="F880" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="881" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B881" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="303" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6F3F9AB-7DA2-41FA-886D-5DE20A353326}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{211FC343-C7DA-45F3-9CFD-5E476B8C1465}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="114">
   <si>
     <t>Custo</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>SHF2B16</t>
+  </si>
+  <si>
+    <t>HJF5G06</t>
   </si>
 </sst>
 </file>
@@ -14241,39 +14244,79 @@
       </c>
     </row>
     <row r="881" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B881" s="11"/>
+      <c r="B881" s="11" t="s">
+        <v>113</v>
+      </c>
       <c r="C881" s="5"/>
-      <c r="D881" s="3"/>
-      <c r="E881" s="19"/>
-      <c r="F881" s="7"/>
+      <c r="D881" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E881" s="19">
+        <v>173</v>
+      </c>
+      <c r="F881" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="882" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B882" s="11"/>
+      <c r="B882" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C882" s="5"/>
-      <c r="D882" s="3"/>
-      <c r="E882" s="19"/>
-      <c r="F882" s="7"/>
+      <c r="D882" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E882" s="19">
+        <v>200</v>
+      </c>
+      <c r="F882" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="883" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B883" s="11"/>
+      <c r="B883" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C883" s="5"/>
-      <c r="D883" s="3"/>
-      <c r="E883" s="19"/>
-      <c r="F883" s="7"/>
+      <c r="D883" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E883" s="19">
+        <v>270</v>
+      </c>
+      <c r="F883" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="884" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B884" s="11"/>
+      <c r="B884" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C884" s="5"/>
-      <c r="D884" s="3"/>
-      <c r="E884" s="19"/>
-      <c r="F884" s="7"/>
+      <c r="D884" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E884" s="19">
+        <v>1805</v>
+      </c>
+      <c r="F884" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="885" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B885" s="11"/>
+      <c r="B885" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="C885" s="5"/>
-      <c r="D885" s="3"/>
-      <c r="E885" s="19"/>
-      <c r="F885" s="7"/>
+      <c r="D885" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E885" s="19">
+        <v>1650</v>
+      </c>
+      <c r="F885" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="886" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B886" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{211FC343-C7DA-45F3-9CFD-5E476B8C1465}"/>
+  <xr:revisionPtr revIDLastSave="351" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76A1380D-3232-43BC-B189-3B04B6655887}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="114">
   <si>
     <t>Custo</t>
   </si>
@@ -1046,6 +1046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
+  <sheetPr filterMode="1"/>
   <dimension ref="B2:G4245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1075,7 +1076,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>19</v>
       </c>
@@ -1090,7 +1091,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" s="36" t="s">
         <v>18</v>
       </c>
@@ -1105,7 +1106,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
@@ -1120,7 +1121,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>18</v>
       </c>
@@ -1135,7 +1136,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>18</v>
       </c>
@@ -1150,7 +1151,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>18</v>
       </c>
@@ -1165,7 +1166,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>26</v>
       </c>
@@ -1180,7 +1181,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
         <v>26</v>
       </c>
@@ -1195,7 +1196,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>21</v>
       </c>
@@ -1210,7 +1211,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>9</v>
       </c>
@@ -1225,7 +1226,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>8</v>
       </c>
@@ -1240,7 +1241,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>8</v>
       </c>
@@ -1255,7 +1256,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>8</v>
       </c>
@@ -1270,7 +1271,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>8</v>
       </c>
@@ -1285,7 +1286,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>8</v>
       </c>
@@ -1300,7 +1301,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>8</v>
       </c>
@@ -1315,7 +1316,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>8</v>
       </c>
@@ -1330,7 +1331,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>3</v>
       </c>
@@ -1345,7 +1346,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>3</v>
       </c>
@@ -1360,7 +1361,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>3</v>
       </c>
@@ -1375,7 +1376,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>3</v>
       </c>
@@ -1390,7 +1391,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>3</v>
       </c>
@@ -1405,7 +1406,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>3</v>
       </c>
@@ -1420,7 +1421,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B26" s="29" t="s">
         <v>3</v>
       </c>
@@ -1435,7 +1436,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B27" s="29" t="s">
         <v>30</v>
       </c>
@@ -1450,7 +1451,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B28" s="29" t="s">
         <v>15</v>
       </c>
@@ -1465,7 +1466,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B29" s="29" t="s">
         <v>15</v>
       </c>
@@ -1480,7 +1481,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B30" s="29" t="s">
         <v>15</v>
       </c>
@@ -1495,7 +1496,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B31" s="28" t="s">
         <v>15</v>
       </c>
@@ -1510,7 +1511,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B32" s="28" t="s">
         <v>15</v>
       </c>
@@ -1525,7 +1526,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B33" s="28" t="s">
         <v>15</v>
       </c>
@@ -1540,7 +1541,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B34" s="28" t="s">
         <v>15</v>
       </c>
@@ -1555,7 +1556,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B35" s="28" t="s">
         <v>15</v>
       </c>
@@ -1570,7 +1571,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B36" s="28" t="s">
         <v>15</v>
       </c>
@@ -1585,7 +1586,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B37" s="28" t="s">
         <v>15</v>
       </c>
@@ -1600,7 +1601,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B38" s="28" t="s">
         <v>6</v>
       </c>
@@ -1615,7 +1616,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B39" s="28" t="s">
         <v>6</v>
       </c>
@@ -1630,7 +1631,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B40" s="28" t="s">
         <v>26</v>
       </c>
@@ -1645,7 +1646,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B41" s="28" t="s">
         <v>26</v>
       </c>
@@ -1660,7 +1661,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B42" s="28" t="s">
         <v>4</v>
       </c>
@@ -1675,7 +1676,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B43" s="28" t="s">
         <v>5</v>
       </c>
@@ -1690,7 +1691,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B44" s="28" t="s">
         <v>5</v>
       </c>
@@ -1705,7 +1706,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B45" s="28" t="s">
         <v>5</v>
       </c>
@@ -1720,7 +1721,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B46" s="28" t="s">
         <v>12</v>
       </c>
@@ -1735,7 +1736,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B47" s="28" t="s">
         <v>22</v>
       </c>
@@ -1750,7 +1751,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B48" s="28" t="s">
         <v>22</v>
       </c>
@@ -1765,7 +1766,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B49" s="28" t="s">
         <v>22</v>
       </c>
@@ -1780,7 +1781,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B50" s="28" t="s">
         <v>22</v>
       </c>
@@ -1795,7 +1796,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B51" s="28" t="s">
         <v>22</v>
       </c>
@@ -1810,7 +1811,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B52" s="28" t="s">
         <v>22</v>
       </c>
@@ -1825,7 +1826,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B53" s="28" t="s">
         <v>22</v>
       </c>
@@ -1840,7 +1841,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B54" s="28" t="s">
         <v>22</v>
       </c>
@@ -1855,7 +1856,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B55" s="28" t="s">
         <v>22</v>
       </c>
@@ -1870,7 +1871,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B56" s="28" t="s">
         <v>22</v>
       </c>
@@ -1885,7 +1886,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B57" s="28" t="s">
         <v>22</v>
       </c>
@@ -1900,7 +1901,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B58" s="28" t="s">
         <v>21</v>
       </c>
@@ -1915,7 +1916,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B59" s="28" t="s">
         <v>7</v>
       </c>
@@ -1930,7 +1931,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B60" s="28" t="s">
         <v>83</v>
       </c>
@@ -1945,7 +1946,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B61" s="28" t="s">
         <v>83</v>
       </c>
@@ -1960,7 +1961,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B62" s="28" t="s">
         <v>10</v>
       </c>
@@ -1975,7 +1976,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B63" s="28" t="s">
         <v>10</v>
       </c>
@@ -1990,7 +1991,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B64" s="28" t="s">
         <v>8</v>
       </c>
@@ -2005,7 +2006,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B65" s="28" t="s">
         <v>8</v>
       </c>
@@ -2020,7 +2021,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B66" s="28" t="s">
         <v>8</v>
       </c>
@@ -2035,7 +2036,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B67" s="28" t="s">
         <v>8</v>
       </c>
@@ -2050,7 +2051,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B68" s="28" t="s">
         <v>8</v>
       </c>
@@ -2065,7 +2066,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B69" s="28" t="s">
         <v>8</v>
       </c>
@@ -2080,7 +2081,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B70" s="28" t="s">
         <v>8</v>
       </c>
@@ -2095,7 +2096,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B71" s="28" t="s">
         <v>8</v>
       </c>
@@ -2110,7 +2111,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B72" s="28" t="s">
         <v>8</v>
       </c>
@@ -2125,7 +2126,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B73" s="28" t="s">
         <v>8</v>
       </c>
@@ -2140,7 +2141,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B74" s="28" t="s">
         <v>8</v>
       </c>
@@ -2155,7 +2156,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B75" s="28" t="s">
         <v>8</v>
       </c>
@@ -2170,7 +2171,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B76" s="28" t="s">
         <v>3</v>
       </c>
@@ -2185,7 +2186,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B77" s="11" t="s">
         <v>19</v>
       </c>
@@ -2200,7 +2201,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B78" s="11" t="s">
         <v>30</v>
       </c>
@@ -2215,7 +2216,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B79" s="11" t="s">
         <v>2</v>
       </c>
@@ -2230,7 +2231,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B80" s="11" t="s">
         <v>6</v>
       </c>
@@ -2245,7 +2246,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B81" s="11" t="s">
         <v>6</v>
       </c>
@@ -2260,7 +2261,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B82" s="11" t="s">
         <v>6</v>
       </c>
@@ -2275,7 +2276,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B83" s="11" t="s">
         <v>6</v>
       </c>
@@ -2290,7 +2291,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B84" s="11" t="s">
         <v>6</v>
       </c>
@@ -2305,7 +2306,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B85" s="11" t="s">
         <v>6</v>
       </c>
@@ -2320,7 +2321,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B86" s="11" t="s">
         <v>6</v>
       </c>
@@ -2335,7 +2336,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B87" s="11" t="s">
         <v>20</v>
       </c>
@@ -2350,7 +2351,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B88" s="11" t="s">
         <v>20</v>
       </c>
@@ -2365,7 +2366,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B89" s="11" t="s">
         <v>20</v>
       </c>
@@ -2380,7 +2381,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B90" s="11" t="s">
         <v>20</v>
       </c>
@@ -2395,7 +2396,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B91" s="11" t="s">
         <v>20</v>
       </c>
@@ -2410,7 +2411,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B92" s="11" t="s">
         <v>20</v>
       </c>
@@ -2425,7 +2426,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B93" s="11" t="s">
         <v>20</v>
       </c>
@@ -2440,7 +2441,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B94" s="11" t="s">
         <v>18</v>
       </c>
@@ -2455,7 +2456,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B95" s="11" t="s">
         <v>18</v>
       </c>
@@ -2470,7 +2471,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B96" s="11" t="s">
         <v>18</v>
       </c>
@@ -2485,7 +2486,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B97" s="11" t="s">
         <v>18</v>
       </c>
@@ -2500,7 +2501,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B98" s="11" t="s">
         <v>18</v>
       </c>
@@ -2515,7 +2516,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B99" s="11" t="s">
         <v>13</v>
       </c>
@@ -2530,7 +2531,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B100" s="11" t="s">
         <v>11</v>
       </c>
@@ -2545,7 +2546,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B101" s="11" t="s">
         <v>11</v>
       </c>
@@ -2560,7 +2561,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B102" s="11" t="s">
         <v>11</v>
       </c>
@@ -2575,7 +2576,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B103" s="11" t="s">
         <v>11</v>
       </c>
@@ -2590,7 +2591,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B104" s="11" t="s">
         <v>11</v>
       </c>
@@ -2605,7 +2606,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B105" s="11" t="s">
         <v>26</v>
       </c>
@@ -2620,7 +2621,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B106" s="11" t="s">
         <v>26</v>
       </c>
@@ -2635,7 +2636,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B107" s="11" t="s">
         <v>26</v>
       </c>
@@ -2650,7 +2651,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B108" s="11" t="s">
         <v>26</v>
       </c>
@@ -2665,7 +2666,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B109" s="11" t="s">
         <v>4</v>
       </c>
@@ -2680,7 +2681,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B110" s="11" t="s">
         <v>4</v>
       </c>
@@ -2695,7 +2696,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B111" s="11" t="s">
         <v>4</v>
       </c>
@@ -2710,7 +2711,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B112" s="11" t="s">
         <v>4</v>
       </c>
@@ -2725,7 +2726,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B113" s="11" t="s">
         <v>4</v>
       </c>
@@ -2740,7 +2741,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B114" s="11" t="s">
         <v>4</v>
       </c>
@@ -2755,7 +2756,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B115" s="11" t="s">
         <v>4</v>
       </c>
@@ -2770,7 +2771,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B116" s="11" t="s">
         <v>4</v>
       </c>
@@ -2785,7 +2786,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B117" s="11" t="s">
         <v>4</v>
       </c>
@@ -2800,7 +2801,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B118" s="11" t="s">
         <v>4</v>
       </c>
@@ -2815,7 +2816,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B119" s="11" t="s">
         <v>4</v>
       </c>
@@ -2830,7 +2831,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B120" s="11" t="s">
         <v>4</v>
       </c>
@@ -2845,7 +2846,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B121" s="11" t="s">
         <v>4</v>
       </c>
@@ -2860,7 +2861,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B122" s="11" t="s">
         <v>24</v>
       </c>
@@ -2875,7 +2876,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B123" s="11" t="s">
         <v>24</v>
       </c>
@@ -2890,7 +2891,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B124" s="11" t="s">
         <v>24</v>
       </c>
@@ -2905,7 +2906,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B125" s="11" t="s">
         <v>24</v>
       </c>
@@ -2920,7 +2921,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B126" s="11" t="s">
         <v>24</v>
       </c>
@@ -2935,7 +2936,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B127" s="11" t="s">
         <v>24</v>
       </c>
@@ -2950,7 +2951,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="128" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B128" s="11" t="s">
         <v>16</v>
       </c>
@@ -2965,7 +2966,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B129" s="11" t="s">
         <v>16</v>
       </c>
@@ -2980,7 +2981,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B130" s="11" t="s">
         <v>5</v>
       </c>
@@ -2995,7 +2996,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B131" s="11" t="s">
         <v>5</v>
       </c>
@@ -3010,7 +3011,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B132" s="11" t="s">
         <v>5</v>
       </c>
@@ -3025,7 +3026,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B133" s="11" t="s">
         <v>5</v>
       </c>
@@ -3040,7 +3041,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B134" s="11" t="s">
         <v>28</v>
       </c>
@@ -3055,7 +3056,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B135" s="11" t="s">
         <v>28</v>
       </c>
@@ -3070,7 +3071,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B136" s="11" t="s">
         <v>28</v>
       </c>
@@ -3085,7 +3086,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B137" s="11" t="s">
         <v>28</v>
       </c>
@@ -3100,7 +3101,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B138" s="11" t="s">
         <v>28</v>
       </c>
@@ -3115,7 +3116,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B139" s="11" t="s">
         <v>28</v>
       </c>
@@ -3130,7 +3131,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B140" s="11" t="s">
         <v>28</v>
       </c>
@@ -3145,7 +3146,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B141" s="11" t="s">
         <v>28</v>
       </c>
@@ -3160,7 +3161,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B142" s="11" t="s">
         <v>28</v>
       </c>
@@ -3175,7 +3176,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B143" s="11" t="s">
         <v>28</v>
       </c>
@@ -3190,7 +3191,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B144" s="11" t="s">
         <v>28</v>
       </c>
@@ -3205,7 +3206,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B145" s="11" t="s">
         <v>28</v>
       </c>
@@ -3220,7 +3221,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B146" s="11" t="s">
         <v>17</v>
       </c>
@@ -3235,7 +3236,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B147" s="11" t="s">
         <v>17</v>
       </c>
@@ -3250,7 +3251,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B148" s="11" t="s">
         <v>29</v>
       </c>
@@ -3265,7 +3266,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B149" s="11" t="s">
         <v>29</v>
       </c>
@@ -3280,7 +3281,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B150" s="11" t="s">
         <v>22</v>
       </c>
@@ -3295,7 +3296,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B151" s="11" t="s">
         <v>22</v>
       </c>
@@ -3310,7 +3311,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B152" s="11" t="s">
         <v>22</v>
       </c>
@@ -3325,7 +3326,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B153" s="11" t="s">
         <v>22</v>
       </c>
@@ -3340,7 +3341,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B154" s="11" t="s">
         <v>22</v>
       </c>
@@ -3355,7 +3356,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B155" s="11" t="s">
         <v>55</v>
       </c>
@@ -3370,7 +3371,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B156" s="11" t="s">
         <v>21</v>
       </c>
@@ -3385,7 +3386,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B157" s="11" t="s">
         <v>21</v>
       </c>
@@ -3400,7 +3401,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B158" s="11" t="s">
         <v>21</v>
       </c>
@@ -3415,7 +3416,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B159" s="11" t="s">
         <v>21</v>
       </c>
@@ -3430,7 +3431,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B160" s="11" t="s">
         <v>21</v>
       </c>
@@ -3445,7 +3446,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B161" s="11" t="s">
         <v>21</v>
       </c>
@@ -3460,7 +3461,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B162" s="11" t="s">
         <v>21</v>
       </c>
@@ -3475,7 +3476,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B163" s="11" t="s">
         <v>21</v>
       </c>
@@ -3490,7 +3491,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B164" s="11" t="s">
         <v>21</v>
       </c>
@@ -3505,7 +3506,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B165" s="11" t="s">
         <v>21</v>
       </c>
@@ -3520,7 +3521,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B166" s="11" t="s">
         <v>21</v>
       </c>
@@ -3535,7 +3536,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B167" s="11" t="s">
         <v>21</v>
       </c>
@@ -3550,7 +3551,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B168" s="11" t="s">
         <v>9</v>
       </c>
@@ -3565,7 +3566,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B169" s="11" t="s">
         <v>9</v>
       </c>
@@ -3580,7 +3581,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="170" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B170" s="11" t="s">
         <v>9</v>
       </c>
@@ -3595,7 +3596,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B171" s="11" t="s">
         <v>9</v>
       </c>
@@ -3610,7 +3611,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B172" s="11" t="s">
         <v>9</v>
       </c>
@@ -3625,7 +3626,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B173" s="11" t="s">
         <v>9</v>
       </c>
@@ -3640,7 +3641,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B174" s="11" t="s">
         <v>9</v>
       </c>
@@ -3655,7 +3656,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B175" s="11" t="s">
         <v>9</v>
       </c>
@@ -3670,7 +3671,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="176" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B176" s="11" t="s">
         <v>9</v>
       </c>
@@ -3685,7 +3686,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B177" s="11" t="s">
         <v>9</v>
       </c>
@@ -3700,7 +3701,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B178" s="11" t="s">
         <v>9</v>
       </c>
@@ -3715,7 +3716,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B179" s="11" t="s">
         <v>9</v>
       </c>
@@ -3730,7 +3731,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B180" s="11" t="s">
         <v>7</v>
       </c>
@@ -3745,7 +3746,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B181" s="11" t="s">
         <v>83</v>
       </c>
@@ -3760,7 +3761,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B182" s="11" t="s">
         <v>83</v>
       </c>
@@ -3775,7 +3776,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B183" s="11" t="s">
         <v>14</v>
       </c>
@@ -3790,7 +3791,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B184" s="11" t="s">
         <v>14</v>
       </c>
@@ -3805,7 +3806,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B185" s="11" t="s">
         <v>10</v>
       </c>
@@ -3820,7 +3821,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B186" s="11" t="s">
         <v>10</v>
       </c>
@@ -3835,7 +3836,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B187" s="11" t="s">
         <v>10</v>
       </c>
@@ -3850,7 +3851,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B188" s="11" t="s">
         <v>10</v>
       </c>
@@ -3865,7 +3866,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B189" s="11" t="s">
         <v>10</v>
       </c>
@@ -3880,7 +3881,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B190" s="11" t="s">
         <v>10</v>
       </c>
@@ -3895,7 +3896,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B191" s="11" t="s">
         <v>8</v>
       </c>
@@ -3910,7 +3911,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B192" s="11" t="s">
         <v>8</v>
       </c>
@@ -3925,7 +3926,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B193" s="11" t="s">
         <v>8</v>
       </c>
@@ -3940,7 +3941,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B194" s="11" t="s">
         <v>8</v>
       </c>
@@ -3955,7 +3956,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B195" s="11" t="s">
         <v>3</v>
       </c>
@@ -3970,7 +3971,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B196" s="11" t="s">
         <v>3</v>
       </c>
@@ -3985,7 +3986,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B197" s="11" t="s">
         <v>3</v>
       </c>
@@ -4000,7 +4001,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B198" s="11" t="s">
         <v>3</v>
       </c>
@@ -4015,7 +4016,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="199" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B199" s="11" t="s">
         <v>3</v>
       </c>
@@ -4030,7 +4031,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="200" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B200" s="11" t="s">
         <v>3</v>
       </c>
@@ -4045,7 +4046,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="201" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B201" s="11" t="s">
         <v>3</v>
       </c>
@@ -4060,7 +4061,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="202" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B202" s="11" t="s">
         <v>3</v>
       </c>
@@ -4075,7 +4076,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="203" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B203" s="11" t="s">
         <v>3</v>
       </c>
@@ -4090,7 +4091,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="204" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B204" s="11" t="s">
         <v>19</v>
       </c>
@@ -4105,7 +4106,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="205" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B205" s="11" t="s">
         <v>30</v>
       </c>
@@ -4120,7 +4121,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="206" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B206" s="11" t="s">
         <v>32</v>
       </c>
@@ -4135,7 +4136,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="207" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B207" s="11" t="s">
         <v>32</v>
       </c>
@@ -4150,7 +4151,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="208" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B208" s="11" t="s">
         <v>32</v>
       </c>
@@ -4165,7 +4166,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="209" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B209" s="11" t="s">
         <v>15</v>
       </c>
@@ -4180,7 +4181,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="210" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B210" s="11" t="s">
         <v>15</v>
       </c>
@@ -4195,7 +4196,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="211" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B211" s="11" t="s">
         <v>15</v>
       </c>
@@ -4210,7 +4211,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="212" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B212" s="11" t="s">
         <v>15</v>
       </c>
@@ -4225,7 +4226,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="213" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B213" s="11" t="s">
         <v>15</v>
       </c>
@@ -4240,7 +4241,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="214" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B214" s="11" t="s">
         <v>15</v>
       </c>
@@ -4255,7 +4256,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="215" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B215" s="11" t="s">
         <v>15</v>
       </c>
@@ -4270,7 +4271,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="216" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B216" s="11" t="s">
         <v>15</v>
       </c>
@@ -4285,7 +4286,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="217" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B217" s="11" t="s">
         <v>15</v>
       </c>
@@ -4300,7 +4301,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="218" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B218" s="11" t="s">
         <v>6</v>
       </c>
@@ -4315,7 +4316,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="219" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B219" s="11" t="s">
         <v>6</v>
       </c>
@@ -4330,7 +4331,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="220" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B220" s="11" t="s">
         <v>6</v>
       </c>
@@ -4345,7 +4346,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="221" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B221" s="11" t="s">
         <v>6</v>
       </c>
@@ -4360,7 +4361,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="222" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B222" s="11" t="s">
         <v>6</v>
       </c>
@@ -4375,7 +4376,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="223" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B223" s="11" t="s">
         <v>6</v>
       </c>
@@ -4390,7 +4391,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="224" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B224" s="11" t="s">
         <v>6</v>
       </c>
@@ -4405,7 +4406,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="225" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B225" s="11" t="s">
         <v>6</v>
       </c>
@@ -4420,7 +4421,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="226" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B226" s="11" t="s">
         <v>6</v>
       </c>
@@ -4435,7 +4436,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="227" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B227" s="11" t="s">
         <v>20</v>
       </c>
@@ -4450,7 +4451,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="228" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B228" s="11" t="s">
         <v>20</v>
       </c>
@@ -4465,7 +4466,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="229" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B229" s="11" t="s">
         <v>20</v>
       </c>
@@ -4480,7 +4481,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="230" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B230" s="11" t="s">
         <v>20</v>
       </c>
@@ -4495,7 +4496,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="231" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B231" s="11" t="s">
         <v>20</v>
       </c>
@@ -4510,7 +4511,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="232" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B232" s="11" t="s">
         <v>20</v>
       </c>
@@ -4525,7 +4526,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="233" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B233" s="11" t="s">
         <v>20</v>
       </c>
@@ -4540,7 +4541,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="234" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B234" s="11" t="s">
         <v>20</v>
       </c>
@@ -4555,7 +4556,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="235" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B235" s="11" t="s">
         <v>20</v>
       </c>
@@ -4570,7 +4571,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="236" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B236" s="11" t="s">
         <v>20</v>
       </c>
@@ -4585,7 +4586,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="237" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B237" s="11" t="s">
         <v>20</v>
       </c>
@@ -4600,7 +4601,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="238" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B238" s="11" t="s">
         <v>18</v>
       </c>
@@ -4615,7 +4616,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="239" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B239" s="11" t="s">
         <v>18</v>
       </c>
@@ -4630,7 +4631,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="240" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B240" s="11" t="s">
         <v>18</v>
       </c>
@@ -4645,7 +4646,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="241" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B241" s="11" t="s">
         <v>18</v>
       </c>
@@ -4660,7 +4661,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="242" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B242" s="11" t="s">
         <v>18</v>
       </c>
@@ -4675,7 +4676,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="243" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B243" s="11" t="s">
         <v>18</v>
       </c>
@@ -4690,7 +4691,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="244" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B244" s="11" t="s">
         <v>18</v>
       </c>
@@ -4705,7 +4706,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="245" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B245" s="11" t="s">
         <v>18</v>
       </c>
@@ -4720,7 +4721,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="246" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B246" s="11" t="s">
         <v>13</v>
       </c>
@@ -4735,7 +4736,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="247" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B247" s="11" t="s">
         <v>13</v>
       </c>
@@ -4750,7 +4751,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="248" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B248" s="11" t="s">
         <v>13</v>
       </c>
@@ -4765,7 +4766,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="249" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B249" s="11" t="s">
         <v>13</v>
       </c>
@@ -4780,7 +4781,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="250" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B250" s="11" t="s">
         <v>13</v>
       </c>
@@ -4795,7 +4796,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="251" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B251" s="11" t="s">
         <v>11</v>
       </c>
@@ -4810,7 +4811,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="252" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B252" s="11" t="s">
         <v>11</v>
       </c>
@@ -4825,7 +4826,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="253" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B253" s="11" t="s">
         <v>11</v>
       </c>
@@ -4840,7 +4841,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="254" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B254" s="11" t="s">
         <v>11</v>
       </c>
@@ -4855,7 +4856,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="255" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B255" s="11" t="s">
         <v>11</v>
       </c>
@@ -4870,7 +4871,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="256" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B256" s="11" t="s">
         <v>11</v>
       </c>
@@ -4885,7 +4886,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="257" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B257" s="11" t="s">
         <v>11</v>
       </c>
@@ -4900,7 +4901,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="258" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B258" s="11" t="s">
         <v>4</v>
       </c>
@@ -4915,7 +4916,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="259" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B259" s="11" t="s">
         <v>4</v>
       </c>
@@ -4930,7 +4931,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="260" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B260" s="11" t="s">
         <v>4</v>
       </c>
@@ -4945,7 +4946,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="261" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B261" s="11" t="s">
         <v>4</v>
       </c>
@@ -4960,7 +4961,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="262" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B262" s="11" t="s">
         <v>4</v>
       </c>
@@ -4975,7 +4976,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="263" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B263" s="11" t="s">
         <v>4</v>
       </c>
@@ -4990,7 +4991,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="264" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B264" s="11" t="s">
         <v>4</v>
       </c>
@@ -5005,7 +5006,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="265" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B265" s="11" t="s">
         <v>4</v>
       </c>
@@ -5020,7 +5021,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="266" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B266" s="11" t="s">
         <v>4</v>
       </c>
@@ -5035,7 +5036,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="267" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B267" s="11" t="s">
         <v>4</v>
       </c>
@@ -5050,7 +5051,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="268" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B268" s="11" t="s">
         <v>4</v>
       </c>
@@ -5065,7 +5066,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="269" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B269" s="11" t="s">
         <v>24</v>
       </c>
@@ -5080,7 +5081,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="270" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B270" s="11" t="s">
         <v>25</v>
       </c>
@@ -5095,7 +5096,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="271" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B271" s="11" t="s">
         <v>25</v>
       </c>
@@ -5110,7 +5111,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="272" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B272" s="11" t="s">
         <v>25</v>
       </c>
@@ -5125,7 +5126,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B273" s="11" t="s">
         <v>16</v>
       </c>
@@ -5140,7 +5141,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="274" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B274" s="11" t="s">
         <v>5</v>
       </c>
@@ -5155,7 +5156,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="275" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B275" s="11" t="s">
         <v>5</v>
       </c>
@@ -5170,7 +5171,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="276" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B276" s="11" t="s">
         <v>5</v>
       </c>
@@ -5185,7 +5186,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="277" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B277" s="11" t="s">
         <v>5</v>
       </c>
@@ -5200,7 +5201,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="278" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B278" s="11" t="s">
         <v>5</v>
       </c>
@@ -5215,7 +5216,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="279" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B279" s="11" t="s">
         <v>5</v>
       </c>
@@ -5230,7 +5231,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="280" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B280" s="11" t="s">
         <v>5</v>
       </c>
@@ -5245,7 +5246,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="281" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B281" s="11" t="s">
         <v>5</v>
       </c>
@@ -5260,7 +5261,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="282" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B282" s="11" t="s">
         <v>5</v>
       </c>
@@ -5275,7 +5276,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="283" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B283" s="11" t="s">
         <v>5</v>
       </c>
@@ -5290,7 +5291,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="284" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B284" s="11" t="s">
         <v>5</v>
       </c>
@@ -5305,7 +5306,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="285" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B285" s="11" t="s">
         <v>5</v>
       </c>
@@ -5320,7 +5321,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="286" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B286" s="11" t="s">
         <v>5</v>
       </c>
@@ -5335,7 +5336,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="287" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B287" s="11" t="s">
         <v>5</v>
       </c>
@@ -5350,7 +5351,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="288" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B288" s="11" t="s">
         <v>5</v>
       </c>
@@ -5365,7 +5366,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="289" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B289" s="11" t="s">
         <v>5</v>
       </c>
@@ -5380,7 +5381,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="290" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B290" s="11" t="s">
         <v>5</v>
       </c>
@@ -5395,7 +5396,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="291" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B291" s="11" t="s">
         <v>28</v>
       </c>
@@ -5410,7 +5411,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="292" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B292" s="11" t="s">
         <v>45</v>
       </c>
@@ -5425,7 +5426,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="293" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B293" s="11" t="s">
         <v>17</v>
       </c>
@@ -5440,7 +5441,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="294" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B294" s="11" t="s">
         <v>17</v>
       </c>
@@ -5455,7 +5456,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="295" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B295" s="11" t="s">
         <v>17</v>
       </c>
@@ -5470,7 +5471,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="296" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B296" s="11" t="s">
         <v>17</v>
       </c>
@@ -5485,7 +5486,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="297" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B297" s="11" t="s">
         <v>17</v>
       </c>
@@ -5500,7 +5501,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="298" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B298" s="11" t="s">
         <v>17</v>
       </c>
@@ -5515,7 +5516,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="299" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B299" s="11" t="s">
         <v>17</v>
       </c>
@@ -5530,7 +5531,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="300" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B300" s="11" t="s">
         <v>22</v>
       </c>
@@ -5545,7 +5546,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="301" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B301" s="11" t="s">
         <v>22</v>
       </c>
@@ -5560,7 +5561,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="302" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B302" s="11" t="s">
         <v>22</v>
       </c>
@@ -5575,7 +5576,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="303" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B303" s="11" t="s">
         <v>22</v>
       </c>
@@ -5590,7 +5591,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="304" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B304" s="11" t="s">
         <v>34</v>
       </c>
@@ -5605,7 +5606,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="305" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B305" s="11" t="s">
         <v>21</v>
       </c>
@@ -5620,7 +5621,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="306" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B306" s="11" t="s">
         <v>21</v>
       </c>
@@ -5635,7 +5636,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="307" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B307" s="11" t="s">
         <v>21</v>
       </c>
@@ -5650,7 +5651,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="308" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B308" s="11" t="s">
         <v>21</v>
       </c>
@@ -5665,7 +5666,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="309" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B309" s="11" t="s">
         <v>21</v>
       </c>
@@ -5680,7 +5681,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="310" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B310" s="11" t="s">
         <v>21</v>
       </c>
@@ -5695,7 +5696,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="311" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B311" s="11" t="s">
         <v>21</v>
       </c>
@@ -5710,7 +5711,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="312" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B312" s="11" t="s">
         <v>21</v>
       </c>
@@ -5725,7 +5726,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="313" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B313" s="11" t="s">
         <v>21</v>
       </c>
@@ -5740,7 +5741,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="314" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B314" s="11" t="s">
         <v>21</v>
       </c>
@@ -5755,7 +5756,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="315" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B315" s="11" t="s">
         <v>21</v>
       </c>
@@ -5770,7 +5771,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="316" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B316" s="11" t="s">
         <v>21</v>
       </c>
@@ -5785,7 +5786,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="317" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B317" s="11" t="s">
         <v>21</v>
       </c>
@@ -5800,7 +5801,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="318" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B318" s="11" t="s">
         <v>21</v>
       </c>
@@ -5815,7 +5816,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="319" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B319" s="11" t="s">
         <v>21</v>
       </c>
@@ -5830,7 +5831,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="320" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B320" s="11" t="s">
         <v>9</v>
       </c>
@@ -5845,7 +5846,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="321" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B321" s="11" t="s">
         <v>9</v>
       </c>
@@ -5860,7 +5861,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="322" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B322" s="11" t="s">
         <v>9</v>
       </c>
@@ -5875,7 +5876,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="323" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B323" s="11" t="s">
         <v>9</v>
       </c>
@@ -5890,7 +5891,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="324" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B324" s="11" t="s">
         <v>9</v>
       </c>
@@ -5905,7 +5906,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="325" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B325" s="11" t="s">
         <v>9</v>
       </c>
@@ -5920,7 +5921,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="326" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B326" s="11" t="s">
         <v>9</v>
       </c>
@@ -5935,7 +5936,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="327" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B327" s="11" t="s">
         <v>7</v>
       </c>
@@ -5950,7 +5951,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="328" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B328" s="11" t="s">
         <v>7</v>
       </c>
@@ -5965,7 +5966,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="329" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B329" s="11" t="s">
         <v>7</v>
       </c>
@@ -5980,7 +5981,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="330" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B330" s="11" t="s">
         <v>7</v>
       </c>
@@ -5995,7 +5996,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="331" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B331" s="11" t="s">
         <v>7</v>
       </c>
@@ -6010,7 +6011,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="332" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B332" s="11" t="s">
         <v>7</v>
       </c>
@@ -6025,7 +6026,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="333" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B333" s="11" t="s">
         <v>7</v>
       </c>
@@ -6040,7 +6041,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="334" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B334" s="11" t="s">
         <v>7</v>
       </c>
@@ -6055,7 +6056,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="335" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B335" s="27" t="s">
         <v>31</v>
       </c>
@@ -6070,7 +6071,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="336" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B336" s="27" t="s">
         <v>31</v>
       </c>
@@ -6085,7 +6086,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="337" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B337" s="27" t="s">
         <v>31</v>
       </c>
@@ -6100,7 +6101,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="338" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B338" s="27" t="s">
         <v>31</v>
       </c>
@@ -6115,7 +6116,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="339" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B339" s="27" t="s">
         <v>31</v>
       </c>
@@ -6130,7 +6131,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="340" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B340" s="11" t="s">
         <v>10</v>
       </c>
@@ -6145,7 +6146,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="341" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B341" s="11" t="s">
         <v>8</v>
       </c>
@@ -6160,7 +6161,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="342" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B342" s="11" t="s">
         <v>8</v>
       </c>
@@ -6175,7 +6176,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="343" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B343" s="11" t="s">
         <v>8</v>
       </c>
@@ -6190,7 +6191,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="344" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B344" s="11" t="s">
         <v>8</v>
       </c>
@@ -6205,7 +6206,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="345" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B345" s="11" t="s">
         <v>8</v>
       </c>
@@ -6220,7 +6221,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="346" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B346" s="11" t="s">
         <v>8</v>
       </c>
@@ -6235,7 +6236,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="347" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B347" s="11" t="s">
         <v>8</v>
       </c>
@@ -6250,7 +6251,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="348" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B348" s="11" t="s">
         <v>8</v>
       </c>
@@ -6265,7 +6266,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="349" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B349" s="11" t="s">
         <v>3</v>
       </c>
@@ -6280,7 +6281,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="350" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B350" s="11" t="s">
         <v>3</v>
       </c>
@@ -6295,7 +6296,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="351" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B351" s="11" t="s">
         <v>3</v>
       </c>
@@ -6310,7 +6311,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="352" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B352" s="11" t="s">
         <v>3</v>
       </c>
@@ -6325,7 +6326,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="353" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B353" s="11" t="s">
         <v>3</v>
       </c>
@@ -6340,7 +6341,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="354" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B354" s="11" t="s">
         <v>87</v>
       </c>
@@ -6355,7 +6356,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="355" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B355" s="11" t="s">
         <v>19</v>
       </c>
@@ -6370,7 +6371,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="356" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B356" s="11" t="s">
         <v>19</v>
       </c>
@@ -6385,7 +6386,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="357" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B357" s="11" t="s">
         <v>19</v>
       </c>
@@ -6400,7 +6401,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="358" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B358" s="11" t="s">
         <v>19</v>
       </c>
@@ -6415,7 +6416,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="359" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B359" s="11" t="s">
         <v>19</v>
       </c>
@@ -6430,7 +6431,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="360" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B360" s="11" t="s">
         <v>19</v>
       </c>
@@ -6445,7 +6446,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="361" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B361" s="11" t="s">
         <v>19</v>
       </c>
@@ -6460,7 +6461,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="362" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B362" s="11" t="s">
         <v>19</v>
       </c>
@@ -6475,7 +6476,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="363" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B363" s="11" t="s">
         <v>19</v>
       </c>
@@ -6490,7 +6491,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="364" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B364" s="11" t="s">
         <v>19</v>
       </c>
@@ -6505,7 +6506,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="365" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B365" s="11" t="s">
         <v>19</v>
       </c>
@@ -6520,7 +6521,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="366" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B366" s="11" t="s">
         <v>19</v>
       </c>
@@ -6535,7 +6536,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="367" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B367" s="11" t="s">
         <v>30</v>
       </c>
@@ -6550,7 +6551,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="368" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B368" s="11" t="s">
         <v>30</v>
       </c>
@@ -6565,7 +6566,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="369" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B369" s="11" t="s">
         <v>32</v>
       </c>
@@ -6580,7 +6581,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="370" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B370" s="27" t="s">
         <v>39</v>
       </c>
@@ -6595,7 +6596,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="371" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B371" s="11" t="s">
         <v>59</v>
       </c>
@@ -6610,7 +6611,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="372" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B372" s="11" t="s">
         <v>15</v>
       </c>
@@ -6625,7 +6626,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="373" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B373" s="11" t="s">
         <v>15</v>
       </c>
@@ -6640,7 +6641,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="374" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B374" s="11" t="s">
         <v>15</v>
       </c>
@@ -6655,7 +6656,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="375" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B375" s="11" t="s">
         <v>15</v>
       </c>
@@ -6670,7 +6671,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="376" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B376" s="11" t="s">
         <v>15</v>
       </c>
@@ -6685,7 +6686,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="377" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B377" s="11" t="s">
         <v>6</v>
       </c>
@@ -6700,7 +6701,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="378" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B378" s="11" t="s">
         <v>6</v>
       </c>
@@ -6715,7 +6716,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="379" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B379" s="11" t="s">
         <v>6</v>
       </c>
@@ -6730,7 +6731,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="380" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B380" s="11" t="s">
         <v>6</v>
       </c>
@@ -6745,7 +6746,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="381" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B381" s="11" t="s">
         <v>6</v>
       </c>
@@ -6760,7 +6761,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="382" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B382" s="11" t="s">
         <v>6</v>
       </c>
@@ -6775,7 +6776,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="383" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B383" s="11" t="s">
         <v>6</v>
       </c>
@@ -6790,7 +6791,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="384" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B384" s="11" t="s">
         <v>20</v>
       </c>
@@ -6805,7 +6806,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="385" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B385" s="11" t="s">
         <v>20</v>
       </c>
@@ -6820,7 +6821,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="386" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B386" s="11" t="s">
         <v>20</v>
       </c>
@@ -6835,7 +6836,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="387" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B387" s="11" t="s">
         <v>18</v>
       </c>
@@ -6850,7 +6851,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="388" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B388" s="11" t="s">
         <v>18</v>
       </c>
@@ -6865,7 +6866,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="389" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B389" s="11" t="s">
         <v>18</v>
       </c>
@@ -6880,7 +6881,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="390" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B390" s="11" t="s">
         <v>13</v>
       </c>
@@ -6895,7 +6896,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="391" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B391" s="11" t="s">
         <v>13</v>
       </c>
@@ -6910,7 +6911,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="392" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B392" s="11" t="s">
         <v>13</v>
       </c>
@@ -6925,7 +6926,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="393" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B393" s="27" t="s">
         <v>11</v>
       </c>
@@ -6940,7 +6941,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="394" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B394" s="27" t="s">
         <v>11</v>
       </c>
@@ -6955,7 +6956,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="395" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B395" s="27" t="s">
         <v>11</v>
       </c>
@@ -6970,7 +6971,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="396" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B396" s="27" t="s">
         <v>11</v>
       </c>
@@ -6985,7 +6986,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="397" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B397" s="27" t="s">
         <v>11</v>
       </c>
@@ -7000,7 +7001,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="398" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B398" s="27" t="s">
         <v>11</v>
       </c>
@@ -7015,7 +7016,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="399" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B399" s="27" t="s">
         <v>11</v>
       </c>
@@ -7030,7 +7031,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="400" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B400" s="27" t="s">
         <v>11</v>
       </c>
@@ -7045,7 +7046,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="401" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B401" s="27" t="s">
         <v>11</v>
       </c>
@@ -7060,7 +7061,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="402" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B402" s="27" t="s">
         <v>11</v>
       </c>
@@ -7075,7 +7076,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="403" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B403" s="27" t="s">
         <v>11</v>
       </c>
@@ -7090,7 +7091,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="404" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B404" s="27" t="s">
         <v>11</v>
       </c>
@@ -7105,7 +7106,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="405" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B405" s="27" t="s">
         <v>11</v>
       </c>
@@ -7120,7 +7121,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="406" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B406" s="27" t="s">
         <v>11</v>
       </c>
@@ -7135,7 +7136,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="407" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B407" s="27" t="s">
         <v>11</v>
       </c>
@@ -7150,7 +7151,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="408" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B408" s="27" t="s">
         <v>11</v>
       </c>
@@ -7165,7 +7166,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="409" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B409" s="27" t="s">
         <v>11</v>
       </c>
@@ -7180,7 +7181,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="410" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B410" s="27" t="s">
         <v>11</v>
       </c>
@@ -7195,7 +7196,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="411" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B411" s="27" t="s">
         <v>11</v>
       </c>
@@ -7210,7 +7211,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="412" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B412" s="27" t="s">
         <v>11</v>
       </c>
@@ -7225,7 +7226,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="413" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B413" s="27" t="s">
         <v>11</v>
       </c>
@@ -7240,7 +7241,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="414" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B414" s="27" t="s">
         <v>11</v>
       </c>
@@ -7255,7 +7256,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="415" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B415" s="27" t="s">
         <v>11</v>
       </c>
@@ -7270,7 +7271,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="416" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B416" s="27" t="s">
         <v>11</v>
       </c>
@@ -7285,7 +7286,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="417" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B417" s="27" t="s">
         <v>11</v>
       </c>
@@ -7300,7 +7301,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="418" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B418" s="27" t="s">
         <v>11</v>
       </c>
@@ -7315,7 +7316,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="419" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B419" s="11" t="s">
         <v>11</v>
       </c>
@@ -7330,7 +7331,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="420" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B420" s="11" t="s">
         <v>11</v>
       </c>
@@ -7345,7 +7346,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="421" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B421" s="11" t="s">
         <v>11</v>
       </c>
@@ -7360,7 +7361,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="422" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B422" s="11" t="s">
         <v>11</v>
       </c>
@@ -7375,7 +7376,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="423" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B423" s="11" t="s">
         <v>11</v>
       </c>
@@ -7390,7 +7391,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="424" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B424" s="11" t="s">
         <v>11</v>
       </c>
@@ -7405,7 +7406,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="425" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B425" s="11" t="s">
         <v>11</v>
       </c>
@@ -7420,7 +7421,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="426" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B426" s="11" t="s">
         <v>11</v>
       </c>
@@ -7435,7 +7436,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="427" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B427" s="11" t="s">
         <v>11</v>
       </c>
@@ -7450,7 +7451,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="428" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B428" s="11" t="s">
         <v>23</v>
       </c>
@@ -7465,7 +7466,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="429" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B429" s="11" t="s">
         <v>23</v>
       </c>
@@ -7480,7 +7481,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="430" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B430" s="11" t="s">
         <v>23</v>
       </c>
@@ -7495,7 +7496,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="431" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B431" s="27" t="s">
         <v>4</v>
       </c>
@@ -7510,7 +7511,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="432" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B432" s="11" t="s">
         <v>4</v>
       </c>
@@ -7525,7 +7526,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="433" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B433" s="11" t="s">
         <v>4</v>
       </c>
@@ -7540,7 +7541,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="434" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B434" s="11" t="s">
         <v>4</v>
       </c>
@@ -7555,7 +7556,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="435" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B435" s="11" t="s">
         <v>4</v>
       </c>
@@ -7570,7 +7571,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="436" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B436" s="11" t="s">
         <v>4</v>
       </c>
@@ -7585,7 +7586,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="437" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B437" s="11" t="s">
         <v>4</v>
       </c>
@@ -7600,7 +7601,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="438" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B438" s="11" t="s">
         <v>4</v>
       </c>
@@ -7615,7 +7616,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="439" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B439" s="11" t="s">
         <v>4</v>
       </c>
@@ -7630,7 +7631,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="440" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B440" s="11" t="s">
         <v>4</v>
       </c>
@@ -7645,7 +7646,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="441" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B441" s="11" t="s">
         <v>4</v>
       </c>
@@ -7660,7 +7661,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="442" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B442" s="11" t="s">
         <v>4</v>
       </c>
@@ -7675,7 +7676,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="443" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B443" s="11" t="s">
         <v>4</v>
       </c>
@@ -7690,7 +7691,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="444" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B444" s="11" t="s">
         <v>4</v>
       </c>
@@ -7705,7 +7706,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="445" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B445" s="11" t="s">
         <v>4</v>
       </c>
@@ -7720,7 +7721,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="446" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B446" s="11" t="s">
         <v>4</v>
       </c>
@@ -7735,7 +7736,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="447" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B447" s="11" t="s">
         <v>4</v>
       </c>
@@ -7750,7 +7751,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="448" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B448" s="11" t="s">
         <v>4</v>
       </c>
@@ -7765,7 +7766,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="449" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B449" s="11" t="s">
         <v>4</v>
       </c>
@@ -7780,7 +7781,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="450" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B450" s="11" t="s">
         <v>4</v>
       </c>
@@ -7795,7 +7796,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="451" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B451" s="11" t="s">
         <v>4</v>
       </c>
@@ -7810,7 +7811,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="452" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B452" s="11" t="s">
         <v>4</v>
       </c>
@@ -7825,7 +7826,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="453" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B453" s="11" t="s">
         <v>4</v>
       </c>
@@ -7840,7 +7841,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="454" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B454" s="11" t="s">
         <v>4</v>
       </c>
@@ -7855,7 +7856,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="455" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B455" s="11" t="s">
         <v>4</v>
       </c>
@@ -7870,7 +7871,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="456" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B456" s="11" t="s">
         <v>4</v>
       </c>
@@ -7885,7 +7886,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="457" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B457" s="11" t="s">
         <v>4</v>
       </c>
@@ -7900,7 +7901,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="458" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B458" s="11" t="s">
         <v>4</v>
       </c>
@@ -7915,7 +7916,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="459" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B459" s="11" t="s">
         <v>24</v>
       </c>
@@ -7930,7 +7931,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="460" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B460" s="11" t="s">
         <v>24</v>
       </c>
@@ -7945,7 +7946,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="461" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B461" s="11" t="s">
         <v>24</v>
       </c>
@@ -7960,7 +7961,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="462" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B462" s="11" t="s">
         <v>24</v>
       </c>
@@ -7975,7 +7976,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="463" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B463" s="11" t="s">
         <v>24</v>
       </c>
@@ -7990,7 +7991,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="464" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B464" s="11" t="s">
         <v>24</v>
       </c>
@@ -8005,7 +8006,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="465" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B465" s="11" t="s">
         <v>24</v>
       </c>
@@ -8020,7 +8021,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="466" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B466" s="11" t="s">
         <v>24</v>
       </c>
@@ -8035,7 +8036,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="467" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B467" s="11" t="s">
         <v>24</v>
       </c>
@@ -8050,7 +8051,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="468" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B468" s="11" t="s">
         <v>24</v>
       </c>
@@ -8065,7 +8066,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="469" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B469" s="11" t="s">
         <v>24</v>
       </c>
@@ -8080,7 +8081,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="470" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B470" s="11" t="s">
         <v>24</v>
       </c>
@@ -8095,7 +8096,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="471" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B471" s="11" t="s">
         <v>24</v>
       </c>
@@ -8110,7 +8111,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="472" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B472" s="11" t="s">
         <v>24</v>
       </c>
@@ -8125,7 +8126,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="473" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B473" s="11" t="s">
         <v>24</v>
       </c>
@@ -8140,7 +8141,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="474" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B474" s="11" t="s">
         <v>24</v>
       </c>
@@ -8155,7 +8156,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="475" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B475" s="11" t="s">
         <v>24</v>
       </c>
@@ -8170,7 +8171,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="476" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B476" s="11" t="s">
         <v>24</v>
       </c>
@@ -8185,7 +8186,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="477" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B477" s="11" t="s">
         <v>24</v>
       </c>
@@ -8200,7 +8201,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="478" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B478" s="11" t="s">
         <v>24</v>
       </c>
@@ -8215,7 +8216,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="479" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B479" s="11" t="s">
         <v>24</v>
       </c>
@@ -8230,7 +8231,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="480" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B480" s="11" t="s">
         <v>24</v>
       </c>
@@ -8245,7 +8246,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="481" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B481" s="11" t="s">
         <v>24</v>
       </c>
@@ -8260,7 +8261,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="482" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B482" s="11" t="s">
         <v>24</v>
       </c>
@@ -8275,7 +8276,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="483" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B483" s="11" t="s">
         <v>24</v>
       </c>
@@ -8290,7 +8291,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="484" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B484" s="11" t="s">
         <v>24</v>
       </c>
@@ -8305,7 +8306,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="485" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B485" s="11" t="s">
         <v>24</v>
       </c>
@@ -8320,7 +8321,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="486" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B486" s="11" t="s">
         <v>24</v>
       </c>
@@ -8335,7 +8336,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="487" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B487" s="11" t="s">
         <v>24</v>
       </c>
@@ -8350,7 +8351,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="488" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B488" s="11" t="s">
         <v>24</v>
       </c>
@@ -8365,7 +8366,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="489" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B489" s="11" t="s">
         <v>24</v>
       </c>
@@ -8380,7 +8381,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="490" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B490" s="11" t="s">
         <v>24</v>
       </c>
@@ -8395,7 +8396,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="491" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B491" s="11" t="s">
         <v>24</v>
       </c>
@@ -8410,7 +8411,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="492" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B492" s="11" t="s">
         <v>24</v>
       </c>
@@ -8425,7 +8426,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="493" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B493" s="11" t="s">
         <v>24</v>
       </c>
@@ -8440,7 +8441,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="494" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B494" s="11" t="s">
         <v>24</v>
       </c>
@@ -8455,7 +8456,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="495" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B495" s="11" t="s">
         <v>24</v>
       </c>
@@ -8470,7 +8471,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="496" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B496" s="11" t="s">
         <v>24</v>
       </c>
@@ -8485,7 +8486,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="497" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B497" s="11" t="s">
         <v>24</v>
       </c>
@@ -8500,7 +8501,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="498" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B498" s="11" t="s">
         <v>24</v>
       </c>
@@ -8515,7 +8516,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="499" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B499" s="11" t="s">
         <v>24</v>
       </c>
@@ -8530,7 +8531,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="500" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B500" s="11" t="s">
         <v>24</v>
       </c>
@@ -8545,7 +8546,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="501" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B501" s="11" t="s">
         <v>24</v>
       </c>
@@ -8560,7 +8561,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="502" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B502" s="11" t="s">
         <v>24</v>
       </c>
@@ -8575,7 +8576,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="503" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B503" s="11" t="s">
         <v>25</v>
       </c>
@@ -8590,7 +8591,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="504" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B504" s="11" t="s">
         <v>25</v>
       </c>
@@ -8605,7 +8606,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="505" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B505" s="11" t="s">
         <v>25</v>
       </c>
@@ -8620,7 +8621,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="506" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B506" s="11" t="s">
         <v>25</v>
       </c>
@@ -8635,7 +8636,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="507" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B507" s="11" t="s">
         <v>25</v>
       </c>
@@ -8650,7 +8651,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="508" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B508" s="11" t="s">
         <v>25</v>
       </c>
@@ -8665,7 +8666,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="509" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B509" s="11" t="s">
         <v>25</v>
       </c>
@@ -8680,7 +8681,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="510" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B510" s="11" t="s">
         <v>25</v>
       </c>
@@ -8695,7 +8696,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="511" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B511" s="11" t="s">
         <v>25</v>
       </c>
@@ -8710,7 +8711,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="512" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B512" s="11" t="s">
         <v>25</v>
       </c>
@@ -8725,7 +8726,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="513" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B513" s="11" t="s">
         <v>25</v>
       </c>
@@ -8740,7 +8741,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="514" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B514" s="11" t="s">
         <v>25</v>
       </c>
@@ -8755,7 +8756,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="515" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B515" s="11" t="s">
         <v>25</v>
       </c>
@@ -8770,7 +8771,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="516" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B516" s="11" t="s">
         <v>25</v>
       </c>
@@ -8785,7 +8786,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="517" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B517" s="11" t="s">
         <v>25</v>
       </c>
@@ -8800,7 +8801,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="518" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B518" s="11" t="s">
         <v>25</v>
       </c>
@@ -8815,7 +8816,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="519" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B519" s="11" t="s">
         <v>25</v>
       </c>
@@ -8830,7 +8831,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="520" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B520" s="11" t="s">
         <v>25</v>
       </c>
@@ -8845,7 +8846,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="521" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B521" s="11" t="s">
         <v>25</v>
       </c>
@@ -8860,7 +8861,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="522" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B522" s="11" t="s">
         <v>25</v>
       </c>
@@ -8875,7 +8876,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="523" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B523" s="11" t="s">
         <v>25</v>
       </c>
@@ -8890,7 +8891,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="524" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B524" s="11" t="s">
         <v>5</v>
       </c>
@@ -8905,7 +8906,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="525" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B525" s="11" t="s">
         <v>5</v>
       </c>
@@ -8920,7 +8921,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="526" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B526" s="11" t="s">
         <v>5</v>
       </c>
@@ -8935,7 +8936,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="527" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B527" s="11" t="s">
         <v>5</v>
       </c>
@@ -8950,7 +8951,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="528" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B528" s="11" t="s">
         <v>28</v>
       </c>
@@ -8965,7 +8966,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="529" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B529" s="11" t="s">
         <v>28</v>
       </c>
@@ -8980,7 +8981,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="530" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B530" s="11" t="s">
         <v>28</v>
       </c>
@@ -8995,7 +8996,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="531" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B531" s="11" t="s">
         <v>28</v>
       </c>
@@ -9010,7 +9011,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="532" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B532" s="11" t="s">
         <v>17</v>
       </c>
@@ -9025,7 +9026,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="533" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B533" s="11" t="s">
         <v>17</v>
       </c>
@@ -9040,7 +9041,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="534" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B534" s="11" t="s">
         <v>17</v>
       </c>
@@ -9055,7 +9056,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="535" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B535" s="11" t="s">
         <v>17</v>
       </c>
@@ -9070,7 +9071,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="536" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B536" s="11" t="s">
         <v>17</v>
       </c>
@@ -9085,7 +9086,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="537" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B537" s="11" t="s">
         <v>17</v>
       </c>
@@ -9100,7 +9101,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="538" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B538" s="11" t="s">
         <v>17</v>
       </c>
@@ -9115,7 +9116,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="539" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B539" s="11" t="s">
         <v>22</v>
       </c>
@@ -9130,7 +9131,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="540" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B540" s="11" t="s">
         <v>22</v>
       </c>
@@ -9145,7 +9146,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="541" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B541" s="11" t="s">
         <v>22</v>
       </c>
@@ -9160,7 +9161,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="542" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B542" s="11" t="s">
         <v>22</v>
       </c>
@@ -9175,7 +9176,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="543" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B543" s="27" t="s">
         <v>21</v>
       </c>
@@ -9190,7 +9191,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="544" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B544" s="27" t="s">
         <v>21</v>
       </c>
@@ -9205,7 +9206,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="545" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B545" s="27" t="s">
         <v>21</v>
       </c>
@@ -9220,7 +9221,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="546" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B546" s="27" t="s">
         <v>21</v>
       </c>
@@ -9235,7 +9236,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="547" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B547" s="27" t="s">
         <v>21</v>
       </c>
@@ -9250,7 +9251,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="548" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B548" s="27" t="s">
         <v>21</v>
       </c>
@@ -9265,7 +9266,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="549" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B549" s="27" t="s">
         <v>21</v>
       </c>
@@ -9280,7 +9281,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="550" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B550" s="27" t="s">
         <v>21</v>
       </c>
@@ -9295,7 +9296,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="551" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B551" s="27" t="s">
         <v>21</v>
       </c>
@@ -9310,7 +9311,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="552" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B552" s="27" t="s">
         <v>21</v>
       </c>
@@ -9325,7 +9326,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="553" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B553" s="27" t="s">
         <v>21</v>
       </c>
@@ -9340,7 +9341,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="554" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B554" s="27" t="s">
         <v>21</v>
       </c>
@@ -9355,7 +9356,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="555" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B555" s="27" t="s">
         <v>21</v>
       </c>
@@ -9370,7 +9371,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="556" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B556" s="27" t="s">
         <v>21</v>
       </c>
@@ -9385,7 +9386,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="557" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B557" s="27" t="s">
         <v>21</v>
       </c>
@@ -9400,7 +9401,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="558" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B558" s="27" t="s">
         <v>21</v>
       </c>
@@ -9415,7 +9416,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="559" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B559" s="27" t="s">
         <v>21</v>
       </c>
@@ -9430,7 +9431,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="560" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B560" s="27" t="s">
         <v>21</v>
       </c>
@@ -9445,7 +9446,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="561" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B561" s="11" t="s">
         <v>21</v>
       </c>
@@ -9460,7 +9461,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="562" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B562" s="11" t="s">
         <v>21</v>
       </c>
@@ -9475,7 +9476,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="563" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B563" s="11" t="s">
         <v>9</v>
       </c>
@@ -9490,7 +9491,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="564" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B564" s="11" t="s">
         <v>9</v>
       </c>
@@ -9505,7 +9506,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="565" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B565" s="11" t="s">
         <v>9</v>
       </c>
@@ -9520,7 +9521,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="566" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B566" s="11" t="s">
         <v>9</v>
       </c>
@@ -9535,7 +9536,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="567" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B567" s="11" t="s">
         <v>9</v>
       </c>
@@ -9550,7 +9551,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="568" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B568" s="11" t="s">
         <v>9</v>
       </c>
@@ -9565,7 +9566,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="569" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B569" s="11" t="s">
         <v>37</v>
       </c>
@@ -9580,7 +9581,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="570" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B570" s="11" t="s">
         <v>37</v>
       </c>
@@ -9595,7 +9596,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="571" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B571" s="11" t="s">
         <v>37</v>
       </c>
@@ -9610,7 +9611,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="572" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B572" s="11" t="s">
         <v>37</v>
       </c>
@@ -9625,7 +9626,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="573" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B573" s="11" t="s">
         <v>37</v>
       </c>
@@ -9640,7 +9641,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="574" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B574" s="11" t="s">
         <v>37</v>
       </c>
@@ -9655,7 +9656,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="575" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B575" s="11" t="s">
         <v>37</v>
       </c>
@@ -9670,7 +9671,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="576" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B576" s="11" t="s">
         <v>7</v>
       </c>
@@ -9685,7 +9686,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="577" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B577" s="11" t="s">
         <v>7</v>
       </c>
@@ -9700,7 +9701,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="578" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B578" s="11" t="s">
         <v>7</v>
       </c>
@@ -9715,7 +9716,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="579" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B579" s="11" t="s">
         <v>7</v>
       </c>
@@ -9730,7 +9731,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="580" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B580" s="11" t="s">
         <v>7</v>
       </c>
@@ -9745,7 +9746,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="581" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B581" s="11" t="s">
         <v>7</v>
       </c>
@@ -9760,7 +9761,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="582" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B582" s="11" t="s">
         <v>7</v>
       </c>
@@ -9775,7 +9776,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="583" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B583" s="11" t="s">
         <v>7</v>
       </c>
@@ -9790,7 +9791,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="584" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B584" s="11" t="s">
         <v>83</v>
       </c>
@@ -9805,7 +9806,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="585" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B585" s="11" t="s">
         <v>83</v>
       </c>
@@ -9820,7 +9821,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="586" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B586" s="11" t="s">
         <v>83</v>
       </c>
@@ -9835,7 +9836,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="587" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B587" s="11" t="s">
         <v>31</v>
       </c>
@@ -9850,7 +9851,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="588" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B588" s="11" t="s">
         <v>8</v>
       </c>
@@ -9865,7 +9866,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="589" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B589" s="11" t="s">
         <v>8</v>
       </c>
@@ -9880,7 +9881,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="590" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B590" s="11" t="s">
         <v>8</v>
       </c>
@@ -9895,7 +9896,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="591" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B591" s="11" t="s">
         <v>3</v>
       </c>
@@ -9910,7 +9911,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="592" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B592" s="11" t="s">
         <v>3</v>
       </c>
@@ -9925,7 +9926,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="593" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B593" s="11" t="s">
         <v>3</v>
       </c>
@@ -9940,7 +9941,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="594" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B594" s="11" t="s">
         <v>3</v>
       </c>
@@ -9955,7 +9956,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="595" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B595" s="11" t="s">
         <v>3</v>
       </c>
@@ -9970,7 +9971,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="596" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B596" s="11" t="s">
         <v>3</v>
       </c>
@@ -9985,7 +9986,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="597" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B597" s="11" t="s">
         <v>19</v>
       </c>
@@ -10000,7 +10001,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="598" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B598" s="11" t="s">
         <v>30</v>
       </c>
@@ -10015,7 +10016,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="599" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B599" s="11" t="s">
         <v>30</v>
       </c>
@@ -10030,7 +10031,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="600" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B600" s="11" t="s">
         <v>30</v>
       </c>
@@ -10045,7 +10046,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="601" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B601" s="11" t="s">
         <v>32</v>
       </c>
@@ -10060,7 +10061,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="602" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B602" s="11" t="s">
         <v>32</v>
       </c>
@@ -10075,7 +10076,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="603" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B603" s="11" t="s">
         <v>32</v>
       </c>
@@ -10090,7 +10091,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="604" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B604" s="11" t="s">
         <v>32</v>
       </c>
@@ -10105,7 +10106,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="605" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B605" s="11" t="s">
         <v>15</v>
       </c>
@@ -10120,7 +10121,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="606" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B606" s="11" t="s">
         <v>15</v>
       </c>
@@ -10135,7 +10136,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="607" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B607" s="11" t="s">
         <v>15</v>
       </c>
@@ -10150,7 +10151,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="608" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B608" s="11" t="s">
         <v>15</v>
       </c>
@@ -10165,7 +10166,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="609" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B609" s="11" t="s">
         <v>20</v>
       </c>
@@ -10180,7 +10181,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="610" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B610" s="11" t="s">
         <v>20</v>
       </c>
@@ -10193,7 +10194,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="611" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B611" s="11" t="s">
         <v>20</v>
       </c>
@@ -10208,7 +10209,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="612" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B612" s="11" t="s">
         <v>20</v>
       </c>
@@ -10223,7 +10224,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="613" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B613" s="11" t="s">
         <v>20</v>
       </c>
@@ -10238,7 +10239,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="614" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B614" s="11" t="s">
         <v>20</v>
       </c>
@@ -10253,7 +10254,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="615" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B615" s="11" t="s">
         <v>18</v>
       </c>
@@ -10268,7 +10269,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="616" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B616" s="11" t="s">
         <v>18</v>
       </c>
@@ -10283,7 +10284,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="617" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B617" s="11" t="s">
         <v>18</v>
       </c>
@@ -10298,7 +10299,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="618" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B618" s="11" t="s">
         <v>18</v>
       </c>
@@ -10313,7 +10314,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="619" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B619" s="11" t="s">
         <v>18</v>
       </c>
@@ -10328,7 +10329,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="620" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B620" s="11" t="s">
         <v>13</v>
       </c>
@@ -10343,7 +10344,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="621" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B621" s="11" t="s">
         <v>13</v>
       </c>
@@ -10358,7 +10359,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="622" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B622" s="11" t="s">
         <v>11</v>
       </c>
@@ -10373,7 +10374,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="623" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B623" s="11" t="s">
         <v>11</v>
       </c>
@@ -10388,7 +10389,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="624" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B624" s="11" t="s">
         <v>11</v>
       </c>
@@ -10403,7 +10404,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="625" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B625" s="11" t="s">
         <v>23</v>
       </c>
@@ -10418,7 +10419,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="626" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B626" s="11" t="s">
         <v>4</v>
       </c>
@@ -10433,7 +10434,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="627" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B627" s="11" t="s">
         <v>4</v>
       </c>
@@ -10448,7 +10449,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="628" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B628" s="11" t="s">
         <v>24</v>
       </c>
@@ -10463,7 +10464,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="629" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B629" s="11" t="s">
         <v>24</v>
       </c>
@@ -10478,7 +10479,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="630" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B630" s="11" t="s">
         <v>24</v>
       </c>
@@ -10493,7 +10494,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="631" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B631" s="11" t="s">
         <v>27</v>
       </c>
@@ -10508,7 +10509,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="632" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B632" s="11" t="s">
         <v>25</v>
       </c>
@@ -10523,7 +10524,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="633" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B633" s="11" t="s">
         <v>5</v>
       </c>
@@ -10538,7 +10539,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="634" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B634" s="11" t="s">
         <v>5</v>
       </c>
@@ -10553,7 +10554,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="635" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B635" s="11" t="s">
         <v>5</v>
       </c>
@@ -10568,7 +10569,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="636" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B636" s="11" t="s">
         <v>28</v>
       </c>
@@ -10583,7 +10584,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="637" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B637" s="11" t="s">
         <v>28</v>
       </c>
@@ -10598,7 +10599,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="638" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B638" s="15" t="s">
         <v>28</v>
       </c>
@@ -10613,7 +10614,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="639" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B639" s="11" t="s">
         <v>28</v>
       </c>
@@ -10628,7 +10629,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="640" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B640" s="11" t="s">
         <v>28</v>
       </c>
@@ -10643,7 +10644,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="641" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B641" s="11" t="s">
         <v>28</v>
       </c>
@@ -10658,7 +10659,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="642" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B642" s="11" t="s">
         <v>28</v>
       </c>
@@ -10673,7 +10674,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="643" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B643" s="11" t="s">
         <v>28</v>
       </c>
@@ -10688,7 +10689,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="644" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B644" s="11" t="s">
         <v>17</v>
       </c>
@@ -10703,7 +10704,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="645" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B645" s="11" t="s">
         <v>17</v>
       </c>
@@ -10718,7 +10719,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="646" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B646" s="11" t="s">
         <v>29</v>
       </c>
@@ -10733,7 +10734,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="647" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B647" s="11" t="s">
         <v>21</v>
       </c>
@@ -10748,7 +10749,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="648" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B648" s="11" t="s">
         <v>21</v>
       </c>
@@ -10763,7 +10764,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="649" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B649" s="11" t="s">
         <v>21</v>
       </c>
@@ -10778,7 +10779,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="650" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B650" s="11" t="s">
         <v>9</v>
       </c>
@@ -10793,7 +10794,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="651" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B651" s="11" t="s">
         <v>7</v>
       </c>
@@ -10808,7 +10809,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="652" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B652" s="11" t="s">
         <v>7</v>
       </c>
@@ -10823,7 +10824,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="653" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B653" s="11" t="s">
         <v>7</v>
       </c>
@@ -10838,7 +10839,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="654" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B654" s="11" t="s">
         <v>14</v>
       </c>
@@ -10853,7 +10854,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="655" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="655" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B655" s="11" t="s">
         <v>31</v>
       </c>
@@ -10868,7 +10869,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="656" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B656" s="11" t="s">
         <v>8</v>
       </c>
@@ -10883,7 +10884,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="657" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B657" s="11" t="s">
         <v>3</v>
       </c>
@@ -10898,7 +10899,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="658" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B658" s="11" t="s">
         <v>3</v>
       </c>
@@ -10913,7 +10914,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="659" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B659" s="11" t="s">
         <v>3</v>
       </c>
@@ -10928,7 +10929,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="660" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B660" s="11" t="s">
         <v>19</v>
       </c>
@@ -10943,7 +10944,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="661" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B661" s="11" t="s">
         <v>30</v>
       </c>
@@ -10958,7 +10959,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="662" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B662" s="11" t="s">
         <v>32</v>
       </c>
@@ -10973,7 +10974,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="663" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B663" s="11" t="s">
         <v>32</v>
       </c>
@@ -10988,7 +10989,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="664" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B664" s="11" t="s">
         <v>32</v>
       </c>
@@ -11003,7 +11004,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="665" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B665" s="11" t="s">
         <v>32</v>
       </c>
@@ -11018,7 +11019,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="666" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B666" s="11" t="s">
         <v>32</v>
       </c>
@@ -11033,7 +11034,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="667" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B667" s="11" t="s">
         <v>32</v>
       </c>
@@ -11048,7 +11049,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="668" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B668" s="11" t="s">
         <v>32</v>
       </c>
@@ -11063,7 +11064,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="669" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B669" s="11" t="s">
         <v>32</v>
       </c>
@@ -11078,7 +11079,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="670" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B670" s="11" t="s">
         <v>32</v>
       </c>
@@ -11093,7 +11094,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="671" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B671" s="11" t="s">
         <v>39</v>
       </c>
@@ -11108,7 +11109,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="672" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B672" s="11" t="s">
         <v>15</v>
       </c>
@@ -11123,7 +11124,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="673" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="673" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B673" s="11" t="s">
         <v>6</v>
       </c>
@@ -11138,7 +11139,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="674" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="674" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B674" s="11" t="s">
         <v>6</v>
       </c>
@@ -11153,7 +11154,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="675" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="675" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B675" s="11" t="s">
         <v>6</v>
       </c>
@@ -11168,7 +11169,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="676" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="676" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B676" s="11" t="s">
         <v>6</v>
       </c>
@@ -11183,7 +11184,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="677" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="677" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B677" s="11" t="s">
         <v>6</v>
       </c>
@@ -11198,7 +11199,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="678" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="678" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B678" s="11" t="s">
         <v>6</v>
       </c>
@@ -11213,7 +11214,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="679" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="679" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B679" s="11" t="s">
         <v>20</v>
       </c>
@@ -11228,7 +11229,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="680" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="680" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B680" s="11" t="s">
         <v>18</v>
       </c>
@@ -11243,7 +11244,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="681" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="681" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B681" s="11" t="s">
         <v>18</v>
       </c>
@@ -11258,7 +11259,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="682" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="682" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B682" s="11" t="s">
         <v>13</v>
       </c>
@@ -11273,7 +11274,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="683" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="683" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B683" s="11" t="s">
         <v>13</v>
       </c>
@@ -11288,7 +11289,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="684" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="684" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B684" s="11" t="s">
         <v>11</v>
       </c>
@@ -11303,7 +11304,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="685" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="685" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B685" s="11" t="s">
         <v>11</v>
       </c>
@@ -11318,7 +11319,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="686" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="686" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B686" s="11" t="s">
         <v>11</v>
       </c>
@@ -11333,7 +11334,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="687" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="687" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B687" s="11" t="s">
         <v>11</v>
       </c>
@@ -11348,7 +11349,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="688" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="688" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B688" s="11" t="s">
         <v>11</v>
       </c>
@@ -11363,7 +11364,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="689" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="689" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B689" s="11" t="s">
         <v>11</v>
       </c>
@@ -11378,7 +11379,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="690" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="690" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B690" s="11" t="s">
         <v>11</v>
       </c>
@@ -11393,7 +11394,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="691" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="691" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B691" s="11" t="s">
         <v>11</v>
       </c>
@@ -11408,7 +11409,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="692" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="692" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B692" s="11" t="s">
         <v>11</v>
       </c>
@@ -11423,7 +11424,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="693" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="693" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B693" s="11" t="s">
         <v>26</v>
       </c>
@@ -11438,7 +11439,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="694" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="694" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B694" s="11" t="s">
         <v>4</v>
       </c>
@@ -11453,7 +11454,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="695" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="695" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B695" s="11" t="s">
         <v>24</v>
       </c>
@@ -11468,7 +11469,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="696" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="696" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B696" s="11" t="s">
         <v>24</v>
       </c>
@@ -11483,7 +11484,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="697" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="697" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B697" s="11" t="s">
         <v>24</v>
       </c>
@@ -11498,7 +11499,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="698" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="698" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B698" s="11" t="s">
         <v>24</v>
       </c>
@@ -11513,7 +11514,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="699" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="699" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B699" s="11" t="s">
         <v>5</v>
       </c>
@@ -11528,7 +11529,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="700" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="700" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B700" s="11" t="s">
         <v>5</v>
       </c>
@@ -11543,7 +11544,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="701" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="701" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B701" s="11" t="s">
         <v>5</v>
       </c>
@@ -11558,7 +11559,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="702" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="702" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B702" s="11" t="s">
         <v>12</v>
       </c>
@@ -11573,7 +11574,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="703" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="703" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B703" s="11" t="s">
         <v>28</v>
       </c>
@@ -11588,7 +11589,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="704" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="704" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B704" s="11" t="s">
         <v>98</v>
       </c>
@@ -11603,7 +11604,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="705" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="705" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B705" s="11" t="s">
         <v>29</v>
       </c>
@@ -11618,7 +11619,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="706" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="706" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B706" s="11" t="s">
         <v>29</v>
       </c>
@@ -11633,7 +11634,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="707" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="707" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B707" s="11" t="s">
         <v>29</v>
       </c>
@@ -11648,7 +11649,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="708" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="708" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B708" s="11" t="s">
         <v>29</v>
       </c>
@@ -11663,7 +11664,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="709" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="709" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B709" s="11" t="s">
         <v>29</v>
       </c>
@@ -11678,7 +11679,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="710" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="710" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B710" s="11" t="s">
         <v>29</v>
       </c>
@@ -11693,7 +11694,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="711" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="711" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B711" s="11" t="s">
         <v>22</v>
       </c>
@@ -11708,7 +11709,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="712" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="712" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B712" s="11" t="s">
         <v>21</v>
       </c>
@@ -11723,7 +11724,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="713" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="713" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B713" s="11" t="s">
         <v>21</v>
       </c>
@@ -11738,7 +11739,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="714" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="714" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B714" s="11" t="s">
         <v>9</v>
       </c>
@@ -11753,7 +11754,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="715" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="715" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B715" s="11" t="s">
         <v>9</v>
       </c>
@@ -11768,7 +11769,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="716" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="716" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B716" s="11" t="s">
         <v>7</v>
       </c>
@@ -11783,7 +11784,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="717" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="717" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B717" s="11" t="s">
         <v>7</v>
       </c>
@@ -11798,7 +11799,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="718" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="718" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B718" s="11" t="s">
         <v>93</v>
       </c>
@@ -11813,7 +11814,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="719" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="719" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B719" s="11" t="s">
         <v>14</v>
       </c>
@@ -11828,7 +11829,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="720" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="720" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B720" s="11" t="s">
         <v>14</v>
       </c>
@@ -11843,7 +11844,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="721" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="721" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B721" s="11" t="s">
         <v>14</v>
       </c>
@@ -11858,7 +11859,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="722" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="722" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B722" s="11" t="s">
         <v>103</v>
       </c>
@@ -11873,7 +11874,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="723" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="723" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B723" s="11" t="s">
         <v>8</v>
       </c>
@@ -11888,7 +11889,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="724" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="724" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B724" s="11" t="s">
         <v>3</v>
       </c>
@@ -11903,7 +11904,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="725" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="725" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B725" s="11" t="s">
         <v>3</v>
       </c>
@@ -11918,7 +11919,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="726" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="726" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B726" s="11" t="s">
         <v>19</v>
       </c>
@@ -11933,7 +11934,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="727" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="727" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B727" s="11" t="s">
         <v>19</v>
       </c>
@@ -11948,7 +11949,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="728" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="728" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B728" s="11" t="s">
         <v>19</v>
       </c>
@@ -11963,7 +11964,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="729" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="729" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B729" s="11" t="s">
         <v>19</v>
       </c>
@@ -11978,7 +11979,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="730" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="730" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B730" s="11" t="s">
         <v>19</v>
       </c>
@@ -11993,7 +11994,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="731" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="731" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B731" s="11" t="s">
         <v>19</v>
       </c>
@@ -12008,7 +12009,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="732" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="732" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B732" s="11" t="s">
         <v>32</v>
       </c>
@@ -12023,7 +12024,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="733" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="733" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B733" s="11" t="s">
         <v>32</v>
       </c>
@@ -12038,7 +12039,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="734" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="734" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B734" s="11" t="s">
         <v>32</v>
       </c>
@@ -12053,7 +12054,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="735" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="735" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B735" s="11" t="s">
         <v>32</v>
       </c>
@@ -12068,7 +12069,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="736" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="736" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B736" s="11" t="s">
         <v>32</v>
       </c>
@@ -12083,7 +12084,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="737" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="737" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B737" s="11" t="s">
         <v>32</v>
       </c>
@@ -12098,7 +12099,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="738" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="738" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B738" s="11" t="s">
         <v>32</v>
       </c>
@@ -12113,7 +12114,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="739" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="739" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B739" s="11" t="s">
         <v>15</v>
       </c>
@@ -12128,7 +12129,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="740" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="740" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B740" s="11" t="s">
         <v>15</v>
       </c>
@@ -12143,7 +12144,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="741" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="741" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B741" s="11" t="s">
         <v>15</v>
       </c>
@@ -12158,7 +12159,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="742" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="742" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B742" s="11" t="s">
         <v>15</v>
       </c>
@@ -12173,7 +12174,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="743" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="743" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B743" s="11" t="s">
         <v>6</v>
       </c>
@@ -12188,7 +12189,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="744" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="744" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B744" s="11" t="s">
         <v>6</v>
       </c>
@@ -12203,7 +12204,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="745" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="745" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B745" s="11" t="s">
         <v>6</v>
       </c>
@@ -12218,7 +12219,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="746" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="746" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B746" s="11" t="s">
         <v>6</v>
       </c>
@@ -12233,7 +12234,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="747" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="747" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B747" s="11" t="s">
         <v>6</v>
       </c>
@@ -12248,7 +12249,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="748" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="748" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B748" s="11" t="s">
         <v>6</v>
       </c>
@@ -12263,7 +12264,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="749" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="749" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B749" s="11" t="s">
         <v>6</v>
       </c>
@@ -12278,7 +12279,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="750" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="750" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B750" s="11" t="s">
         <v>20</v>
       </c>
@@ -12293,7 +12294,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="751" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="751" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B751" s="11" t="s">
         <v>20</v>
       </c>
@@ -12308,7 +12309,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="752" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="752" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B752" s="11" t="s">
         <v>18</v>
       </c>
@@ -12323,7 +12324,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="753" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="753" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B753" s="11" t="s">
         <v>18</v>
       </c>
@@ -12338,7 +12339,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="754" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="754" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B754" s="11" t="s">
         <v>18</v>
       </c>
@@ -12353,7 +12354,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="755" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="755" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B755" s="11" t="s">
         <v>18</v>
       </c>
@@ -12368,7 +12369,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="756" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="756" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B756" s="11" t="s">
         <v>18</v>
       </c>
@@ -12383,7 +12384,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="757" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="757" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B757" s="11" t="s">
         <v>18</v>
       </c>
@@ -12398,7 +12399,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="758" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="758" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B758" s="11" t="s">
         <v>18</v>
       </c>
@@ -12413,7 +12414,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="759" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="759" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B759" s="11" t="s">
         <v>13</v>
       </c>
@@ -12428,7 +12429,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="760" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="760" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B760" s="11" t="s">
         <v>13</v>
       </c>
@@ -12443,7 +12444,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="761" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="761" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B761" s="11" t="s">
         <v>13</v>
       </c>
@@ -12458,7 +12459,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="762" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="762" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B762" s="11" t="s">
         <v>13</v>
       </c>
@@ -12473,7 +12474,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="763" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="763" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B763" s="11" t="s">
         <v>11</v>
       </c>
@@ -12488,7 +12489,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="764" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="764" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B764" s="11" t="s">
         <v>11</v>
       </c>
@@ -12503,7 +12504,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="765" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="765" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B765" s="11" t="s">
         <v>11</v>
       </c>
@@ -12518,7 +12519,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="766" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="766" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B766" s="11" t="s">
         <v>11</v>
       </c>
@@ -12533,7 +12534,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="767" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="767" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B767" s="11" t="s">
         <v>26</v>
       </c>
@@ -12548,7 +12549,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="768" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="768" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B768" s="11" t="s">
         <v>26</v>
       </c>
@@ -12563,7 +12564,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="769" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="769" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B769" s="11" t="s">
         <v>26</v>
       </c>
@@ -12578,7 +12579,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="770" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="770" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B770" s="11" t="s">
         <v>26</v>
       </c>
@@ -12593,7 +12594,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="771" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="771" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B771" s="11" t="s">
         <v>23</v>
       </c>
@@ -12608,7 +12609,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="772" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="772" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B772" s="11" t="s">
         <v>23</v>
       </c>
@@ -12623,7 +12624,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="773" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="773" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B773" s="11" t="s">
         <v>4</v>
       </c>
@@ -12638,7 +12639,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="774" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="774" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B774" s="11" t="s">
         <v>4</v>
       </c>
@@ -12653,7 +12654,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="775" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="775" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B775" s="11" t="s">
         <v>4</v>
       </c>
@@ -12668,7 +12669,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="776" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="776" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B776" s="11" t="s">
         <v>4</v>
       </c>
@@ -12683,7 +12684,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="777" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="777" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B777" s="11" t="s">
         <v>4</v>
       </c>
@@ -12698,7 +12699,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="778" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="778" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B778" s="11" t="s">
         <v>4</v>
       </c>
@@ -12713,7 +12714,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="779" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="779" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B779" s="11" t="s">
         <v>4</v>
       </c>
@@ -12728,7 +12729,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="780" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="780" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B780" s="11" t="s">
         <v>4</v>
       </c>
@@ -12743,7 +12744,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="781" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="781" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B781" s="11" t="s">
         <v>24</v>
       </c>
@@ -12758,7 +12759,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="782" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="782" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B782" s="11" t="s">
         <v>24</v>
       </c>
@@ -12773,7 +12774,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="783" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="783" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B783" s="11" t="s">
         <v>24</v>
       </c>
@@ -12788,7 +12789,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="784" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="784" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B784" s="11" t="s">
         <v>24</v>
       </c>
@@ -12803,7 +12804,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="785" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="785" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B785" s="11" t="s">
         <v>24</v>
       </c>
@@ -12818,7 +12819,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="786" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="786" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B786" s="11" t="s">
         <v>24</v>
       </c>
@@ -12833,7 +12834,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="787" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="787" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B787" s="11" t="s">
         <v>27</v>
       </c>
@@ -12848,7 +12849,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="788" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="788" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B788" s="11" t="s">
         <v>25</v>
       </c>
@@ -12863,7 +12864,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="789" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="789" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B789" s="11" t="s">
         <v>25</v>
       </c>
@@ -12878,7 +12879,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="790" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="790" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B790" s="11" t="s">
         <v>5</v>
       </c>
@@ -12893,7 +12894,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="791" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="791" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B791" s="11" t="s">
         <v>5</v>
       </c>
@@ -12908,7 +12909,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="792" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="792" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B792" s="11" t="s">
         <v>28</v>
       </c>
@@ -12923,7 +12924,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="793" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="793" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B793" s="11" t="s">
         <v>28</v>
       </c>
@@ -12938,7 +12939,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="794" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="794" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B794" s="11" t="s">
         <v>28</v>
       </c>
@@ -12953,7 +12954,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="795" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="795" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B795" s="11" t="s">
         <v>28</v>
       </c>
@@ -12968,7 +12969,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="796" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="796" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B796" s="11" t="s">
         <v>28</v>
       </c>
@@ -12983,7 +12984,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="797" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="797" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B797" s="11" t="s">
         <v>28</v>
       </c>
@@ -12998,7 +12999,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="798" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="798" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B798" s="11" t="s">
         <v>28</v>
       </c>
@@ -13013,7 +13014,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="799" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="799" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B799" s="11" t="s">
         <v>28</v>
       </c>
@@ -13028,7 +13029,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="800" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="800" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B800" s="11" t="s">
         <v>28</v>
       </c>
@@ -13043,7 +13044,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="801" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="801" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B801" s="11" t="s">
         <v>28</v>
       </c>
@@ -13058,7 +13059,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="802" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="802" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B802" s="11" t="s">
         <v>28</v>
       </c>
@@ -13073,7 +13074,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="803" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="803" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B803" s="11" t="s">
         <v>17</v>
       </c>
@@ -13088,7 +13089,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="804" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="804" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B804" s="11" t="s">
         <v>17</v>
       </c>
@@ -13103,7 +13104,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="805" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="805" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B805" s="11" t="s">
         <v>29</v>
       </c>
@@ -13118,7 +13119,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="806" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="806" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B806" s="11" t="s">
         <v>29</v>
       </c>
@@ -13133,7 +13134,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="807" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="807" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B807" s="11" t="s">
         <v>29</v>
       </c>
@@ -13148,7 +13149,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="808" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="808" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B808" s="11" t="s">
         <v>29</v>
       </c>
@@ -13163,7 +13164,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="809" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="809" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B809" s="11" t="s">
         <v>22</v>
       </c>
@@ -13178,7 +13179,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="810" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="810" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B810" s="11" t="s">
         <v>22</v>
       </c>
@@ -13193,7 +13194,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="811" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="811" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B811" s="11" t="s">
         <v>22</v>
       </c>
@@ -13208,7 +13209,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="812" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="812" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B812" s="11" t="s">
         <v>22</v>
       </c>
@@ -13223,7 +13224,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="813" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="813" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B813" s="11" t="s">
         <v>22</v>
       </c>
@@ -13238,7 +13239,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="814" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="814" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B814" s="11" t="s">
         <v>22</v>
       </c>
@@ -13253,7 +13254,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="815" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="815" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B815" s="11" t="s">
         <v>22</v>
       </c>
@@ -13268,7 +13269,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="816" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="816" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B816" s="11" t="s">
         <v>22</v>
       </c>
@@ -13283,7 +13284,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="817" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="817" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B817" s="11" t="s">
         <v>22</v>
       </c>
@@ -13298,7 +13299,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="818" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="818" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B818" s="11" t="s">
         <v>22</v>
       </c>
@@ -13313,7 +13314,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="819" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="819" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B819" s="11" t="s">
         <v>22</v>
       </c>
@@ -13328,7 +13329,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="820" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="820" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B820" s="11" t="s">
         <v>101</v>
       </c>
@@ -13343,7 +13344,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="821" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="821" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B821" s="11" t="s">
         <v>21</v>
       </c>
@@ -13358,7 +13359,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="822" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="822" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B822" s="11" t="s">
         <v>21</v>
       </c>
@@ -13373,7 +13374,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="823" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="823" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B823" s="11" t="s">
         <v>21</v>
       </c>
@@ -13388,7 +13389,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="824" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="824" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B824" s="11" t="s">
         <v>9</v>
       </c>
@@ -13403,7 +13404,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="825" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="825" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B825" s="11" t="s">
         <v>9</v>
       </c>
@@ -13418,7 +13419,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="826" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="826" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B826" s="11" t="s">
         <v>7</v>
       </c>
@@ -13433,7 +13434,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="827" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="827" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B827" s="11" t="s">
         <v>7</v>
       </c>
@@ -13448,7 +13449,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="828" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="828" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B828" s="11" t="s">
         <v>7</v>
       </c>
@@ -13463,7 +13464,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="829" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="829" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B829" s="11" t="s">
         <v>7</v>
       </c>
@@ -13478,7 +13479,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="830" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="830" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B830" s="11" t="s">
         <v>14</v>
       </c>
@@ -13493,7 +13494,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="831" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="831" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B831" s="11" t="s">
         <v>14</v>
       </c>
@@ -13508,7 +13509,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="832" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="832" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B832" s="11" t="s">
         <v>103</v>
       </c>
@@ -13523,7 +13524,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="833" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="833" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B833" s="11" t="s">
         <v>3</v>
       </c>
@@ -13538,7 +13539,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="834" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="834" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B834" s="11" t="s">
         <v>3</v>
       </c>
@@ -13553,7 +13554,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="835" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="835" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B835" s="11" t="s">
         <v>19</v>
       </c>
@@ -13568,7 +13569,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="836" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="836" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B836" s="11" t="s">
         <v>19</v>
       </c>
@@ -13583,7 +13584,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="837" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="837" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B837" s="11" t="s">
         <v>19</v>
       </c>
@@ -13598,7 +13599,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="838" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="838" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B838" s="11" t="s">
         <v>32</v>
       </c>
@@ -13613,7 +13614,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="839" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="839" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B839" s="11" t="s">
         <v>39</v>
       </c>
@@ -13628,7 +13629,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="840" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="840" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B840" s="11" t="s">
         <v>6</v>
       </c>
@@ -13643,7 +13644,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="841" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="841" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B841" s="11" t="s">
         <v>6</v>
       </c>
@@ -13658,7 +13659,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="842" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="842" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B842" s="11" t="s">
         <v>20</v>
       </c>
@@ -13673,7 +13674,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="843" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="843" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B843" s="15" t="s">
         <v>20</v>
       </c>
@@ -13688,7 +13689,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="844" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="844" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B844" s="11" t="s">
         <v>20</v>
       </c>
@@ -13703,7 +13704,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="845" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="845" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B845" s="11" t="s">
         <v>20</v>
       </c>
@@ -13718,7 +13719,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="846" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="846" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B846" s="11" t="s">
         <v>18</v>
       </c>
@@ -13733,7 +13734,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="847" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="847" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B847" s="11" t="s">
         <v>13</v>
       </c>
@@ -13748,7 +13749,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="848" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="848" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B848" s="11" t="s">
         <v>13</v>
       </c>
@@ -13763,7 +13764,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="849" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="849" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B849" s="11" t="s">
         <v>23</v>
       </c>
@@ -13778,7 +13779,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="850" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="850" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B850" s="11" t="s">
         <v>23</v>
       </c>
@@ -13793,7 +13794,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="851" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="851" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B851" s="11" t="s">
         <v>4</v>
       </c>
@@ -13808,7 +13809,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="852" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="852" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B852" s="11" t="s">
         <v>4</v>
       </c>
@@ -13823,7 +13824,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="853" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="853" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B853" s="11" t="s">
         <v>4</v>
       </c>
@@ -13838,7 +13839,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="854" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="854" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B854" s="11" t="s">
         <v>25</v>
       </c>
@@ -13853,7 +13854,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="855" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="855" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B855" s="11" t="s">
         <v>25</v>
       </c>
@@ -13868,7 +13869,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="856" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="856" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B856" s="11" t="s">
         <v>28</v>
       </c>
@@ -13883,7 +13884,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="857" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="857" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B857" s="11" t="s">
         <v>28</v>
       </c>
@@ -13898,7 +13899,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="858" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="858" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B858" s="11" t="s">
         <v>28</v>
       </c>
@@ -13913,7 +13914,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="859" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="859" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B859" s="11" t="s">
         <v>28</v>
       </c>
@@ -13928,7 +13929,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="860" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="860" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B860" s="11" t="s">
         <v>17</v>
       </c>
@@ -13943,7 +13944,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="861" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="861" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B861" s="11" t="s">
         <v>29</v>
       </c>
@@ -13958,7 +13959,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="862" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="862" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B862" s="11" t="s">
         <v>22</v>
       </c>
@@ -13973,7 +13974,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="863" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="863" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B863" s="11" t="s">
         <v>101</v>
       </c>
@@ -13988,7 +13989,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="864" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="864" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B864" s="11" t="s">
         <v>21</v>
       </c>
@@ -14003,7 +14004,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="865" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="865" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B865" s="11" t="s">
         <v>21</v>
       </c>
@@ -14018,7 +14019,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="866" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="866" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B866" s="11" t="s">
         <v>21</v>
       </c>
@@ -14033,7 +14034,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="867" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="867" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B867" s="11" t="s">
         <v>21</v>
       </c>
@@ -14048,7 +14049,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="868" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="868" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B868" s="11" t="s">
         <v>9</v>
       </c>
@@ -14063,7 +14064,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="869" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="869" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B869" s="11" t="s">
         <v>9</v>
       </c>
@@ -14078,7 +14079,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="870" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="870" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B870" s="11" t="s">
         <v>9</v>
       </c>
@@ -14093,7 +14094,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="871" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="871" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B871" s="11" t="s">
         <v>14</v>
       </c>
@@ -14108,7 +14109,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="872" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="872" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B872" s="11" t="s">
         <v>14</v>
       </c>
@@ -14123,7 +14124,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="873" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="873" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B873" s="11" t="s">
         <v>14</v>
       </c>
@@ -14138,7 +14139,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="874" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="874" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B874" s="11" t="s">
         <v>28</v>
       </c>
@@ -14153,7 +14154,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="875" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="875" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B875" s="11" t="s">
         <v>22</v>
       </c>
@@ -14168,7 +14169,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="876" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="876" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B876" s="11" t="s">
         <v>30</v>
       </c>
@@ -14183,7 +14184,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="877" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="877" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B877" s="11" t="s">
         <v>112</v>
       </c>
@@ -14198,7 +14199,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="878" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="878" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B878" s="11" t="s">
         <v>28</v>
       </c>
@@ -14213,7 +14214,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="879" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="879" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B879" s="11" t="s">
         <v>3</v>
       </c>
@@ -14228,7 +14229,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="880" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="880" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B880" s="11" t="s">
         <v>3</v>
       </c>
@@ -14243,7 +14244,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="881" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="881" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B881" s="11" t="s">
         <v>113</v>
       </c>
@@ -14258,7 +14259,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="882" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="882" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B882" s="11" t="s">
         <v>29</v>
       </c>
@@ -14273,7 +14274,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="883" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="883" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B883" s="11" t="s">
         <v>20</v>
       </c>
@@ -14288,7 +14289,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="884" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="884" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B884" s="11" t="s">
         <v>5</v>
       </c>
@@ -14303,7 +14304,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="885" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="885" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B885" s="11" t="s">
         <v>11</v>
       </c>
@@ -14319,46 +14320,94 @@
       </c>
     </row>
     <row r="886" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B886" s="11"/>
+      <c r="B886" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C886" s="5"/>
-      <c r="D886" s="3"/>
-      <c r="E886" s="19"/>
-      <c r="F886" s="7"/>
+      <c r="D886" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E886" s="19">
+        <v>59</v>
+      </c>
+      <c r="F886" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="887" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B887" s="11"/>
+      <c r="B887" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="C887" s="5"/>
-      <c r="D887" s="3"/>
-      <c r="E887" s="19"/>
-      <c r="F887" s="7"/>
+      <c r="D887" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E887" s="19">
+        <v>134</v>
+      </c>
+      <c r="F887" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="888" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B888" s="11"/>
+      <c r="B888" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="C888" s="5"/>
-      <c r="D888" s="3"/>
-      <c r="E888" s="19"/>
-      <c r="F888" s="7"/>
+      <c r="D888" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E888" s="19">
+        <v>80</v>
+      </c>
+      <c r="F888" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="889" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B889" s="11"/>
+      <c r="B889" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C889" s="5"/>
-      <c r="D889" s="3"/>
-      <c r="E889" s="19"/>
-      <c r="F889" s="7"/>
+      <c r="D889" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E889" s="19">
+        <v>80</v>
+      </c>
+      <c r="F889" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="890" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B890" s="11"/>
+      <c r="B890" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C890" s="5"/>
-      <c r="D890" s="3"/>
-      <c r="E890" s="19"/>
-      <c r="F890" s="7"/>
+      <c r="D890" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E890" s="19">
+        <v>280</v>
+      </c>
+      <c r="F890" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="891" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B891" s="11"/>
+      <c r="B891" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C891" s="5"/>
-      <c r="D891" s="3"/>
-      <c r="E891" s="19"/>
-      <c r="F891" s="7"/>
+      <c r="D891" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E891" s="19">
+        <v>185</v>
+      </c>
+      <c r="F891" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="892" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B892" s="11"/>
@@ -37839,7 +37888,11 @@
       <c r="F4245" s="38"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G4194" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
+  <autoFilter ref="B2:G4194" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G875">
     <sortCondition ref="F3:F875" customList="janeiro,fevereiro,março,abril,maio,junho,julho,agosto,setembro,outubro,novembro,dezembro"/>
   </sortState>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="351" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76A1380D-3232-43BC-B189-3B04B6655887}"/>
+  <xr:revisionPtr revIDLastSave="362" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F441F280-F942-4CFA-AC7C-6F0D28561522}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="115">
   <si>
     <t>Custo</t>
   </si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>HJF5G06</t>
+  </si>
+  <si>
+    <t>ROCHA PEÇAS DIESEL</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1049,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
-  <sheetPr filterMode="1"/>
   <dimension ref="B2:G4245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1076,7 +1078,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>19</v>
       </c>
@@ -1091,7 +1093,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="4" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="36" t="s">
         <v>18</v>
       </c>
@@ -1106,7 +1108,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="5" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
@@ -1121,7 +1123,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="6" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>18</v>
       </c>
@@ -1136,7 +1138,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="7" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>18</v>
       </c>
@@ -1151,7 +1153,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="8" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>18</v>
       </c>
@@ -1166,7 +1168,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="9" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>26</v>
       </c>
@@ -1181,7 +1183,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="10" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
         <v>26</v>
       </c>
@@ -1196,7 +1198,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="11" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>21</v>
       </c>
@@ -1211,7 +1213,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="12" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>9</v>
       </c>
@@ -1226,7 +1228,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="13" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>8</v>
       </c>
@@ -1241,7 +1243,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="14" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>8</v>
       </c>
@@ -1256,7 +1258,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="15" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>8</v>
       </c>
@@ -1271,7 +1273,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="16" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>8</v>
       </c>
@@ -1286,7 +1288,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="17" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>8</v>
       </c>
@@ -1301,7 +1303,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="18" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>8</v>
       </c>
@@ -1316,7 +1318,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="19" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>8</v>
       </c>
@@ -1331,7 +1333,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="20" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>3</v>
       </c>
@@ -1346,7 +1348,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="21" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>3</v>
       </c>
@@ -1361,7 +1363,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="22" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>3</v>
       </c>
@@ -1376,7 +1378,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="23" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>3</v>
       </c>
@@ -1391,7 +1393,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="24" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>3</v>
       </c>
@@ -1406,7 +1408,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="25" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>3</v>
       </c>
@@ -1421,7 +1423,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="26" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="29" t="s">
         <v>3</v>
       </c>
@@ -1436,7 +1438,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="27" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="29" t="s">
         <v>30</v>
       </c>
@@ -1451,7 +1453,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="28" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="29" t="s">
         <v>15</v>
       </c>
@@ -1466,7 +1468,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="29" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="29" t="s">
         <v>15</v>
       </c>
@@ -1481,7 +1483,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="30" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="29" t="s">
         <v>15</v>
       </c>
@@ -1496,7 +1498,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="28" t="s">
         <v>15</v>
       </c>
@@ -1511,7 +1513,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="32" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="28" t="s">
         <v>15</v>
       </c>
@@ -1526,7 +1528,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="33" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="28" t="s">
         <v>15</v>
       </c>
@@ -1541,7 +1543,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="34" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="28" t="s">
         <v>15</v>
       </c>
@@ -1556,7 +1558,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="28" t="s">
         <v>15</v>
       </c>
@@ -1571,7 +1573,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" s="28" t="s">
         <v>15</v>
       </c>
@@ -1586,7 +1588,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="28" t="s">
         <v>15</v>
       </c>
@@ -1601,7 +1603,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="38" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="28" t="s">
         <v>6</v>
       </c>
@@ -1616,7 +1618,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" s="28" t="s">
         <v>6</v>
       </c>
@@ -1631,7 +1633,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" s="28" t="s">
         <v>26</v>
       </c>
@@ -1646,7 +1648,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="28" t="s">
         <v>26</v>
       </c>
@@ -1661,7 +1663,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42" s="28" t="s">
         <v>4</v>
       </c>
@@ -1676,7 +1678,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="43" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43" s="28" t="s">
         <v>5</v>
       </c>
@@ -1691,7 +1693,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44" s="28" t="s">
         <v>5</v>
       </c>
@@ -1706,7 +1708,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45" s="28" t="s">
         <v>5</v>
       </c>
@@ -1721,7 +1723,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46" s="28" t="s">
         <v>12</v>
       </c>
@@ -1736,7 +1738,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47" s="28" t="s">
         <v>22</v>
       </c>
@@ -1751,7 +1753,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B48" s="28" t="s">
         <v>22</v>
       </c>
@@ -1766,7 +1768,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" s="28" t="s">
         <v>22</v>
       </c>
@@ -1781,7 +1783,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50" s="28" t="s">
         <v>22</v>
       </c>
@@ -1796,7 +1798,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B51" s="28" t="s">
         <v>22</v>
       </c>
@@ -1811,7 +1813,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="52" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52" s="28" t="s">
         <v>22</v>
       </c>
@@ -1826,7 +1828,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="53" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" s="28" t="s">
         <v>22</v>
       </c>
@@ -1841,7 +1843,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="54" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B54" s="28" t="s">
         <v>22</v>
       </c>
@@ -1856,7 +1858,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="55" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B55" s="28" t="s">
         <v>22</v>
       </c>
@@ -1871,7 +1873,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="56" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B56" s="28" t="s">
         <v>22</v>
       </c>
@@ -1886,7 +1888,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="57" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B57" s="28" t="s">
         <v>22</v>
       </c>
@@ -1901,7 +1903,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="58" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B58" s="28" t="s">
         <v>21</v>
       </c>
@@ -1916,7 +1918,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="59" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B59" s="28" t="s">
         <v>7</v>
       </c>
@@ -1931,7 +1933,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="60" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60" s="28" t="s">
         <v>83</v>
       </c>
@@ -1946,7 +1948,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B61" s="28" t="s">
         <v>83</v>
       </c>
@@ -1961,7 +1963,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B62" s="28" t="s">
         <v>10</v>
       </c>
@@ -1976,7 +1978,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="63" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B63" s="28" t="s">
         <v>10</v>
       </c>
@@ -1991,7 +1993,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="64" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B64" s="28" t="s">
         <v>8</v>
       </c>
@@ -2006,7 +2008,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B65" s="28" t="s">
         <v>8</v>
       </c>
@@ -2021,7 +2023,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66" s="28" t="s">
         <v>8</v>
       </c>
@@ -2036,7 +2038,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B67" s="28" t="s">
         <v>8</v>
       </c>
@@ -2051,7 +2053,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B68" s="28" t="s">
         <v>8</v>
       </c>
@@ -2066,7 +2068,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B69" s="28" t="s">
         <v>8</v>
       </c>
@@ -2081,7 +2083,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B70" s="28" t="s">
         <v>8</v>
       </c>
@@ -2096,7 +2098,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B71" s="28" t="s">
         <v>8</v>
       </c>
@@ -2111,7 +2113,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72" s="28" t="s">
         <v>8</v>
       </c>
@@ -2126,7 +2128,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B73" s="28" t="s">
         <v>8</v>
       </c>
@@ -2141,7 +2143,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B74" s="28" t="s">
         <v>8</v>
       </c>
@@ -2156,7 +2158,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B75" s="28" t="s">
         <v>8</v>
       </c>
@@ -2171,7 +2173,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="76" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B76" s="28" t="s">
         <v>3</v>
       </c>
@@ -2186,7 +2188,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="77" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77" s="11" t="s">
         <v>19</v>
       </c>
@@ -2201,7 +2203,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="78" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B78" s="11" t="s">
         <v>30</v>
       </c>
@@ -2216,7 +2218,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="79" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B79" s="11" t="s">
         <v>2</v>
       </c>
@@ -2231,7 +2233,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="80" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B80" s="11" t="s">
         <v>6</v>
       </c>
@@ -2246,7 +2248,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="81" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81" s="11" t="s">
         <v>6</v>
       </c>
@@ -2261,7 +2263,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="82" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82" s="11" t="s">
         <v>6</v>
       </c>
@@ -2276,7 +2278,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="83" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" s="11" t="s">
         <v>6</v>
       </c>
@@ -2291,7 +2293,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="84" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B84" s="11" t="s">
         <v>6</v>
       </c>
@@ -2306,7 +2308,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="85" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B85" s="11" t="s">
         <v>6</v>
       </c>
@@ -2321,7 +2323,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="86" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B86" s="11" t="s">
         <v>6</v>
       </c>
@@ -2336,7 +2338,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="87" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87" s="11" t="s">
         <v>20</v>
       </c>
@@ -2351,7 +2353,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="88" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B88" s="11" t="s">
         <v>20</v>
       </c>
@@ -2366,7 +2368,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="89" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B89" s="11" t="s">
         <v>20</v>
       </c>
@@ -2381,7 +2383,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="90" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B90" s="11" t="s">
         <v>20</v>
       </c>
@@ -2396,7 +2398,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="91" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B91" s="11" t="s">
         <v>20</v>
       </c>
@@ -2411,7 +2413,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="92" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B92" s="11" t="s">
         <v>20</v>
       </c>
@@ -2426,7 +2428,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="93" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B93" s="11" t="s">
         <v>20</v>
       </c>
@@ -2441,7 +2443,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="94" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B94" s="11" t="s">
         <v>18</v>
       </c>
@@ -2456,7 +2458,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="95" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B95" s="11" t="s">
         <v>18</v>
       </c>
@@ -2471,7 +2473,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="96" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B96" s="11" t="s">
         <v>18</v>
       </c>
@@ -2486,7 +2488,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="97" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B97" s="11" t="s">
         <v>18</v>
       </c>
@@ -2501,7 +2503,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="98" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B98" s="11" t="s">
         <v>18</v>
       </c>
@@ -2516,7 +2518,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="99" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B99" s="11" t="s">
         <v>13</v>
       </c>
@@ -2531,7 +2533,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="100" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B100" s="11" t="s">
         <v>11</v>
       </c>
@@ -2546,7 +2548,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="101" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B101" s="11" t="s">
         <v>11</v>
       </c>
@@ -2561,7 +2563,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="102" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B102" s="11" t="s">
         <v>11</v>
       </c>
@@ -2576,7 +2578,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="103" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B103" s="11" t="s">
         <v>11</v>
       </c>
@@ -2591,7 +2593,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="104" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B104" s="11" t="s">
         <v>11</v>
       </c>
@@ -2606,7 +2608,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="105" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B105" s="11" t="s">
         <v>26</v>
       </c>
@@ -2621,7 +2623,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="106" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B106" s="11" t="s">
         <v>26</v>
       </c>
@@ -2636,7 +2638,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="107" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B107" s="11" t="s">
         <v>26</v>
       </c>
@@ -2651,7 +2653,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="108" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B108" s="11" t="s">
         <v>26</v>
       </c>
@@ -2666,7 +2668,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="109" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B109" s="11" t="s">
         <v>4</v>
       </c>
@@ -2681,7 +2683,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="110" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B110" s="11" t="s">
         <v>4</v>
       </c>
@@ -2696,7 +2698,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="111" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B111" s="11" t="s">
         <v>4</v>
       </c>
@@ -2711,7 +2713,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="112" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B112" s="11" t="s">
         <v>4</v>
       </c>
@@ -2726,7 +2728,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="113" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B113" s="11" t="s">
         <v>4</v>
       </c>
@@ -2741,7 +2743,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="114" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B114" s="11" t="s">
         <v>4</v>
       </c>
@@ -2756,7 +2758,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B115" s="11" t="s">
         <v>4</v>
       </c>
@@ -2771,7 +2773,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="116" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B116" s="11" t="s">
         <v>4</v>
       </c>
@@ -2786,7 +2788,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="117" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B117" s="11" t="s">
         <v>4</v>
       </c>
@@ -2801,7 +2803,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="118" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B118" s="11" t="s">
         <v>4</v>
       </c>
@@ -2816,7 +2818,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="119" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B119" s="11" t="s">
         <v>4</v>
       </c>
@@ -2831,7 +2833,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="120" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B120" s="11" t="s">
         <v>4</v>
       </c>
@@ -2846,7 +2848,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="121" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B121" s="11" t="s">
         <v>4</v>
       </c>
@@ -2861,7 +2863,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="122" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B122" s="11" t="s">
         <v>24</v>
       </c>
@@ -2876,7 +2878,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="123" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B123" s="11" t="s">
         <v>24</v>
       </c>
@@ -2891,7 +2893,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="124" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B124" s="11" t="s">
         <v>24</v>
       </c>
@@ -2906,7 +2908,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="125" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B125" s="11" t="s">
         <v>24</v>
       </c>
@@ -2921,7 +2923,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="126" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B126" s="11" t="s">
         <v>24</v>
       </c>
@@ -2936,7 +2938,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="127" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B127" s="11" t="s">
         <v>24</v>
       </c>
@@ -2951,7 +2953,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="128" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B128" s="11" t="s">
         <v>16</v>
       </c>
@@ -2966,7 +2968,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="129" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B129" s="11" t="s">
         <v>16</v>
       </c>
@@ -2981,7 +2983,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="130" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B130" s="11" t="s">
         <v>5</v>
       </c>
@@ -2996,7 +2998,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="131" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B131" s="11" t="s">
         <v>5</v>
       </c>
@@ -3011,7 +3013,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="132" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B132" s="11" t="s">
         <v>5</v>
       </c>
@@ -3026,7 +3028,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="133" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B133" s="11" t="s">
         <v>5</v>
       </c>
@@ -3041,7 +3043,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="134" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B134" s="11" t="s">
         <v>28</v>
       </c>
@@ -3056,7 +3058,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="135" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B135" s="11" t="s">
         <v>28</v>
       </c>
@@ -3071,7 +3073,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="136" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B136" s="11" t="s">
         <v>28</v>
       </c>
@@ -3086,7 +3088,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="137" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B137" s="11" t="s">
         <v>28</v>
       </c>
@@ -3101,7 +3103,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="138" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B138" s="11" t="s">
         <v>28</v>
       </c>
@@ -3116,7 +3118,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="139" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B139" s="11" t="s">
         <v>28</v>
       </c>
@@ -3131,7 +3133,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="140" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B140" s="11" t="s">
         <v>28</v>
       </c>
@@ -3146,7 +3148,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="141" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B141" s="11" t="s">
         <v>28</v>
       </c>
@@ -3161,7 +3163,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="142" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B142" s="11" t="s">
         <v>28</v>
       </c>
@@ -3176,7 +3178,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="143" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B143" s="11" t="s">
         <v>28</v>
       </c>
@@ -3191,7 +3193,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="144" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B144" s="11" t="s">
         <v>28</v>
       </c>
@@ -3206,7 +3208,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="145" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B145" s="11" t="s">
         <v>28</v>
       </c>
@@ -3221,7 +3223,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="146" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B146" s="11" t="s">
         <v>17</v>
       </c>
@@ -3236,7 +3238,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="147" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B147" s="11" t="s">
         <v>17</v>
       </c>
@@ -3251,7 +3253,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="148" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B148" s="11" t="s">
         <v>29</v>
       </c>
@@ -3266,7 +3268,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="149" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B149" s="11" t="s">
         <v>29</v>
       </c>
@@ -3281,7 +3283,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="150" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B150" s="11" t="s">
         <v>22</v>
       </c>
@@ -3296,7 +3298,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="151" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B151" s="11" t="s">
         <v>22</v>
       </c>
@@ -3311,7 +3313,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="152" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B152" s="11" t="s">
         <v>22</v>
       </c>
@@ -3326,7 +3328,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="153" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B153" s="11" t="s">
         <v>22</v>
       </c>
@@ -3341,7 +3343,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="154" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B154" s="11" t="s">
         <v>22</v>
       </c>
@@ -3356,7 +3358,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="155" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B155" s="11" t="s">
         <v>55</v>
       </c>
@@ -3371,7 +3373,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="156" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B156" s="11" t="s">
         <v>21</v>
       </c>
@@ -3386,7 +3388,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="157" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B157" s="11" t="s">
         <v>21</v>
       </c>
@@ -3401,7 +3403,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="158" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B158" s="11" t="s">
         <v>21</v>
       </c>
@@ -3416,7 +3418,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="159" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B159" s="11" t="s">
         <v>21</v>
       </c>
@@ -3431,7 +3433,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="160" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B160" s="11" t="s">
         <v>21</v>
       </c>
@@ -3446,7 +3448,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="161" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B161" s="11" t="s">
         <v>21</v>
       </c>
@@ -3461,7 +3463,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="162" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B162" s="11" t="s">
         <v>21</v>
       </c>
@@ -3476,7 +3478,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="163" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B163" s="11" t="s">
         <v>21</v>
       </c>
@@ -3491,7 +3493,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="164" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B164" s="11" t="s">
         <v>21</v>
       </c>
@@ -3506,7 +3508,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="165" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B165" s="11" t="s">
         <v>21</v>
       </c>
@@ -3521,7 +3523,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="166" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B166" s="11" t="s">
         <v>21</v>
       </c>
@@ -3536,7 +3538,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="167" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B167" s="11" t="s">
         <v>21</v>
       </c>
@@ -3551,7 +3553,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="168" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B168" s="11" t="s">
         <v>9</v>
       </c>
@@ -3566,7 +3568,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="169" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B169" s="11" t="s">
         <v>9</v>
       </c>
@@ -3581,7 +3583,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="170" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B170" s="11" t="s">
         <v>9</v>
       </c>
@@ -3596,7 +3598,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="171" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B171" s="11" t="s">
         <v>9</v>
       </c>
@@ -3611,7 +3613,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="172" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B172" s="11" t="s">
         <v>9</v>
       </c>
@@ -3626,7 +3628,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="173" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B173" s="11" t="s">
         <v>9</v>
       </c>
@@ -3641,7 +3643,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="174" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B174" s="11" t="s">
         <v>9</v>
       </c>
@@ -3656,7 +3658,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="175" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B175" s="11" t="s">
         <v>9</v>
       </c>
@@ -3671,7 +3673,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="176" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B176" s="11" t="s">
         <v>9</v>
       </c>
@@ -3686,7 +3688,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="177" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B177" s="11" t="s">
         <v>9</v>
       </c>
@@ -3701,7 +3703,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="178" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B178" s="11" t="s">
         <v>9</v>
       </c>
@@ -3716,7 +3718,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="179" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B179" s="11" t="s">
         <v>9</v>
       </c>
@@ -3731,7 +3733,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="180" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B180" s="11" t="s">
         <v>7</v>
       </c>
@@ -3746,7 +3748,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="181" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B181" s="11" t="s">
         <v>83</v>
       </c>
@@ -3761,7 +3763,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="182" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B182" s="11" t="s">
         <v>83</v>
       </c>
@@ -3776,7 +3778,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="183" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B183" s="11" t="s">
         <v>14</v>
       </c>
@@ -3791,7 +3793,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="184" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B184" s="11" t="s">
         <v>14</v>
       </c>
@@ -3806,7 +3808,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="185" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B185" s="11" t="s">
         <v>10</v>
       </c>
@@ -3821,7 +3823,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="186" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B186" s="11" t="s">
         <v>10</v>
       </c>
@@ -3836,7 +3838,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="187" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B187" s="11" t="s">
         <v>10</v>
       </c>
@@ -3851,7 +3853,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="188" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B188" s="11" t="s">
         <v>10</v>
       </c>
@@ -3866,7 +3868,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="189" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B189" s="11" t="s">
         <v>10</v>
       </c>
@@ -3881,7 +3883,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="190" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B190" s="11" t="s">
         <v>10</v>
       </c>
@@ -3896,7 +3898,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="191" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B191" s="11" t="s">
         <v>8</v>
       </c>
@@ -3911,7 +3913,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="192" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B192" s="11" t="s">
         <v>8</v>
       </c>
@@ -3926,7 +3928,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="193" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B193" s="11" t="s">
         <v>8</v>
       </c>
@@ -3941,7 +3943,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="194" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B194" s="11" t="s">
         <v>8</v>
       </c>
@@ -3956,7 +3958,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="195" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B195" s="11" t="s">
         <v>3</v>
       </c>
@@ -3971,7 +3973,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="196" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B196" s="11" t="s">
         <v>3</v>
       </c>
@@ -3986,7 +3988,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="197" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B197" s="11" t="s">
         <v>3</v>
       </c>
@@ -4001,7 +4003,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="198" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B198" s="11" t="s">
         <v>3</v>
       </c>
@@ -4016,7 +4018,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="199" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B199" s="11" t="s">
         <v>3</v>
       </c>
@@ -4031,7 +4033,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="200" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B200" s="11" t="s">
         <v>3</v>
       </c>
@@ -4046,7 +4048,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="201" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B201" s="11" t="s">
         <v>3</v>
       </c>
@@ -4061,7 +4063,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="202" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B202" s="11" t="s">
         <v>3</v>
       </c>
@@ -4076,7 +4078,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="203" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B203" s="11" t="s">
         <v>3</v>
       </c>
@@ -4091,7 +4093,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="204" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B204" s="11" t="s">
         <v>19</v>
       </c>
@@ -4106,7 +4108,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="205" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B205" s="11" t="s">
         <v>30</v>
       </c>
@@ -4121,7 +4123,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="206" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B206" s="11" t="s">
         <v>32</v>
       </c>
@@ -4136,7 +4138,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="207" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B207" s="11" t="s">
         <v>32</v>
       </c>
@@ -4151,7 +4153,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="208" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B208" s="11" t="s">
         <v>32</v>
       </c>
@@ -4166,7 +4168,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="209" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B209" s="11" t="s">
         <v>15</v>
       </c>
@@ -4181,7 +4183,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="210" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B210" s="11" t="s">
         <v>15</v>
       </c>
@@ -4196,7 +4198,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="211" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B211" s="11" t="s">
         <v>15</v>
       </c>
@@ -4211,7 +4213,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="212" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B212" s="11" t="s">
         <v>15</v>
       </c>
@@ -4226,7 +4228,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="213" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B213" s="11" t="s">
         <v>15</v>
       </c>
@@ -4241,7 +4243,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="214" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B214" s="11" t="s">
         <v>15</v>
       </c>
@@ -4256,7 +4258,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="215" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B215" s="11" t="s">
         <v>15</v>
       </c>
@@ -4271,7 +4273,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="216" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B216" s="11" t="s">
         <v>15</v>
       </c>
@@ -4286,7 +4288,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="217" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B217" s="11" t="s">
         <v>15</v>
       </c>
@@ -4301,7 +4303,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="218" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B218" s="11" t="s">
         <v>6</v>
       </c>
@@ -4316,7 +4318,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="219" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B219" s="11" t="s">
         <v>6</v>
       </c>
@@ -4331,7 +4333,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="220" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B220" s="11" t="s">
         <v>6</v>
       </c>
@@ -4346,7 +4348,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="221" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B221" s="11" t="s">
         <v>6</v>
       </c>
@@ -4361,7 +4363,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="222" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B222" s="11" t="s">
         <v>6</v>
       </c>
@@ -4376,7 +4378,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="223" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B223" s="11" t="s">
         <v>6</v>
       </c>
@@ -4391,7 +4393,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="224" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B224" s="11" t="s">
         <v>6</v>
       </c>
@@ -4406,7 +4408,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="225" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B225" s="11" t="s">
         <v>6</v>
       </c>
@@ -4421,7 +4423,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="226" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B226" s="11" t="s">
         <v>6</v>
       </c>
@@ -4436,7 +4438,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="227" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B227" s="11" t="s">
         <v>20</v>
       </c>
@@ -4451,7 +4453,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="228" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B228" s="11" t="s">
         <v>20</v>
       </c>
@@ -4466,7 +4468,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="229" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B229" s="11" t="s">
         <v>20</v>
       </c>
@@ -4481,7 +4483,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="230" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B230" s="11" t="s">
         <v>20</v>
       </c>
@@ -4496,7 +4498,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="231" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B231" s="11" t="s">
         <v>20</v>
       </c>
@@ -4511,7 +4513,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="232" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B232" s="11" t="s">
         <v>20</v>
       </c>
@@ -4526,7 +4528,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="233" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B233" s="11" t="s">
         <v>20</v>
       </c>
@@ -4541,7 +4543,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="234" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B234" s="11" t="s">
         <v>20</v>
       </c>
@@ -4556,7 +4558,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="235" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B235" s="11" t="s">
         <v>20</v>
       </c>
@@ -4571,7 +4573,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="236" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B236" s="11" t="s">
         <v>20</v>
       </c>
@@ -4586,7 +4588,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="237" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B237" s="11" t="s">
         <v>20</v>
       </c>
@@ -4601,7 +4603,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="238" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B238" s="11" t="s">
         <v>18</v>
       </c>
@@ -4616,7 +4618,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="239" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B239" s="11" t="s">
         <v>18</v>
       </c>
@@ -4631,7 +4633,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="240" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B240" s="11" t="s">
         <v>18</v>
       </c>
@@ -4646,7 +4648,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="241" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B241" s="11" t="s">
         <v>18</v>
       </c>
@@ -4661,7 +4663,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="242" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B242" s="11" t="s">
         <v>18</v>
       </c>
@@ -4676,7 +4678,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="243" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B243" s="11" t="s">
         <v>18</v>
       </c>
@@ -4691,7 +4693,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="244" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B244" s="11" t="s">
         <v>18</v>
       </c>
@@ -4706,7 +4708,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="245" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B245" s="11" t="s">
         <v>18</v>
       </c>
@@ -4721,7 +4723,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="246" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B246" s="11" t="s">
         <v>13</v>
       </c>
@@ -4736,7 +4738,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="247" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B247" s="11" t="s">
         <v>13</v>
       </c>
@@ -4751,7 +4753,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="248" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B248" s="11" t="s">
         <v>13</v>
       </c>
@@ -4766,7 +4768,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="249" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B249" s="11" t="s">
         <v>13</v>
       </c>
@@ -4781,7 +4783,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="250" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B250" s="11" t="s">
         <v>13</v>
       </c>
@@ -4796,7 +4798,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="251" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B251" s="11" t="s">
         <v>11</v>
       </c>
@@ -4811,7 +4813,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="252" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B252" s="11" t="s">
         <v>11</v>
       </c>
@@ -4826,7 +4828,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="253" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B253" s="11" t="s">
         <v>11</v>
       </c>
@@ -4841,7 +4843,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="254" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B254" s="11" t="s">
         <v>11</v>
       </c>
@@ -4856,7 +4858,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="255" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B255" s="11" t="s">
         <v>11</v>
       </c>
@@ -4871,7 +4873,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="256" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B256" s="11" t="s">
         <v>11</v>
       </c>
@@ -4886,7 +4888,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="257" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B257" s="11" t="s">
         <v>11</v>
       </c>
@@ -4901,7 +4903,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="258" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B258" s="11" t="s">
         <v>4</v>
       </c>
@@ -4916,7 +4918,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="259" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B259" s="11" t="s">
         <v>4</v>
       </c>
@@ -4931,7 +4933,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="260" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B260" s="11" t="s">
         <v>4</v>
       </c>
@@ -4946,7 +4948,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="261" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B261" s="11" t="s">
         <v>4</v>
       </c>
@@ -4961,7 +4963,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="262" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B262" s="11" t="s">
         <v>4</v>
       </c>
@@ -4976,7 +4978,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="263" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B263" s="11" t="s">
         <v>4</v>
       </c>
@@ -4991,7 +4993,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="264" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B264" s="11" t="s">
         <v>4</v>
       </c>
@@ -5006,7 +5008,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="265" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B265" s="11" t="s">
         <v>4</v>
       </c>
@@ -5021,7 +5023,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="266" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B266" s="11" t="s">
         <v>4</v>
       </c>
@@ -5036,7 +5038,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="267" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B267" s="11" t="s">
         <v>4</v>
       </c>
@@ -5051,7 +5053,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="268" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B268" s="11" t="s">
         <v>4</v>
       </c>
@@ -5066,7 +5068,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="269" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B269" s="11" t="s">
         <v>24</v>
       </c>
@@ -5081,7 +5083,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="270" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B270" s="11" t="s">
         <v>25</v>
       </c>
@@ -5096,7 +5098,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="271" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B271" s="11" t="s">
         <v>25</v>
       </c>
@@ -5111,7 +5113,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="272" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B272" s="11" t="s">
         <v>25</v>
       </c>
@@ -5126,7 +5128,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="273" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B273" s="11" t="s">
         <v>16</v>
       </c>
@@ -5141,7 +5143,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="274" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B274" s="11" t="s">
         <v>5</v>
       </c>
@@ -5156,7 +5158,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="275" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B275" s="11" t="s">
         <v>5</v>
       </c>
@@ -5171,7 +5173,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="276" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B276" s="11" t="s">
         <v>5</v>
       </c>
@@ -5186,7 +5188,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="277" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B277" s="11" t="s">
         <v>5</v>
       </c>
@@ -5201,7 +5203,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="278" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B278" s="11" t="s">
         <v>5</v>
       </c>
@@ -5216,7 +5218,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="279" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B279" s="11" t="s">
         <v>5</v>
       </c>
@@ -5231,7 +5233,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="280" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B280" s="11" t="s">
         <v>5</v>
       </c>
@@ -5246,7 +5248,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="281" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B281" s="11" t="s">
         <v>5</v>
       </c>
@@ -5261,7 +5263,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="282" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B282" s="11" t="s">
         <v>5</v>
       </c>
@@ -5276,7 +5278,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="283" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B283" s="11" t="s">
         <v>5</v>
       </c>
@@ -5291,7 +5293,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="284" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B284" s="11" t="s">
         <v>5</v>
       </c>
@@ -5306,7 +5308,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="285" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B285" s="11" t="s">
         <v>5</v>
       </c>
@@ -5321,7 +5323,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="286" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B286" s="11" t="s">
         <v>5</v>
       </c>
@@ -5336,7 +5338,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="287" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B287" s="11" t="s">
         <v>5</v>
       </c>
@@ -5351,7 +5353,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="288" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B288" s="11" t="s">
         <v>5</v>
       </c>
@@ -5366,7 +5368,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="289" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B289" s="11" t="s">
         <v>5</v>
       </c>
@@ -5381,7 +5383,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="290" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B290" s="11" t="s">
         <v>5</v>
       </c>
@@ -5396,7 +5398,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="291" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B291" s="11" t="s">
         <v>28</v>
       </c>
@@ -5411,7 +5413,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="292" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B292" s="11" t="s">
         <v>45</v>
       </c>
@@ -5426,7 +5428,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="293" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B293" s="11" t="s">
         <v>17</v>
       </c>
@@ -5441,7 +5443,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="294" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B294" s="11" t="s">
         <v>17</v>
       </c>
@@ -5456,7 +5458,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="295" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B295" s="11" t="s">
         <v>17</v>
       </c>
@@ -5471,7 +5473,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="296" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B296" s="11" t="s">
         <v>17</v>
       </c>
@@ -5486,7 +5488,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="297" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B297" s="11" t="s">
         <v>17</v>
       </c>
@@ -5501,7 +5503,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="298" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B298" s="11" t="s">
         <v>17</v>
       </c>
@@ -5516,7 +5518,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="299" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B299" s="11" t="s">
         <v>17</v>
       </c>
@@ -5531,7 +5533,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="300" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B300" s="11" t="s">
         <v>22</v>
       </c>
@@ -5546,7 +5548,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="301" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B301" s="11" t="s">
         <v>22</v>
       </c>
@@ -5561,7 +5563,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="302" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B302" s="11" t="s">
         <v>22</v>
       </c>
@@ -5576,7 +5578,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="303" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B303" s="11" t="s">
         <v>22</v>
       </c>
@@ -5591,7 +5593,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="304" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B304" s="11" t="s">
         <v>34</v>
       </c>
@@ -5606,7 +5608,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="305" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B305" s="11" t="s">
         <v>21</v>
       </c>
@@ -5621,7 +5623,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="306" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B306" s="11" t="s">
         <v>21</v>
       </c>
@@ -5636,7 +5638,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="307" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B307" s="11" t="s">
         <v>21</v>
       </c>
@@ -5651,7 +5653,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="308" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B308" s="11" t="s">
         <v>21</v>
       </c>
@@ -5666,7 +5668,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="309" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B309" s="11" t="s">
         <v>21</v>
       </c>
@@ -5681,7 +5683,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="310" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B310" s="11" t="s">
         <v>21</v>
       </c>
@@ -5696,7 +5698,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="311" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B311" s="11" t="s">
         <v>21</v>
       </c>
@@ -5711,7 +5713,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="312" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B312" s="11" t="s">
         <v>21</v>
       </c>
@@ -5726,7 +5728,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="313" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B313" s="11" t="s">
         <v>21</v>
       </c>
@@ -5741,7 +5743,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="314" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B314" s="11" t="s">
         <v>21</v>
       </c>
@@ -5756,7 +5758,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="315" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B315" s="11" t="s">
         <v>21</v>
       </c>
@@ -5771,7 +5773,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="316" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B316" s="11" t="s">
         <v>21</v>
       </c>
@@ -5786,7 +5788,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="317" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B317" s="11" t="s">
         <v>21</v>
       </c>
@@ -5801,7 +5803,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="318" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B318" s="11" t="s">
         <v>21</v>
       </c>
@@ -5816,7 +5818,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="319" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B319" s="11" t="s">
         <v>21</v>
       </c>
@@ -5831,7 +5833,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="320" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B320" s="11" t="s">
         <v>9</v>
       </c>
@@ -5846,7 +5848,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="321" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B321" s="11" t="s">
         <v>9</v>
       </c>
@@ -5861,7 +5863,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="322" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B322" s="11" t="s">
         <v>9</v>
       </c>
@@ -5876,7 +5878,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="323" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B323" s="11" t="s">
         <v>9</v>
       </c>
@@ -5891,7 +5893,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="324" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B324" s="11" t="s">
         <v>9</v>
       </c>
@@ -5906,7 +5908,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="325" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B325" s="11" t="s">
         <v>9</v>
       </c>
@@ -5921,7 +5923,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="326" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B326" s="11" t="s">
         <v>9</v>
       </c>
@@ -5936,7 +5938,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="327" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B327" s="11" t="s">
         <v>7</v>
       </c>
@@ -5951,7 +5953,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="328" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B328" s="11" t="s">
         <v>7</v>
       </c>
@@ -5966,7 +5968,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="329" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B329" s="11" t="s">
         <v>7</v>
       </c>
@@ -5981,7 +5983,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="330" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B330" s="11" t="s">
         <v>7</v>
       </c>
@@ -5996,7 +5998,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="331" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B331" s="11" t="s">
         <v>7</v>
       </c>
@@ -6011,7 +6013,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="332" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B332" s="11" t="s">
         <v>7</v>
       </c>
@@ -6026,7 +6028,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="333" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B333" s="11" t="s">
         <v>7</v>
       </c>
@@ -6041,7 +6043,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="334" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B334" s="11" t="s">
         <v>7</v>
       </c>
@@ -6056,7 +6058,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="335" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B335" s="27" t="s">
         <v>31</v>
       </c>
@@ -6071,7 +6073,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="336" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B336" s="27" t="s">
         <v>31</v>
       </c>
@@ -6086,7 +6088,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="337" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B337" s="27" t="s">
         <v>31</v>
       </c>
@@ -6101,7 +6103,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="338" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B338" s="27" t="s">
         <v>31</v>
       </c>
@@ -6116,7 +6118,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="339" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B339" s="27" t="s">
         <v>31</v>
       </c>
@@ -6131,7 +6133,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="340" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B340" s="11" t="s">
         <v>10</v>
       </c>
@@ -6146,7 +6148,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="341" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B341" s="11" t="s">
         <v>8</v>
       </c>
@@ -6161,7 +6163,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="342" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B342" s="11" t="s">
         <v>8</v>
       </c>
@@ -6176,7 +6178,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="343" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B343" s="11" t="s">
         <v>8</v>
       </c>
@@ -6191,7 +6193,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="344" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B344" s="11" t="s">
         <v>8</v>
       </c>
@@ -6206,7 +6208,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="345" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B345" s="11" t="s">
         <v>8</v>
       </c>
@@ -6221,7 +6223,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="346" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B346" s="11" t="s">
         <v>8</v>
       </c>
@@ -6236,7 +6238,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="347" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B347" s="11" t="s">
         <v>8</v>
       </c>
@@ -6251,7 +6253,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="348" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B348" s="11" t="s">
         <v>8</v>
       </c>
@@ -6266,7 +6268,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="349" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B349" s="11" t="s">
         <v>3</v>
       </c>
@@ -6281,7 +6283,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="350" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B350" s="11" t="s">
         <v>3</v>
       </c>
@@ -6296,7 +6298,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="351" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B351" s="11" t="s">
         <v>3</v>
       </c>
@@ -6311,7 +6313,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="352" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B352" s="11" t="s">
         <v>3</v>
       </c>
@@ -6326,7 +6328,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="353" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B353" s="11" t="s">
         <v>3</v>
       </c>
@@ -6341,7 +6343,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="354" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B354" s="11" t="s">
         <v>87</v>
       </c>
@@ -6356,7 +6358,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="355" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B355" s="11" t="s">
         <v>19</v>
       </c>
@@ -6371,7 +6373,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="356" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B356" s="11" t="s">
         <v>19</v>
       </c>
@@ -6386,7 +6388,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="357" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B357" s="11" t="s">
         <v>19</v>
       </c>
@@ -6401,7 +6403,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="358" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B358" s="11" t="s">
         <v>19</v>
       </c>
@@ -6416,7 +6418,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="359" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B359" s="11" t="s">
         <v>19</v>
       </c>
@@ -6431,7 +6433,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="360" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B360" s="11" t="s">
         <v>19</v>
       </c>
@@ -6446,7 +6448,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="361" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B361" s="11" t="s">
         <v>19</v>
       </c>
@@ -6461,7 +6463,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="362" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B362" s="11" t="s">
         <v>19</v>
       </c>
@@ -6476,7 +6478,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="363" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B363" s="11" t="s">
         <v>19</v>
       </c>
@@ -6491,7 +6493,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="364" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B364" s="11" t="s">
         <v>19</v>
       </c>
@@ -6506,7 +6508,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="365" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B365" s="11" t="s">
         <v>19</v>
       </c>
@@ -6521,7 +6523,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="366" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B366" s="11" t="s">
         <v>19</v>
       </c>
@@ -6536,7 +6538,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="367" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B367" s="11" t="s">
         <v>30</v>
       </c>
@@ -6551,7 +6553,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="368" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B368" s="11" t="s">
         <v>30</v>
       </c>
@@ -6566,7 +6568,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="369" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B369" s="11" t="s">
         <v>32</v>
       </c>
@@ -6581,7 +6583,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="370" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B370" s="27" t="s">
         <v>39</v>
       </c>
@@ -6596,7 +6598,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="371" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B371" s="11" t="s">
         <v>59</v>
       </c>
@@ -6611,7 +6613,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="372" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B372" s="11" t="s">
         <v>15</v>
       </c>
@@ -6626,7 +6628,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="373" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B373" s="11" t="s">
         <v>15</v>
       </c>
@@ -6641,7 +6643,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="374" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B374" s="11" t="s">
         <v>15</v>
       </c>
@@ -6656,7 +6658,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="375" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B375" s="11" t="s">
         <v>15</v>
       </c>
@@ -6671,7 +6673,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="376" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B376" s="11" t="s">
         <v>15</v>
       </c>
@@ -6686,7 +6688,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="377" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B377" s="11" t="s">
         <v>6</v>
       </c>
@@ -6701,7 +6703,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="378" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B378" s="11" t="s">
         <v>6</v>
       </c>
@@ -6716,7 +6718,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="379" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B379" s="11" t="s">
         <v>6</v>
       </c>
@@ -6731,7 +6733,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="380" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B380" s="11" t="s">
         <v>6</v>
       </c>
@@ -6746,7 +6748,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="381" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B381" s="11" t="s">
         <v>6</v>
       </c>
@@ -6761,7 +6763,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="382" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B382" s="11" t="s">
         <v>6</v>
       </c>
@@ -6776,7 +6778,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="383" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B383" s="11" t="s">
         <v>6</v>
       </c>
@@ -6791,7 +6793,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="384" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B384" s="11" t="s">
         <v>20</v>
       </c>
@@ -6806,7 +6808,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="385" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B385" s="11" t="s">
         <v>20</v>
       </c>
@@ -6821,7 +6823,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="386" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B386" s="11" t="s">
         <v>20</v>
       </c>
@@ -6836,7 +6838,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="387" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B387" s="11" t="s">
         <v>18</v>
       </c>
@@ -6851,7 +6853,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="388" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B388" s="11" t="s">
         <v>18</v>
       </c>
@@ -6866,7 +6868,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="389" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B389" s="11" t="s">
         <v>18</v>
       </c>
@@ -6881,7 +6883,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="390" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B390" s="11" t="s">
         <v>13</v>
       </c>
@@ -6896,7 +6898,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="391" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B391" s="11" t="s">
         <v>13</v>
       </c>
@@ -6911,7 +6913,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="392" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B392" s="11" t="s">
         <v>13</v>
       </c>
@@ -6926,7 +6928,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="393" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B393" s="27" t="s">
         <v>11</v>
       </c>
@@ -6941,7 +6943,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="394" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B394" s="27" t="s">
         <v>11</v>
       </c>
@@ -6956,7 +6958,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="395" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B395" s="27" t="s">
         <v>11</v>
       </c>
@@ -6971,7 +6973,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="396" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B396" s="27" t="s">
         <v>11</v>
       </c>
@@ -6986,7 +6988,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="397" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B397" s="27" t="s">
         <v>11</v>
       </c>
@@ -7001,7 +7003,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="398" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B398" s="27" t="s">
         <v>11</v>
       </c>
@@ -7016,7 +7018,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="399" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B399" s="27" t="s">
         <v>11</v>
       </c>
@@ -7031,7 +7033,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="400" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B400" s="27" t="s">
         <v>11</v>
       </c>
@@ -7046,7 +7048,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="401" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B401" s="27" t="s">
         <v>11</v>
       </c>
@@ -7061,7 +7063,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="402" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B402" s="27" t="s">
         <v>11</v>
       </c>
@@ -7076,7 +7078,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="403" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B403" s="27" t="s">
         <v>11</v>
       </c>
@@ -7091,7 +7093,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="404" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B404" s="27" t="s">
         <v>11</v>
       </c>
@@ -7106,7 +7108,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="405" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B405" s="27" t="s">
         <v>11</v>
       </c>
@@ -7121,7 +7123,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="406" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B406" s="27" t="s">
         <v>11</v>
       </c>
@@ -7136,7 +7138,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="407" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B407" s="27" t="s">
         <v>11</v>
       </c>
@@ -7151,7 +7153,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="408" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B408" s="27" t="s">
         <v>11</v>
       </c>
@@ -7166,7 +7168,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="409" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B409" s="27" t="s">
         <v>11</v>
       </c>
@@ -7181,7 +7183,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="410" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B410" s="27" t="s">
         <v>11</v>
       </c>
@@ -7196,7 +7198,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="411" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B411" s="27" t="s">
         <v>11</v>
       </c>
@@ -7211,7 +7213,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="412" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B412" s="27" t="s">
         <v>11</v>
       </c>
@@ -7226,7 +7228,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="413" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B413" s="27" t="s">
         <v>11</v>
       </c>
@@ -7241,7 +7243,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="414" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B414" s="27" t="s">
         <v>11</v>
       </c>
@@ -7256,7 +7258,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="415" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B415" s="27" t="s">
         <v>11</v>
       </c>
@@ -7271,7 +7273,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="416" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B416" s="27" t="s">
         <v>11</v>
       </c>
@@ -7286,7 +7288,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="417" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B417" s="27" t="s">
         <v>11</v>
       </c>
@@ -7301,7 +7303,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="418" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B418" s="27" t="s">
         <v>11</v>
       </c>
@@ -7316,7 +7318,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="419" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B419" s="11" t="s">
         <v>11</v>
       </c>
@@ -7331,7 +7333,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="420" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B420" s="11" t="s">
         <v>11</v>
       </c>
@@ -7346,7 +7348,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="421" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B421" s="11" t="s">
         <v>11</v>
       </c>
@@ -7361,7 +7363,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="422" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B422" s="11" t="s">
         <v>11</v>
       </c>
@@ -7376,7 +7378,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="423" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B423" s="11" t="s">
         <v>11</v>
       </c>
@@ -7391,7 +7393,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="424" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B424" s="11" t="s">
         <v>11</v>
       </c>
@@ -7406,7 +7408,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="425" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B425" s="11" t="s">
         <v>11</v>
       </c>
@@ -7421,7 +7423,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="426" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B426" s="11" t="s">
         <v>11</v>
       </c>
@@ -7436,7 +7438,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="427" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B427" s="11" t="s">
         <v>11</v>
       </c>
@@ -7451,7 +7453,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="428" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B428" s="11" t="s">
         <v>23</v>
       </c>
@@ -7466,7 +7468,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="429" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B429" s="11" t="s">
         <v>23</v>
       </c>
@@ -7481,7 +7483,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="430" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B430" s="11" t="s">
         <v>23</v>
       </c>
@@ -7496,7 +7498,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="431" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B431" s="27" t="s">
         <v>4</v>
       </c>
@@ -7511,7 +7513,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="432" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B432" s="11" t="s">
         <v>4</v>
       </c>
@@ -7526,7 +7528,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="433" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B433" s="11" t="s">
         <v>4</v>
       </c>
@@ -7541,7 +7543,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="434" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B434" s="11" t="s">
         <v>4</v>
       </c>
@@ -7556,7 +7558,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="435" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B435" s="11" t="s">
         <v>4</v>
       </c>
@@ -7571,7 +7573,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="436" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B436" s="11" t="s">
         <v>4</v>
       </c>
@@ -7586,7 +7588,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="437" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B437" s="11" t="s">
         <v>4</v>
       </c>
@@ -7601,7 +7603,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="438" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B438" s="11" t="s">
         <v>4</v>
       </c>
@@ -7616,7 +7618,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="439" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B439" s="11" t="s">
         <v>4</v>
       </c>
@@ -7631,7 +7633,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="440" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B440" s="11" t="s">
         <v>4</v>
       </c>
@@ -7646,7 +7648,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="441" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B441" s="11" t="s">
         <v>4</v>
       </c>
@@ -7661,7 +7663,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="442" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B442" s="11" t="s">
         <v>4</v>
       </c>
@@ -7676,7 +7678,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="443" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B443" s="11" t="s">
         <v>4</v>
       </c>
@@ -7691,7 +7693,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="444" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B444" s="11" t="s">
         <v>4</v>
       </c>
@@ -7706,7 +7708,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="445" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B445" s="11" t="s">
         <v>4</v>
       </c>
@@ -7721,7 +7723,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="446" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B446" s="11" t="s">
         <v>4</v>
       </c>
@@ -7736,7 +7738,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="447" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B447" s="11" t="s">
         <v>4</v>
       </c>
@@ -7751,7 +7753,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="448" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B448" s="11" t="s">
         <v>4</v>
       </c>
@@ -7766,7 +7768,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="449" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B449" s="11" t="s">
         <v>4</v>
       </c>
@@ -7781,7 +7783,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="450" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B450" s="11" t="s">
         <v>4</v>
       </c>
@@ -7796,7 +7798,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="451" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B451" s="11" t="s">
         <v>4</v>
       </c>
@@ -7811,7 +7813,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="452" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B452" s="11" t="s">
         <v>4</v>
       </c>
@@ -7826,7 +7828,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="453" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B453" s="11" t="s">
         <v>4</v>
       </c>
@@ -7841,7 +7843,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="454" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B454" s="11" t="s">
         <v>4</v>
       </c>
@@ -7856,7 +7858,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="455" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B455" s="11" t="s">
         <v>4</v>
       </c>
@@ -7871,7 +7873,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="456" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B456" s="11" t="s">
         <v>4</v>
       </c>
@@ -7886,7 +7888,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="457" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B457" s="11" t="s">
         <v>4</v>
       </c>
@@ -7901,7 +7903,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="458" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B458" s="11" t="s">
         <v>4</v>
       </c>
@@ -7916,7 +7918,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="459" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B459" s="11" t="s">
         <v>24</v>
       </c>
@@ -7931,7 +7933,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="460" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B460" s="11" t="s">
         <v>24</v>
       </c>
@@ -7946,7 +7948,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="461" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B461" s="11" t="s">
         <v>24</v>
       </c>
@@ -7961,7 +7963,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="462" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B462" s="11" t="s">
         <v>24</v>
       </c>
@@ -7976,7 +7978,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="463" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B463" s="11" t="s">
         <v>24</v>
       </c>
@@ -7991,7 +7993,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="464" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B464" s="11" t="s">
         <v>24</v>
       </c>
@@ -8006,7 +8008,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="465" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B465" s="11" t="s">
         <v>24</v>
       </c>
@@ -8021,7 +8023,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="466" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B466" s="11" t="s">
         <v>24</v>
       </c>
@@ -8036,7 +8038,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="467" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B467" s="11" t="s">
         <v>24</v>
       </c>
@@ -8051,7 +8053,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="468" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B468" s="11" t="s">
         <v>24</v>
       </c>
@@ -8066,7 +8068,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="469" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B469" s="11" t="s">
         <v>24</v>
       </c>
@@ -8081,7 +8083,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="470" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B470" s="11" t="s">
         <v>24</v>
       </c>
@@ -8096,7 +8098,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="471" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B471" s="11" t="s">
         <v>24</v>
       </c>
@@ -8111,7 +8113,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="472" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B472" s="11" t="s">
         <v>24</v>
       </c>
@@ -8126,7 +8128,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="473" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B473" s="11" t="s">
         <v>24</v>
       </c>
@@ -8141,7 +8143,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="474" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B474" s="11" t="s">
         <v>24</v>
       </c>
@@ -8156,7 +8158,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="475" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B475" s="11" t="s">
         <v>24</v>
       </c>
@@ -8171,7 +8173,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="476" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B476" s="11" t="s">
         <v>24</v>
       </c>
@@ -8186,7 +8188,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="477" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B477" s="11" t="s">
         <v>24</v>
       </c>
@@ -8201,7 +8203,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="478" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B478" s="11" t="s">
         <v>24</v>
       </c>
@@ -8216,7 +8218,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="479" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B479" s="11" t="s">
         <v>24</v>
       </c>
@@ -8231,7 +8233,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="480" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B480" s="11" t="s">
         <v>24</v>
       </c>
@@ -8246,7 +8248,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="481" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B481" s="11" t="s">
         <v>24</v>
       </c>
@@ -8261,7 +8263,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="482" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B482" s="11" t="s">
         <v>24</v>
       </c>
@@ -8276,7 +8278,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="483" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B483" s="11" t="s">
         <v>24</v>
       </c>
@@ -8291,7 +8293,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="484" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B484" s="11" t="s">
         <v>24</v>
       </c>
@@ -8306,7 +8308,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="485" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B485" s="11" t="s">
         <v>24</v>
       </c>
@@ -8321,7 +8323,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="486" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B486" s="11" t="s">
         <v>24</v>
       </c>
@@ -8336,7 +8338,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="487" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B487" s="11" t="s">
         <v>24</v>
       </c>
@@ -8351,7 +8353,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="488" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B488" s="11" t="s">
         <v>24</v>
       </c>
@@ -8366,7 +8368,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="489" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B489" s="11" t="s">
         <v>24</v>
       </c>
@@ -8381,7 +8383,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="490" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B490" s="11" t="s">
         <v>24</v>
       </c>
@@ -8396,7 +8398,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="491" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B491" s="11" t="s">
         <v>24</v>
       </c>
@@ -8411,7 +8413,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="492" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B492" s="11" t="s">
         <v>24</v>
       </c>
@@ -8426,7 +8428,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="493" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B493" s="11" t="s">
         <v>24</v>
       </c>
@@ -8441,7 +8443,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="494" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B494" s="11" t="s">
         <v>24</v>
       </c>
@@ -8456,7 +8458,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="495" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B495" s="11" t="s">
         <v>24</v>
       </c>
@@ -8471,7 +8473,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="496" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B496" s="11" t="s">
         <v>24</v>
       </c>
@@ -8486,7 +8488,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="497" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B497" s="11" t="s">
         <v>24</v>
       </c>
@@ -8501,7 +8503,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="498" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B498" s="11" t="s">
         <v>24</v>
       </c>
@@ -8516,7 +8518,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="499" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B499" s="11" t="s">
         <v>24</v>
       </c>
@@ -8531,7 +8533,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="500" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B500" s="11" t="s">
         <v>24</v>
       </c>
@@ -8546,7 +8548,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="501" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B501" s="11" t="s">
         <v>24</v>
       </c>
@@ -8561,7 +8563,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="502" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B502" s="11" t="s">
         <v>24</v>
       </c>
@@ -8576,7 +8578,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="503" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B503" s="11" t="s">
         <v>25</v>
       </c>
@@ -8591,7 +8593,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="504" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B504" s="11" t="s">
         <v>25</v>
       </c>
@@ -8606,7 +8608,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="505" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B505" s="11" t="s">
         <v>25</v>
       </c>
@@ -8621,7 +8623,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="506" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B506" s="11" t="s">
         <v>25</v>
       </c>
@@ -8636,7 +8638,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="507" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B507" s="11" t="s">
         <v>25</v>
       </c>
@@ -8651,7 +8653,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="508" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B508" s="11" t="s">
         <v>25</v>
       </c>
@@ -8666,7 +8668,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="509" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B509" s="11" t="s">
         <v>25</v>
       </c>
@@ -8681,7 +8683,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="510" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B510" s="11" t="s">
         <v>25</v>
       </c>
@@ -8696,7 +8698,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="511" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B511" s="11" t="s">
         <v>25</v>
       </c>
@@ -8711,7 +8713,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="512" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B512" s="11" t="s">
         <v>25</v>
       </c>
@@ -8726,7 +8728,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="513" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B513" s="11" t="s">
         <v>25</v>
       </c>
@@ -8741,7 +8743,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="514" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B514" s="11" t="s">
         <v>25</v>
       </c>
@@ -8756,7 +8758,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="515" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B515" s="11" t="s">
         <v>25</v>
       </c>
@@ -8771,7 +8773,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="516" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B516" s="11" t="s">
         <v>25</v>
       </c>
@@ -8786,7 +8788,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="517" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B517" s="11" t="s">
         <v>25</v>
       </c>
@@ -8801,7 +8803,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="518" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B518" s="11" t="s">
         <v>25</v>
       </c>
@@ -8816,7 +8818,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="519" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B519" s="11" t="s">
         <v>25</v>
       </c>
@@ -8831,7 +8833,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="520" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B520" s="11" t="s">
         <v>25</v>
       </c>
@@ -8846,7 +8848,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="521" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B521" s="11" t="s">
         <v>25</v>
       </c>
@@ -8861,7 +8863,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="522" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B522" s="11" t="s">
         <v>25</v>
       </c>
@@ -8876,7 +8878,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="523" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B523" s="11" t="s">
         <v>25</v>
       </c>
@@ -8891,7 +8893,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="524" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B524" s="11" t="s">
         <v>5</v>
       </c>
@@ -8906,7 +8908,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="525" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B525" s="11" t="s">
         <v>5</v>
       </c>
@@ -8921,7 +8923,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="526" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B526" s="11" t="s">
         <v>5</v>
       </c>
@@ -8936,7 +8938,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="527" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B527" s="11" t="s">
         <v>5</v>
       </c>
@@ -8951,7 +8953,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="528" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B528" s="11" t="s">
         <v>28</v>
       </c>
@@ -8966,7 +8968,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="529" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B529" s="11" t="s">
         <v>28</v>
       </c>
@@ -8981,7 +8983,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="530" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B530" s="11" t="s">
         <v>28</v>
       </c>
@@ -8996,7 +8998,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="531" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B531" s="11" t="s">
         <v>28</v>
       </c>
@@ -9011,7 +9013,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="532" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B532" s="11" t="s">
         <v>17</v>
       </c>
@@ -9026,7 +9028,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="533" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B533" s="11" t="s">
         <v>17</v>
       </c>
@@ -9041,7 +9043,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="534" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B534" s="11" t="s">
         <v>17</v>
       </c>
@@ -9056,7 +9058,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="535" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B535" s="11" t="s">
         <v>17</v>
       </c>
@@ -9071,7 +9073,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="536" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B536" s="11" t="s">
         <v>17</v>
       </c>
@@ -9086,7 +9088,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="537" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B537" s="11" t="s">
         <v>17</v>
       </c>
@@ -9101,7 +9103,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="538" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B538" s="11" t="s">
         <v>17</v>
       </c>
@@ -9116,7 +9118,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="539" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B539" s="11" t="s">
         <v>22</v>
       </c>
@@ -9131,7 +9133,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="540" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B540" s="11" t="s">
         <v>22</v>
       </c>
@@ -9146,7 +9148,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="541" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B541" s="11" t="s">
         <v>22</v>
       </c>
@@ -9161,7 +9163,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="542" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B542" s="11" t="s">
         <v>22</v>
       </c>
@@ -9176,7 +9178,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="543" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B543" s="27" t="s">
         <v>21</v>
       </c>
@@ -9191,7 +9193,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="544" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B544" s="27" t="s">
         <v>21</v>
       </c>
@@ -9206,7 +9208,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="545" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B545" s="27" t="s">
         <v>21</v>
       </c>
@@ -9221,7 +9223,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="546" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B546" s="27" t="s">
         <v>21</v>
       </c>
@@ -9236,7 +9238,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="547" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B547" s="27" t="s">
         <v>21</v>
       </c>
@@ -9251,7 +9253,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="548" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B548" s="27" t="s">
         <v>21</v>
       </c>
@@ -9266,7 +9268,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="549" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B549" s="27" t="s">
         <v>21</v>
       </c>
@@ -9281,7 +9283,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="550" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B550" s="27" t="s">
         <v>21</v>
       </c>
@@ -9296,7 +9298,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="551" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B551" s="27" t="s">
         <v>21</v>
       </c>
@@ -9311,7 +9313,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="552" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B552" s="27" t="s">
         <v>21</v>
       </c>
@@ -9326,7 +9328,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="553" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B553" s="27" t="s">
         <v>21</v>
       </c>
@@ -9341,7 +9343,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="554" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B554" s="27" t="s">
         <v>21</v>
       </c>
@@ -9356,7 +9358,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="555" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B555" s="27" t="s">
         <v>21</v>
       </c>
@@ -9371,7 +9373,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="556" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B556" s="27" t="s">
         <v>21</v>
       </c>
@@ -9386,7 +9388,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="557" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B557" s="27" t="s">
         <v>21</v>
       </c>
@@ -9401,7 +9403,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="558" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B558" s="27" t="s">
         <v>21</v>
       </c>
@@ -9416,7 +9418,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="559" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B559" s="27" t="s">
         <v>21</v>
       </c>
@@ -9431,7 +9433,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="560" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B560" s="27" t="s">
         <v>21</v>
       </c>
@@ -9446,7 +9448,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="561" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B561" s="11" t="s">
         <v>21</v>
       </c>
@@ -9461,7 +9463,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="562" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B562" s="11" t="s">
         <v>21</v>
       </c>
@@ -9476,7 +9478,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="563" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B563" s="11" t="s">
         <v>9</v>
       </c>
@@ -9491,7 +9493,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="564" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B564" s="11" t="s">
         <v>9</v>
       </c>
@@ -9506,7 +9508,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="565" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B565" s="11" t="s">
         <v>9</v>
       </c>
@@ -9521,7 +9523,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="566" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B566" s="11" t="s">
         <v>9</v>
       </c>
@@ -9536,7 +9538,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="567" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B567" s="11" t="s">
         <v>9</v>
       </c>
@@ -9551,7 +9553,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="568" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B568" s="11" t="s">
         <v>9</v>
       </c>
@@ -9566,7 +9568,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="569" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B569" s="11" t="s">
         <v>37</v>
       </c>
@@ -9581,7 +9583,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="570" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B570" s="11" t="s">
         <v>37</v>
       </c>
@@ -9596,7 +9598,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="571" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B571" s="11" t="s">
         <v>37</v>
       </c>
@@ -9611,7 +9613,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="572" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B572" s="11" t="s">
         <v>37</v>
       </c>
@@ -9626,7 +9628,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="573" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B573" s="11" t="s">
         <v>37</v>
       </c>
@@ -9641,7 +9643,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="574" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B574" s="11" t="s">
         <v>37</v>
       </c>
@@ -9656,7 +9658,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="575" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B575" s="11" t="s">
         <v>37</v>
       </c>
@@ -9671,7 +9673,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="576" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B576" s="11" t="s">
         <v>7</v>
       </c>
@@ -9686,7 +9688,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="577" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B577" s="11" t="s">
         <v>7</v>
       </c>
@@ -9701,7 +9703,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="578" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B578" s="11" t="s">
         <v>7</v>
       </c>
@@ -9716,7 +9718,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="579" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B579" s="11" t="s">
         <v>7</v>
       </c>
@@ -9731,7 +9733,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="580" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B580" s="11" t="s">
         <v>7</v>
       </c>
@@ -9746,7 +9748,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="581" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B581" s="11" t="s">
         <v>7</v>
       </c>
@@ -9761,7 +9763,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="582" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B582" s="11" t="s">
         <v>7</v>
       </c>
@@ -9776,7 +9778,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="583" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B583" s="11" t="s">
         <v>7</v>
       </c>
@@ -9791,7 +9793,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="584" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B584" s="11" t="s">
         <v>83</v>
       </c>
@@ -9806,7 +9808,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="585" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B585" s="11" t="s">
         <v>83</v>
       </c>
@@ -9821,7 +9823,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="586" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B586" s="11" t="s">
         <v>83</v>
       </c>
@@ -9836,7 +9838,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="587" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B587" s="11" t="s">
         <v>31</v>
       </c>
@@ -9851,7 +9853,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="588" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B588" s="11" t="s">
         <v>8</v>
       </c>
@@ -9866,7 +9868,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="589" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B589" s="11" t="s">
         <v>8</v>
       </c>
@@ -9881,7 +9883,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="590" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B590" s="11" t="s">
         <v>8</v>
       </c>
@@ -9896,7 +9898,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="591" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B591" s="11" t="s">
         <v>3</v>
       </c>
@@ -9911,7 +9913,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="592" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B592" s="11" t="s">
         <v>3</v>
       </c>
@@ -9926,7 +9928,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="593" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B593" s="11" t="s">
         <v>3</v>
       </c>
@@ -9941,7 +9943,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="594" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B594" s="11" t="s">
         <v>3</v>
       </c>
@@ -9956,7 +9958,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="595" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B595" s="11" t="s">
         <v>3</v>
       </c>
@@ -9971,7 +9973,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="596" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B596" s="11" t="s">
         <v>3</v>
       </c>
@@ -9986,7 +9988,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="597" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B597" s="11" t="s">
         <v>19</v>
       </c>
@@ -10001,7 +10003,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="598" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B598" s="11" t="s">
         <v>30</v>
       </c>
@@ -10016,7 +10018,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="599" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B599" s="11" t="s">
         <v>30</v>
       </c>
@@ -10031,7 +10033,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="600" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B600" s="11" t="s">
         <v>30</v>
       </c>
@@ -10046,7 +10048,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="601" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B601" s="11" t="s">
         <v>32</v>
       </c>
@@ -10061,7 +10063,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="602" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B602" s="11" t="s">
         <v>32</v>
       </c>
@@ -10076,7 +10078,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="603" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B603" s="11" t="s">
         <v>32</v>
       </c>
@@ -10091,7 +10093,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="604" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B604" s="11" t="s">
         <v>32</v>
       </c>
@@ -10106,7 +10108,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="605" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B605" s="11" t="s">
         <v>15</v>
       </c>
@@ -10121,7 +10123,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="606" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B606" s="11" t="s">
         <v>15</v>
       </c>
@@ -10136,7 +10138,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="607" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B607" s="11" t="s">
         <v>15</v>
       </c>
@@ -10151,7 +10153,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="608" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B608" s="11" t="s">
         <v>15</v>
       </c>
@@ -10166,7 +10168,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="609" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B609" s="11" t="s">
         <v>20</v>
       </c>
@@ -10181,7 +10183,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="610" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B610" s="11" t="s">
         <v>20</v>
       </c>
@@ -10194,7 +10196,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="611" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B611" s="11" t="s">
         <v>20</v>
       </c>
@@ -10209,7 +10211,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="612" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B612" s="11" t="s">
         <v>20</v>
       </c>
@@ -10224,7 +10226,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="613" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B613" s="11" t="s">
         <v>20</v>
       </c>
@@ -10239,7 +10241,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="614" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B614" s="11" t="s">
         <v>20</v>
       </c>
@@ -10254,7 +10256,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="615" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B615" s="11" t="s">
         <v>18</v>
       </c>
@@ -10269,7 +10271,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="616" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B616" s="11" t="s">
         <v>18</v>
       </c>
@@ -10284,7 +10286,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="617" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B617" s="11" t="s">
         <v>18</v>
       </c>
@@ -10299,7 +10301,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="618" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B618" s="11" t="s">
         <v>18</v>
       </c>
@@ -10314,7 +10316,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="619" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B619" s="11" t="s">
         <v>18</v>
       </c>
@@ -10329,7 +10331,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="620" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B620" s="11" t="s">
         <v>13</v>
       </c>
@@ -10344,7 +10346,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="621" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B621" s="11" t="s">
         <v>13</v>
       </c>
@@ -10359,7 +10361,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="622" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B622" s="11" t="s">
         <v>11</v>
       </c>
@@ -10374,7 +10376,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="623" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B623" s="11" t="s">
         <v>11</v>
       </c>
@@ -10389,7 +10391,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="624" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B624" s="11" t="s">
         <v>11</v>
       </c>
@@ -10404,7 +10406,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="625" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B625" s="11" t="s">
         <v>23</v>
       </c>
@@ -10419,7 +10421,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="626" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B626" s="11" t="s">
         <v>4</v>
       </c>
@@ -10434,7 +10436,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="627" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B627" s="11" t="s">
         <v>4</v>
       </c>
@@ -10449,7 +10451,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="628" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B628" s="11" t="s">
         <v>24</v>
       </c>
@@ -10464,7 +10466,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="629" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B629" s="11" t="s">
         <v>24</v>
       </c>
@@ -10479,7 +10481,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="630" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B630" s="11" t="s">
         <v>24</v>
       </c>
@@ -10494,7 +10496,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="631" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B631" s="11" t="s">
         <v>27</v>
       </c>
@@ -10509,7 +10511,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="632" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B632" s="11" t="s">
         <v>25</v>
       </c>
@@ -10524,7 +10526,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="633" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B633" s="11" t="s">
         <v>5</v>
       </c>
@@ -10539,7 +10541,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="634" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B634" s="11" t="s">
         <v>5</v>
       </c>
@@ -10554,7 +10556,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="635" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B635" s="11" t="s">
         <v>5</v>
       </c>
@@ -10569,7 +10571,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="636" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B636" s="11" t="s">
         <v>28</v>
       </c>
@@ -10584,7 +10586,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="637" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B637" s="11" t="s">
         <v>28</v>
       </c>
@@ -10599,7 +10601,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="638" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B638" s="15" t="s">
         <v>28</v>
       </c>
@@ -10614,7 +10616,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="639" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B639" s="11" t="s">
         <v>28</v>
       </c>
@@ -10629,7 +10631,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="640" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B640" s="11" t="s">
         <v>28</v>
       </c>
@@ -10644,7 +10646,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="641" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B641" s="11" t="s">
         <v>28</v>
       </c>
@@ -10659,7 +10661,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="642" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B642" s="11" t="s">
         <v>28</v>
       </c>
@@ -10674,7 +10676,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="643" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B643" s="11" t="s">
         <v>28</v>
       </c>
@@ -10689,7 +10691,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="644" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B644" s="11" t="s">
         <v>17</v>
       </c>
@@ -10704,7 +10706,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="645" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B645" s="11" t="s">
         <v>17</v>
       </c>
@@ -10719,7 +10721,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="646" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B646" s="11" t="s">
         <v>29</v>
       </c>
@@ -10734,7 +10736,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="647" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B647" s="11" t="s">
         <v>21</v>
       </c>
@@ -10749,7 +10751,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="648" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B648" s="11" t="s">
         <v>21</v>
       </c>
@@ -10764,7 +10766,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="649" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B649" s="11" t="s">
         <v>21</v>
       </c>
@@ -10779,7 +10781,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="650" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B650" s="11" t="s">
         <v>9</v>
       </c>
@@ -10794,7 +10796,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="651" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B651" s="11" t="s">
         <v>7</v>
       </c>
@@ -10809,7 +10811,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="652" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B652" s="11" t="s">
         <v>7</v>
       </c>
@@ -10824,7 +10826,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="653" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B653" s="11" t="s">
         <v>7</v>
       </c>
@@ -10839,7 +10841,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="654" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B654" s="11" t="s">
         <v>14</v>
       </c>
@@ -10854,7 +10856,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="655" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B655" s="11" t="s">
         <v>31</v>
       </c>
@@ -10869,7 +10871,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="656" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B656" s="11" t="s">
         <v>8</v>
       </c>
@@ -10884,7 +10886,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="657" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B657" s="11" t="s">
         <v>3</v>
       </c>
@@ -10899,7 +10901,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="658" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B658" s="11" t="s">
         <v>3</v>
       </c>
@@ -10914,7 +10916,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="659" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B659" s="11" t="s">
         <v>3</v>
       </c>
@@ -10929,7 +10931,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="660" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B660" s="11" t="s">
         <v>19</v>
       </c>
@@ -10944,7 +10946,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="661" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B661" s="11" t="s">
         <v>30</v>
       </c>
@@ -10959,7 +10961,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="662" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B662" s="11" t="s">
         <v>32</v>
       </c>
@@ -10974,7 +10976,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="663" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B663" s="11" t="s">
         <v>32</v>
       </c>
@@ -10989,7 +10991,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="664" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B664" s="11" t="s">
         <v>32</v>
       </c>
@@ -11004,7 +11006,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="665" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B665" s="11" t="s">
         <v>32</v>
       </c>
@@ -11019,7 +11021,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="666" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B666" s="11" t="s">
         <v>32</v>
       </c>
@@ -11034,7 +11036,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="667" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B667" s="11" t="s">
         <v>32</v>
       </c>
@@ -11049,7 +11051,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="668" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B668" s="11" t="s">
         <v>32</v>
       </c>
@@ -11064,7 +11066,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="669" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B669" s="11" t="s">
         <v>32</v>
       </c>
@@ -11079,7 +11081,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="670" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B670" s="11" t="s">
         <v>32</v>
       </c>
@@ -11094,7 +11096,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="671" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B671" s="11" t="s">
         <v>39</v>
       </c>
@@ -11109,7 +11111,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="672" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B672" s="11" t="s">
         <v>15</v>
       </c>
@@ -11124,7 +11126,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="673" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B673" s="11" t="s">
         <v>6</v>
       </c>
@@ -11139,7 +11141,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="674" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B674" s="11" t="s">
         <v>6</v>
       </c>
@@ -11154,7 +11156,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="675" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B675" s="11" t="s">
         <v>6</v>
       </c>
@@ -11169,7 +11171,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="676" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B676" s="11" t="s">
         <v>6</v>
       </c>
@@ -11184,7 +11186,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="677" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B677" s="11" t="s">
         <v>6</v>
       </c>
@@ -11199,7 +11201,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="678" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B678" s="11" t="s">
         <v>6</v>
       </c>
@@ -11214,7 +11216,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="679" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B679" s="11" t="s">
         <v>20</v>
       </c>
@@ -11229,7 +11231,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="680" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B680" s="11" t="s">
         <v>18</v>
       </c>
@@ -11244,7 +11246,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="681" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B681" s="11" t="s">
         <v>18</v>
       </c>
@@ -11259,7 +11261,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="682" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B682" s="11" t="s">
         <v>13</v>
       </c>
@@ -11274,7 +11276,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="683" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B683" s="11" t="s">
         <v>13</v>
       </c>
@@ -11289,7 +11291,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="684" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B684" s="11" t="s">
         <v>11</v>
       </c>
@@ -11304,7 +11306,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="685" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B685" s="11" t="s">
         <v>11</v>
       </c>
@@ -11319,7 +11321,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="686" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B686" s="11" t="s">
         <v>11</v>
       </c>
@@ -11334,7 +11336,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="687" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B687" s="11" t="s">
         <v>11</v>
       </c>
@@ -11349,7 +11351,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="688" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B688" s="11" t="s">
         <v>11</v>
       </c>
@@ -11364,7 +11366,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="689" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B689" s="11" t="s">
         <v>11</v>
       </c>
@@ -11379,7 +11381,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="690" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B690" s="11" t="s">
         <v>11</v>
       </c>
@@ -11394,7 +11396,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="691" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B691" s="11" t="s">
         <v>11</v>
       </c>
@@ -11409,7 +11411,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="692" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B692" s="11" t="s">
         <v>11</v>
       </c>
@@ -11424,7 +11426,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="693" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B693" s="11" t="s">
         <v>26</v>
       </c>
@@ -11439,7 +11441,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="694" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B694" s="11" t="s">
         <v>4</v>
       </c>
@@ -11454,7 +11456,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="695" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B695" s="11" t="s">
         <v>24</v>
       </c>
@@ -11469,7 +11471,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="696" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B696" s="11" t="s">
         <v>24</v>
       </c>
@@ -11484,7 +11486,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="697" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B697" s="11" t="s">
         <v>24</v>
       </c>
@@ -11499,7 +11501,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="698" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B698" s="11" t="s">
         <v>24</v>
       </c>
@@ -11514,7 +11516,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="699" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B699" s="11" t="s">
         <v>5</v>
       </c>
@@ -11529,7 +11531,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="700" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B700" s="11" t="s">
         <v>5</v>
       </c>
@@ -11544,7 +11546,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="701" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B701" s="11" t="s">
         <v>5</v>
       </c>
@@ -11559,7 +11561,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="702" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B702" s="11" t="s">
         <v>12</v>
       </c>
@@ -11574,7 +11576,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="703" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B703" s="11" t="s">
         <v>28</v>
       </c>
@@ -11589,7 +11591,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="704" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B704" s="11" t="s">
         <v>98</v>
       </c>
@@ -11604,7 +11606,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="705" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B705" s="11" t="s">
         <v>29</v>
       </c>
@@ -11619,7 +11621,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="706" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B706" s="11" t="s">
         <v>29</v>
       </c>
@@ -11634,7 +11636,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="707" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B707" s="11" t="s">
         <v>29</v>
       </c>
@@ -11649,7 +11651,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="708" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B708" s="11" t="s">
         <v>29</v>
       </c>
@@ -11664,7 +11666,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="709" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B709" s="11" t="s">
         <v>29</v>
       </c>
@@ -11679,7 +11681,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="710" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B710" s="11" t="s">
         <v>29</v>
       </c>
@@ -11694,7 +11696,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="711" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B711" s="11" t="s">
         <v>22</v>
       </c>
@@ -11709,7 +11711,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="712" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B712" s="11" t="s">
         <v>21</v>
       </c>
@@ -11724,7 +11726,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="713" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B713" s="11" t="s">
         <v>21</v>
       </c>
@@ -11739,7 +11741,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="714" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B714" s="11" t="s">
         <v>9</v>
       </c>
@@ -11754,7 +11756,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="715" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B715" s="11" t="s">
         <v>9</v>
       </c>
@@ -11769,7 +11771,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="716" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B716" s="11" t="s">
         <v>7</v>
       </c>
@@ -11784,7 +11786,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="717" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B717" s="11" t="s">
         <v>7</v>
       </c>
@@ -11799,7 +11801,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="718" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B718" s="11" t="s">
         <v>93</v>
       </c>
@@ -11814,7 +11816,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="719" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B719" s="11" t="s">
         <v>14</v>
       </c>
@@ -11829,7 +11831,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="720" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B720" s="11" t="s">
         <v>14</v>
       </c>
@@ -11844,7 +11846,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="721" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B721" s="11" t="s">
         <v>14</v>
       </c>
@@ -11859,7 +11861,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="722" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B722" s="11" t="s">
         <v>103</v>
       </c>
@@ -11874,7 +11876,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="723" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B723" s="11" t="s">
         <v>8</v>
       </c>
@@ -11889,7 +11891,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="724" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B724" s="11" t="s">
         <v>3</v>
       </c>
@@ -11904,7 +11906,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="725" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B725" s="11" t="s">
         <v>3</v>
       </c>
@@ -11919,7 +11921,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="726" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B726" s="11" t="s">
         <v>19</v>
       </c>
@@ -11934,7 +11936,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="727" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B727" s="11" t="s">
         <v>19</v>
       </c>
@@ -11949,7 +11951,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="728" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B728" s="11" t="s">
         <v>19</v>
       </c>
@@ -11964,7 +11966,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="729" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B729" s="11" t="s">
         <v>19</v>
       </c>
@@ -11979,7 +11981,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="730" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B730" s="11" t="s">
         <v>19</v>
       </c>
@@ -11994,7 +11996,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="731" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B731" s="11" t="s">
         <v>19</v>
       </c>
@@ -12009,7 +12011,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="732" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B732" s="11" t="s">
         <v>32</v>
       </c>
@@ -12024,7 +12026,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="733" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B733" s="11" t="s">
         <v>32</v>
       </c>
@@ -12039,7 +12041,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="734" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B734" s="11" t="s">
         <v>32</v>
       </c>
@@ -12054,7 +12056,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="735" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B735" s="11" t="s">
         <v>32</v>
       </c>
@@ -12069,7 +12071,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="736" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B736" s="11" t="s">
         <v>32</v>
       </c>
@@ -12084,7 +12086,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="737" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B737" s="11" t="s">
         <v>32</v>
       </c>
@@ -12099,7 +12101,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="738" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B738" s="11" t="s">
         <v>32</v>
       </c>
@@ -12114,7 +12116,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="739" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B739" s="11" t="s">
         <v>15</v>
       </c>
@@ -12129,7 +12131,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="740" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B740" s="11" t="s">
         <v>15</v>
       </c>
@@ -12144,7 +12146,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="741" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B741" s="11" t="s">
         <v>15</v>
       </c>
@@ -12159,7 +12161,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="742" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B742" s="11" t="s">
         <v>15</v>
       </c>
@@ -12174,7 +12176,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="743" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B743" s="11" t="s">
         <v>6</v>
       </c>
@@ -12189,7 +12191,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="744" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B744" s="11" t="s">
         <v>6</v>
       </c>
@@ -12204,7 +12206,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="745" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B745" s="11" t="s">
         <v>6</v>
       </c>
@@ -12219,7 +12221,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="746" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B746" s="11" t="s">
         <v>6</v>
       </c>
@@ -12234,7 +12236,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="747" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B747" s="11" t="s">
         <v>6</v>
       </c>
@@ -12249,7 +12251,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="748" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B748" s="11" t="s">
         <v>6</v>
       </c>
@@ -12264,7 +12266,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="749" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B749" s="11" t="s">
         <v>6</v>
       </c>
@@ -12279,7 +12281,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="750" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B750" s="11" t="s">
         <v>20</v>
       </c>
@@ -12294,7 +12296,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="751" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B751" s="11" t="s">
         <v>20</v>
       </c>
@@ -12309,7 +12311,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="752" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B752" s="11" t="s">
         <v>18</v>
       </c>
@@ -12324,7 +12326,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="753" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B753" s="11" t="s">
         <v>18</v>
       </c>
@@ -12339,7 +12341,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="754" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B754" s="11" t="s">
         <v>18</v>
       </c>
@@ -12354,7 +12356,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="755" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B755" s="11" t="s">
         <v>18</v>
       </c>
@@ -12369,7 +12371,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="756" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B756" s="11" t="s">
         <v>18</v>
       </c>
@@ -12384,7 +12386,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="757" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B757" s="11" t="s">
         <v>18</v>
       </c>
@@ -12399,7 +12401,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="758" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B758" s="11" t="s">
         <v>18</v>
       </c>
@@ -12414,7 +12416,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="759" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B759" s="11" t="s">
         <v>13</v>
       </c>
@@ -12429,7 +12431,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="760" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B760" s="11" t="s">
         <v>13</v>
       </c>
@@ -12444,7 +12446,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="761" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B761" s="11" t="s">
         <v>13</v>
       </c>
@@ -12459,7 +12461,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="762" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B762" s="11" t="s">
         <v>13</v>
       </c>
@@ -12474,7 +12476,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="763" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B763" s="11" t="s">
         <v>11</v>
       </c>
@@ -12489,7 +12491,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="764" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B764" s="11" t="s">
         <v>11</v>
       </c>
@@ -12504,7 +12506,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="765" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B765" s="11" t="s">
         <v>11</v>
       </c>
@@ -12519,7 +12521,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="766" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B766" s="11" t="s">
         <v>11</v>
       </c>
@@ -12534,7 +12536,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="767" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B767" s="11" t="s">
         <v>26</v>
       </c>
@@ -12549,7 +12551,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="768" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B768" s="11" t="s">
         <v>26</v>
       </c>
@@ -12564,7 +12566,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="769" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B769" s="11" t="s">
         <v>26</v>
       </c>
@@ -12579,7 +12581,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="770" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B770" s="11" t="s">
         <v>26</v>
       </c>
@@ -12594,7 +12596,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="771" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B771" s="11" t="s">
         <v>23</v>
       </c>
@@ -12609,7 +12611,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="772" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B772" s="11" t="s">
         <v>23</v>
       </c>
@@ -12624,7 +12626,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="773" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B773" s="11" t="s">
         <v>4</v>
       </c>
@@ -12639,7 +12641,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="774" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B774" s="11" t="s">
         <v>4</v>
       </c>
@@ -12654,7 +12656,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="775" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B775" s="11" t="s">
         <v>4</v>
       </c>
@@ -12669,7 +12671,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="776" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B776" s="11" t="s">
         <v>4</v>
       </c>
@@ -12684,7 +12686,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="777" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B777" s="11" t="s">
         <v>4</v>
       </c>
@@ -12699,7 +12701,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="778" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B778" s="11" t="s">
         <v>4</v>
       </c>
@@ -12714,7 +12716,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="779" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B779" s="11" t="s">
         <v>4</v>
       </c>
@@ -12729,7 +12731,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="780" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B780" s="11" t="s">
         <v>4</v>
       </c>
@@ -12744,7 +12746,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="781" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B781" s="11" t="s">
         <v>24</v>
       </c>
@@ -12759,7 +12761,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="782" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B782" s="11" t="s">
         <v>24</v>
       </c>
@@ -12774,7 +12776,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="783" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B783" s="11" t="s">
         <v>24</v>
       </c>
@@ -12789,7 +12791,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="784" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B784" s="11" t="s">
         <v>24</v>
       </c>
@@ -12804,7 +12806,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="785" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B785" s="11" t="s">
         <v>24</v>
       </c>
@@ -12819,7 +12821,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="786" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B786" s="11" t="s">
         <v>24</v>
       </c>
@@ -12834,7 +12836,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="787" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B787" s="11" t="s">
         <v>27</v>
       </c>
@@ -12849,7 +12851,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="788" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B788" s="11" t="s">
         <v>25</v>
       </c>
@@ -12864,7 +12866,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="789" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B789" s="11" t="s">
         <v>25</v>
       </c>
@@ -12879,7 +12881,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="790" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B790" s="11" t="s">
         <v>5</v>
       </c>
@@ -12894,7 +12896,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="791" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B791" s="11" t="s">
         <v>5</v>
       </c>
@@ -12909,7 +12911,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="792" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B792" s="11" t="s">
         <v>28</v>
       </c>
@@ -12924,7 +12926,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="793" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B793" s="11" t="s">
         <v>28</v>
       </c>
@@ -12939,7 +12941,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="794" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B794" s="11" t="s">
         <v>28</v>
       </c>
@@ -12954,7 +12956,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="795" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B795" s="11" t="s">
         <v>28</v>
       </c>
@@ -12969,7 +12971,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="796" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B796" s="11" t="s">
         <v>28</v>
       </c>
@@ -12984,7 +12986,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="797" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B797" s="11" t="s">
         <v>28</v>
       </c>
@@ -12999,7 +13001,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="798" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B798" s="11" t="s">
         <v>28</v>
       </c>
@@ -13014,7 +13016,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="799" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B799" s="11" t="s">
         <v>28</v>
       </c>
@@ -13029,7 +13031,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="800" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B800" s="11" t="s">
         <v>28</v>
       </c>
@@ -13044,7 +13046,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="801" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B801" s="11" t="s">
         <v>28</v>
       </c>
@@ -13059,7 +13061,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="802" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B802" s="11" t="s">
         <v>28</v>
       </c>
@@ -13074,7 +13076,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="803" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B803" s="11" t="s">
         <v>17</v>
       </c>
@@ -13089,7 +13091,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="804" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B804" s="11" t="s">
         <v>17</v>
       </c>
@@ -13104,7 +13106,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="805" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B805" s="11" t="s">
         <v>29</v>
       </c>
@@ -13119,7 +13121,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="806" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B806" s="11" t="s">
         <v>29</v>
       </c>
@@ -13134,7 +13136,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="807" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B807" s="11" t="s">
         <v>29</v>
       </c>
@@ -13149,7 +13151,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="808" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B808" s="11" t="s">
         <v>29</v>
       </c>
@@ -13164,7 +13166,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="809" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B809" s="11" t="s">
         <v>22</v>
       </c>
@@ -13179,7 +13181,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="810" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B810" s="11" t="s">
         <v>22</v>
       </c>
@@ -13194,7 +13196,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="811" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B811" s="11" t="s">
         <v>22</v>
       </c>
@@ -13209,7 +13211,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="812" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B812" s="11" t="s">
         <v>22</v>
       </c>
@@ -13224,7 +13226,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="813" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B813" s="11" t="s">
         <v>22</v>
       </c>
@@ -13239,7 +13241,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="814" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B814" s="11" t="s">
         <v>22</v>
       </c>
@@ -13254,7 +13256,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="815" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B815" s="11" t="s">
         <v>22</v>
       </c>
@@ -13269,7 +13271,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="816" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B816" s="11" t="s">
         <v>22</v>
       </c>
@@ -13284,7 +13286,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="817" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B817" s="11" t="s">
         <v>22</v>
       </c>
@@ -13299,7 +13301,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="818" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B818" s="11" t="s">
         <v>22</v>
       </c>
@@ -13314,7 +13316,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="819" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B819" s="11" t="s">
         <v>22</v>
       </c>
@@ -13329,7 +13331,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="820" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B820" s="11" t="s">
         <v>101</v>
       </c>
@@ -13344,7 +13346,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="821" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B821" s="11" t="s">
         <v>21</v>
       </c>
@@ -13359,7 +13361,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="822" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B822" s="11" t="s">
         <v>21</v>
       </c>
@@ -13374,7 +13376,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="823" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B823" s="11" t="s">
         <v>21</v>
       </c>
@@ -13389,7 +13391,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="824" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B824" s="11" t="s">
         <v>9</v>
       </c>
@@ -13404,7 +13406,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="825" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B825" s="11" t="s">
         <v>9</v>
       </c>
@@ -13419,7 +13421,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="826" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B826" s="11" t="s">
         <v>7</v>
       </c>
@@ -13434,7 +13436,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="827" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B827" s="11" t="s">
         <v>7</v>
       </c>
@@ -13449,7 +13451,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="828" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B828" s="11" t="s">
         <v>7</v>
       </c>
@@ -13464,7 +13466,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="829" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B829" s="11" t="s">
         <v>7</v>
       </c>
@@ -13479,7 +13481,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="830" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B830" s="11" t="s">
         <v>14</v>
       </c>
@@ -13494,7 +13496,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="831" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B831" s="11" t="s">
         <v>14</v>
       </c>
@@ -13509,7 +13511,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="832" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B832" s="11" t="s">
         <v>103</v>
       </c>
@@ -13524,7 +13526,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="833" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B833" s="11" t="s">
         <v>3</v>
       </c>
@@ -13539,7 +13541,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="834" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B834" s="11" t="s">
         <v>3</v>
       </c>
@@ -13554,7 +13556,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="835" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B835" s="11" t="s">
         <v>19</v>
       </c>
@@ -13569,7 +13571,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="836" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B836" s="11" t="s">
         <v>19</v>
       </c>
@@ -13584,7 +13586,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="837" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B837" s="11" t="s">
         <v>19</v>
       </c>
@@ -13599,7 +13601,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="838" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B838" s="11" t="s">
         <v>32</v>
       </c>
@@ -13614,7 +13616,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="839" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B839" s="11" t="s">
         <v>39</v>
       </c>
@@ -13629,7 +13631,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="840" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B840" s="11" t="s">
         <v>6</v>
       </c>
@@ -13644,7 +13646,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="841" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B841" s="11" t="s">
         <v>6</v>
       </c>
@@ -13659,7 +13661,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="842" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B842" s="11" t="s">
         <v>20</v>
       </c>
@@ -13674,7 +13676,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="843" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B843" s="15" t="s">
         <v>20</v>
       </c>
@@ -13689,7 +13691,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="844" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B844" s="11" t="s">
         <v>20</v>
       </c>
@@ -13704,7 +13706,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="845" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B845" s="11" t="s">
         <v>20</v>
       </c>
@@ -13719,7 +13721,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="846" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B846" s="11" t="s">
         <v>18</v>
       </c>
@@ -13734,7 +13736,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="847" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B847" s="11" t="s">
         <v>13</v>
       </c>
@@ -13749,7 +13751,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="848" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B848" s="11" t="s">
         <v>13</v>
       </c>
@@ -13764,7 +13766,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="849" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B849" s="11" t="s">
         <v>23</v>
       </c>
@@ -13779,7 +13781,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="850" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B850" s="11" t="s">
         <v>23</v>
       </c>
@@ -13794,7 +13796,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="851" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B851" s="11" t="s">
         <v>4</v>
       </c>
@@ -13809,7 +13811,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="852" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B852" s="11" t="s">
         <v>4</v>
       </c>
@@ -13824,7 +13826,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="853" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B853" s="11" t="s">
         <v>4</v>
       </c>
@@ -13839,7 +13841,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="854" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B854" s="11" t="s">
         <v>25</v>
       </c>
@@ -13854,7 +13856,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="855" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B855" s="11" t="s">
         <v>25</v>
       </c>
@@ -13869,7 +13871,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="856" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B856" s="11" t="s">
         <v>28</v>
       </c>
@@ -13884,7 +13886,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="857" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B857" s="11" t="s">
         <v>28</v>
       </c>
@@ -13899,7 +13901,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="858" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B858" s="11" t="s">
         <v>28</v>
       </c>
@@ -13914,7 +13916,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="859" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B859" s="11" t="s">
         <v>28</v>
       </c>
@@ -13929,7 +13931,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="860" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B860" s="11" t="s">
         <v>17</v>
       </c>
@@ -13944,7 +13946,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="861" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B861" s="11" t="s">
         <v>29</v>
       </c>
@@ -13959,7 +13961,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="862" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B862" s="11" t="s">
         <v>22</v>
       </c>
@@ -13974,7 +13976,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="863" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B863" s="11" t="s">
         <v>101</v>
       </c>
@@ -13989,7 +13991,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="864" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B864" s="11" t="s">
         <v>21</v>
       </c>
@@ -14004,7 +14006,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="865" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B865" s="11" t="s">
         <v>21</v>
       </c>
@@ -14019,7 +14021,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="866" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B866" s="11" t="s">
         <v>21</v>
       </c>
@@ -14034,7 +14036,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="867" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B867" s="11" t="s">
         <v>21</v>
       </c>
@@ -14049,7 +14051,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="868" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B868" s="11" t="s">
         <v>9</v>
       </c>
@@ -14064,7 +14066,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="869" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B869" s="11" t="s">
         <v>9</v>
       </c>
@@ -14079,7 +14081,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="870" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B870" s="11" t="s">
         <v>9</v>
       </c>
@@ -14094,7 +14096,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="871" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B871" s="11" t="s">
         <v>14</v>
       </c>
@@ -14109,7 +14111,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="872" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B872" s="11" t="s">
         <v>14</v>
       </c>
@@ -14124,7 +14126,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="873" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B873" s="11" t="s">
         <v>14</v>
       </c>
@@ -14139,7 +14141,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="874" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B874" s="11" t="s">
         <v>28</v>
       </c>
@@ -14154,7 +14156,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="875" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B875" s="11" t="s">
         <v>22</v>
       </c>
@@ -14169,7 +14171,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="876" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B876" s="11" t="s">
         <v>30</v>
       </c>
@@ -14184,7 +14186,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="877" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B877" s="11" t="s">
         <v>112</v>
       </c>
@@ -14199,7 +14201,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="878" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B878" s="11" t="s">
         <v>28</v>
       </c>
@@ -14214,7 +14216,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="879" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B879" s="11" t="s">
         <v>3</v>
       </c>
@@ -14229,7 +14231,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="880" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B880" s="11" t="s">
         <v>3</v>
       </c>
@@ -14244,7 +14246,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="881" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B881" s="11" t="s">
         <v>113</v>
       </c>
@@ -14259,7 +14261,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="882" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B882" s="11" t="s">
         <v>29</v>
       </c>
@@ -14274,7 +14276,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="883" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B883" s="11" t="s">
         <v>20</v>
       </c>
@@ -14289,7 +14291,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="884" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B884" s="11" t="s">
         <v>5</v>
       </c>
@@ -14304,7 +14306,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="885" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B885" s="11" t="s">
         <v>11</v>
       </c>
@@ -14410,18 +14412,34 @@
       </c>
     </row>
     <row r="892" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B892" s="11"/>
+      <c r="B892" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C892" s="5"/>
-      <c r="D892" s="3"/>
-      <c r="E892" s="12"/>
-      <c r="F892" s="7"/>
+      <c r="D892" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E892" s="12">
+        <v>1149.46</v>
+      </c>
+      <c r="F892" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="893" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B893" s="11"/>
+      <c r="B893" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C893" s="5"/>
-      <c r="D893" s="3"/>
-      <c r="E893" s="12"/>
-      <c r="F893" s="7"/>
+      <c r="D893" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E893" s="12">
+        <v>312</v>
+      </c>
+      <c r="F893" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="894" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B894" s="11"/>
@@ -37888,11 +37906,7 @@
       <c r="F4245" s="38"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G4194" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
-    <filterColumn colId="0">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B2:G4194" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G875">
     <sortCondition ref="F3:F875" customList="janeiro,fevereiro,março,abril,maio,junho,julho,agosto,setembro,outubro,novembro,dezembro"/>
   </sortState>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="362" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F441F280-F942-4CFA-AC7C-6F0D28561522}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D476208-1DAD-4259-924C-853928F04D33}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="115">
   <si>
     <t>Custo</t>
   </si>
@@ -1049,6 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
+  <sheetPr filterMode="1"/>
   <dimension ref="B2:G4245"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1078,7 +1079,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>19</v>
       </c>
@@ -1093,7 +1094,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" s="36" t="s">
         <v>18</v>
       </c>
@@ -1108,7 +1109,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
@@ -1123,7 +1124,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>18</v>
       </c>
@@ -1138,7 +1139,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>18</v>
       </c>
@@ -1153,7 +1154,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>18</v>
       </c>
@@ -1168,7 +1169,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>26</v>
       </c>
@@ -1183,7 +1184,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
         <v>26</v>
       </c>
@@ -1198,7 +1199,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>21</v>
       </c>
@@ -1213,7 +1214,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>9</v>
       </c>
@@ -1228,7 +1229,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>8</v>
       </c>
@@ -1243,7 +1244,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>8</v>
       </c>
@@ -1258,7 +1259,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>8</v>
       </c>
@@ -1273,7 +1274,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>8</v>
       </c>
@@ -1288,7 +1289,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>8</v>
       </c>
@@ -1303,7 +1304,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>8</v>
       </c>
@@ -1318,7 +1319,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>8</v>
       </c>
@@ -1333,7 +1334,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>3</v>
       </c>
@@ -1348,7 +1349,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>3</v>
       </c>
@@ -1363,7 +1364,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>3</v>
       </c>
@@ -1378,7 +1379,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>3</v>
       </c>
@@ -1393,7 +1394,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>3</v>
       </c>
@@ -1408,7 +1409,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>3</v>
       </c>
@@ -1423,7 +1424,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B26" s="29" t="s">
         <v>3</v>
       </c>
@@ -1438,7 +1439,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B27" s="29" t="s">
         <v>30</v>
       </c>
@@ -1453,7 +1454,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B28" s="29" t="s">
         <v>15</v>
       </c>
@@ -1468,7 +1469,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B29" s="29" t="s">
         <v>15</v>
       </c>
@@ -1483,7 +1484,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B30" s="29" t="s">
         <v>15</v>
       </c>
@@ -1498,7 +1499,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B31" s="28" t="s">
         <v>15</v>
       </c>
@@ -1513,7 +1514,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B32" s="28" t="s">
         <v>15</v>
       </c>
@@ -1528,7 +1529,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B33" s="28" t="s">
         <v>15</v>
       </c>
@@ -1543,7 +1544,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B34" s="28" t="s">
         <v>15</v>
       </c>
@@ -1558,7 +1559,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B35" s="28" t="s">
         <v>15</v>
       </c>
@@ -1573,7 +1574,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B36" s="28" t="s">
         <v>15</v>
       </c>
@@ -1588,7 +1589,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B37" s="28" t="s">
         <v>15</v>
       </c>
@@ -1603,7 +1604,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B38" s="28" t="s">
         <v>6</v>
       </c>
@@ -1618,7 +1619,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B39" s="28" t="s">
         <v>6</v>
       </c>
@@ -1633,7 +1634,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B40" s="28" t="s">
         <v>26</v>
       </c>
@@ -1648,7 +1649,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B41" s="28" t="s">
         <v>26</v>
       </c>
@@ -1663,7 +1664,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B42" s="28" t="s">
         <v>4</v>
       </c>
@@ -1678,7 +1679,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B43" s="28" t="s">
         <v>5</v>
       </c>
@@ -1693,7 +1694,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B44" s="28" t="s">
         <v>5</v>
       </c>
@@ -1708,7 +1709,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B45" s="28" t="s">
         <v>5</v>
       </c>
@@ -1723,7 +1724,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B46" s="28" t="s">
         <v>12</v>
       </c>
@@ -1738,7 +1739,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B47" s="28" t="s">
         <v>22</v>
       </c>
@@ -1753,7 +1754,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B48" s="28" t="s">
         <v>22</v>
       </c>
@@ -1768,7 +1769,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B49" s="28" t="s">
         <v>22</v>
       </c>
@@ -1783,7 +1784,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B50" s="28" t="s">
         <v>22</v>
       </c>
@@ -1798,7 +1799,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B51" s="28" t="s">
         <v>22</v>
       </c>
@@ -1813,7 +1814,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B52" s="28" t="s">
         <v>22</v>
       </c>
@@ -1828,7 +1829,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B53" s="28" t="s">
         <v>22</v>
       </c>
@@ -1843,7 +1844,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B54" s="28" t="s">
         <v>22</v>
       </c>
@@ -1858,7 +1859,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B55" s="28" t="s">
         <v>22</v>
       </c>
@@ -1873,7 +1874,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B56" s="28" t="s">
         <v>22</v>
       </c>
@@ -1888,7 +1889,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B57" s="28" t="s">
         <v>22</v>
       </c>
@@ -1903,7 +1904,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B58" s="28" t="s">
         <v>21</v>
       </c>
@@ -1918,7 +1919,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B59" s="28" t="s">
         <v>7</v>
       </c>
@@ -1933,7 +1934,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B60" s="28" t="s">
         <v>83</v>
       </c>
@@ -1948,7 +1949,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B61" s="28" t="s">
         <v>83</v>
       </c>
@@ -1963,7 +1964,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B62" s="28" t="s">
         <v>10</v>
       </c>
@@ -1978,7 +1979,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B63" s="28" t="s">
         <v>10</v>
       </c>
@@ -1993,7 +1994,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B64" s="28" t="s">
         <v>8</v>
       </c>
@@ -2008,7 +2009,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B65" s="28" t="s">
         <v>8</v>
       </c>
@@ -2023,7 +2024,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B66" s="28" t="s">
         <v>8</v>
       </c>
@@ -2038,7 +2039,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B67" s="28" t="s">
         <v>8</v>
       </c>
@@ -2053,7 +2054,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B68" s="28" t="s">
         <v>8</v>
       </c>
@@ -2068,7 +2069,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B69" s="28" t="s">
         <v>8</v>
       </c>
@@ -2083,7 +2084,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B70" s="28" t="s">
         <v>8</v>
       </c>
@@ -2098,7 +2099,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B71" s="28" t="s">
         <v>8</v>
       </c>
@@ -2113,7 +2114,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B72" s="28" t="s">
         <v>8</v>
       </c>
@@ -2128,7 +2129,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B73" s="28" t="s">
         <v>8</v>
       </c>
@@ -2143,7 +2144,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B74" s="28" t="s">
         <v>8</v>
       </c>
@@ -2158,7 +2159,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B75" s="28" t="s">
         <v>8</v>
       </c>
@@ -2173,7 +2174,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B76" s="28" t="s">
         <v>3</v>
       </c>
@@ -2188,7 +2189,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B77" s="11" t="s">
         <v>19</v>
       </c>
@@ -2203,7 +2204,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B78" s="11" t="s">
         <v>30</v>
       </c>
@@ -2218,7 +2219,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B79" s="11" t="s">
         <v>2</v>
       </c>
@@ -2233,7 +2234,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B80" s="11" t="s">
         <v>6</v>
       </c>
@@ -2248,7 +2249,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B81" s="11" t="s">
         <v>6</v>
       </c>
@@ -2263,7 +2264,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B82" s="11" t="s">
         <v>6</v>
       </c>
@@ -2278,7 +2279,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B83" s="11" t="s">
         <v>6</v>
       </c>
@@ -2293,7 +2294,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B84" s="11" t="s">
         <v>6</v>
       </c>
@@ -2308,7 +2309,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B85" s="11" t="s">
         <v>6</v>
       </c>
@@ -2323,7 +2324,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B86" s="11" t="s">
         <v>6</v>
       </c>
@@ -2338,7 +2339,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B87" s="11" t="s">
         <v>20</v>
       </c>
@@ -2353,7 +2354,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B88" s="11" t="s">
         <v>20</v>
       </c>
@@ -2368,7 +2369,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B89" s="11" t="s">
         <v>20</v>
       </c>
@@ -2383,7 +2384,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B90" s="11" t="s">
         <v>20</v>
       </c>
@@ -2398,7 +2399,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B91" s="11" t="s">
         <v>20</v>
       </c>
@@ -2413,7 +2414,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B92" s="11" t="s">
         <v>20</v>
       </c>
@@ -2428,7 +2429,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B93" s="11" t="s">
         <v>20</v>
       </c>
@@ -2443,7 +2444,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B94" s="11" t="s">
         <v>18</v>
       </c>
@@ -2458,7 +2459,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B95" s="11" t="s">
         <v>18</v>
       </c>
@@ -2473,7 +2474,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B96" s="11" t="s">
         <v>18</v>
       </c>
@@ -2488,7 +2489,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B97" s="11" t="s">
         <v>18</v>
       </c>
@@ -2503,7 +2504,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B98" s="11" t="s">
         <v>18</v>
       </c>
@@ -2518,7 +2519,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B99" s="11" t="s">
         <v>13</v>
       </c>
@@ -2533,7 +2534,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B100" s="11" t="s">
         <v>11</v>
       </c>
@@ -2548,7 +2549,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B101" s="11" t="s">
         <v>11</v>
       </c>
@@ -2563,7 +2564,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B102" s="11" t="s">
         <v>11</v>
       </c>
@@ -2578,7 +2579,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B103" s="11" t="s">
         <v>11</v>
       </c>
@@ -2593,7 +2594,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B104" s="11" t="s">
         <v>11</v>
       </c>
@@ -2608,7 +2609,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B105" s="11" t="s">
         <v>26</v>
       </c>
@@ -2623,7 +2624,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B106" s="11" t="s">
         <v>26</v>
       </c>
@@ -2638,7 +2639,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B107" s="11" t="s">
         <v>26</v>
       </c>
@@ -2653,7 +2654,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B108" s="11" t="s">
         <v>26</v>
       </c>
@@ -2668,7 +2669,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B109" s="11" t="s">
         <v>4</v>
       </c>
@@ -2683,7 +2684,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B110" s="11" t="s">
         <v>4</v>
       </c>
@@ -2698,7 +2699,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B111" s="11" t="s">
         <v>4</v>
       </c>
@@ -2713,7 +2714,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B112" s="11" t="s">
         <v>4</v>
       </c>
@@ -2728,7 +2729,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B113" s="11" t="s">
         <v>4</v>
       </c>
@@ -2743,7 +2744,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B114" s="11" t="s">
         <v>4</v>
       </c>
@@ -2758,7 +2759,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B115" s="11" t="s">
         <v>4</v>
       </c>
@@ -2773,7 +2774,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B116" s="11" t="s">
         <v>4</v>
       </c>
@@ -2788,7 +2789,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B117" s="11" t="s">
         <v>4</v>
       </c>
@@ -2803,7 +2804,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B118" s="11" t="s">
         <v>4</v>
       </c>
@@ -2818,7 +2819,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B119" s="11" t="s">
         <v>4</v>
       </c>
@@ -2833,7 +2834,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B120" s="11" t="s">
         <v>4</v>
       </c>
@@ -2848,7 +2849,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B121" s="11" t="s">
         <v>4</v>
       </c>
@@ -2863,7 +2864,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B122" s="11" t="s">
         <v>24</v>
       </c>
@@ -2878,7 +2879,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B123" s="11" t="s">
         <v>24</v>
       </c>
@@ -2893,7 +2894,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B124" s="11" t="s">
         <v>24</v>
       </c>
@@ -2908,7 +2909,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B125" s="11" t="s">
         <v>24</v>
       </c>
@@ -2923,7 +2924,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B126" s="11" t="s">
         <v>24</v>
       </c>
@@ -2938,7 +2939,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B127" s="11" t="s">
         <v>24</v>
       </c>
@@ -2953,7 +2954,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="128" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B128" s="11" t="s">
         <v>16</v>
       </c>
@@ -2968,7 +2969,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B129" s="11" t="s">
         <v>16</v>
       </c>
@@ -2983,7 +2984,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B130" s="11" t="s">
         <v>5</v>
       </c>
@@ -2998,7 +2999,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B131" s="11" t="s">
         <v>5</v>
       </c>
@@ -3013,7 +3014,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B132" s="11" t="s">
         <v>5</v>
       </c>
@@ -3028,7 +3029,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B133" s="11" t="s">
         <v>5</v>
       </c>
@@ -3043,7 +3044,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B134" s="11" t="s">
         <v>28</v>
       </c>
@@ -3058,7 +3059,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B135" s="11" t="s">
         <v>28</v>
       </c>
@@ -3073,7 +3074,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B136" s="11" t="s">
         <v>28</v>
       </c>
@@ -3088,7 +3089,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B137" s="11" t="s">
         <v>28</v>
       </c>
@@ -3103,7 +3104,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B138" s="11" t="s">
         <v>28</v>
       </c>
@@ -3118,7 +3119,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B139" s="11" t="s">
         <v>28</v>
       </c>
@@ -3133,7 +3134,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B140" s="11" t="s">
         <v>28</v>
       </c>
@@ -3148,7 +3149,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B141" s="11" t="s">
         <v>28</v>
       </c>
@@ -3163,7 +3164,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B142" s="11" t="s">
         <v>28</v>
       </c>
@@ -3178,7 +3179,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B143" s="11" t="s">
         <v>28</v>
       </c>
@@ -3193,7 +3194,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B144" s="11" t="s">
         <v>28</v>
       </c>
@@ -3208,7 +3209,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B145" s="11" t="s">
         <v>28</v>
       </c>
@@ -3223,7 +3224,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B146" s="11" t="s">
         <v>17</v>
       </c>
@@ -3238,7 +3239,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B147" s="11" t="s">
         <v>17</v>
       </c>
@@ -3253,7 +3254,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B148" s="11" t="s">
         <v>29</v>
       </c>
@@ -3268,7 +3269,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B149" s="11" t="s">
         <v>29</v>
       </c>
@@ -3283,7 +3284,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B150" s="11" t="s">
         <v>22</v>
       </c>
@@ -3298,7 +3299,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B151" s="11" t="s">
         <v>22</v>
       </c>
@@ -3313,7 +3314,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B152" s="11" t="s">
         <v>22</v>
       </c>
@@ -3328,7 +3329,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B153" s="11" t="s">
         <v>22</v>
       </c>
@@ -3343,7 +3344,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B154" s="11" t="s">
         <v>22</v>
       </c>
@@ -3358,7 +3359,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B155" s="11" t="s">
         <v>55</v>
       </c>
@@ -3373,7 +3374,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B156" s="11" t="s">
         <v>21</v>
       </c>
@@ -3388,7 +3389,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B157" s="11" t="s">
         <v>21</v>
       </c>
@@ -3403,7 +3404,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B158" s="11" t="s">
         <v>21</v>
       </c>
@@ -3418,7 +3419,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B159" s="11" t="s">
         <v>21</v>
       </c>
@@ -3433,7 +3434,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B160" s="11" t="s">
         <v>21</v>
       </c>
@@ -3448,7 +3449,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B161" s="11" t="s">
         <v>21</v>
       </c>
@@ -3463,7 +3464,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B162" s="11" t="s">
         <v>21</v>
       </c>
@@ -3478,7 +3479,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B163" s="11" t="s">
         <v>21</v>
       </c>
@@ -3493,7 +3494,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B164" s="11" t="s">
         <v>21</v>
       </c>
@@ -3508,7 +3509,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B165" s="11" t="s">
         <v>21</v>
       </c>
@@ -3523,7 +3524,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B166" s="11" t="s">
         <v>21</v>
       </c>
@@ -3538,7 +3539,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B167" s="11" t="s">
         <v>21</v>
       </c>
@@ -3553,7 +3554,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B168" s="11" t="s">
         <v>9</v>
       </c>
@@ -3568,7 +3569,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B169" s="11" t="s">
         <v>9</v>
       </c>
@@ -3583,7 +3584,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="170" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B170" s="11" t="s">
         <v>9</v>
       </c>
@@ -3598,7 +3599,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B171" s="11" t="s">
         <v>9</v>
       </c>
@@ -3613,7 +3614,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B172" s="11" t="s">
         <v>9</v>
       </c>
@@ -3628,7 +3629,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B173" s="11" t="s">
         <v>9</v>
       </c>
@@ -3643,7 +3644,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B174" s="11" t="s">
         <v>9</v>
       </c>
@@ -3658,7 +3659,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B175" s="11" t="s">
         <v>9</v>
       </c>
@@ -3673,7 +3674,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="176" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B176" s="11" t="s">
         <v>9</v>
       </c>
@@ -3688,7 +3689,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B177" s="11" t="s">
         <v>9</v>
       </c>
@@ -3703,7 +3704,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B178" s="11" t="s">
         <v>9</v>
       </c>
@@ -3718,7 +3719,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B179" s="11" t="s">
         <v>9</v>
       </c>
@@ -3733,7 +3734,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B180" s="11" t="s">
         <v>7</v>
       </c>
@@ -3748,7 +3749,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B181" s="11" t="s">
         <v>83</v>
       </c>
@@ -3763,7 +3764,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B182" s="11" t="s">
         <v>83</v>
       </c>
@@ -3778,7 +3779,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B183" s="11" t="s">
         <v>14</v>
       </c>
@@ -3793,7 +3794,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B184" s="11" t="s">
         <v>14</v>
       </c>
@@ -3808,7 +3809,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B185" s="11" t="s">
         <v>10</v>
       </c>
@@ -3823,7 +3824,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B186" s="11" t="s">
         <v>10</v>
       </c>
@@ -3838,7 +3839,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B187" s="11" t="s">
         <v>10</v>
       </c>
@@ -3853,7 +3854,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B188" s="11" t="s">
         <v>10</v>
       </c>
@@ -3868,7 +3869,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B189" s="11" t="s">
         <v>10</v>
       </c>
@@ -3883,7 +3884,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B190" s="11" t="s">
         <v>10</v>
       </c>
@@ -3898,7 +3899,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B191" s="11" t="s">
         <v>8</v>
       </c>
@@ -3913,7 +3914,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B192" s="11" t="s">
         <v>8</v>
       </c>
@@ -3928,7 +3929,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B193" s="11" t="s">
         <v>8</v>
       </c>
@@ -3943,7 +3944,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B194" s="11" t="s">
         <v>8</v>
       </c>
@@ -3958,7 +3959,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B195" s="11" t="s">
         <v>3</v>
       </c>
@@ -3973,7 +3974,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B196" s="11" t="s">
         <v>3</v>
       </c>
@@ -3988,7 +3989,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B197" s="11" t="s">
         <v>3</v>
       </c>
@@ -4003,7 +4004,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B198" s="11" t="s">
         <v>3</v>
       </c>
@@ -4018,7 +4019,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="199" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B199" s="11" t="s">
         <v>3</v>
       </c>
@@ -4033,7 +4034,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="200" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B200" s="11" t="s">
         <v>3</v>
       </c>
@@ -4048,7 +4049,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="201" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B201" s="11" t="s">
         <v>3</v>
       </c>
@@ -4063,7 +4064,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="202" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B202" s="11" t="s">
         <v>3</v>
       </c>
@@ -4078,7 +4079,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="203" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B203" s="11" t="s">
         <v>3</v>
       </c>
@@ -4093,7 +4094,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="204" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B204" s="11" t="s">
         <v>19</v>
       </c>
@@ -4108,7 +4109,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="205" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B205" s="11" t="s">
         <v>30</v>
       </c>
@@ -4123,7 +4124,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="206" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B206" s="11" t="s">
         <v>32</v>
       </c>
@@ -4138,7 +4139,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="207" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B207" s="11" t="s">
         <v>32</v>
       </c>
@@ -4153,7 +4154,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="208" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B208" s="11" t="s">
         <v>32</v>
       </c>
@@ -4168,7 +4169,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="209" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B209" s="11" t="s">
         <v>15</v>
       </c>
@@ -4183,7 +4184,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="210" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B210" s="11" t="s">
         <v>15</v>
       </c>
@@ -4198,7 +4199,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="211" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B211" s="11" t="s">
         <v>15</v>
       </c>
@@ -4213,7 +4214,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="212" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B212" s="11" t="s">
         <v>15</v>
       </c>
@@ -4228,7 +4229,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="213" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B213" s="11" t="s">
         <v>15</v>
       </c>
@@ -4243,7 +4244,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="214" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B214" s="11" t="s">
         <v>15</v>
       </c>
@@ -4258,7 +4259,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="215" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B215" s="11" t="s">
         <v>15</v>
       </c>
@@ -4273,7 +4274,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="216" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B216" s="11" t="s">
         <v>15</v>
       </c>
@@ -4288,7 +4289,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="217" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B217" s="11" t="s">
         <v>15</v>
       </c>
@@ -4303,7 +4304,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="218" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B218" s="11" t="s">
         <v>6</v>
       </c>
@@ -4318,7 +4319,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="219" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B219" s="11" t="s">
         <v>6</v>
       </c>
@@ -4333,7 +4334,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="220" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B220" s="11" t="s">
         <v>6</v>
       </c>
@@ -4348,7 +4349,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="221" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B221" s="11" t="s">
         <v>6</v>
       </c>
@@ -4363,7 +4364,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="222" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B222" s="11" t="s">
         <v>6</v>
       </c>
@@ -4378,7 +4379,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="223" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B223" s="11" t="s">
         <v>6</v>
       </c>
@@ -4393,7 +4394,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="224" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B224" s="11" t="s">
         <v>6</v>
       </c>
@@ -4408,7 +4409,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="225" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B225" s="11" t="s">
         <v>6</v>
       </c>
@@ -4423,7 +4424,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="226" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B226" s="11" t="s">
         <v>6</v>
       </c>
@@ -4438,7 +4439,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="227" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B227" s="11" t="s">
         <v>20</v>
       </c>
@@ -4453,7 +4454,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="228" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B228" s="11" t="s">
         <v>20</v>
       </c>
@@ -4468,7 +4469,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="229" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B229" s="11" t="s">
         <v>20</v>
       </c>
@@ -4483,7 +4484,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="230" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B230" s="11" t="s">
         <v>20</v>
       </c>
@@ -4498,7 +4499,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="231" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B231" s="11" t="s">
         <v>20</v>
       </c>
@@ -4513,7 +4514,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="232" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B232" s="11" t="s">
         <v>20</v>
       </c>
@@ -4528,7 +4529,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="233" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B233" s="11" t="s">
         <v>20</v>
       </c>
@@ -4543,7 +4544,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="234" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B234" s="11" t="s">
         <v>20</v>
       </c>
@@ -4558,7 +4559,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="235" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B235" s="11" t="s">
         <v>20</v>
       </c>
@@ -4573,7 +4574,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="236" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B236" s="11" t="s">
         <v>20</v>
       </c>
@@ -4588,7 +4589,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="237" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B237" s="11" t="s">
         <v>20</v>
       </c>
@@ -4603,7 +4604,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="238" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B238" s="11" t="s">
         <v>18</v>
       </c>
@@ -4618,7 +4619,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="239" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B239" s="11" t="s">
         <v>18</v>
       </c>
@@ -4633,7 +4634,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="240" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B240" s="11" t="s">
         <v>18</v>
       </c>
@@ -4648,7 +4649,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="241" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B241" s="11" t="s">
         <v>18</v>
       </c>
@@ -4663,7 +4664,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="242" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B242" s="11" t="s">
         <v>18</v>
       </c>
@@ -4678,7 +4679,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="243" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B243" s="11" t="s">
         <v>18</v>
       </c>
@@ -4693,7 +4694,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="244" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B244" s="11" t="s">
         <v>18</v>
       </c>
@@ -4708,7 +4709,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="245" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B245" s="11" t="s">
         <v>18</v>
       </c>
@@ -4723,7 +4724,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="246" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B246" s="11" t="s">
         <v>13</v>
       </c>
@@ -4738,7 +4739,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="247" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B247" s="11" t="s">
         <v>13</v>
       </c>
@@ -4753,7 +4754,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="248" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B248" s="11" t="s">
         <v>13</v>
       </c>
@@ -4768,7 +4769,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="249" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B249" s="11" t="s">
         <v>13</v>
       </c>
@@ -4783,7 +4784,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="250" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B250" s="11" t="s">
         <v>13</v>
       </c>
@@ -4798,7 +4799,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="251" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B251" s="11" t="s">
         <v>11</v>
       </c>
@@ -4813,7 +4814,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="252" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B252" s="11" t="s">
         <v>11</v>
       </c>
@@ -4828,7 +4829,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="253" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B253" s="11" t="s">
         <v>11</v>
       </c>
@@ -4843,7 +4844,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="254" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B254" s="11" t="s">
         <v>11</v>
       </c>
@@ -4858,7 +4859,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="255" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B255" s="11" t="s">
         <v>11</v>
       </c>
@@ -4873,7 +4874,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="256" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B256" s="11" t="s">
         <v>11</v>
       </c>
@@ -4888,7 +4889,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="257" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B257" s="11" t="s">
         <v>11</v>
       </c>
@@ -4903,7 +4904,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="258" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B258" s="11" t="s">
         <v>4</v>
       </c>
@@ -4918,7 +4919,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="259" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B259" s="11" t="s">
         <v>4</v>
       </c>
@@ -4933,7 +4934,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="260" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B260" s="11" t="s">
         <v>4</v>
       </c>
@@ -4948,7 +4949,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="261" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B261" s="11" t="s">
         <v>4</v>
       </c>
@@ -4963,7 +4964,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="262" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B262" s="11" t="s">
         <v>4</v>
       </c>
@@ -4978,7 +4979,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="263" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B263" s="11" t="s">
         <v>4</v>
       </c>
@@ -4993,7 +4994,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="264" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B264" s="11" t="s">
         <v>4</v>
       </c>
@@ -5008,7 +5009,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="265" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B265" s="11" t="s">
         <v>4</v>
       </c>
@@ -5023,7 +5024,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="266" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B266" s="11" t="s">
         <v>4</v>
       </c>
@@ -5038,7 +5039,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="267" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B267" s="11" t="s">
         <v>4</v>
       </c>
@@ -5053,7 +5054,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="268" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B268" s="11" t="s">
         <v>4</v>
       </c>
@@ -5068,7 +5069,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="269" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B269" s="11" t="s">
         <v>24</v>
       </c>
@@ -5083,7 +5084,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="270" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B270" s="11" t="s">
         <v>25</v>
       </c>
@@ -5098,7 +5099,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="271" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B271" s="11" t="s">
         <v>25</v>
       </c>
@@ -5113,7 +5114,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="272" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B272" s="11" t="s">
         <v>25</v>
       </c>
@@ -5128,7 +5129,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B273" s="11" t="s">
         <v>16</v>
       </c>
@@ -5143,7 +5144,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="274" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B274" s="11" t="s">
         <v>5</v>
       </c>
@@ -5158,7 +5159,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="275" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B275" s="11" t="s">
         <v>5</v>
       </c>
@@ -5173,7 +5174,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="276" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B276" s="11" t="s">
         <v>5</v>
       </c>
@@ -5188,7 +5189,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="277" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B277" s="11" t="s">
         <v>5</v>
       </c>
@@ -5203,7 +5204,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="278" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B278" s="11" t="s">
         <v>5</v>
       </c>
@@ -5218,7 +5219,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="279" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B279" s="11" t="s">
         <v>5</v>
       </c>
@@ -5233,7 +5234,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="280" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B280" s="11" t="s">
         <v>5</v>
       </c>
@@ -5248,7 +5249,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="281" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B281" s="11" t="s">
         <v>5</v>
       </c>
@@ -5263,7 +5264,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="282" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B282" s="11" t="s">
         <v>5</v>
       </c>
@@ -5278,7 +5279,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="283" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B283" s="11" t="s">
         <v>5</v>
       </c>
@@ -5293,7 +5294,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="284" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B284" s="11" t="s">
         <v>5</v>
       </c>
@@ -5308,7 +5309,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="285" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B285" s="11" t="s">
         <v>5</v>
       </c>
@@ -5323,7 +5324,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="286" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B286" s="11" t="s">
         <v>5</v>
       </c>
@@ -5338,7 +5339,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="287" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B287" s="11" t="s">
         <v>5</v>
       </c>
@@ -5353,7 +5354,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="288" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B288" s="11" t="s">
         <v>5</v>
       </c>
@@ -5368,7 +5369,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="289" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B289" s="11" t="s">
         <v>5</v>
       </c>
@@ -5383,7 +5384,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="290" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B290" s="11" t="s">
         <v>5</v>
       </c>
@@ -5398,7 +5399,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="291" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B291" s="11" t="s">
         <v>28</v>
       </c>
@@ -5413,7 +5414,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="292" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B292" s="11" t="s">
         <v>45</v>
       </c>
@@ -5428,7 +5429,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="293" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B293" s="11" t="s">
         <v>17</v>
       </c>
@@ -5443,7 +5444,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="294" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B294" s="11" t="s">
         <v>17</v>
       </c>
@@ -5458,7 +5459,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="295" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B295" s="11" t="s">
         <v>17</v>
       </c>
@@ -5473,7 +5474,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="296" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B296" s="11" t="s">
         <v>17</v>
       </c>
@@ -5488,7 +5489,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="297" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B297" s="11" t="s">
         <v>17</v>
       </c>
@@ -5503,7 +5504,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="298" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B298" s="11" t="s">
         <v>17</v>
       </c>
@@ -5518,7 +5519,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="299" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B299" s="11" t="s">
         <v>17</v>
       </c>
@@ -5533,7 +5534,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="300" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B300" s="11" t="s">
         <v>22</v>
       </c>
@@ -5548,7 +5549,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="301" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B301" s="11" t="s">
         <v>22</v>
       </c>
@@ -5563,7 +5564,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="302" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B302" s="11" t="s">
         <v>22</v>
       </c>
@@ -5578,7 +5579,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="303" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B303" s="11" t="s">
         <v>22</v>
       </c>
@@ -5593,7 +5594,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="304" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B304" s="11" t="s">
         <v>34</v>
       </c>
@@ -5608,7 +5609,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="305" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B305" s="11" t="s">
         <v>21</v>
       </c>
@@ -5623,7 +5624,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="306" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B306" s="11" t="s">
         <v>21</v>
       </c>
@@ -5638,7 +5639,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="307" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B307" s="11" t="s">
         <v>21</v>
       </c>
@@ -5653,7 +5654,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="308" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B308" s="11" t="s">
         <v>21</v>
       </c>
@@ -5668,7 +5669,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="309" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B309" s="11" t="s">
         <v>21</v>
       </c>
@@ -5683,7 +5684,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="310" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B310" s="11" t="s">
         <v>21</v>
       </c>
@@ -5698,7 +5699,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="311" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B311" s="11" t="s">
         <v>21</v>
       </c>
@@ -5713,7 +5714,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="312" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B312" s="11" t="s">
         <v>21</v>
       </c>
@@ -5728,7 +5729,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="313" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B313" s="11" t="s">
         <v>21</v>
       </c>
@@ -5743,7 +5744,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="314" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B314" s="11" t="s">
         <v>21</v>
       </c>
@@ -5758,7 +5759,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="315" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B315" s="11" t="s">
         <v>21</v>
       </c>
@@ -5773,7 +5774,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="316" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B316" s="11" t="s">
         <v>21</v>
       </c>
@@ -5788,7 +5789,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="317" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B317" s="11" t="s">
         <v>21</v>
       </c>
@@ -5803,7 +5804,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="318" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B318" s="11" t="s">
         <v>21</v>
       </c>
@@ -5818,7 +5819,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="319" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B319" s="11" t="s">
         <v>21</v>
       </c>
@@ -5833,7 +5834,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="320" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B320" s="11" t="s">
         <v>9</v>
       </c>
@@ -5848,7 +5849,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="321" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B321" s="11" t="s">
         <v>9</v>
       </c>
@@ -5863,7 +5864,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="322" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B322" s="11" t="s">
         <v>9</v>
       </c>
@@ -5878,7 +5879,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="323" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B323" s="11" t="s">
         <v>9</v>
       </c>
@@ -5893,7 +5894,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="324" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B324" s="11" t="s">
         <v>9</v>
       </c>
@@ -5908,7 +5909,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="325" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B325" s="11" t="s">
         <v>9</v>
       </c>
@@ -5923,7 +5924,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="326" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B326" s="11" t="s">
         <v>9</v>
       </c>
@@ -5938,7 +5939,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="327" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B327" s="11" t="s">
         <v>7</v>
       </c>
@@ -5953,7 +5954,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="328" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B328" s="11" t="s">
         <v>7</v>
       </c>
@@ -5968,7 +5969,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="329" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B329" s="11" t="s">
         <v>7</v>
       </c>
@@ -5983,7 +5984,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="330" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B330" s="11" t="s">
         <v>7</v>
       </c>
@@ -5998,7 +5999,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="331" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B331" s="11" t="s">
         <v>7</v>
       </c>
@@ -6013,7 +6014,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="332" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B332" s="11" t="s">
         <v>7</v>
       </c>
@@ -6028,7 +6029,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="333" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B333" s="11" t="s">
         <v>7</v>
       </c>
@@ -6043,7 +6044,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="334" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B334" s="11" t="s">
         <v>7</v>
       </c>
@@ -6058,7 +6059,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="335" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B335" s="27" t="s">
         <v>31</v>
       </c>
@@ -6073,7 +6074,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="336" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B336" s="27" t="s">
         <v>31</v>
       </c>
@@ -6088,7 +6089,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="337" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B337" s="27" t="s">
         <v>31</v>
       </c>
@@ -6103,7 +6104,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="338" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B338" s="27" t="s">
         <v>31</v>
       </c>
@@ -6118,7 +6119,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="339" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B339" s="27" t="s">
         <v>31</v>
       </c>
@@ -6133,7 +6134,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="340" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B340" s="11" t="s">
         <v>10</v>
       </c>
@@ -6148,7 +6149,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="341" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B341" s="11" t="s">
         <v>8</v>
       </c>
@@ -6163,7 +6164,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="342" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B342" s="11" t="s">
         <v>8</v>
       </c>
@@ -6178,7 +6179,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="343" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B343" s="11" t="s">
         <v>8</v>
       </c>
@@ -6193,7 +6194,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="344" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B344" s="11" t="s">
         <v>8</v>
       </c>
@@ -6208,7 +6209,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="345" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B345" s="11" t="s">
         <v>8</v>
       </c>
@@ -6223,7 +6224,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="346" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B346" s="11" t="s">
         <v>8</v>
       </c>
@@ -6238,7 +6239,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="347" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B347" s="11" t="s">
         <v>8</v>
       </c>
@@ -6253,7 +6254,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="348" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B348" s="11" t="s">
         <v>8</v>
       </c>
@@ -6268,7 +6269,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="349" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B349" s="11" t="s">
         <v>3</v>
       </c>
@@ -6283,7 +6284,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="350" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B350" s="11" t="s">
         <v>3</v>
       </c>
@@ -6298,7 +6299,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="351" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B351" s="11" t="s">
         <v>3</v>
       </c>
@@ -6313,7 +6314,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="352" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B352" s="11" t="s">
         <v>3</v>
       </c>
@@ -6328,7 +6329,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="353" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B353" s="11" t="s">
         <v>3</v>
       </c>
@@ -6343,7 +6344,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="354" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B354" s="11" t="s">
         <v>87</v>
       </c>
@@ -6358,7 +6359,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="355" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B355" s="11" t="s">
         <v>19</v>
       </c>
@@ -6373,7 +6374,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="356" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B356" s="11" t="s">
         <v>19</v>
       </c>
@@ -6388,7 +6389,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="357" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B357" s="11" t="s">
         <v>19</v>
       </c>
@@ -6403,7 +6404,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="358" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B358" s="11" t="s">
         <v>19</v>
       </c>
@@ -6418,7 +6419,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="359" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B359" s="11" t="s">
         <v>19</v>
       </c>
@@ -6433,7 +6434,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="360" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B360" s="11" t="s">
         <v>19</v>
       </c>
@@ -6448,7 +6449,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="361" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B361" s="11" t="s">
         <v>19</v>
       </c>
@@ -6463,7 +6464,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="362" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B362" s="11" t="s">
         <v>19</v>
       </c>
@@ -6478,7 +6479,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="363" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B363" s="11" t="s">
         <v>19</v>
       </c>
@@ -6493,7 +6494,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="364" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B364" s="11" t="s">
         <v>19</v>
       </c>
@@ -6508,7 +6509,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="365" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B365" s="11" t="s">
         <v>19</v>
       </c>
@@ -6523,7 +6524,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="366" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B366" s="11" t="s">
         <v>19</v>
       </c>
@@ -6538,7 +6539,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="367" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B367" s="11" t="s">
         <v>30</v>
       </c>
@@ -6553,7 +6554,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="368" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B368" s="11" t="s">
         <v>30</v>
       </c>
@@ -6568,7 +6569,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="369" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B369" s="11" t="s">
         <v>32</v>
       </c>
@@ -6583,7 +6584,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="370" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B370" s="27" t="s">
         <v>39</v>
       </c>
@@ -6598,7 +6599,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="371" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B371" s="11" t="s">
         <v>59</v>
       </c>
@@ -6613,7 +6614,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="372" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B372" s="11" t="s">
         <v>15</v>
       </c>
@@ -6628,7 +6629,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="373" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B373" s="11" t="s">
         <v>15</v>
       </c>
@@ -6643,7 +6644,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="374" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B374" s="11" t="s">
         <v>15</v>
       </c>
@@ -6658,7 +6659,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="375" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B375" s="11" t="s">
         <v>15</v>
       </c>
@@ -6673,7 +6674,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="376" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B376" s="11" t="s">
         <v>15</v>
       </c>
@@ -6688,7 +6689,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="377" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B377" s="11" t="s">
         <v>6</v>
       </c>
@@ -6703,7 +6704,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="378" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B378" s="11" t="s">
         <v>6</v>
       </c>
@@ -6718,7 +6719,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="379" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B379" s="11" t="s">
         <v>6</v>
       </c>
@@ -6733,7 +6734,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="380" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B380" s="11" t="s">
         <v>6</v>
       </c>
@@ -6748,7 +6749,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="381" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B381" s="11" t="s">
         <v>6</v>
       </c>
@@ -6763,7 +6764,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="382" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B382" s="11" t="s">
         <v>6</v>
       </c>
@@ -6778,7 +6779,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="383" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B383" s="11" t="s">
         <v>6</v>
       </c>
@@ -6793,7 +6794,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="384" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B384" s="11" t="s">
         <v>20</v>
       </c>
@@ -6808,7 +6809,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="385" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B385" s="11" t="s">
         <v>20</v>
       </c>
@@ -6823,7 +6824,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="386" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B386" s="11" t="s">
         <v>20</v>
       </c>
@@ -6838,7 +6839,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="387" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B387" s="11" t="s">
         <v>18</v>
       </c>
@@ -6853,7 +6854,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="388" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B388" s="11" t="s">
         <v>18</v>
       </c>
@@ -6868,7 +6869,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="389" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B389" s="11" t="s">
         <v>18</v>
       </c>
@@ -6883,7 +6884,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="390" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B390" s="11" t="s">
         <v>13</v>
       </c>
@@ -6898,7 +6899,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="391" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B391" s="11" t="s">
         <v>13</v>
       </c>
@@ -6913,7 +6914,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="392" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B392" s="11" t="s">
         <v>13</v>
       </c>
@@ -6928,7 +6929,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="393" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B393" s="27" t="s">
         <v>11</v>
       </c>
@@ -6943,7 +6944,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="394" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B394" s="27" t="s">
         <v>11</v>
       </c>
@@ -6958,7 +6959,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="395" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B395" s="27" t="s">
         <v>11</v>
       </c>
@@ -6973,7 +6974,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="396" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B396" s="27" t="s">
         <v>11</v>
       </c>
@@ -6988,7 +6989,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="397" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B397" s="27" t="s">
         <v>11</v>
       </c>
@@ -7003,7 +7004,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="398" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B398" s="27" t="s">
         <v>11</v>
       </c>
@@ -7018,7 +7019,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="399" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B399" s="27" t="s">
         <v>11</v>
       </c>
@@ -7033,7 +7034,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="400" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B400" s="27" t="s">
         <v>11</v>
       </c>
@@ -7048,7 +7049,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="401" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B401" s="27" t="s">
         <v>11</v>
       </c>
@@ -7063,7 +7064,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="402" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B402" s="27" t="s">
         <v>11</v>
       </c>
@@ -7078,7 +7079,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="403" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B403" s="27" t="s">
         <v>11</v>
       </c>
@@ -7093,7 +7094,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="404" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B404" s="27" t="s">
         <v>11</v>
       </c>
@@ -7108,7 +7109,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="405" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B405" s="27" t="s">
         <v>11</v>
       </c>
@@ -7123,7 +7124,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="406" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B406" s="27" t="s">
         <v>11</v>
       </c>
@@ -7138,7 +7139,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="407" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B407" s="27" t="s">
         <v>11</v>
       </c>
@@ -7153,7 +7154,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="408" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B408" s="27" t="s">
         <v>11</v>
       </c>
@@ -7168,7 +7169,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="409" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B409" s="27" t="s">
         <v>11</v>
       </c>
@@ -7183,7 +7184,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="410" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B410" s="27" t="s">
         <v>11</v>
       </c>
@@ -7198,7 +7199,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="411" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B411" s="27" t="s">
         <v>11</v>
       </c>
@@ -7213,7 +7214,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="412" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B412" s="27" t="s">
         <v>11</v>
       </c>
@@ -7228,7 +7229,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="413" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B413" s="27" t="s">
         <v>11</v>
       </c>
@@ -7243,7 +7244,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="414" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B414" s="27" t="s">
         <v>11</v>
       </c>
@@ -7258,7 +7259,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="415" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B415" s="27" t="s">
         <v>11</v>
       </c>
@@ -7273,7 +7274,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="416" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B416" s="27" t="s">
         <v>11</v>
       </c>
@@ -7288,7 +7289,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="417" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B417" s="27" t="s">
         <v>11</v>
       </c>
@@ -7303,7 +7304,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="418" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B418" s="27" t="s">
         <v>11</v>
       </c>
@@ -7318,7 +7319,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="419" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B419" s="11" t="s">
         <v>11</v>
       </c>
@@ -7333,7 +7334,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="420" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B420" s="11" t="s">
         <v>11</v>
       </c>
@@ -7348,7 +7349,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="421" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B421" s="11" t="s">
         <v>11</v>
       </c>
@@ -7363,7 +7364,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="422" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B422" s="11" t="s">
         <v>11</v>
       </c>
@@ -7378,7 +7379,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="423" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B423" s="11" t="s">
         <v>11</v>
       </c>
@@ -7393,7 +7394,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="424" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B424" s="11" t="s">
         <v>11</v>
       </c>
@@ -7408,7 +7409,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="425" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B425" s="11" t="s">
         <v>11</v>
       </c>
@@ -7423,7 +7424,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="426" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B426" s="11" t="s">
         <v>11</v>
       </c>
@@ -7438,7 +7439,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="427" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B427" s="11" t="s">
         <v>11</v>
       </c>
@@ -7453,7 +7454,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="428" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B428" s="11" t="s">
         <v>23</v>
       </c>
@@ -7468,7 +7469,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="429" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B429" s="11" t="s">
         <v>23</v>
       </c>
@@ -7483,7 +7484,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="430" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B430" s="11" t="s">
         <v>23</v>
       </c>
@@ -7498,7 +7499,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="431" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B431" s="27" t="s">
         <v>4</v>
       </c>
@@ -7513,7 +7514,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="432" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B432" s="11" t="s">
         <v>4</v>
       </c>
@@ -7528,7 +7529,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="433" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B433" s="11" t="s">
         <v>4</v>
       </c>
@@ -7543,7 +7544,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="434" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B434" s="11" t="s">
         <v>4</v>
       </c>
@@ -7558,7 +7559,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="435" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B435" s="11" t="s">
         <v>4</v>
       </c>
@@ -7573,7 +7574,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="436" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B436" s="11" t="s">
         <v>4</v>
       </c>
@@ -7588,7 +7589,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="437" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B437" s="11" t="s">
         <v>4</v>
       </c>
@@ -7603,7 +7604,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="438" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B438" s="11" t="s">
         <v>4</v>
       </c>
@@ -7618,7 +7619,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="439" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B439" s="11" t="s">
         <v>4</v>
       </c>
@@ -7633,7 +7634,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="440" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B440" s="11" t="s">
         <v>4</v>
       </c>
@@ -7648,7 +7649,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="441" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B441" s="11" t="s">
         <v>4</v>
       </c>
@@ -7663,7 +7664,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="442" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B442" s="11" t="s">
         <v>4</v>
       </c>
@@ -7678,7 +7679,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="443" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B443" s="11" t="s">
         <v>4</v>
       </c>
@@ -7693,7 +7694,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="444" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B444" s="11" t="s">
         <v>4</v>
       </c>
@@ -7708,7 +7709,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="445" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B445" s="11" t="s">
         <v>4</v>
       </c>
@@ -7723,7 +7724,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="446" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B446" s="11" t="s">
         <v>4</v>
       </c>
@@ -7738,7 +7739,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="447" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B447" s="11" t="s">
         <v>4</v>
       </c>
@@ -7753,7 +7754,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="448" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B448" s="11" t="s">
         <v>4</v>
       </c>
@@ -7768,7 +7769,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="449" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B449" s="11" t="s">
         <v>4</v>
       </c>
@@ -7783,7 +7784,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="450" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B450" s="11" t="s">
         <v>4</v>
       </c>
@@ -7798,7 +7799,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="451" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B451" s="11" t="s">
         <v>4</v>
       </c>
@@ -7813,7 +7814,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="452" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B452" s="11" t="s">
         <v>4</v>
       </c>
@@ -7828,7 +7829,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="453" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B453" s="11" t="s">
         <v>4</v>
       </c>
@@ -7843,7 +7844,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="454" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B454" s="11" t="s">
         <v>4</v>
       </c>
@@ -7858,7 +7859,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="455" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B455" s="11" t="s">
         <v>4</v>
       </c>
@@ -7873,7 +7874,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="456" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B456" s="11" t="s">
         <v>4</v>
       </c>
@@ -7888,7 +7889,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="457" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B457" s="11" t="s">
         <v>4</v>
       </c>
@@ -7903,7 +7904,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="458" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B458" s="11" t="s">
         <v>4</v>
       </c>
@@ -7918,7 +7919,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="459" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B459" s="11" t="s">
         <v>24</v>
       </c>
@@ -7933,7 +7934,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="460" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B460" s="11" t="s">
         <v>24</v>
       </c>
@@ -7948,7 +7949,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="461" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B461" s="11" t="s">
         <v>24</v>
       </c>
@@ -7963,7 +7964,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="462" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B462" s="11" t="s">
         <v>24</v>
       </c>
@@ -7978,7 +7979,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="463" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B463" s="11" t="s">
         <v>24</v>
       </c>
@@ -7993,7 +7994,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="464" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B464" s="11" t="s">
         <v>24</v>
       </c>
@@ -8008,7 +8009,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="465" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B465" s="11" t="s">
         <v>24</v>
       </c>
@@ -8023,7 +8024,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="466" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B466" s="11" t="s">
         <v>24</v>
       </c>
@@ -8038,7 +8039,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="467" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B467" s="11" t="s">
         <v>24</v>
       </c>
@@ -8053,7 +8054,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="468" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B468" s="11" t="s">
         <v>24</v>
       </c>
@@ -8068,7 +8069,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="469" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B469" s="11" t="s">
         <v>24</v>
       </c>
@@ -8083,7 +8084,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="470" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B470" s="11" t="s">
         <v>24</v>
       </c>
@@ -8098,7 +8099,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="471" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B471" s="11" t="s">
         <v>24</v>
       </c>
@@ -8113,7 +8114,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="472" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B472" s="11" t="s">
         <v>24</v>
       </c>
@@ -8128,7 +8129,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="473" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B473" s="11" t="s">
         <v>24</v>
       </c>
@@ -8143,7 +8144,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="474" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B474" s="11" t="s">
         <v>24</v>
       </c>
@@ -8158,7 +8159,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="475" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B475" s="11" t="s">
         <v>24</v>
       </c>
@@ -8173,7 +8174,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="476" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B476" s="11" t="s">
         <v>24</v>
       </c>
@@ -8188,7 +8189,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="477" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B477" s="11" t="s">
         <v>24</v>
       </c>
@@ -8203,7 +8204,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="478" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B478" s="11" t="s">
         <v>24</v>
       </c>
@@ -8218,7 +8219,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="479" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B479" s="11" t="s">
         <v>24</v>
       </c>
@@ -8233,7 +8234,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="480" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B480" s="11" t="s">
         <v>24</v>
       </c>
@@ -8248,7 +8249,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="481" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B481" s="11" t="s">
         <v>24</v>
       </c>
@@ -8263,7 +8264,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="482" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B482" s="11" t="s">
         <v>24</v>
       </c>
@@ -8278,7 +8279,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="483" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B483" s="11" t="s">
         <v>24</v>
       </c>
@@ -8293,7 +8294,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="484" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B484" s="11" t="s">
         <v>24</v>
       </c>
@@ -8308,7 +8309,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="485" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B485" s="11" t="s">
         <v>24</v>
       </c>
@@ -8323,7 +8324,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="486" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B486" s="11" t="s">
         <v>24</v>
       </c>
@@ -8338,7 +8339,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="487" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B487" s="11" t="s">
         <v>24</v>
       </c>
@@ -8353,7 +8354,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="488" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B488" s="11" t="s">
         <v>24</v>
       </c>
@@ -8368,7 +8369,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="489" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B489" s="11" t="s">
         <v>24</v>
       </c>
@@ -8383,7 +8384,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="490" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B490" s="11" t="s">
         <v>24</v>
       </c>
@@ -8398,7 +8399,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="491" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B491" s="11" t="s">
         <v>24</v>
       </c>
@@ -8413,7 +8414,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="492" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B492" s="11" t="s">
         <v>24</v>
       </c>
@@ -8428,7 +8429,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="493" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B493" s="11" t="s">
         <v>24</v>
       </c>
@@ -8443,7 +8444,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="494" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B494" s="11" t="s">
         <v>24</v>
       </c>
@@ -8458,7 +8459,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="495" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B495" s="11" t="s">
         <v>24</v>
       </c>
@@ -8473,7 +8474,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="496" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B496" s="11" t="s">
         <v>24</v>
       </c>
@@ -8488,7 +8489,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="497" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B497" s="11" t="s">
         <v>24</v>
       </c>
@@ -8503,7 +8504,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="498" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B498" s="11" t="s">
         <v>24</v>
       </c>
@@ -8518,7 +8519,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="499" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B499" s="11" t="s">
         <v>24</v>
       </c>
@@ -8533,7 +8534,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="500" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B500" s="11" t="s">
         <v>24</v>
       </c>
@@ -8548,7 +8549,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="501" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B501" s="11" t="s">
         <v>24</v>
       </c>
@@ -8563,7 +8564,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="502" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B502" s="11" t="s">
         <v>24</v>
       </c>
@@ -8578,7 +8579,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="503" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B503" s="11" t="s">
         <v>25</v>
       </c>
@@ -8593,7 +8594,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="504" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B504" s="11" t="s">
         <v>25</v>
       </c>
@@ -8608,7 +8609,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="505" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B505" s="11" t="s">
         <v>25</v>
       </c>
@@ -8623,7 +8624,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="506" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B506" s="11" t="s">
         <v>25</v>
       </c>
@@ -8638,7 +8639,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="507" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B507" s="11" t="s">
         <v>25</v>
       </c>
@@ -8653,7 +8654,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="508" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B508" s="11" t="s">
         <v>25</v>
       </c>
@@ -8668,7 +8669,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="509" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B509" s="11" t="s">
         <v>25</v>
       </c>
@@ -8683,7 +8684,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="510" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B510" s="11" t="s">
         <v>25</v>
       </c>
@@ -8698,7 +8699,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="511" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B511" s="11" t="s">
         <v>25</v>
       </c>
@@ -8713,7 +8714,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="512" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B512" s="11" t="s">
         <v>25</v>
       </c>
@@ -8728,7 +8729,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="513" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B513" s="11" t="s">
         <v>25</v>
       </c>
@@ -8743,7 +8744,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="514" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B514" s="11" t="s">
         <v>25</v>
       </c>
@@ -8758,7 +8759,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="515" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B515" s="11" t="s">
         <v>25</v>
       </c>
@@ -8773,7 +8774,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="516" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B516" s="11" t="s">
         <v>25</v>
       </c>
@@ -8788,7 +8789,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="517" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B517" s="11" t="s">
         <v>25</v>
       </c>
@@ -8803,7 +8804,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="518" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B518" s="11" t="s">
         <v>25</v>
       </c>
@@ -8818,7 +8819,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="519" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B519" s="11" t="s">
         <v>25</v>
       </c>
@@ -8833,7 +8834,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="520" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B520" s="11" t="s">
         <v>25</v>
       </c>
@@ -8848,7 +8849,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="521" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B521" s="11" t="s">
         <v>25</v>
       </c>
@@ -8863,7 +8864,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="522" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B522" s="11" t="s">
         <v>25</v>
       </c>
@@ -8878,7 +8879,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="523" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B523" s="11" t="s">
         <v>25</v>
       </c>
@@ -8893,7 +8894,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="524" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B524" s="11" t="s">
         <v>5</v>
       </c>
@@ -8908,7 +8909,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="525" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B525" s="11" t="s">
         <v>5</v>
       </c>
@@ -8923,7 +8924,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="526" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B526" s="11" t="s">
         <v>5</v>
       </c>
@@ -8938,7 +8939,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="527" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B527" s="11" t="s">
         <v>5</v>
       </c>
@@ -8953,7 +8954,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="528" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B528" s="11" t="s">
         <v>28</v>
       </c>
@@ -8968,7 +8969,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="529" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B529" s="11" t="s">
         <v>28</v>
       </c>
@@ -8983,7 +8984,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="530" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B530" s="11" t="s">
         <v>28</v>
       </c>
@@ -8998,7 +8999,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="531" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B531" s="11" t="s">
         <v>28</v>
       </c>
@@ -9013,7 +9014,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="532" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B532" s="11" t="s">
         <v>17</v>
       </c>
@@ -9028,7 +9029,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="533" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B533" s="11" t="s">
         <v>17</v>
       </c>
@@ -9043,7 +9044,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="534" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B534" s="11" t="s">
         <v>17</v>
       </c>
@@ -9058,7 +9059,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="535" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B535" s="11" t="s">
         <v>17</v>
       </c>
@@ -9073,7 +9074,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="536" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B536" s="11" t="s">
         <v>17</v>
       </c>
@@ -9088,7 +9089,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="537" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B537" s="11" t="s">
         <v>17</v>
       </c>
@@ -9103,7 +9104,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="538" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B538" s="11" t="s">
         <v>17</v>
       </c>
@@ -9118,7 +9119,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="539" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B539" s="11" t="s">
         <v>22</v>
       </c>
@@ -9133,7 +9134,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="540" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B540" s="11" t="s">
         <v>22</v>
       </c>
@@ -9148,7 +9149,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="541" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B541" s="11" t="s">
         <v>22</v>
       </c>
@@ -9163,7 +9164,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="542" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B542" s="11" t="s">
         <v>22</v>
       </c>
@@ -9178,7 +9179,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="543" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B543" s="27" t="s">
         <v>21</v>
       </c>
@@ -9193,7 +9194,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="544" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B544" s="27" t="s">
         <v>21</v>
       </c>
@@ -9208,7 +9209,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="545" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B545" s="27" t="s">
         <v>21</v>
       </c>
@@ -9223,7 +9224,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="546" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B546" s="27" t="s">
         <v>21</v>
       </c>
@@ -9238,7 +9239,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="547" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B547" s="27" t="s">
         <v>21</v>
       </c>
@@ -9253,7 +9254,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="548" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B548" s="27" t="s">
         <v>21</v>
       </c>
@@ -9268,7 +9269,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="549" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B549" s="27" t="s">
         <v>21</v>
       </c>
@@ -9283,7 +9284,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="550" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B550" s="27" t="s">
         <v>21</v>
       </c>
@@ -9298,7 +9299,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="551" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B551" s="27" t="s">
         <v>21</v>
       </c>
@@ -9313,7 +9314,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="552" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B552" s="27" t="s">
         <v>21</v>
       </c>
@@ -9328,7 +9329,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="553" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B553" s="27" t="s">
         <v>21</v>
       </c>
@@ -9343,7 +9344,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="554" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B554" s="27" t="s">
         <v>21</v>
       </c>
@@ -9358,7 +9359,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="555" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B555" s="27" t="s">
         <v>21</v>
       </c>
@@ -9373,7 +9374,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="556" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B556" s="27" t="s">
         <v>21</v>
       </c>
@@ -9388,7 +9389,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="557" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B557" s="27" t="s">
         <v>21</v>
       </c>
@@ -9403,7 +9404,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="558" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B558" s="27" t="s">
         <v>21</v>
       </c>
@@ -9418,7 +9419,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="559" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B559" s="27" t="s">
         <v>21</v>
       </c>
@@ -9433,7 +9434,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="560" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B560" s="27" t="s">
         <v>21</v>
       </c>
@@ -9448,7 +9449,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="561" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B561" s="11" t="s">
         <v>21</v>
       </c>
@@ -9463,7 +9464,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="562" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B562" s="11" t="s">
         <v>21</v>
       </c>
@@ -9478,7 +9479,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="563" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B563" s="11" t="s">
         <v>9</v>
       </c>
@@ -9493,7 +9494,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="564" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B564" s="11" t="s">
         <v>9</v>
       </c>
@@ -9508,7 +9509,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="565" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B565" s="11" t="s">
         <v>9</v>
       </c>
@@ -9523,7 +9524,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="566" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B566" s="11" t="s">
         <v>9</v>
       </c>
@@ -9538,7 +9539,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="567" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B567" s="11" t="s">
         <v>9</v>
       </c>
@@ -9553,7 +9554,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="568" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B568" s="11" t="s">
         <v>9</v>
       </c>
@@ -9568,7 +9569,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="569" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B569" s="11" t="s">
         <v>37</v>
       </c>
@@ -9583,7 +9584,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="570" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B570" s="11" t="s">
         <v>37</v>
       </c>
@@ -9598,7 +9599,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="571" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B571" s="11" t="s">
         <v>37</v>
       </c>
@@ -9613,7 +9614,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="572" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B572" s="11" t="s">
         <v>37</v>
       </c>
@@ -9628,7 +9629,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="573" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B573" s="11" t="s">
         <v>37</v>
       </c>
@@ -9643,7 +9644,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="574" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B574" s="11" t="s">
         <v>37</v>
       </c>
@@ -9658,7 +9659,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="575" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B575" s="11" t="s">
         <v>37</v>
       </c>
@@ -9673,7 +9674,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="576" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B576" s="11" t="s">
         <v>7</v>
       </c>
@@ -9688,7 +9689,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="577" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B577" s="11" t="s">
         <v>7</v>
       </c>
@@ -9703,7 +9704,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="578" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B578" s="11" t="s">
         <v>7</v>
       </c>
@@ -9718,7 +9719,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="579" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B579" s="11" t="s">
         <v>7</v>
       </c>
@@ -9733,7 +9734,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="580" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B580" s="11" t="s">
         <v>7</v>
       </c>
@@ -9748,7 +9749,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="581" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B581" s="11" t="s">
         <v>7</v>
       </c>
@@ -9763,7 +9764,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="582" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B582" s="11" t="s">
         <v>7</v>
       </c>
@@ -9778,7 +9779,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="583" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B583" s="11" t="s">
         <v>7</v>
       </c>
@@ -9793,7 +9794,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="584" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B584" s="11" t="s">
         <v>83</v>
       </c>
@@ -9808,7 +9809,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="585" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B585" s="11" t="s">
         <v>83</v>
       </c>
@@ -9823,7 +9824,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="586" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B586" s="11" t="s">
         <v>83</v>
       </c>
@@ -9838,7 +9839,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="587" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B587" s="11" t="s">
         <v>31</v>
       </c>
@@ -9853,7 +9854,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="588" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B588" s="11" t="s">
         <v>8</v>
       </c>
@@ -9868,7 +9869,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="589" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B589" s="11" t="s">
         <v>8</v>
       </c>
@@ -9883,7 +9884,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="590" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B590" s="11" t="s">
         <v>8</v>
       </c>
@@ -9898,7 +9899,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="591" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B591" s="11" t="s">
         <v>3</v>
       </c>
@@ -9913,7 +9914,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="592" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B592" s="11" t="s">
         <v>3</v>
       </c>
@@ -9928,7 +9929,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="593" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B593" s="11" t="s">
         <v>3</v>
       </c>
@@ -9943,7 +9944,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="594" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B594" s="11" t="s">
         <v>3</v>
       </c>
@@ -9958,7 +9959,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="595" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B595" s="11" t="s">
         <v>3</v>
       </c>
@@ -9973,7 +9974,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="596" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B596" s="11" t="s">
         <v>3</v>
       </c>
@@ -9988,7 +9989,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="597" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B597" s="11" t="s">
         <v>19</v>
       </c>
@@ -10003,7 +10004,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="598" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B598" s="11" t="s">
         <v>30</v>
       </c>
@@ -10018,7 +10019,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="599" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B599" s="11" t="s">
         <v>30</v>
       </c>
@@ -10033,7 +10034,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="600" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B600" s="11" t="s">
         <v>30</v>
       </c>
@@ -10048,7 +10049,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="601" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B601" s="11" t="s">
         <v>32</v>
       </c>
@@ -10063,7 +10064,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="602" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B602" s="11" t="s">
         <v>32</v>
       </c>
@@ -10078,7 +10079,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="603" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B603" s="11" t="s">
         <v>32</v>
       </c>
@@ -10093,7 +10094,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="604" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B604" s="11" t="s">
         <v>32</v>
       </c>
@@ -10108,7 +10109,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="605" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B605" s="11" t="s">
         <v>15</v>
       </c>
@@ -10123,7 +10124,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="606" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B606" s="11" t="s">
         <v>15</v>
       </c>
@@ -10138,7 +10139,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="607" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B607" s="11" t="s">
         <v>15</v>
       </c>
@@ -10153,7 +10154,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="608" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B608" s="11" t="s">
         <v>15</v>
       </c>
@@ -10168,7 +10169,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="609" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B609" s="11" t="s">
         <v>20</v>
       </c>
@@ -10183,7 +10184,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="610" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B610" s="11" t="s">
         <v>20</v>
       </c>
@@ -10196,7 +10197,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="611" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B611" s="11" t="s">
         <v>20</v>
       </c>
@@ -10211,7 +10212,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="612" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B612" s="11" t="s">
         <v>20</v>
       </c>
@@ -10226,7 +10227,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="613" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B613" s="11" t="s">
         <v>20</v>
       </c>
@@ -10241,7 +10242,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="614" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B614" s="11" t="s">
         <v>20</v>
       </c>
@@ -10256,7 +10257,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="615" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B615" s="11" t="s">
         <v>18</v>
       </c>
@@ -10271,7 +10272,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="616" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B616" s="11" t="s">
         <v>18</v>
       </c>
@@ -10286,7 +10287,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="617" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B617" s="11" t="s">
         <v>18</v>
       </c>
@@ -10301,7 +10302,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="618" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B618" s="11" t="s">
         <v>18</v>
       </c>
@@ -10316,7 +10317,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="619" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B619" s="11" t="s">
         <v>18</v>
       </c>
@@ -10331,7 +10332,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="620" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B620" s="11" t="s">
         <v>13</v>
       </c>
@@ -10346,7 +10347,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="621" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B621" s="11" t="s">
         <v>13</v>
       </c>
@@ -10361,7 +10362,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="622" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B622" s="11" t="s">
         <v>11</v>
       </c>
@@ -10376,7 +10377,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="623" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B623" s="11" t="s">
         <v>11</v>
       </c>
@@ -10391,7 +10392,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="624" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B624" s="11" t="s">
         <v>11</v>
       </c>
@@ -10406,7 +10407,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="625" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B625" s="11" t="s">
         <v>23</v>
       </c>
@@ -10421,7 +10422,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="626" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B626" s="11" t="s">
         <v>4</v>
       </c>
@@ -10436,7 +10437,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="627" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B627" s="11" t="s">
         <v>4</v>
       </c>
@@ -10451,7 +10452,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="628" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B628" s="11" t="s">
         <v>24</v>
       </c>
@@ -10466,7 +10467,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="629" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B629" s="11" t="s">
         <v>24</v>
       </c>
@@ -10481,7 +10482,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="630" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B630" s="11" t="s">
         <v>24</v>
       </c>
@@ -10496,7 +10497,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="631" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B631" s="11" t="s">
         <v>27</v>
       </c>
@@ -10511,7 +10512,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="632" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B632" s="11" t="s">
         <v>25</v>
       </c>
@@ -10526,7 +10527,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="633" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B633" s="11" t="s">
         <v>5</v>
       </c>
@@ -10541,7 +10542,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="634" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B634" s="11" t="s">
         <v>5</v>
       </c>
@@ -10556,7 +10557,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="635" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B635" s="11" t="s">
         <v>5</v>
       </c>
@@ -10571,7 +10572,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="636" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B636" s="11" t="s">
         <v>28</v>
       </c>
@@ -10586,7 +10587,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="637" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B637" s="11" t="s">
         <v>28</v>
       </c>
@@ -10601,7 +10602,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="638" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B638" s="15" t="s">
         <v>28</v>
       </c>
@@ -10616,7 +10617,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="639" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B639" s="11" t="s">
         <v>28</v>
       </c>
@@ -10631,7 +10632,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="640" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B640" s="11" t="s">
         <v>28</v>
       </c>
@@ -10646,7 +10647,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="641" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B641" s="11" t="s">
         <v>28</v>
       </c>
@@ -10661,7 +10662,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="642" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B642" s="11" t="s">
         <v>28</v>
       </c>
@@ -10676,7 +10677,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="643" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B643" s="11" t="s">
         <v>28</v>
       </c>
@@ -10691,7 +10692,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="644" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B644" s="11" t="s">
         <v>17</v>
       </c>
@@ -10706,7 +10707,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="645" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B645" s="11" t="s">
         <v>17</v>
       </c>
@@ -10721,7 +10722,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="646" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B646" s="11" t="s">
         <v>29</v>
       </c>
@@ -10736,7 +10737,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="647" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B647" s="11" t="s">
         <v>21</v>
       </c>
@@ -10751,7 +10752,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="648" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B648" s="11" t="s">
         <v>21</v>
       </c>
@@ -10766,7 +10767,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="649" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B649" s="11" t="s">
         <v>21</v>
       </c>
@@ -10781,7 +10782,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="650" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B650" s="11" t="s">
         <v>9</v>
       </c>
@@ -10796,7 +10797,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="651" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B651" s="11" t="s">
         <v>7</v>
       </c>
@@ -10811,7 +10812,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="652" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B652" s="11" t="s">
         <v>7</v>
       </c>
@@ -10826,7 +10827,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="653" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B653" s="11" t="s">
         <v>7</v>
       </c>
@@ -10841,7 +10842,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="654" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B654" s="11" t="s">
         <v>14</v>
       </c>
@@ -10856,7 +10857,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="655" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="655" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B655" s="11" t="s">
         <v>31</v>
       </c>
@@ -10871,7 +10872,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="656" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B656" s="11" t="s">
         <v>8</v>
       </c>
@@ -10886,7 +10887,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="657" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B657" s="11" t="s">
         <v>3</v>
       </c>
@@ -10901,7 +10902,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="658" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B658" s="11" t="s">
         <v>3</v>
       </c>
@@ -10916,7 +10917,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="659" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B659" s="11" t="s">
         <v>3</v>
       </c>
@@ -10931,7 +10932,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="660" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B660" s="11" t="s">
         <v>19</v>
       </c>
@@ -10946,7 +10947,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="661" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B661" s="11" t="s">
         <v>30</v>
       </c>
@@ -10961,7 +10962,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="662" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B662" s="11" t="s">
         <v>32</v>
       </c>
@@ -10976,7 +10977,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="663" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B663" s="11" t="s">
         <v>32</v>
       </c>
@@ -10991,7 +10992,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="664" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B664" s="11" t="s">
         <v>32</v>
       </c>
@@ -11006,7 +11007,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="665" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B665" s="11" t="s">
         <v>32</v>
       </c>
@@ -11021,7 +11022,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="666" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B666" s="11" t="s">
         <v>32</v>
       </c>
@@ -11036,7 +11037,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="667" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B667" s="11" t="s">
         <v>32</v>
       </c>
@@ -11051,7 +11052,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="668" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B668" s="11" t="s">
         <v>32</v>
       </c>
@@ -11066,7 +11067,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="669" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B669" s="11" t="s">
         <v>32</v>
       </c>
@@ -11081,7 +11082,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="670" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B670" s="11" t="s">
         <v>32</v>
       </c>
@@ -11096,7 +11097,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="671" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B671" s="11" t="s">
         <v>39</v>
       </c>
@@ -11111,7 +11112,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="672" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B672" s="11" t="s">
         <v>15</v>
       </c>
@@ -11126,7 +11127,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="673" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="673" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B673" s="11" t="s">
         <v>6</v>
       </c>
@@ -11141,7 +11142,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="674" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="674" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B674" s="11" t="s">
         <v>6</v>
       </c>
@@ -11156,7 +11157,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="675" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="675" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B675" s="11" t="s">
         <v>6</v>
       </c>
@@ -11171,7 +11172,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="676" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="676" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B676" s="11" t="s">
         <v>6</v>
       </c>
@@ -11186,7 +11187,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="677" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="677" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B677" s="11" t="s">
         <v>6</v>
       </c>
@@ -11201,7 +11202,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="678" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="678" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B678" s="11" t="s">
         <v>6</v>
       </c>
@@ -11216,7 +11217,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="679" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="679" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B679" s="11" t="s">
         <v>20</v>
       </c>
@@ -11231,7 +11232,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="680" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="680" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B680" s="11" t="s">
         <v>18</v>
       </c>
@@ -11246,7 +11247,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="681" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="681" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B681" s="11" t="s">
         <v>18</v>
       </c>
@@ -11261,7 +11262,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="682" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="682" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B682" s="11" t="s">
         <v>13</v>
       </c>
@@ -11276,7 +11277,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="683" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="683" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B683" s="11" t="s">
         <v>13</v>
       </c>
@@ -11291,7 +11292,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="684" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="684" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B684" s="11" t="s">
         <v>11</v>
       </c>
@@ -11306,7 +11307,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="685" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="685" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B685" s="11" t="s">
         <v>11</v>
       </c>
@@ -11321,7 +11322,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="686" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="686" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B686" s="11" t="s">
         <v>11</v>
       </c>
@@ -11336,7 +11337,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="687" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="687" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B687" s="11" t="s">
         <v>11</v>
       </c>
@@ -11351,7 +11352,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="688" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="688" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B688" s="11" t="s">
         <v>11</v>
       </c>
@@ -11366,7 +11367,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="689" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="689" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B689" s="11" t="s">
         <v>11</v>
       </c>
@@ -11381,7 +11382,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="690" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="690" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B690" s="11" t="s">
         <v>11</v>
       </c>
@@ -11396,7 +11397,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="691" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="691" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B691" s="11" t="s">
         <v>11</v>
       </c>
@@ -11411,7 +11412,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="692" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="692" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B692" s="11" t="s">
         <v>11</v>
       </c>
@@ -11426,7 +11427,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="693" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="693" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B693" s="11" t="s">
         <v>26</v>
       </c>
@@ -11441,7 +11442,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="694" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="694" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B694" s="11" t="s">
         <v>4</v>
       </c>
@@ -11456,7 +11457,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="695" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="695" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B695" s="11" t="s">
         <v>24</v>
       </c>
@@ -11471,7 +11472,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="696" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="696" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B696" s="11" t="s">
         <v>24</v>
       </c>
@@ -11486,7 +11487,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="697" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="697" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B697" s="11" t="s">
         <v>24</v>
       </c>
@@ -11501,7 +11502,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="698" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="698" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B698" s="11" t="s">
         <v>24</v>
       </c>
@@ -11516,7 +11517,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="699" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="699" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B699" s="11" t="s">
         <v>5</v>
       </c>
@@ -11531,7 +11532,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="700" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="700" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B700" s="11" t="s">
         <v>5</v>
       </c>
@@ -11546,7 +11547,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="701" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="701" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B701" s="11" t="s">
         <v>5</v>
       </c>
@@ -11561,7 +11562,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="702" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="702" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B702" s="11" t="s">
         <v>12</v>
       </c>
@@ -11576,7 +11577,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="703" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="703" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B703" s="11" t="s">
         <v>28</v>
       </c>
@@ -11591,7 +11592,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="704" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="704" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B704" s="11" t="s">
         <v>98</v>
       </c>
@@ -11606,7 +11607,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="705" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="705" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B705" s="11" t="s">
         <v>29</v>
       </c>
@@ -11621,7 +11622,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="706" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="706" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B706" s="11" t="s">
         <v>29</v>
       </c>
@@ -11636,7 +11637,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="707" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="707" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B707" s="11" t="s">
         <v>29</v>
       </c>
@@ -11651,7 +11652,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="708" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="708" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B708" s="11" t="s">
         <v>29</v>
       </c>
@@ -11666,7 +11667,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="709" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="709" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B709" s="11" t="s">
         <v>29</v>
       </c>
@@ -11681,7 +11682,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="710" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="710" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B710" s="11" t="s">
         <v>29</v>
       </c>
@@ -11696,7 +11697,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="711" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="711" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B711" s="11" t="s">
         <v>22</v>
       </c>
@@ -11711,7 +11712,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="712" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="712" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B712" s="11" t="s">
         <v>21</v>
       </c>
@@ -11726,7 +11727,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="713" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="713" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B713" s="11" t="s">
         <v>21</v>
       </c>
@@ -11741,7 +11742,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="714" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="714" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B714" s="11" t="s">
         <v>9</v>
       </c>
@@ -11756,7 +11757,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="715" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="715" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B715" s="11" t="s">
         <v>9</v>
       </c>
@@ -11771,7 +11772,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="716" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="716" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B716" s="11" t="s">
         <v>7</v>
       </c>
@@ -11786,7 +11787,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="717" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="717" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B717" s="11" t="s">
         <v>7</v>
       </c>
@@ -11801,7 +11802,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="718" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="718" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B718" s="11" t="s">
         <v>93</v>
       </c>
@@ -11816,7 +11817,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="719" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="719" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B719" s="11" t="s">
         <v>14</v>
       </c>
@@ -11831,7 +11832,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="720" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="720" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B720" s="11" t="s">
         <v>14</v>
       </c>
@@ -11846,7 +11847,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="721" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="721" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B721" s="11" t="s">
         <v>14</v>
       </c>
@@ -11861,7 +11862,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="722" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="722" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B722" s="11" t="s">
         <v>103</v>
       </c>
@@ -11876,7 +11877,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="723" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="723" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B723" s="11" t="s">
         <v>8</v>
       </c>
@@ -11891,7 +11892,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="724" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="724" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B724" s="11" t="s">
         <v>3</v>
       </c>
@@ -11906,7 +11907,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="725" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="725" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B725" s="11" t="s">
         <v>3</v>
       </c>
@@ -11921,7 +11922,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="726" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="726" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B726" s="11" t="s">
         <v>19</v>
       </c>
@@ -11936,7 +11937,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="727" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="727" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B727" s="11" t="s">
         <v>19</v>
       </c>
@@ -11951,7 +11952,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="728" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="728" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B728" s="11" t="s">
         <v>19</v>
       </c>
@@ -11966,7 +11967,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="729" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="729" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B729" s="11" t="s">
         <v>19</v>
       </c>
@@ -11981,7 +11982,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="730" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="730" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B730" s="11" t="s">
         <v>19</v>
       </c>
@@ -11996,7 +11997,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="731" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="731" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B731" s="11" t="s">
         <v>19</v>
       </c>
@@ -12011,7 +12012,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="732" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="732" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B732" s="11" t="s">
         <v>32</v>
       </c>
@@ -12026,7 +12027,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="733" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="733" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B733" s="11" t="s">
         <v>32</v>
       </c>
@@ -12041,7 +12042,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="734" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="734" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B734" s="11" t="s">
         <v>32</v>
       </c>
@@ -12056,7 +12057,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="735" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="735" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B735" s="11" t="s">
         <v>32</v>
       </c>
@@ -12071,7 +12072,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="736" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="736" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B736" s="11" t="s">
         <v>32</v>
       </c>
@@ -12086,7 +12087,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="737" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="737" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B737" s="11" t="s">
         <v>32</v>
       </c>
@@ -12101,7 +12102,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="738" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="738" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B738" s="11" t="s">
         <v>32</v>
       </c>
@@ -12116,7 +12117,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="739" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="739" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B739" s="11" t="s">
         <v>15</v>
       </c>
@@ -12131,7 +12132,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="740" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="740" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B740" s="11" t="s">
         <v>15</v>
       </c>
@@ -12146,7 +12147,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="741" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="741" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B741" s="11" t="s">
         <v>15</v>
       </c>
@@ -12161,7 +12162,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="742" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="742" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B742" s="11" t="s">
         <v>15</v>
       </c>
@@ -12176,7 +12177,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="743" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="743" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B743" s="11" t="s">
         <v>6</v>
       </c>
@@ -12191,7 +12192,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="744" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="744" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B744" s="11" t="s">
         <v>6</v>
       </c>
@@ -12206,7 +12207,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="745" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="745" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B745" s="11" t="s">
         <v>6</v>
       </c>
@@ -12221,7 +12222,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="746" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="746" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B746" s="11" t="s">
         <v>6</v>
       </c>
@@ -12236,7 +12237,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="747" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="747" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B747" s="11" t="s">
         <v>6</v>
       </c>
@@ -12251,7 +12252,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="748" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="748" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B748" s="11" t="s">
         <v>6</v>
       </c>
@@ -12266,7 +12267,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="749" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="749" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B749" s="11" t="s">
         <v>6</v>
       </c>
@@ -12281,7 +12282,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="750" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="750" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B750" s="11" t="s">
         <v>20</v>
       </c>
@@ -12296,7 +12297,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="751" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="751" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B751" s="11" t="s">
         <v>20</v>
       </c>
@@ -12311,7 +12312,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="752" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="752" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B752" s="11" t="s">
         <v>18</v>
       </c>
@@ -12326,7 +12327,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="753" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="753" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B753" s="11" t="s">
         <v>18</v>
       </c>
@@ -12341,7 +12342,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="754" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="754" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B754" s="11" t="s">
         <v>18</v>
       </c>
@@ -12356,7 +12357,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="755" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="755" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B755" s="11" t="s">
         <v>18</v>
       </c>
@@ -12371,7 +12372,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="756" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="756" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B756" s="11" t="s">
         <v>18</v>
       </c>
@@ -12386,7 +12387,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="757" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="757" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B757" s="11" t="s">
         <v>18</v>
       </c>
@@ -12401,7 +12402,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="758" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="758" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B758" s="11" t="s">
         <v>18</v>
       </c>
@@ -12416,7 +12417,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="759" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="759" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B759" s="11" t="s">
         <v>13</v>
       </c>
@@ -12431,7 +12432,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="760" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="760" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B760" s="11" t="s">
         <v>13</v>
       </c>
@@ -12446,7 +12447,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="761" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="761" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B761" s="11" t="s">
         <v>13</v>
       </c>
@@ -12461,7 +12462,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="762" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="762" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B762" s="11" t="s">
         <v>13</v>
       </c>
@@ -12476,7 +12477,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="763" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="763" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B763" s="11" t="s">
         <v>11</v>
       </c>
@@ -12491,7 +12492,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="764" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="764" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B764" s="11" t="s">
         <v>11</v>
       </c>
@@ -12506,7 +12507,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="765" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="765" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B765" s="11" t="s">
         <v>11</v>
       </c>
@@ -12521,7 +12522,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="766" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="766" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B766" s="11" t="s">
         <v>11</v>
       </c>
@@ -12536,7 +12537,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="767" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="767" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B767" s="11" t="s">
         <v>26</v>
       </c>
@@ -12551,7 +12552,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="768" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="768" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B768" s="11" t="s">
         <v>26</v>
       </c>
@@ -12566,7 +12567,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="769" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="769" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B769" s="11" t="s">
         <v>26</v>
       </c>
@@ -12581,7 +12582,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="770" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="770" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B770" s="11" t="s">
         <v>26</v>
       </c>
@@ -12596,7 +12597,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="771" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="771" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B771" s="11" t="s">
         <v>23</v>
       </c>
@@ -12611,7 +12612,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="772" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="772" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B772" s="11" t="s">
         <v>23</v>
       </c>
@@ -12626,7 +12627,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="773" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="773" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B773" s="11" t="s">
         <v>4</v>
       </c>
@@ -12641,7 +12642,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="774" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="774" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B774" s="11" t="s">
         <v>4</v>
       </c>
@@ -12656,7 +12657,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="775" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="775" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B775" s="11" t="s">
         <v>4</v>
       </c>
@@ -12671,7 +12672,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="776" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="776" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B776" s="11" t="s">
         <v>4</v>
       </c>
@@ -12686,7 +12687,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="777" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="777" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B777" s="11" t="s">
         <v>4</v>
       </c>
@@ -12701,7 +12702,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="778" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="778" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B778" s="11" t="s">
         <v>4</v>
       </c>
@@ -12716,7 +12717,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="779" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="779" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B779" s="11" t="s">
         <v>4</v>
       </c>
@@ -12731,7 +12732,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="780" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="780" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B780" s="11" t="s">
         <v>4</v>
       </c>
@@ -12746,7 +12747,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="781" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="781" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B781" s="11" t="s">
         <v>24</v>
       </c>
@@ -12761,7 +12762,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="782" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="782" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B782" s="11" t="s">
         <v>24</v>
       </c>
@@ -12776,7 +12777,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="783" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="783" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B783" s="11" t="s">
         <v>24</v>
       </c>
@@ -12791,7 +12792,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="784" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="784" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B784" s="11" t="s">
         <v>24</v>
       </c>
@@ -12806,7 +12807,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="785" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="785" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B785" s="11" t="s">
         <v>24</v>
       </c>
@@ -12821,7 +12822,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="786" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="786" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B786" s="11" t="s">
         <v>24</v>
       </c>
@@ -12836,7 +12837,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="787" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="787" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B787" s="11" t="s">
         <v>27</v>
       </c>
@@ -12851,7 +12852,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="788" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="788" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B788" s="11" t="s">
         <v>25</v>
       </c>
@@ -12866,7 +12867,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="789" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="789" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B789" s="11" t="s">
         <v>25</v>
       </c>
@@ -12881,7 +12882,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="790" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="790" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B790" s="11" t="s">
         <v>5</v>
       </c>
@@ -12896,7 +12897,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="791" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="791" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B791" s="11" t="s">
         <v>5</v>
       </c>
@@ -12911,7 +12912,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="792" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="792" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B792" s="11" t="s">
         <v>28</v>
       </c>
@@ -12926,7 +12927,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="793" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="793" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B793" s="11" t="s">
         <v>28</v>
       </c>
@@ -12941,7 +12942,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="794" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="794" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B794" s="11" t="s">
         <v>28</v>
       </c>
@@ -12956,7 +12957,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="795" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="795" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B795" s="11" t="s">
         <v>28</v>
       </c>
@@ -12971,7 +12972,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="796" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="796" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B796" s="11" t="s">
         <v>28</v>
       </c>
@@ -12986,7 +12987,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="797" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="797" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B797" s="11" t="s">
         <v>28</v>
       </c>
@@ -13001,7 +13002,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="798" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="798" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B798" s="11" t="s">
         <v>28</v>
       </c>
@@ -13016,7 +13017,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="799" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="799" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B799" s="11" t="s">
         <v>28</v>
       </c>
@@ -13031,7 +13032,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="800" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="800" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B800" s="11" t="s">
         <v>28</v>
       </c>
@@ -13046,7 +13047,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="801" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="801" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B801" s="11" t="s">
         <v>28</v>
       </c>
@@ -13061,7 +13062,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="802" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="802" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B802" s="11" t="s">
         <v>28</v>
       </c>
@@ -13076,7 +13077,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="803" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="803" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B803" s="11" t="s">
         <v>17</v>
       </c>
@@ -13091,7 +13092,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="804" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="804" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B804" s="11" t="s">
         <v>17</v>
       </c>
@@ -13106,7 +13107,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="805" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="805" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B805" s="11" t="s">
         <v>29</v>
       </c>
@@ -13121,7 +13122,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="806" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="806" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B806" s="11" t="s">
         <v>29</v>
       </c>
@@ -13136,7 +13137,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="807" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="807" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B807" s="11" t="s">
         <v>29</v>
       </c>
@@ -13151,7 +13152,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="808" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="808" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B808" s="11" t="s">
         <v>29</v>
       </c>
@@ -13166,7 +13167,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="809" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="809" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B809" s="11" t="s">
         <v>22</v>
       </c>
@@ -13181,7 +13182,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="810" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="810" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B810" s="11" t="s">
         <v>22</v>
       </c>
@@ -13196,7 +13197,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="811" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="811" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B811" s="11" t="s">
         <v>22</v>
       </c>
@@ -13211,7 +13212,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="812" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="812" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B812" s="11" t="s">
         <v>22</v>
       </c>
@@ -13226,7 +13227,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="813" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="813" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B813" s="11" t="s">
         <v>22</v>
       </c>
@@ -13241,7 +13242,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="814" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="814" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B814" s="11" t="s">
         <v>22</v>
       </c>
@@ -13256,7 +13257,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="815" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="815" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B815" s="11" t="s">
         <v>22</v>
       </c>
@@ -13271,7 +13272,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="816" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="816" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B816" s="11" t="s">
         <v>22</v>
       </c>
@@ -13286,7 +13287,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="817" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="817" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B817" s="11" t="s">
         <v>22</v>
       </c>
@@ -13301,7 +13302,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="818" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="818" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B818" s="11" t="s">
         <v>22</v>
       </c>
@@ -13316,7 +13317,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="819" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="819" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B819" s="11" t="s">
         <v>22</v>
       </c>
@@ -13331,7 +13332,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="820" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="820" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B820" s="11" t="s">
         <v>101</v>
       </c>
@@ -13346,7 +13347,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="821" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="821" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B821" s="11" t="s">
         <v>21</v>
       </c>
@@ -13361,7 +13362,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="822" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="822" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B822" s="11" t="s">
         <v>21</v>
       </c>
@@ -13376,7 +13377,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="823" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="823" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B823" s="11" t="s">
         <v>21</v>
       </c>
@@ -13391,7 +13392,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="824" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="824" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B824" s="11" t="s">
         <v>9</v>
       </c>
@@ -13406,7 +13407,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="825" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="825" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B825" s="11" t="s">
         <v>9</v>
       </c>
@@ -13421,7 +13422,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="826" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="826" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B826" s="11" t="s">
         <v>7</v>
       </c>
@@ -13436,7 +13437,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="827" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="827" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B827" s="11" t="s">
         <v>7</v>
       </c>
@@ -13451,7 +13452,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="828" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="828" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B828" s="11" t="s">
         <v>7</v>
       </c>
@@ -13466,7 +13467,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="829" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="829" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B829" s="11" t="s">
         <v>7</v>
       </c>
@@ -13481,7 +13482,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="830" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="830" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B830" s="11" t="s">
         <v>14</v>
       </c>
@@ -13496,7 +13497,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="831" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="831" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B831" s="11" t="s">
         <v>14</v>
       </c>
@@ -13511,7 +13512,7 @@
         <v>45901</v>
       </c>
     </row>
-    <row r="832" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="832" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B832" s="11" t="s">
         <v>103</v>
       </c>
@@ -13526,7 +13527,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="833" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="833" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B833" s="11" t="s">
         <v>3</v>
       </c>
@@ -13541,7 +13542,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="834" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="834" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B834" s="11" t="s">
         <v>3</v>
       </c>
@@ -13556,7 +13557,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="835" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="835" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B835" s="11" t="s">
         <v>19</v>
       </c>
@@ -13571,7 +13572,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="836" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="836" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B836" s="11" t="s">
         <v>19</v>
       </c>
@@ -13586,7 +13587,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="837" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="837" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B837" s="11" t="s">
         <v>19</v>
       </c>
@@ -13601,7 +13602,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="838" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="838" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B838" s="11" t="s">
         <v>32</v>
       </c>
@@ -13616,7 +13617,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="839" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="839" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B839" s="11" t="s">
         <v>39</v>
       </c>
@@ -13631,7 +13632,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="840" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="840" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B840" s="11" t="s">
         <v>6</v>
       </c>
@@ -13646,7 +13647,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="841" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="841" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B841" s="11" t="s">
         <v>6</v>
       </c>
@@ -13661,7 +13662,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="842" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="842" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B842" s="11" t="s">
         <v>20</v>
       </c>
@@ -13676,7 +13677,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="843" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="843" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B843" s="15" t="s">
         <v>20</v>
       </c>
@@ -13691,7 +13692,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="844" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="844" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B844" s="11" t="s">
         <v>20</v>
       </c>
@@ -13706,7 +13707,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="845" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="845" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B845" s="11" t="s">
         <v>20</v>
       </c>
@@ -13721,7 +13722,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="846" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="846" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B846" s="11" t="s">
         <v>18</v>
       </c>
@@ -13736,7 +13737,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="847" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="847" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B847" s="11" t="s">
         <v>13</v>
       </c>
@@ -13751,7 +13752,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="848" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="848" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B848" s="11" t="s">
         <v>13</v>
       </c>
@@ -13766,7 +13767,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="849" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="849" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B849" s="11" t="s">
         <v>23</v>
       </c>
@@ -13781,7 +13782,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="850" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="850" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B850" s="11" t="s">
         <v>23</v>
       </c>
@@ -13796,7 +13797,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="851" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="851" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B851" s="11" t="s">
         <v>4</v>
       </c>
@@ -13811,7 +13812,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="852" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="852" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B852" s="11" t="s">
         <v>4</v>
       </c>
@@ -13826,7 +13827,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="853" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="853" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B853" s="11" t="s">
         <v>4</v>
       </c>
@@ -13841,7 +13842,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="854" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="854" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B854" s="11" t="s">
         <v>25</v>
       </c>
@@ -13856,7 +13857,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="855" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="855" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B855" s="11" t="s">
         <v>25</v>
       </c>
@@ -13871,7 +13872,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="856" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="856" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B856" s="11" t="s">
         <v>28</v>
       </c>
@@ -13886,7 +13887,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="857" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="857" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B857" s="11" t="s">
         <v>28</v>
       </c>
@@ -13901,7 +13902,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="858" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="858" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B858" s="11" t="s">
         <v>28</v>
       </c>
@@ -13916,7 +13917,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="859" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="859" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B859" s="11" t="s">
         <v>28</v>
       </c>
@@ -13931,7 +13932,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="860" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="860" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B860" s="11" t="s">
         <v>17</v>
       </c>
@@ -13946,7 +13947,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="861" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="861" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B861" s="11" t="s">
         <v>29</v>
       </c>
@@ -13961,7 +13962,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="862" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="862" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B862" s="11" t="s">
         <v>22</v>
       </c>
@@ -13976,7 +13977,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="863" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="863" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B863" s="11" t="s">
         <v>101</v>
       </c>
@@ -13991,7 +13992,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="864" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="864" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B864" s="11" t="s">
         <v>21</v>
       </c>
@@ -14006,7 +14007,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="865" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="865" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B865" s="11" t="s">
         <v>21</v>
       </c>
@@ -14021,7 +14022,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="866" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="866" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B866" s="11" t="s">
         <v>21</v>
       </c>
@@ -14036,7 +14037,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="867" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="867" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B867" s="11" t="s">
         <v>21</v>
       </c>
@@ -14051,7 +14052,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="868" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="868" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B868" s="11" t="s">
         <v>9</v>
       </c>
@@ -14066,7 +14067,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="869" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="869" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B869" s="11" t="s">
         <v>9</v>
       </c>
@@ -14081,7 +14082,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="870" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="870" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B870" s="11" t="s">
         <v>9</v>
       </c>
@@ -14096,7 +14097,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="871" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="871" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B871" s="11" t="s">
         <v>14</v>
       </c>
@@ -14111,7 +14112,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="872" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="872" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B872" s="11" t="s">
         <v>14</v>
       </c>
@@ -14126,7 +14127,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="873" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="873" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B873" s="11" t="s">
         <v>14</v>
       </c>
@@ -14141,7 +14142,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="874" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="874" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B874" s="11" t="s">
         <v>28</v>
       </c>
@@ -14156,7 +14157,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="875" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="875" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B875" s="11" t="s">
         <v>22</v>
       </c>
@@ -14171,7 +14172,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="876" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="876" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B876" s="11" t="s">
         <v>30</v>
       </c>
@@ -14186,7 +14187,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="877" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="877" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B877" s="11" t="s">
         <v>112</v>
       </c>
@@ -14201,7 +14202,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="878" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="878" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B878" s="11" t="s">
         <v>28</v>
       </c>
@@ -14216,7 +14217,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="879" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="879" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B879" s="11" t="s">
         <v>3</v>
       </c>
@@ -14231,7 +14232,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="880" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="880" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B880" s="11" t="s">
         <v>3</v>
       </c>
@@ -14246,7 +14247,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="881" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="881" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B881" s="11" t="s">
         <v>113</v>
       </c>
@@ -14261,7 +14262,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="882" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="882" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B882" s="11" t="s">
         <v>29</v>
       </c>
@@ -14276,7 +14277,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="883" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="883" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B883" s="11" t="s">
         <v>20</v>
       </c>
@@ -14291,7 +14292,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="884" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="884" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B884" s="11" t="s">
         <v>5</v>
       </c>
@@ -14306,7 +14307,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="885" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="885" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B885" s="11" t="s">
         <v>11</v>
       </c>
@@ -14321,7 +14322,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="886" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="886" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B886" s="11" t="s">
         <v>20</v>
       </c>
@@ -14336,7 +14337,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="887" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="887" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B887" s="11" t="s">
         <v>11</v>
       </c>
@@ -14351,7 +14352,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="888" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="888" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B888" s="11" t="s">
         <v>11</v>
       </c>
@@ -14366,7 +14367,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="889" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="889" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B889" s="11" t="s">
         <v>27</v>
       </c>
@@ -14381,7 +14382,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="890" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="890" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B890" s="11" t="s">
         <v>3</v>
       </c>
@@ -14396,7 +14397,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="891" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="891" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B891" s="11" t="s">
         <v>3</v>
       </c>
@@ -14411,7 +14412,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="892" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="892" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B892" s="11" t="s">
         <v>27</v>
       </c>
@@ -14426,7 +14427,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="893" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="893" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B893" s="11" t="s">
         <v>22</v>
       </c>
@@ -14442,32 +14443,64 @@
       </c>
     </row>
     <row r="894" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B894" s="11"/>
+      <c r="B894" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C894" s="5"/>
-      <c r="D894" s="3"/>
-      <c r="E894" s="12"/>
-      <c r="F894" s="7"/>
+      <c r="D894" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E894" s="12">
+        <v>332.9</v>
+      </c>
+      <c r="F894" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="895" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B895" s="11"/>
+      <c r="B895" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="C895" s="5"/>
-      <c r="D895" s="3"/>
-      <c r="E895" s="12"/>
-      <c r="F895" s="7"/>
+      <c r="D895" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E895" s="12">
+        <v>42</v>
+      </c>
+      <c r="F895" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="896" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B896" s="11"/>
+      <c r="B896" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C896" s="5"/>
-      <c r="D896" s="3"/>
-      <c r="E896" s="12"/>
-      <c r="F896" s="7"/>
+      <c r="D896" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E896" s="12">
+        <v>58.35</v>
+      </c>
+      <c r="F896" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="897" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B897" s="11"/>
+      <c r="B897" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C897" s="5"/>
-      <c r="D897" s="3"/>
-      <c r="E897" s="12"/>
-      <c r="F897" s="7"/>
+      <c r="D897" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E897" s="12">
+        <v>180</v>
+      </c>
+      <c r="F897" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="898" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B898" s="11"/>
@@ -37906,7 +37939,11 @@
       <c r="F4245" s="38"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G4194" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
+  <autoFilter ref="B2:G4194" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G875">
     <sortCondition ref="F3:F875" customList="janeiro,fevereiro,março,abril,maio,junho,julho,agosto,setembro,outubro,novembro,dezembro"/>
   </sortState>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="380" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D476208-1DAD-4259-924C-853928F04D33}"/>
+  <xr:revisionPtr revIDLastSave="384" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8440537-1EF3-4AAF-9038-977A2F4FF466}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="115">
   <si>
     <t>Custo</t>
   </si>
@@ -14503,11 +14503,19 @@
       </c>
     </row>
     <row r="898" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B898" s="11"/>
+      <c r="B898" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C898" s="5"/>
-      <c r="D898" s="3"/>
-      <c r="E898" s="19"/>
-      <c r="F898" s="7"/>
+      <c r="D898" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E898" s="19">
+        <v>310</v>
+      </c>
+      <c r="F898" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="899" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B899" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="551" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A5ED4E6-0AD1-4423-8FFE-BCD989E2C857}"/>
+  <xr:revisionPtr revIDLastSave="700" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E98BBA67-7AE7-4922-95D3-D12C181226CF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="120">
   <si>
     <t>Custo</t>
   </si>
@@ -393,6 +393,12 @@
   </si>
   <si>
     <t>LINHA CARROCERIAS</t>
+  </si>
+  <si>
+    <t>PCD7I11</t>
+  </si>
+  <si>
+    <t>SIDER DIVI</t>
   </si>
 </sst>
 </file>
@@ -15152,291 +15158,619 @@
       </c>
     </row>
     <row r="940" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B940" s="11"/>
+      <c r="B940" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C940" s="5"/>
-      <c r="D940" s="3"/>
-      <c r="E940" s="19"/>
-      <c r="F940" s="7"/>
+      <c r="D940" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E940" s="19">
+        <v>220</v>
+      </c>
+      <c r="F940" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="941" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B941" s="11"/>
+      <c r="B941" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="C941" s="5"/>
-      <c r="D941" s="3"/>
-      <c r="E941" s="19"/>
-      <c r="F941" s="7"/>
+      <c r="D941" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E941" s="19">
+        <v>48</v>
+      </c>
+      <c r="F941" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="942" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B942" s="11"/>
+      <c r="B942" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C942" s="5"/>
-      <c r="D942" s="3"/>
-      <c r="E942" s="19"/>
-      <c r="F942" s="7"/>
+      <c r="D942" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E942" s="19">
+        <v>501.2</v>
+      </c>
+      <c r="F942" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="943" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B943" s="11"/>
+      <c r="B943" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C943" s="5"/>
-      <c r="D943" s="3"/>
-      <c r="E943" s="19"/>
-      <c r="F943" s="7"/>
+      <c r="D943" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E943" s="19">
+        <v>15</v>
+      </c>
+      <c r="F943" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="944" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B944" s="11"/>
+      <c r="B944" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C944" s="5"/>
-      <c r="D944" s="3"/>
-      <c r="E944" s="19"/>
-      <c r="F944" s="7"/>
+      <c r="D944" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E944" s="19">
+        <v>375</v>
+      </c>
+      <c r="F944" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="945" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B945" s="11"/>
+      <c r="B945" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C945" s="5"/>
-      <c r="D945" s="3"/>
-      <c r="E945" s="19"/>
-      <c r="F945" s="7"/>
+      <c r="D945" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E945" s="19">
+        <v>270</v>
+      </c>
+      <c r="F945" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="946" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B946" s="11"/>
+      <c r="B946" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C946" s="5"/>
-      <c r="D946" s="3"/>
-      <c r="E946" s="19"/>
-      <c r="F946" s="7"/>
+      <c r="D946" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E946" s="19">
+        <v>130</v>
+      </c>
+      <c r="F946" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="947" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B947" s="11"/>
+      <c r="B947" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C947" s="5"/>
-      <c r="D947" s="3"/>
-      <c r="E947" s="19"/>
-      <c r="F947" s="7"/>
+      <c r="D947" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E947" s="19">
+        <v>390.01</v>
+      </c>
+      <c r="F947" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="948" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B948" s="11"/>
+      <c r="B948" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C948" s="5"/>
-      <c r="D948" s="3"/>
-      <c r="E948" s="19"/>
-      <c r="F948" s="7"/>
+      <c r="D948" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E948" s="19">
+        <v>3300</v>
+      </c>
+      <c r="F948" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="949" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B949" s="11"/>
+      <c r="B949" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C949" s="5"/>
-      <c r="D949" s="3"/>
-      <c r="E949" s="19"/>
-      <c r="F949" s="7"/>
+      <c r="D949" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E949" s="19">
+        <v>280</v>
+      </c>
+      <c r="F949" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="950" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B950" s="11"/>
+      <c r="B950" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C950" s="5"/>
-      <c r="D950" s="3"/>
-      <c r="E950" s="19"/>
-      <c r="F950" s="7"/>
+      <c r="D950" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E950" s="19">
+        <v>280</v>
+      </c>
+      <c r="F950" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="951" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B951" s="11"/>
+      <c r="B951" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C951" s="5"/>
-      <c r="D951" s="3"/>
-      <c r="E951" s="19"/>
-      <c r="F951" s="7"/>
+      <c r="D951" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E951" s="19">
+        <v>775</v>
+      </c>
+      <c r="F951" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="952" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B952" s="11"/>
+      <c r="B952" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C952" s="5"/>
-      <c r="D952" s="3"/>
-      <c r="E952" s="19"/>
-      <c r="F952" s="7"/>
+      <c r="D952" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E952" s="19">
+        <v>80</v>
+      </c>
+      <c r="F952" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="953" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B953" s="11"/>
+      <c r="B953" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="C953" s="5"/>
-      <c r="D953" s="3"/>
-      <c r="E953" s="19"/>
-      <c r="F953" s="7"/>
+      <c r="D953" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E953" s="19">
+        <v>250</v>
+      </c>
+      <c r="F953" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="954" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B954" s="11"/>
+      <c r="B954" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C954" s="5"/>
-      <c r="D954" s="3"/>
-      <c r="E954" s="19"/>
-      <c r="F954" s="7"/>
+      <c r="D954" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E954" s="19">
+        <v>200</v>
+      </c>
+      <c r="F954" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="955" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B955" s="11"/>
+      <c r="B955" s="11" t="s">
+        <v>118</v>
+      </c>
       <c r="C955" s="5"/>
-      <c r="D955" s="3"/>
-      <c r="E955" s="19"/>
-      <c r="F955" s="7"/>
+      <c r="D955" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E955" s="19">
+        <v>609.75</v>
+      </c>
+      <c r="F955" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="956" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B956" s="11"/>
+      <c r="B956" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="C956" s="5"/>
-      <c r="D956" s="3"/>
-      <c r="E956" s="19"/>
-      <c r="F956" s="7"/>
+      <c r="D956" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E956" s="19">
+        <v>1062</v>
+      </c>
+      <c r="F956" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="957" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B957" s="11"/>
+      <c r="B957" s="11" t="s">
+        <v>10</v>
+      </c>
       <c r="C957" s="5"/>
-      <c r="D957" s="3"/>
-      <c r="E957" s="19"/>
-      <c r="F957" s="7"/>
+      <c r="D957" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E957" s="19">
+        <v>2347.44</v>
+      </c>
+      <c r="F957" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="958" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B958" s="11"/>
+      <c r="B958" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C958" s="5"/>
-      <c r="D958" s="3"/>
-      <c r="E958" s="19"/>
-      <c r="F958" s="7"/>
+      <c r="D958" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E958" s="19">
+        <v>44</v>
+      </c>
+      <c r="F958" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="959" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B959" s="11"/>
+      <c r="B959" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="C959" s="5"/>
-      <c r="D959" s="3"/>
-      <c r="E959" s="19"/>
-      <c r="F959" s="7"/>
+      <c r="D959" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E959" s="19">
+        <v>200</v>
+      </c>
+      <c r="F959" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="960" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B960" s="11"/>
+      <c r="B960" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C960" s="5"/>
-      <c r="D960" s="3"/>
-      <c r="E960" s="19"/>
-      <c r="F960" s="7"/>
+      <c r="D960" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E960" s="19">
+        <v>20</v>
+      </c>
+      <c r="F960" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="961" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B961" s="11"/>
+      <c r="B961" s="11" t="s">
+        <v>10</v>
+      </c>
       <c r="C961" s="5"/>
-      <c r="D961" s="3"/>
-      <c r="E961" s="19"/>
-      <c r="F961" s="7"/>
+      <c r="D961" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E961" s="19">
+        <v>780</v>
+      </c>
+      <c r="F961" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="962" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B962" s="11"/>
+      <c r="B962" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C962" s="5"/>
-      <c r="D962" s="3"/>
-      <c r="E962" s="19"/>
-      <c r="F962" s="7"/>
+      <c r="D962" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E962" s="19">
+        <v>370</v>
+      </c>
+      <c r="F962" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="963" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B963" s="11"/>
+      <c r="B963" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C963" s="5"/>
-      <c r="D963" s="3"/>
-      <c r="E963" s="19"/>
-      <c r="F963" s="7"/>
+      <c r="D963" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E963" s="19">
+        <v>540</v>
+      </c>
+      <c r="F963" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="964" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B964" s="11"/>
+      <c r="B964" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C964" s="5"/>
-      <c r="D964" s="3"/>
-      <c r="E964" s="19"/>
-      <c r="F964" s="7"/>
+      <c r="D964" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E964" s="19">
+        <v>318</v>
+      </c>
+      <c r="F964" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="965" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B965" s="11"/>
+      <c r="B965" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C965" s="5"/>
-      <c r="D965" s="3"/>
-      <c r="E965" s="19"/>
-      <c r="F965" s="7"/>
+      <c r="D965" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E965" s="19">
+        <v>590</v>
+      </c>
+      <c r="F965" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="966" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B966" s="11"/>
+      <c r="B966" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C966" s="5"/>
-      <c r="D966" s="3"/>
-      <c r="E966" s="19"/>
-      <c r="F966" s="7"/>
+      <c r="D966" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E966" s="19">
+        <v>120</v>
+      </c>
+      <c r="F966" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="967" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B967" s="11"/>
+      <c r="B967" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C967" s="5"/>
-      <c r="D967" s="3"/>
-      <c r="E967" s="19"/>
-      <c r="F967" s="7"/>
+      <c r="D967" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E967" s="19">
+        <v>3369.52</v>
+      </c>
+      <c r="F967" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="968" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B968" s="11"/>
+      <c r="B968" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C968" s="5"/>
-      <c r="D968" s="3"/>
-      <c r="E968" s="19"/>
-      <c r="F968" s="7"/>
+      <c r="D968" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E968" s="19">
+        <v>80</v>
+      </c>
+      <c r="F968" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="969" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B969" s="11"/>
+      <c r="B969" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C969" s="5"/>
-      <c r="D969" s="3"/>
-      <c r="E969" s="19"/>
-      <c r="F969" s="7"/>
+      <c r="D969" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E969" s="19">
+        <v>300</v>
+      </c>
+      <c r="F969" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="970" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B970" s="11"/>
+      <c r="B970" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C970" s="5"/>
-      <c r="D970" s="3"/>
-      <c r="E970" s="19"/>
-      <c r="F970" s="7"/>
+      <c r="D970" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E970" s="19">
+        <v>280</v>
+      </c>
+      <c r="F970" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="971" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B971" s="11"/>
+      <c r="B971" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C971" s="5"/>
-      <c r="D971" s="3"/>
-      <c r="E971" s="19"/>
-      <c r="F971" s="7"/>
+      <c r="D971" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E971" s="19">
+        <v>100</v>
+      </c>
+      <c r="F971" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="972" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B972" s="11"/>
+      <c r="B972" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C972" s="5"/>
-      <c r="D972" s="3"/>
-      <c r="E972" s="19"/>
-      <c r="F972" s="7"/>
+      <c r="D972" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E972" s="19">
+        <v>902.1</v>
+      </c>
+      <c r="F972" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="973" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B973" s="11"/>
+      <c r="B973" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C973" s="5"/>
-      <c r="D973" s="3"/>
-      <c r="E973" s="19"/>
-      <c r="F973" s="7"/>
+      <c r="D973" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E973" s="19">
+        <v>605.6</v>
+      </c>
+      <c r="F973" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="974" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B974" s="11"/>
+      <c r="B974" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C974" s="5"/>
-      <c r="D974" s="3"/>
-      <c r="E974" s="19"/>
-      <c r="F974" s="7"/>
+      <c r="D974" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E974" s="19">
+        <v>735</v>
+      </c>
+      <c r="F974" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="975" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B975" s="11"/>
+      <c r="B975" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C975" s="5"/>
-      <c r="D975" s="3"/>
-      <c r="E975" s="19"/>
-      <c r="F975" s="7"/>
+      <c r="D975" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E975" s="19">
+        <v>200</v>
+      </c>
+      <c r="F975" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="976" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B976" s="11"/>
+      <c r="B976" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="C976" s="5"/>
-      <c r="D976" s="3"/>
-      <c r="E976" s="19"/>
-      <c r="F976" s="7"/>
+      <c r="D976" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E976" s="19">
+        <v>265</v>
+      </c>
+      <c r="F976" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="977" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B977" s="11"/>
+      <c r="B977" s="11" t="s">
+        <v>118</v>
+      </c>
       <c r="C977" s="5"/>
-      <c r="D977" s="3"/>
-      <c r="E977" s="19"/>
-      <c r="F977" s="7"/>
+      <c r="D977" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E977" s="19">
+        <v>1040</v>
+      </c>
+      <c r="F977" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="978" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B978" s="11"/>
+      <c r="B978" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C978" s="5"/>
-      <c r="D978" s="3"/>
-      <c r="E978" s="19"/>
-      <c r="F978" s="7"/>
+      <c r="D978" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E978" s="19">
+        <v>445.2</v>
+      </c>
+      <c r="F978" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="979" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B979" s="11"/>
+      <c r="B979" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C979" s="5"/>
-      <c r="D979" s="3"/>
-      <c r="E979" s="19"/>
-      <c r="F979" s="7"/>
+      <c r="D979" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E979" s="19">
+        <v>90</v>
+      </c>
+      <c r="F979" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="980" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B980" s="11"/>
+      <c r="B980" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="C980" s="5"/>
-      <c r="D980" s="3"/>
-      <c r="E980" s="19"/>
-      <c r="F980" s="7"/>
+      <c r="D980" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E980" s="19">
+        <v>395</v>
+      </c>
+      <c r="F980" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="981" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B981" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="746" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C868B7CC-E4B5-4277-93B5-EA9F3859AB5F}"/>
+  <xr:revisionPtr revIDLastSave="750" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21EEB557-9956-41EB-8D78-DA435AF30C8D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="124">
   <si>
     <t>Custo</t>
   </si>
@@ -15980,11 +15980,19 @@
       </c>
     </row>
     <row r="994" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B994" s="11"/>
+      <c r="B994" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C994" s="5"/>
-      <c r="D994" s="3"/>
-      <c r="E994" s="19"/>
-      <c r="F994" s="7"/>
+      <c r="D994" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E994" s="19">
+        <v>1980</v>
+      </c>
+      <c r="F994" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="995" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B995" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="750" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21EEB557-9956-41EB-8D78-DA435AF30C8D}"/>
+  <xr:revisionPtr revIDLastSave="754" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E62DF2A2-6EEB-4FEC-8CD4-7E0BE1F40E22}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="124">
   <si>
     <t>Custo</t>
   </si>
@@ -15995,11 +15995,19 @@
       </c>
     </row>
     <row r="995" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B995" s="11"/>
+      <c r="B995" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C995" s="5"/>
-      <c r="D995" s="3"/>
-      <c r="E995" s="19"/>
-      <c r="F995" s="7"/>
+      <c r="D995" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E995" s="19">
+        <v>325</v>
+      </c>
+      <c r="F995" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="996" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B996" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="754" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E62DF2A2-6EEB-4FEC-8CD4-7E0BE1F40E22}"/>
+  <xr:revisionPtr revIDLastSave="758" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77E6D82B-5751-485E-B0CF-A0FE39103534}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="124">
   <si>
     <t>Custo</t>
   </si>
@@ -16010,11 +16010,19 @@
       </c>
     </row>
     <row r="996" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B996" s="11"/>
+      <c r="B996" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="C996" s="5"/>
-      <c r="D996" s="3"/>
-      <c r="E996" s="19"/>
-      <c r="F996" s="7"/>
+      <c r="D996" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E996" s="19">
+        <v>136.35</v>
+      </c>
+      <c r="F996" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="997" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B997" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="758" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77E6D82B-5751-485E-B0CF-A0FE39103534}"/>
+  <xr:revisionPtr revIDLastSave="769" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A398A076-F07D-4EB3-98F6-F9231AD2B90B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="124">
   <si>
     <t>Custo</t>
   </si>
@@ -420,7 +420,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,6 +451,14 @@
     </font>
     <font>
       <u val="singleAccounting"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -646,7 +654,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -752,6 +760,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -15964,7 +15973,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="993" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="993" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B993" s="11" t="s">
         <v>28</v>
       </c>
@@ -15979,7 +15988,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="994" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="994" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B994" s="11" t="s">
         <v>28</v>
       </c>
@@ -15994,7 +16003,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="995" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="995" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B995" s="11" t="s">
         <v>22</v>
       </c>
@@ -16009,7 +16018,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="996" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="996" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B996" s="11" t="s">
         <v>11</v>
       </c>
@@ -16024,84 +16033,101 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="997" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B997" s="11"/>
+    <row r="997" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B997" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C997" s="5"/>
-      <c r="D997" s="3"/>
-      <c r="E997" s="19"/>
-      <c r="F997" s="7"/>
-    </row>
-    <row r="998" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B998" s="11"/>
+      <c r="D997" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E997" s="19">
+        <v>2176.25</v>
+      </c>
+      <c r="F997" s="7">
+        <v>45962</v>
+      </c>
+      <c r="G997" s="41"/>
+    </row>
+    <row r="998" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B998" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C998" s="5"/>
-      <c r="D998" s="3"/>
-      <c r="E998" s="19"/>
-      <c r="F998" s="7"/>
-    </row>
-    <row r="999" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D998" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E998" s="19">
+        <v>560</v>
+      </c>
+      <c r="F998" s="7">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="999" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B999" s="11"/>
       <c r="C999" s="5"/>
       <c r="D999" s="3"/>
       <c r="E999" s="19"/>
       <c r="F999" s="7"/>
     </row>
-    <row r="1000" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1000" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1000" s="11"/>
       <c r="C1000" s="5"/>
       <c r="D1000" s="3"/>
       <c r="E1000" s="19"/>
       <c r="F1000" s="7"/>
     </row>
-    <row r="1001" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1001" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1001" s="11"/>
       <c r="C1001" s="5"/>
       <c r="D1001" s="3"/>
       <c r="E1001" s="19"/>
       <c r="F1001" s="7"/>
     </row>
-    <row r="1002" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1002" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1002" s="11"/>
       <c r="C1002" s="5"/>
       <c r="D1002" s="3"/>
       <c r="E1002" s="19"/>
       <c r="F1002" s="7"/>
     </row>
-    <row r="1003" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1003" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1003" s="11"/>
       <c r="C1003" s="5"/>
       <c r="D1003" s="3"/>
       <c r="E1003" s="19"/>
       <c r="F1003" s="7"/>
     </row>
-    <row r="1004" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1004" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1004" s="11"/>
       <c r="C1004" s="5"/>
       <c r="D1004" s="3"/>
       <c r="E1004" s="19"/>
       <c r="F1004" s="7"/>
     </row>
-    <row r="1005" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1005" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1005" s="11"/>
       <c r="C1005" s="5"/>
       <c r="D1005" s="3"/>
       <c r="E1005" s="19"/>
       <c r="F1005" s="7"/>
     </row>
-    <row r="1006" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1006" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1006" s="11"/>
       <c r="C1006" s="5"/>
       <c r="D1006" s="3"/>
       <c r="E1006" s="19"/>
       <c r="F1006" s="7"/>
     </row>
-    <row r="1007" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1007" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1007" s="11"/>
       <c r="C1007" s="5"/>
       <c r="D1007" s="3"/>
       <c r="E1007" s="19"/>
       <c r="F1007" s="7"/>
     </row>
-    <row r="1008" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1008" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1008" s="11"/>
       <c r="C1008" s="5"/>
       <c r="D1008" s="3"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="769" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A398A076-F07D-4EB3-98F6-F9231AD2B90B}"/>
+  <xr:revisionPtr revIDLastSave="789" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{833B8943-5922-4ECE-B462-FCD736867601}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1999" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="125">
   <si>
     <t>Custo</t>
   </si>
@@ -411,6 +411,9 @@
   </si>
   <si>
     <t xml:space="preserve">MS PNEUS </t>
+  </si>
+  <si>
+    <t>AUTO PECAS BD</t>
   </si>
 </sst>
 </file>
@@ -16065,32 +16068,65 @@
       </c>
     </row>
     <row r="999" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B999" s="11"/>
+      <c r="B999" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C999" s="5"/>
-      <c r="D999" s="3"/>
-      <c r="E999" s="19"/>
-      <c r="F999" s="7"/>
+      <c r="D999" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E999" s="19">
+        <v>1100</v>
+      </c>
+      <c r="F999" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="1000" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1000" s="11"/>
+      <c r="B1000" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C1000" s="5"/>
-      <c r="D1000" s="3"/>
-      <c r="E1000" s="19"/>
-      <c r="F1000" s="7"/>
+      <c r="D1000" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1000" s="19">
+        <v>80</v>
+      </c>
+      <c r="F1000" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="1001" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1001" s="11"/>
+      <c r="B1001" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C1001" s="5"/>
-      <c r="D1001" s="3"/>
-      <c r="E1001" s="19"/>
-      <c r="F1001" s="7"/>
+      <c r="D1001" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1001" s="19">
+        <v>280</v>
+      </c>
+      <c r="F1001" s="7">
+        <v>45962</v>
+      </c>
+      <c r="G1001" s="7"/>
     </row>
     <row r="1002" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1002" s="11"/>
+      <c r="B1002" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C1002" s="5"/>
-      <c r="D1002" s="3"/>
-      <c r="E1002" s="19"/>
-      <c r="F1002" s="7"/>
+      <c r="D1002" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1002" s="19">
+        <v>445</v>
+      </c>
+      <c r="F1002" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="1003" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1003" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1083" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3019CEF-2731-4AD7-8CA8-858DD9090BE9}"/>
+  <xr:revisionPtr revIDLastSave="1142" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBF11876-99EB-4989-8126-B8350C5DE72A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="134">
   <si>
     <t>Custo</t>
   </si>
@@ -437,6 +437,12 @@
   </si>
   <si>
     <t>KPD8B86</t>
+  </si>
+  <si>
+    <t>SEM INFORMAÇÃO</t>
+  </si>
+  <si>
+    <t>AG PNEUS</t>
   </si>
 </sst>
 </file>
@@ -17087,95 +17093,199 @@
       </c>
     </row>
     <row r="1066" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1066" s="11"/>
+      <c r="B1066" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C1066" s="5"/>
-      <c r="D1066" s="3"/>
-      <c r="E1066" s="19"/>
-      <c r="F1066" s="7"/>
+      <c r="D1066" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1066" s="19">
+        <v>555</v>
+      </c>
+      <c r="F1066" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1067" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1067" s="11"/>
+      <c r="B1067" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C1067" s="5"/>
-      <c r="D1067" s="3"/>
-      <c r="E1067" s="19"/>
-      <c r="F1067" s="7"/>
+      <c r="D1067" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1067" s="19">
+        <v>2600</v>
+      </c>
+      <c r="F1067" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1068" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1068" s="11"/>
+      <c r="B1068" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C1068" s="5"/>
-      <c r="D1068" s="3"/>
-      <c r="E1068" s="19"/>
-      <c r="F1068" s="7"/>
+      <c r="D1068" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1068" s="19">
+        <v>220</v>
+      </c>
+      <c r="F1068" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1069" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1069" s="11"/>
+      <c r="B1069" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C1069" s="5"/>
-      <c r="D1069" s="3"/>
-      <c r="E1069" s="19"/>
-      <c r="F1069" s="7"/>
+      <c r="D1069" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1069" s="19">
+        <v>80</v>
+      </c>
+      <c r="F1069" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1070" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1070" s="11"/>
+      <c r="B1070" s="11" t="s">
+        <v>132</v>
+      </c>
       <c r="C1070" s="5"/>
-      <c r="D1070" s="3"/>
-      <c r="E1070" s="19"/>
-      <c r="F1070" s="7"/>
+      <c r="D1070" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1070" s="19">
+        <v>702</v>
+      </c>
+      <c r="F1070" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1071" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1071" s="11"/>
+      <c r="B1071" s="11" t="s">
+        <v>92</v>
+      </c>
       <c r="C1071" s="5"/>
-      <c r="D1071" s="3"/>
-      <c r="E1071" s="19"/>
-      <c r="F1071" s="7"/>
+      <c r="D1071" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1071" s="19">
+        <v>540</v>
+      </c>
+      <c r="F1071" s="7">
+        <v>45962</v>
+      </c>
     </row>
     <row r="1072" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1072" s="11"/>
+      <c r="B1072" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C1072" s="5"/>
-      <c r="D1072" s="3"/>
-      <c r="E1072" s="19"/>
-      <c r="F1072" s="7"/>
+      <c r="D1072" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1072" s="19">
+        <v>495</v>
+      </c>
+      <c r="F1072" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1073" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1073" s="11"/>
+      <c r="B1073" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C1073" s="5"/>
-      <c r="D1073" s="3"/>
-      <c r="E1073" s="19"/>
-      <c r="F1073" s="7"/>
+      <c r="D1073" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1073" s="19">
+        <v>1700</v>
+      </c>
+      <c r="F1073" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1074" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1074" s="11"/>
+      <c r="B1074" s="11" t="s">
+        <v>92</v>
+      </c>
       <c r="C1074" s="5"/>
-      <c r="D1074" s="3"/>
-      <c r="E1074" s="19"/>
-      <c r="F1074" s="7"/>
+      <c r="D1074" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1074" s="19">
+        <v>833</v>
+      </c>
+      <c r="F1074" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1075" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1075" s="11"/>
+      <c r="B1075" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C1075" s="5"/>
-      <c r="D1075" s="3"/>
-      <c r="E1075" s="19"/>
-      <c r="F1075" s="7"/>
+      <c r="D1075" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1075" s="19">
+        <v>265</v>
+      </c>
+      <c r="F1075" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1076" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1076" s="11"/>
+      <c r="B1076" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C1076" s="5"/>
-      <c r="D1076" s="3"/>
-      <c r="E1076" s="19"/>
-      <c r="F1076" s="7"/>
+      <c r="D1076" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1076" s="19">
+        <v>3187</v>
+      </c>
+      <c r="F1076" s="7">
+        <v>45931</v>
+      </c>
     </row>
     <row r="1077" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1077" s="11"/>
+      <c r="B1077" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="C1077" s="5"/>
-      <c r="D1077" s="3"/>
-      <c r="E1077" s="19"/>
-      <c r="F1077" s="7"/>
+      <c r="D1077" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1077" s="19">
+        <v>1036</v>
+      </c>
+      <c r="F1077" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1078" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1078" s="11"/>
+      <c r="B1078" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C1078" s="5"/>
-      <c r="D1078" s="3"/>
-      <c r="E1078" s="19"/>
-      <c r="F1078" s="7"/>
+      <c r="D1078" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1078" s="19">
+        <v>690</v>
+      </c>
+      <c r="F1078" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1079" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B1079" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1315" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABFDA1F5-E1BB-4A85-BCA6-A4CFC0D8349D}"/>
+  <xr:revisionPtr revIDLastSave="1323" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A36B252-B537-492E-A120-20979C95B190}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2237" uniqueCount="139">
   <si>
     <t>Custo</t>
   </si>
@@ -40064,18 +40064,34 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="11"/>
+      <c r="B39" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C39" s="5"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="7"/>
+      <c r="D39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="19">
+        <v>1266.2</v>
+      </c>
+      <c r="F39" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="11"/>
+      <c r="B40" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C40" s="5"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="7"/>
+      <c r="D40" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E40" s="19">
+        <v>400</v>
+      </c>
+      <c r="F40" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1323" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A36B252-B537-492E-A120-20979C95B190}"/>
+  <xr:revisionPtr revIDLastSave="1331" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A443FB8B-9ACA-44F0-8084-22C19AE4F901}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2237" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="140">
   <si>
     <t>Custo</t>
   </si>
@@ -458,6 +458,9 @@
   </si>
   <si>
     <t>REFORMA PNEU</t>
+  </si>
+  <si>
+    <t>CENTER TRUCK</t>
   </si>
 </sst>
 </file>
@@ -40094,18 +40097,34 @@
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B41" s="11"/>
+      <c r="B41" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C41" s="5"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="7"/>
+      <c r="D41" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="19">
+        <v>8350</v>
+      </c>
+      <c r="F41" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="11"/>
+      <c r="B42" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="C42" s="5"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="7"/>
+      <c r="D42" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E42" s="19">
+        <v>3500</v>
+      </c>
+      <c r="F42" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1331" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A443FB8B-9ACA-44F0-8084-22C19AE4F901}"/>
+  <xr:revisionPtr revIDLastSave="1335" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{557AD426-6476-4D02-8663-F55208043EA1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
+    <workbookView xWindow="7560" yWindow="3555" windowWidth="18345" windowHeight="11295" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2243" uniqueCount="140">
   <si>
     <t>Custo</t>
   </si>
@@ -40127,11 +40127,19 @@
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B43" s="11"/>
+      <c r="B43" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="7"/>
+      <c r="D43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="19">
+        <v>798.3</v>
+      </c>
+      <c r="F43" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1357" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4FFE0F2-6CBF-460A-AFFA-B4B7E038DF1B}"/>
+  <xr:revisionPtr revIDLastSave="1435" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{159107B4-4097-4185-B560-4A3D61EA7CAD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2249" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="145">
   <si>
     <t>Custo</t>
   </si>
@@ -461,6 +461,21 @@
   </si>
   <si>
     <t>CENTER TRUCK</t>
+  </si>
+  <si>
+    <t>AUTO ELETRICA DO LEO</t>
+  </si>
+  <si>
+    <t>ROBINHO E FILHO</t>
+  </si>
+  <si>
+    <t>HAM3G53</t>
+  </si>
+  <si>
+    <t>JW RADIADORES</t>
+  </si>
+  <si>
+    <t>AUTO PEÇAS</t>
   </si>
 </sst>
 </file>
@@ -40209,137 +40224,289 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="11"/>
+      <c r="B47" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C47" s="5"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="7"/>
+      <c r="D47" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E47" s="43">
+        <v>1772.9</v>
+      </c>
+      <c r="F47" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="11"/>
+      <c r="B48" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C48" s="5"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="7"/>
+      <c r="D48" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E48" s="43">
+        <v>1065</v>
+      </c>
+      <c r="F48" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B49" s="11"/>
+      <c r="B49" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C49" s="5"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="7"/>
+      <c r="D49" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="43">
+        <v>35</v>
+      </c>
+      <c r="F49" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B50" s="11"/>
+      <c r="B50" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C50" s="5"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="7"/>
+      <c r="D50" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="43">
+        <v>1060</v>
+      </c>
+      <c r="F50" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B51" s="11"/>
+      <c r="B51" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C51" s="5"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="7"/>
+      <c r="D51" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E51" s="43">
+        <v>60</v>
+      </c>
+      <c r="F51" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B52" s="11"/>
+      <c r="B52" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C52" s="5"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="7"/>
+      <c r="D52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E52" s="43">
+        <v>120</v>
+      </c>
+      <c r="F52" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B53" s="11"/>
+      <c r="B53" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C53" s="5"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="7"/>
+      <c r="D53" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53" s="43">
+        <v>120</v>
+      </c>
+      <c r="F53" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B54" s="11"/>
+      <c r="B54" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C54" s="5"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="43"/>
-      <c r="F54" s="7"/>
+      <c r="D54" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E54" s="43">
+        <v>380</v>
+      </c>
+      <c r="F54" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B55" s="11"/>
+      <c r="B55" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C55" s="5"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="43"/>
-      <c r="F55" s="7"/>
+      <c r="D55" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" s="43">
+        <v>638.04999999999995</v>
+      </c>
+      <c r="F55" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B56" s="11"/>
+      <c r="B56" s="11" t="s">
+        <v>142</v>
+      </c>
       <c r="C56" s="5"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="43"/>
-      <c r="F56" s="7"/>
+      <c r="D56" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E56" s="43">
+        <v>80</v>
+      </c>
+      <c r="F56" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B57" s="11"/>
+      <c r="B57" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C57" s="5"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="7"/>
+      <c r="D57" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E57" s="43">
+        <v>83</v>
+      </c>
+      <c r="F57" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B58" s="11"/>
+      <c r="B58" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C58" s="5"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="43"/>
-      <c r="F58" s="7"/>
+      <c r="D58" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E58" s="43">
+        <v>141.5</v>
+      </c>
+      <c r="F58" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="11"/>
+      <c r="B59" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C59" s="5"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="43"/>
-      <c r="F59" s="7"/>
+      <c r="D59" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E59" s="43">
+        <v>226</v>
+      </c>
+      <c r="F59" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B60" s="11"/>
+      <c r="B60" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C60" s="5"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="43"/>
-      <c r="F60" s="7"/>
+      <c r="D60" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E60" s="43">
+        <v>600</v>
+      </c>
+      <c r="F60" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B61" s="11"/>
+      <c r="B61" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C61" s="5"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="43"/>
-      <c r="F61" s="7"/>
+      <c r="D61" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E61" s="43">
+        <v>20</v>
+      </c>
+      <c r="F61" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B62" s="11"/>
+      <c r="B62" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C62" s="5"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="43"/>
-      <c r="F62" s="7"/>
+      <c r="D62" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E62" s="43">
+        <v>339.64</v>
+      </c>
+      <c r="F62" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B63" s="11"/>
+      <c r="B63" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C63" s="5"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="43"/>
-      <c r="F63" s="7"/>
+      <c r="D63" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E63" s="43">
+        <v>80</v>
+      </c>
+      <c r="F63" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B64" s="11"/>
+      <c r="B64" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C64" s="5"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="43"/>
-      <c r="F64" s="7"/>
+      <c r="D64" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E64" s="43">
+        <v>552.70000000000005</v>
+      </c>
+      <c r="F64" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B65" s="11"/>
+      <c r="B65" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C65" s="5"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="43"/>
-      <c r="F65" s="7"/>
+      <c r="D65" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E65" s="43">
+        <v>195</v>
+      </c>
+      <c r="F65" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1496" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B331250A-A2B8-4DBD-9139-4C72F4A711B5}"/>
+  <xr:revisionPtr revIDLastSave="1524" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{541D4054-AF43-4099-8FA6-0B4EFEEDB118}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="147">
   <si>
     <t>Custo</t>
   </si>
@@ -40710,53 +40710,109 @@
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B79" s="11"/>
+      <c r="B79" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C79" s="5"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="43"/>
-      <c r="F79" s="7"/>
+      <c r="D79" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E79" s="43">
+        <v>300</v>
+      </c>
+      <c r="F79" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B80" s="11"/>
+      <c r="B80" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C80" s="5"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="43"/>
-      <c r="F80" s="7"/>
+      <c r="D80" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E80" s="43">
+        <v>37.6</v>
+      </c>
+      <c r="F80" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B81" s="11"/>
+      <c r="B81" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C81" s="5"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="43"/>
-      <c r="F81" s="7"/>
+      <c r="D81" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E81" s="43">
+        <v>760</v>
+      </c>
+      <c r="F81" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B82" s="11"/>
+      <c r="B82" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C82" s="5"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="43"/>
-      <c r="F82" s="7"/>
+      <c r="D82" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E82" s="43">
+        <v>100</v>
+      </c>
+      <c r="F82" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B83" s="11"/>
+      <c r="B83" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C83" s="5"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="43"/>
-      <c r="F83" s="7"/>
+      <c r="D83" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E83" s="43">
+        <v>184</v>
+      </c>
+      <c r="F83" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B84" s="11"/>
+      <c r="B84" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C84" s="5"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="43"/>
-      <c r="F84" s="7"/>
+      <c r="D84" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E84" s="43">
+        <v>1884.84</v>
+      </c>
+      <c r="F84" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B85" s="11"/>
+      <c r="B85" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C85" s="5"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="43"/>
-      <c r="F85" s="7"/>
+      <c r="D85" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E85" s="43">
+        <v>165</v>
+      </c>
+      <c r="F85" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B86" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1524" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{541D4054-AF43-4099-8FA6-0B4EFEEDB118}"/>
+  <xr:revisionPtr revIDLastSave="1545" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{150FDE29-9113-41D6-B06B-474907414F11}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2339" uniqueCount="148">
   <si>
     <t>Custo</t>
   </si>
@@ -482,6 +482,9 @@
   </si>
   <si>
     <t>PNEUS</t>
+  </si>
+  <si>
+    <t>NOVA FREIOS E PEÇAS</t>
   </si>
 </sst>
 </file>
@@ -40815,39 +40818,79 @@
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B86" s="11"/>
+      <c r="B86" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C86" s="5"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="43"/>
-      <c r="F86" s="7"/>
+      <c r="D86" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E86" s="43">
+        <v>1182</v>
+      </c>
+      <c r="F86" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B87" s="11"/>
+      <c r="B87" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C87" s="5"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="43"/>
-      <c r="F87" s="7"/>
+      <c r="D87" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E87" s="43">
+        <v>117.41</v>
+      </c>
+      <c r="F87" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B88" s="11"/>
+      <c r="B88" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C88" s="5"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="43"/>
-      <c r="F88" s="7"/>
+      <c r="D88" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E88" s="43">
+        <v>600</v>
+      </c>
+      <c r="F88" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B89" s="11"/>
+      <c r="B89" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C89" s="5"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="43"/>
-      <c r="F89" s="7"/>
+      <c r="D89" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E89" s="43">
+        <v>402</v>
+      </c>
+      <c r="F89" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B90" s="11"/>
+      <c r="B90" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C90" s="5"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="43"/>
-      <c r="F90" s="7"/>
+      <c r="D90" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E90" s="43">
+        <v>902.1</v>
+      </c>
+      <c r="F90" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B91" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1545" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{150FDE29-9113-41D6-B06B-474907414F11}"/>
+  <xr:revisionPtr revIDLastSave="1596" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9297217F-0015-4D63-8416-76ADD9900227}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2339" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="149">
   <si>
     <t>Custo</t>
   </si>
@@ -485,6 +485,9 @@
   </si>
   <si>
     <t>NOVA FREIOS E PEÇAS</t>
+  </si>
+  <si>
+    <t>PNEUS MAX</t>
   </si>
 </sst>
 </file>
@@ -17352,17 +17355,21 @@
       </c>
     </row>
     <row r="1079" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1079" s="11"/>
+      <c r="B1079" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C1079" s="5"/>
-      <c r="D1079" s="3"/>
-      <c r="E1079" s="19"/>
-      <c r="F1079" s="7"/>
+      <c r="D1079" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1079" s="19">
+        <v>12600</v>
+      </c>
+      <c r="F1079" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1080" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1080" s="11"/>
-      <c r="C1080" s="5"/>
-      <c r="D1080" s="3"/>
-      <c r="E1080" s="19"/>
       <c r="F1080" s="7"/>
     </row>
     <row r="1081" spans="2:6" x14ac:dyDescent="0.25">
@@ -40893,67 +40900,139 @@
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B91" s="11"/>
+      <c r="B91" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C91" s="5"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="43"/>
-      <c r="F91" s="7"/>
+      <c r="D91" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E91" s="43">
+        <v>3264</v>
+      </c>
+      <c r="F91" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B92" s="11"/>
+      <c r="B92" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C92" s="5"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="43"/>
-      <c r="F92" s="7"/>
+      <c r="D92" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E92" s="43">
+        <v>2900</v>
+      </c>
+      <c r="F92" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B93" s="11"/>
+      <c r="B93" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C93" s="5"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="43"/>
-      <c r="F93" s="7"/>
+      <c r="D93" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E93" s="43">
+        <v>325</v>
+      </c>
+      <c r="F93" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B94" s="11"/>
+      <c r="B94" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C94" s="5"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="43"/>
-      <c r="F94" s="7"/>
+      <c r="D94" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E94" s="19">
+        <v>1260</v>
+      </c>
+      <c r="F94" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B95" s="11"/>
+      <c r="B95" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C95" s="5"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="43"/>
-      <c r="F95" s="7"/>
+      <c r="D95" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E95" s="43">
+        <v>3000</v>
+      </c>
+      <c r="F95" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B96" s="11"/>
+      <c r="B96" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C96" s="5"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="43"/>
-      <c r="F96" s="7"/>
+      <c r="D96" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E96" s="43">
+        <v>600</v>
+      </c>
+      <c r="F96" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B97" s="11"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="43"/>
-      <c r="F97" s="7"/>
+      <c r="B97" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" s="24"/>
+      <c r="D97" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E97" s="48">
+        <v>518.35</v>
+      </c>
+      <c r="F97" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B98" s="11"/>
+      <c r="B98" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C98" s="5"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="43"/>
-      <c r="F98" s="7"/>
+      <c r="D98" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E98" s="43">
+        <v>100</v>
+      </c>
+      <c r="F98" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B99" s="11"/>
+      <c r="B99" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C99" s="5"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="43"/>
-      <c r="F99" s="7"/>
+      <c r="D99" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E99" s="43">
+        <v>505</v>
+      </c>
+      <c r="F99" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B100" s="11"/>
@@ -60863,21 +60942,6 @@
       <c r="E2943" s="48"/>
       <c r="F2943" s="7"/>
     </row>
-    <row r="2944" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2944" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2944" s="24"/>
-      <c r="D2944" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2944" s="48">
-        <v>518.35</v>
-      </c>
-      <c r="F2944" s="7">
-        <v>46023</v>
-      </c>
-    </row>
     <row r="2945" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2945" s="24"/>
       <c r="C2945" s="24"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1596" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9297217F-0015-4D63-8416-76ADD9900227}"/>
+  <xr:revisionPtr revIDLastSave="1637" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{241F45C3-221F-4D1C-BC8D-5A9199C92226}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="153">
   <si>
     <t>Custo</t>
   </si>
@@ -489,14 +489,25 @@
   <si>
     <t>PNEUS MAX</t>
   </si>
+  <si>
+    <t>LONAS VINIFORTE</t>
+  </si>
+  <si>
+    <t>CASA DOS PNEUS</t>
+  </si>
+  <si>
+    <t>DISCO DIAGRAMA</t>
+  </si>
+  <si>
+    <t>DALMEIDA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -732,7 +743,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -839,25 +850,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -17370,6 +17378,9 @@
       </c>
     </row>
     <row r="1080" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B1080" s="25" t="s">
+        <v>27</v>
+      </c>
       <c r="F1080" s="7"/>
     </row>
     <row r="1081" spans="2:6" x14ac:dyDescent="0.25">
@@ -40997,7 +41008,7 @@
       <c r="D97" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E97" s="48">
+      <c r="E97" s="46">
         <v>518.35</v>
       </c>
       <c r="F97" s="7">
@@ -41035,60 +41046,124 @@
       </c>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B100" s="11"/>
+      <c r="B100" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C100" s="5"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="43"/>
-      <c r="F100" s="7"/>
+      <c r="D100" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E100" s="43">
+        <v>67.2</v>
+      </c>
+      <c r="F100" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B101" s="11"/>
+      <c r="B101" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C101" s="5"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="43"/>
-      <c r="F101" s="7"/>
+      <c r="D101" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E101" s="43">
+        <v>165</v>
+      </c>
+      <c r="F101" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B102" s="11"/>
+      <c r="B102" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C102" s="5"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="43"/>
-      <c r="F102" s="7"/>
+      <c r="D102" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E102" s="43">
+        <v>180</v>
+      </c>
+      <c r="F102" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B103" s="11"/>
+      <c r="B103" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C103" s="5"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="43"/>
-      <c r="F103" s="7"/>
+      <c r="D103" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E103" s="43">
+        <v>170</v>
+      </c>
+      <c r="F103" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B104" s="11"/>
+      <c r="B104" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C104" s="5"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="43"/>
-      <c r="F104" s="7"/>
+      <c r="D104" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E104" s="43">
+        <v>416</v>
+      </c>
+      <c r="F104" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B105" s="11"/>
+      <c r="B105" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C105" s="5"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="43"/>
-      <c r="F105" s="7"/>
+      <c r="D105" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E105" s="43">
+        <v>1100</v>
+      </c>
+      <c r="F105" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B106" s="11"/>
+      <c r="B106" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C106" s="5"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="43"/>
-      <c r="F106" s="7"/>
+      <c r="D106" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E106" s="43">
+        <v>2220</v>
+      </c>
+      <c r="F106" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B107" s="11"/>
+      <c r="B107" s="11" t="s">
+        <v>151</v>
+      </c>
       <c r="C107" s="5"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="43"/>
-      <c r="F107" s="7"/>
+      <c r="D107" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="E107" s="20">
+        <v>1590</v>
+      </c>
+      <c r="F107" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B108" s="11"/>
@@ -55227,2226 +55302,2226 @@
       <c r="B2127" s="11"/>
       <c r="C2127" s="3"/>
       <c r="D2127" s="3"/>
-      <c r="E2127" s="46"/>
+      <c r="E2127" s="45"/>
       <c r="F2127" s="7"/>
     </row>
     <row r="2128" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2128" s="11"/>
       <c r="C2128" s="3"/>
       <c r="D2128" s="3"/>
-      <c r="E2128" s="46"/>
+      <c r="E2128" s="45"/>
       <c r="F2128" s="7"/>
     </row>
     <row r="2129" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2129" s="11"/>
       <c r="C2129" s="3"/>
       <c r="D2129" s="3"/>
-      <c r="E2129" s="46"/>
+      <c r="E2129" s="45"/>
       <c r="F2129" s="7"/>
     </row>
     <row r="2130" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2130" s="11"/>
       <c r="C2130" s="3"/>
       <c r="D2130" s="3"/>
-      <c r="E2130" s="46"/>
+      <c r="E2130" s="45"/>
       <c r="F2130" s="7"/>
     </row>
     <row r="2131" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2131" s="11"/>
       <c r="C2131" s="3"/>
       <c r="D2131" s="3"/>
-      <c r="E2131" s="46"/>
+      <c r="E2131" s="45"/>
       <c r="F2131" s="7"/>
     </row>
     <row r="2132" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2132" s="11"/>
       <c r="C2132" s="3"/>
       <c r="D2132" s="3"/>
-      <c r="E2132" s="46"/>
+      <c r="E2132" s="45"/>
       <c r="F2132" s="7"/>
     </row>
     <row r="2133" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2133" s="11"/>
       <c r="C2133" s="3"/>
       <c r="D2133" s="3"/>
-      <c r="E2133" s="46"/>
+      <c r="E2133" s="45"/>
       <c r="F2133" s="7"/>
     </row>
     <row r="2134" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2134" s="11"/>
       <c r="C2134" s="3"/>
       <c r="D2134" s="3"/>
-      <c r="E2134" s="46"/>
+      <c r="E2134" s="45"/>
       <c r="F2134" s="7"/>
     </row>
     <row r="2135" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2135" s="11"/>
       <c r="C2135" s="3"/>
       <c r="D2135" s="3"/>
-      <c r="E2135" s="46"/>
+      <c r="E2135" s="45"/>
       <c r="F2135" s="7"/>
     </row>
     <row r="2136" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2136" s="11"/>
       <c r="C2136" s="3"/>
       <c r="D2136" s="3"/>
-      <c r="E2136" s="46"/>
+      <c r="E2136" s="45"/>
       <c r="F2136" s="7"/>
     </row>
     <row r="2137" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2137" s="11"/>
       <c r="C2137" s="3"/>
       <c r="D2137" s="3"/>
-      <c r="E2137" s="46"/>
+      <c r="E2137" s="45"/>
       <c r="F2137" s="7"/>
     </row>
     <row r="2138" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2138" s="11"/>
       <c r="C2138" s="3"/>
       <c r="D2138" s="3"/>
-      <c r="E2138" s="46"/>
+      <c r="E2138" s="45"/>
       <c r="F2138" s="7"/>
     </row>
     <row r="2139" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2139" s="11"/>
       <c r="C2139" s="3"/>
       <c r="D2139" s="3"/>
-      <c r="E2139" s="46"/>
+      <c r="E2139" s="45"/>
       <c r="F2139" s="7"/>
     </row>
     <row r="2140" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2140" s="11"/>
       <c r="C2140" s="3"/>
       <c r="D2140" s="3"/>
-      <c r="E2140" s="46"/>
+      <c r="E2140" s="45"/>
       <c r="F2140" s="7"/>
     </row>
     <row r="2141" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2141" s="11"/>
       <c r="C2141" s="3"/>
       <c r="D2141" s="3"/>
-      <c r="E2141" s="46"/>
+      <c r="E2141" s="45"/>
       <c r="F2141" s="7"/>
     </row>
     <row r="2142" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2142" s="11"/>
       <c r="C2142" s="3"/>
       <c r="D2142" s="3"/>
-      <c r="E2142" s="46"/>
+      <c r="E2142" s="45"/>
       <c r="F2142" s="7"/>
     </row>
     <row r="2143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2143" s="11"/>
       <c r="C2143" s="3"/>
       <c r="D2143" s="3"/>
-      <c r="E2143" s="46"/>
+      <c r="E2143" s="45"/>
       <c r="F2143" s="7"/>
     </row>
     <row r="2144" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2144" s="11"/>
       <c r="C2144" s="3"/>
       <c r="D2144" s="3"/>
-      <c r="E2144" s="46"/>
+      <c r="E2144" s="45"/>
       <c r="F2144" s="7"/>
     </row>
     <row r="2145" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2145" s="11"/>
       <c r="C2145" s="3"/>
       <c r="D2145" s="3"/>
-      <c r="E2145" s="46"/>
+      <c r="E2145" s="45"/>
       <c r="F2145" s="7"/>
     </row>
     <row r="2146" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2146" s="11"/>
       <c r="C2146" s="3"/>
       <c r="D2146" s="3"/>
-      <c r="E2146" s="46"/>
+      <c r="E2146" s="45"/>
       <c r="F2146" s="7"/>
     </row>
     <row r="2147" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2147" s="11"/>
       <c r="C2147" s="3"/>
       <c r="D2147" s="3"/>
-      <c r="E2147" s="46"/>
+      <c r="E2147" s="45"/>
       <c r="F2147" s="7"/>
     </row>
     <row r="2148" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2148" s="11"/>
       <c r="C2148" s="3"/>
       <c r="D2148" s="3"/>
-      <c r="E2148" s="46"/>
+      <c r="E2148" s="45"/>
       <c r="F2148" s="7"/>
     </row>
     <row r="2149" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2149" s="11"/>
       <c r="C2149" s="3"/>
       <c r="D2149" s="3"/>
-      <c r="E2149" s="46"/>
+      <c r="E2149" s="45"/>
       <c r="F2149" s="7"/>
     </row>
     <row r="2150" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2150" s="11"/>
       <c r="C2150" s="3"/>
       <c r="D2150" s="3"/>
-      <c r="E2150" s="46"/>
+      <c r="E2150" s="45"/>
       <c r="F2150" s="7"/>
     </row>
     <row r="2151" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2151" s="11"/>
       <c r="C2151" s="3"/>
       <c r="D2151" s="3"/>
-      <c r="E2151" s="46"/>
+      <c r="E2151" s="45"/>
       <c r="F2151" s="7"/>
     </row>
     <row r="2152" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2152" s="11"/>
       <c r="C2152" s="3"/>
       <c r="D2152" s="3"/>
-      <c r="E2152" s="46"/>
+      <c r="E2152" s="45"/>
       <c r="F2152" s="7"/>
     </row>
     <row r="2153" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2153" s="11"/>
       <c r="C2153" s="3"/>
       <c r="D2153" s="3"/>
-      <c r="E2153" s="46"/>
+      <c r="E2153" s="45"/>
       <c r="F2153" s="7"/>
     </row>
     <row r="2154" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2154" s="11"/>
       <c r="C2154" s="3"/>
       <c r="D2154" s="3"/>
-      <c r="E2154" s="46"/>
+      <c r="E2154" s="45"/>
       <c r="F2154" s="7"/>
     </row>
     <row r="2155" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2155" s="11"/>
       <c r="C2155" s="3"/>
       <c r="D2155" s="3"/>
-      <c r="E2155" s="46"/>
+      <c r="E2155" s="45"/>
       <c r="F2155" s="7"/>
     </row>
     <row r="2156" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2156" s="11"/>
       <c r="C2156" s="3"/>
       <c r="D2156" s="3"/>
-      <c r="E2156" s="46"/>
+      <c r="E2156" s="45"/>
       <c r="F2156" s="7"/>
     </row>
     <row r="2157" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2157" s="11"/>
       <c r="C2157" s="3"/>
       <c r="D2157" s="3"/>
-      <c r="E2157" s="46"/>
+      <c r="E2157" s="45"/>
       <c r="F2157" s="7"/>
     </row>
     <row r="2158" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2158" s="11"/>
       <c r="C2158" s="3"/>
       <c r="D2158" s="3"/>
-      <c r="E2158" s="46"/>
+      <c r="E2158" s="45"/>
       <c r="F2158" s="7"/>
     </row>
     <row r="2159" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2159" s="11"/>
       <c r="C2159" s="3"/>
       <c r="D2159" s="3"/>
-      <c r="E2159" s="46"/>
+      <c r="E2159" s="45"/>
       <c r="F2159" s="7"/>
     </row>
     <row r="2160" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2160" s="11"/>
       <c r="C2160" s="3"/>
       <c r="D2160" s="3"/>
-      <c r="E2160" s="46"/>
+      <c r="E2160" s="45"/>
       <c r="F2160" s="7"/>
     </row>
     <row r="2161" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2161" s="11"/>
       <c r="C2161" s="3"/>
       <c r="D2161" s="3"/>
-      <c r="E2161" s="46"/>
+      <c r="E2161" s="45"/>
       <c r="F2161" s="7"/>
     </row>
     <row r="2162" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2162" s="11"/>
       <c r="C2162" s="3"/>
       <c r="D2162" s="3"/>
-      <c r="E2162" s="46"/>
+      <c r="E2162" s="45"/>
       <c r="F2162" s="7"/>
     </row>
     <row r="2163" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2163" s="11"/>
       <c r="C2163" s="3"/>
       <c r="D2163" s="3"/>
-      <c r="E2163" s="46"/>
+      <c r="E2163" s="45"/>
       <c r="F2163" s="7"/>
     </row>
     <row r="2164" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2164" s="11"/>
       <c r="C2164" s="3"/>
       <c r="D2164" s="3"/>
-      <c r="E2164" s="46"/>
+      <c r="E2164" s="45"/>
       <c r="F2164" s="7"/>
     </row>
     <row r="2165" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2165" s="11"/>
       <c r="C2165" s="3"/>
       <c r="D2165" s="3"/>
-      <c r="E2165" s="46"/>
+      <c r="E2165" s="45"/>
       <c r="F2165" s="7"/>
     </row>
     <row r="2166" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2166" s="11"/>
       <c r="C2166" s="3"/>
       <c r="D2166" s="3"/>
-      <c r="E2166" s="46"/>
+      <c r="E2166" s="45"/>
       <c r="F2166" s="7"/>
     </row>
     <row r="2167" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2167" s="11"/>
       <c r="C2167" s="3"/>
       <c r="D2167" s="3"/>
-      <c r="E2167" s="46"/>
+      <c r="E2167" s="45"/>
       <c r="F2167" s="7"/>
     </row>
     <row r="2168" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2168" s="11"/>
       <c r="C2168" s="3"/>
       <c r="D2168" s="3"/>
-      <c r="E2168" s="46"/>
+      <c r="E2168" s="45"/>
       <c r="F2168" s="7"/>
     </row>
     <row r="2169" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2169" s="11"/>
       <c r="C2169" s="3"/>
       <c r="D2169" s="3"/>
-      <c r="E2169" s="46"/>
+      <c r="E2169" s="45"/>
       <c r="F2169" s="7"/>
     </row>
     <row r="2170" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2170" s="11"/>
       <c r="C2170" s="3"/>
       <c r="D2170" s="3"/>
-      <c r="E2170" s="46"/>
+      <c r="E2170" s="45"/>
       <c r="F2170" s="7"/>
     </row>
     <row r="2171" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2171" s="11"/>
       <c r="C2171" s="3"/>
       <c r="D2171" s="3"/>
-      <c r="E2171" s="46"/>
+      <c r="E2171" s="45"/>
       <c r="F2171" s="7"/>
     </row>
     <row r="2172" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2172" s="11"/>
       <c r="C2172" s="3"/>
       <c r="D2172" s="3"/>
-      <c r="E2172" s="46"/>
+      <c r="E2172" s="45"/>
       <c r="F2172" s="7"/>
     </row>
     <row r="2173" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2173" s="11"/>
       <c r="C2173" s="3"/>
       <c r="D2173" s="3"/>
-      <c r="E2173" s="46"/>
+      <c r="E2173" s="45"/>
       <c r="F2173" s="7"/>
     </row>
     <row r="2174" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2174" s="11"/>
       <c r="C2174" s="3"/>
       <c r="D2174" s="3"/>
-      <c r="E2174" s="46"/>
+      <c r="E2174" s="45"/>
       <c r="F2174" s="7"/>
     </row>
     <row r="2175" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2175" s="11"/>
       <c r="C2175" s="3"/>
       <c r="D2175" s="3"/>
-      <c r="E2175" s="46"/>
+      <c r="E2175" s="45"/>
       <c r="F2175" s="7"/>
     </row>
     <row r="2176" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2176" s="11"/>
       <c r="C2176" s="3"/>
       <c r="D2176" s="3"/>
-      <c r="E2176" s="46"/>
+      <c r="E2176" s="45"/>
       <c r="F2176" s="7"/>
     </row>
     <row r="2177" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2177" s="11"/>
       <c r="C2177" s="3"/>
       <c r="D2177" s="3"/>
-      <c r="E2177" s="46"/>
+      <c r="E2177" s="45"/>
       <c r="F2177" s="7"/>
     </row>
     <row r="2178" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2178" s="11"/>
       <c r="C2178" s="3"/>
       <c r="D2178" s="3"/>
-      <c r="E2178" s="46"/>
+      <c r="E2178" s="45"/>
       <c r="F2178" s="7"/>
     </row>
     <row r="2179" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2179" s="11"/>
       <c r="C2179" s="3"/>
       <c r="D2179" s="3"/>
-      <c r="E2179" s="46"/>
+      <c r="E2179" s="45"/>
       <c r="F2179" s="7"/>
     </row>
     <row r="2180" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2180" s="11"/>
       <c r="C2180" s="3"/>
       <c r="D2180" s="3"/>
-      <c r="E2180" s="46"/>
+      <c r="E2180" s="45"/>
       <c r="F2180" s="7"/>
     </row>
     <row r="2181" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2181" s="11"/>
       <c r="C2181" s="3"/>
       <c r="D2181" s="3"/>
-      <c r="E2181" s="46"/>
+      <c r="E2181" s="45"/>
       <c r="F2181" s="7"/>
     </row>
     <row r="2182" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2182" s="11"/>
       <c r="C2182" s="3"/>
       <c r="D2182" s="3"/>
-      <c r="E2182" s="46"/>
+      <c r="E2182" s="45"/>
       <c r="F2182" s="7"/>
     </row>
     <row r="2183" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2183" s="11"/>
       <c r="C2183" s="3"/>
       <c r="D2183" s="3"/>
-      <c r="E2183" s="46"/>
+      <c r="E2183" s="45"/>
       <c r="F2183" s="7"/>
     </row>
     <row r="2184" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2184" s="11"/>
       <c r="C2184" s="3"/>
       <c r="D2184" s="3"/>
-      <c r="E2184" s="46"/>
+      <c r="E2184" s="45"/>
       <c r="F2184" s="7"/>
     </row>
     <row r="2185" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2185" s="11"/>
       <c r="C2185" s="3"/>
       <c r="D2185" s="3"/>
-      <c r="E2185" s="46"/>
+      <c r="E2185" s="45"/>
       <c r="F2185" s="7"/>
     </row>
     <row r="2186" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2186" s="11"/>
       <c r="C2186" s="3"/>
       <c r="D2186" s="3"/>
-      <c r="E2186" s="46"/>
+      <c r="E2186" s="45"/>
       <c r="F2186" s="7"/>
     </row>
     <row r="2187" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2187" s="11"/>
       <c r="C2187" s="3"/>
       <c r="D2187" s="3"/>
-      <c r="E2187" s="46"/>
+      <c r="E2187" s="45"/>
       <c r="F2187" s="7"/>
     </row>
     <row r="2188" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2188" s="11"/>
       <c r="C2188" s="3"/>
       <c r="D2188" s="3"/>
-      <c r="E2188" s="46"/>
+      <c r="E2188" s="45"/>
       <c r="F2188" s="7"/>
     </row>
     <row r="2189" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2189" s="11"/>
       <c r="C2189" s="3"/>
       <c r="D2189" s="3"/>
-      <c r="E2189" s="46"/>
+      <c r="E2189" s="45"/>
       <c r="F2189" s="7"/>
     </row>
     <row r="2190" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2190" s="11"/>
       <c r="C2190" s="3"/>
       <c r="D2190" s="3"/>
-      <c r="E2190" s="46"/>
+      <c r="E2190" s="45"/>
       <c r="F2190" s="7"/>
     </row>
     <row r="2191" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2191" s="11"/>
       <c r="C2191" s="3"/>
       <c r="D2191" s="3"/>
-      <c r="E2191" s="46"/>
+      <c r="E2191" s="45"/>
       <c r="F2191" s="7"/>
     </row>
     <row r="2192" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2192" s="11"/>
       <c r="C2192" s="3"/>
       <c r="D2192" s="3"/>
-      <c r="E2192" s="46"/>
+      <c r="E2192" s="45"/>
       <c r="F2192" s="7"/>
     </row>
     <row r="2193" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2193" s="11"/>
       <c r="C2193" s="3"/>
       <c r="D2193" s="3"/>
-      <c r="E2193" s="46"/>
+      <c r="E2193" s="45"/>
       <c r="F2193" s="7"/>
     </row>
     <row r="2194" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2194" s="11"/>
       <c r="C2194" s="3"/>
       <c r="D2194" s="3"/>
-      <c r="E2194" s="46"/>
+      <c r="E2194" s="45"/>
       <c r="F2194" s="7"/>
     </row>
     <row r="2195" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2195" s="11"/>
       <c r="C2195" s="3"/>
       <c r="D2195" s="3"/>
-      <c r="E2195" s="46"/>
+      <c r="E2195" s="45"/>
       <c r="F2195" s="7"/>
     </row>
     <row r="2196" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2196" s="11"/>
       <c r="C2196" s="3"/>
       <c r="D2196" s="3"/>
-      <c r="E2196" s="46"/>
+      <c r="E2196" s="45"/>
       <c r="F2196" s="7"/>
     </row>
     <row r="2197" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2197" s="11"/>
       <c r="C2197" s="3"/>
       <c r="D2197" s="3"/>
-      <c r="E2197" s="46"/>
+      <c r="E2197" s="45"/>
       <c r="F2197" s="7"/>
     </row>
     <row r="2198" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2198" s="11"/>
       <c r="C2198" s="3"/>
       <c r="D2198" s="3"/>
-      <c r="E2198" s="46"/>
+      <c r="E2198" s="45"/>
       <c r="F2198" s="7"/>
     </row>
     <row r="2199" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2199" s="11"/>
       <c r="C2199" s="3"/>
       <c r="D2199" s="3"/>
-      <c r="E2199" s="46"/>
+      <c r="E2199" s="45"/>
       <c r="F2199" s="7"/>
     </row>
     <row r="2200" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2200" s="11"/>
       <c r="C2200" s="3"/>
       <c r="D2200" s="3"/>
-      <c r="E2200" s="46"/>
+      <c r="E2200" s="45"/>
       <c r="F2200" s="7"/>
     </row>
     <row r="2201" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2201" s="11"/>
       <c r="C2201" s="3"/>
       <c r="D2201" s="3"/>
-      <c r="E2201" s="46"/>
+      <c r="E2201" s="45"/>
       <c r="F2201" s="7"/>
     </row>
     <row r="2202" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2202" s="11"/>
       <c r="C2202" s="3"/>
       <c r="D2202" s="3"/>
-      <c r="E2202" s="46"/>
+      <c r="E2202" s="45"/>
       <c r="F2202" s="7"/>
     </row>
     <row r="2203" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2203" s="11"/>
       <c r="C2203" s="3"/>
       <c r="D2203" s="3"/>
-      <c r="E2203" s="46"/>
+      <c r="E2203" s="45"/>
       <c r="F2203" s="7"/>
     </row>
     <row r="2204" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2204" s="11"/>
       <c r="C2204" s="3"/>
       <c r="D2204" s="3"/>
-      <c r="E2204" s="46"/>
+      <c r="E2204" s="45"/>
       <c r="F2204" s="7"/>
     </row>
     <row r="2205" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2205" s="11"/>
       <c r="C2205" s="3"/>
       <c r="D2205" s="3"/>
-      <c r="E2205" s="46"/>
+      <c r="E2205" s="45"/>
       <c r="F2205" s="7"/>
     </row>
     <row r="2206" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2206" s="11"/>
       <c r="C2206" s="3"/>
       <c r="D2206" s="3"/>
-      <c r="E2206" s="46"/>
+      <c r="E2206" s="45"/>
       <c r="F2206" s="7"/>
     </row>
     <row r="2207" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2207" s="11"/>
       <c r="C2207" s="3"/>
       <c r="D2207" s="3"/>
-      <c r="E2207" s="46"/>
+      <c r="E2207" s="45"/>
       <c r="F2207" s="7"/>
     </row>
     <row r="2208" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2208" s="11"/>
       <c r="C2208" s="3"/>
       <c r="D2208" s="3"/>
-      <c r="E2208" s="46"/>
+      <c r="E2208" s="45"/>
       <c r="F2208" s="7"/>
     </row>
     <row r="2209" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2209" s="11"/>
       <c r="C2209" s="3"/>
       <c r="D2209" s="3"/>
-      <c r="E2209" s="46"/>
+      <c r="E2209" s="45"/>
       <c r="F2209" s="7"/>
     </row>
     <row r="2210" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2210" s="11"/>
       <c r="C2210" s="3"/>
       <c r="D2210" s="3"/>
-      <c r="E2210" s="46"/>
+      <c r="E2210" s="45"/>
       <c r="F2210" s="7"/>
     </row>
     <row r="2211" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2211" s="11"/>
       <c r="C2211" s="3"/>
       <c r="D2211" s="3"/>
-      <c r="E2211" s="46"/>
+      <c r="E2211" s="45"/>
       <c r="F2211" s="7"/>
     </row>
     <row r="2212" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2212" s="11"/>
       <c r="C2212" s="3"/>
       <c r="D2212" s="3"/>
-      <c r="E2212" s="46"/>
+      <c r="E2212" s="45"/>
       <c r="F2212" s="7"/>
     </row>
     <row r="2213" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2213" s="11"/>
       <c r="C2213" s="3"/>
       <c r="D2213" s="3"/>
-      <c r="E2213" s="46"/>
+      <c r="E2213" s="45"/>
       <c r="F2213" s="7"/>
     </row>
     <row r="2214" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2214" s="11"/>
       <c r="C2214" s="3"/>
       <c r="D2214" s="3"/>
-      <c r="E2214" s="46"/>
+      <c r="E2214" s="45"/>
       <c r="F2214" s="7"/>
     </row>
     <row r="2215" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2215" s="11"/>
       <c r="C2215" s="3"/>
       <c r="D2215" s="3"/>
-      <c r="E2215" s="46"/>
+      <c r="E2215" s="45"/>
       <c r="F2215" s="7"/>
     </row>
     <row r="2216" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2216" s="11"/>
       <c r="C2216" s="3"/>
       <c r="D2216" s="3"/>
-      <c r="E2216" s="46"/>
+      <c r="E2216" s="45"/>
       <c r="F2216" s="7"/>
     </row>
     <row r="2217" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2217" s="11"/>
       <c r="C2217" s="3"/>
       <c r="D2217" s="3"/>
-      <c r="E2217" s="46"/>
+      <c r="E2217" s="45"/>
       <c r="F2217" s="7"/>
     </row>
     <row r="2218" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2218" s="11"/>
       <c r="C2218" s="3"/>
       <c r="D2218" s="3"/>
-      <c r="E2218" s="46"/>
+      <c r="E2218" s="45"/>
       <c r="F2218" s="7"/>
     </row>
     <row r="2219" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2219" s="11"/>
       <c r="C2219" s="3"/>
       <c r="D2219" s="3"/>
-      <c r="E2219" s="46"/>
+      <c r="E2219" s="45"/>
       <c r="F2219" s="7"/>
     </row>
     <row r="2220" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2220" s="11"/>
       <c r="C2220" s="3"/>
       <c r="D2220" s="3"/>
-      <c r="E2220" s="46"/>
+      <c r="E2220" s="45"/>
       <c r="F2220" s="7"/>
     </row>
     <row r="2221" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2221" s="11"/>
       <c r="C2221" s="5"/>
       <c r="D2221" s="3"/>
-      <c r="E2221" s="46"/>
+      <c r="E2221" s="45"/>
       <c r="F2221" s="7"/>
     </row>
     <row r="2222" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2222" s="11"/>
       <c r="C2222" s="3"/>
       <c r="D2222" s="3"/>
-      <c r="E2222" s="46"/>
+      <c r="E2222" s="45"/>
       <c r="F2222" s="7"/>
     </row>
     <row r="2223" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2223" s="11"/>
       <c r="C2223" s="3"/>
       <c r="D2223" s="3"/>
-      <c r="E2223" s="46"/>
+      <c r="E2223" s="45"/>
       <c r="F2223" s="7"/>
     </row>
     <row r="2224" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2224" s="11"/>
       <c r="C2224" s="3"/>
       <c r="D2224" s="3"/>
-      <c r="E2224" s="46"/>
+      <c r="E2224" s="45"/>
       <c r="F2224" s="7"/>
     </row>
     <row r="2225" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2225" s="11"/>
       <c r="C2225" s="3"/>
       <c r="D2225" s="3"/>
-      <c r="E2225" s="46"/>
+      <c r="E2225" s="45"/>
       <c r="F2225" s="7"/>
     </row>
     <row r="2226" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2226" s="11"/>
       <c r="C2226" s="3"/>
       <c r="D2226" s="3"/>
-      <c r="E2226" s="46"/>
+      <c r="E2226" s="45"/>
       <c r="F2226" s="7"/>
     </row>
     <row r="2227" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2227" s="11"/>
       <c r="C2227" s="3"/>
       <c r="D2227" s="3"/>
-      <c r="E2227" s="46"/>
+      <c r="E2227" s="45"/>
       <c r="F2227" s="7"/>
     </row>
     <row r="2228" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2228" s="11"/>
       <c r="C2228" s="3"/>
       <c r="D2228" s="3"/>
-      <c r="E2228" s="46"/>
+      <c r="E2228" s="45"/>
       <c r="F2228" s="7"/>
     </row>
     <row r="2229" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2229" s="11"/>
       <c r="C2229" s="3"/>
       <c r="D2229" s="3"/>
-      <c r="E2229" s="46"/>
+      <c r="E2229" s="45"/>
       <c r="F2229" s="7"/>
     </row>
     <row r="2230" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2230" s="11"/>
       <c r="C2230" s="3"/>
       <c r="D2230" s="3"/>
-      <c r="E2230" s="46"/>
+      <c r="E2230" s="45"/>
       <c r="F2230" s="7"/>
     </row>
     <row r="2231" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2231" s="11"/>
       <c r="C2231" s="3"/>
       <c r="D2231" s="3"/>
-      <c r="E2231" s="46"/>
+      <c r="E2231" s="45"/>
       <c r="F2231" s="7"/>
     </row>
     <row r="2232" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2232" s="11"/>
       <c r="C2232" s="3"/>
       <c r="D2232" s="3"/>
-      <c r="E2232" s="46"/>
+      <c r="E2232" s="45"/>
       <c r="F2232" s="7"/>
     </row>
     <row r="2233" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2233" s="11"/>
       <c r="C2233" s="3"/>
       <c r="D2233" s="3"/>
-      <c r="E2233" s="46"/>
+      <c r="E2233" s="45"/>
       <c r="F2233" s="7"/>
     </row>
     <row r="2234" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2234" s="11"/>
       <c r="C2234" s="3"/>
       <c r="D2234" s="3"/>
-      <c r="E2234" s="46"/>
+      <c r="E2234" s="45"/>
       <c r="F2234" s="7"/>
     </row>
     <row r="2235" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2235" s="11"/>
       <c r="C2235" s="3"/>
       <c r="D2235" s="3"/>
-      <c r="E2235" s="46"/>
+      <c r="E2235" s="45"/>
       <c r="F2235" s="7"/>
     </row>
     <row r="2236" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2236" s="11"/>
       <c r="C2236" s="3"/>
       <c r="D2236" s="3"/>
-      <c r="E2236" s="46"/>
+      <c r="E2236" s="45"/>
       <c r="F2236" s="7"/>
     </row>
     <row r="2237" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2237" s="11"/>
       <c r="C2237" s="3"/>
       <c r="D2237" s="3"/>
-      <c r="E2237" s="46"/>
+      <c r="E2237" s="45"/>
       <c r="F2237" s="7"/>
     </row>
     <row r="2238" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2238" s="11"/>
       <c r="C2238" s="3"/>
       <c r="D2238" s="3"/>
-      <c r="E2238" s="46"/>
+      <c r="E2238" s="45"/>
       <c r="F2238" s="7"/>
     </row>
     <row r="2239" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2239" s="11"/>
       <c r="C2239" s="3"/>
       <c r="D2239" s="3"/>
-      <c r="E2239" s="46"/>
+      <c r="E2239" s="45"/>
       <c r="F2239" s="7"/>
     </row>
     <row r="2240" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2240" s="11"/>
       <c r="C2240" s="3"/>
       <c r="D2240" s="3"/>
-      <c r="E2240" s="46"/>
+      <c r="E2240" s="45"/>
       <c r="F2240" s="7"/>
     </row>
     <row r="2241" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2241" s="11"/>
       <c r="C2241" s="3"/>
       <c r="D2241" s="3"/>
-      <c r="E2241" s="46"/>
+      <c r="E2241" s="45"/>
       <c r="F2241" s="7"/>
     </row>
     <row r="2242" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2242" s="11"/>
       <c r="C2242" s="3"/>
       <c r="D2242" s="3"/>
-      <c r="E2242" s="46"/>
+      <c r="E2242" s="45"/>
       <c r="F2242" s="7"/>
     </row>
     <row r="2243" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2243" s="11"/>
       <c r="C2243" s="3"/>
       <c r="D2243" s="3"/>
-      <c r="E2243" s="46"/>
+      <c r="E2243" s="45"/>
       <c r="F2243" s="7"/>
     </row>
     <row r="2244" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2244" s="11"/>
       <c r="C2244" s="3"/>
       <c r="D2244" s="3"/>
-      <c r="E2244" s="46"/>
+      <c r="E2244" s="45"/>
       <c r="F2244" s="7"/>
     </row>
     <row r="2245" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2245" s="11"/>
       <c r="C2245" s="3"/>
       <c r="D2245" s="3"/>
-      <c r="E2245" s="46"/>
+      <c r="E2245" s="45"/>
       <c r="F2245" s="7"/>
     </row>
     <row r="2246" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2246" s="11"/>
       <c r="C2246" s="3"/>
       <c r="D2246" s="3"/>
-      <c r="E2246" s="46"/>
+      <c r="E2246" s="45"/>
       <c r="F2246" s="7"/>
     </row>
     <row r="2247" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2247" s="11"/>
       <c r="C2247" s="3"/>
       <c r="D2247" s="3"/>
-      <c r="E2247" s="46"/>
+      <c r="E2247" s="45"/>
       <c r="F2247" s="7"/>
     </row>
     <row r="2248" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2248" s="11"/>
       <c r="C2248" s="3"/>
       <c r="D2248" s="3"/>
-      <c r="E2248" s="46"/>
+      <c r="E2248" s="45"/>
       <c r="F2248" s="7"/>
     </row>
     <row r="2249" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2249" s="11"/>
       <c r="C2249" s="3"/>
       <c r="D2249" s="3"/>
-      <c r="E2249" s="46"/>
+      <c r="E2249" s="45"/>
       <c r="F2249" s="7"/>
     </row>
     <row r="2250" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2250" s="11"/>
       <c r="C2250" s="3"/>
       <c r="D2250" s="3"/>
-      <c r="E2250" s="46"/>
+      <c r="E2250" s="45"/>
       <c r="F2250" s="7"/>
     </row>
     <row r="2251" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2251" s="11"/>
       <c r="C2251" s="3"/>
       <c r="D2251" s="3"/>
-      <c r="E2251" s="46"/>
+      <c r="E2251" s="45"/>
       <c r="F2251" s="7"/>
     </row>
     <row r="2252" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2252" s="11"/>
       <c r="C2252" s="3"/>
       <c r="D2252" s="3"/>
-      <c r="E2252" s="46"/>
+      <c r="E2252" s="45"/>
       <c r="F2252" s="7"/>
     </row>
     <row r="2253" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2253" s="11"/>
       <c r="C2253" s="3"/>
       <c r="D2253" s="3"/>
-      <c r="E2253" s="46"/>
+      <c r="E2253" s="45"/>
       <c r="F2253" s="7"/>
     </row>
     <row r="2254" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2254" s="11"/>
       <c r="C2254" s="3"/>
       <c r="D2254" s="3"/>
-      <c r="E2254" s="46"/>
+      <c r="E2254" s="45"/>
       <c r="F2254" s="7"/>
     </row>
     <row r="2255" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2255" s="11"/>
       <c r="C2255" s="3"/>
       <c r="D2255" s="3"/>
-      <c r="E2255" s="46"/>
+      <c r="E2255" s="45"/>
       <c r="F2255" s="7"/>
     </row>
     <row r="2256" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2256" s="11"/>
       <c r="C2256" s="3"/>
       <c r="D2256" s="3"/>
-      <c r="E2256" s="46"/>
+      <c r="E2256" s="45"/>
       <c r="F2256" s="7"/>
     </row>
     <row r="2257" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2257" s="11"/>
       <c r="C2257" s="3"/>
       <c r="D2257" s="3"/>
-      <c r="E2257" s="46"/>
+      <c r="E2257" s="45"/>
       <c r="F2257" s="7"/>
     </row>
     <row r="2258" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2258" s="11"/>
       <c r="C2258" s="3"/>
       <c r="D2258" s="3"/>
-      <c r="E2258" s="46"/>
+      <c r="E2258" s="45"/>
       <c r="F2258" s="7"/>
     </row>
     <row r="2259" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2259" s="11"/>
       <c r="C2259" s="3"/>
       <c r="D2259" s="3"/>
-      <c r="E2259" s="46"/>
+      <c r="E2259" s="45"/>
       <c r="F2259" s="7"/>
     </row>
     <row r="2260" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2260" s="11"/>
       <c r="C2260" s="3"/>
       <c r="D2260" s="3"/>
-      <c r="E2260" s="46"/>
+      <c r="E2260" s="45"/>
       <c r="F2260" s="7"/>
     </row>
     <row r="2261" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2261" s="11"/>
       <c r="C2261" s="3"/>
       <c r="D2261" s="3"/>
-      <c r="E2261" s="46"/>
+      <c r="E2261" s="45"/>
       <c r="F2261" s="7"/>
     </row>
     <row r="2262" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2262" s="11"/>
       <c r="C2262" s="3"/>
       <c r="D2262" s="3"/>
-      <c r="E2262" s="46"/>
+      <c r="E2262" s="45"/>
       <c r="F2262" s="7"/>
     </row>
     <row r="2263" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2263" s="11"/>
       <c r="C2263" s="3"/>
       <c r="D2263" s="3"/>
-      <c r="E2263" s="46"/>
+      <c r="E2263" s="45"/>
       <c r="F2263" s="7"/>
     </row>
     <row r="2264" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2264" s="11"/>
       <c r="C2264" s="3"/>
       <c r="D2264" s="3"/>
-      <c r="E2264" s="46"/>
+      <c r="E2264" s="45"/>
       <c r="F2264" s="7"/>
     </row>
     <row r="2265" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2265" s="11"/>
       <c r="C2265" s="3"/>
       <c r="D2265" s="3"/>
-      <c r="E2265" s="46"/>
+      <c r="E2265" s="45"/>
       <c r="F2265" s="7"/>
     </row>
     <row r="2266" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2266" s="11"/>
       <c r="C2266" s="3"/>
       <c r="D2266" s="3"/>
-      <c r="E2266" s="46"/>
+      <c r="E2266" s="45"/>
       <c r="F2266" s="7"/>
     </row>
     <row r="2267" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2267" s="11"/>
       <c r="C2267" s="3"/>
       <c r="D2267" s="3"/>
-      <c r="E2267" s="46"/>
+      <c r="E2267" s="45"/>
       <c r="F2267" s="7"/>
     </row>
     <row r="2268" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2268" s="11"/>
       <c r="C2268" s="3"/>
       <c r="D2268" s="3"/>
-      <c r="E2268" s="46"/>
+      <c r="E2268" s="45"/>
       <c r="F2268" s="7"/>
     </row>
     <row r="2269" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2269" s="11"/>
       <c r="C2269" s="3"/>
       <c r="D2269" s="3"/>
-      <c r="E2269" s="46"/>
+      <c r="E2269" s="45"/>
       <c r="F2269" s="7"/>
     </row>
     <row r="2270" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2270" s="11"/>
       <c r="C2270" s="3"/>
       <c r="D2270" s="3"/>
-      <c r="E2270" s="46"/>
+      <c r="E2270" s="45"/>
       <c r="F2270" s="7"/>
     </row>
     <row r="2271" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2271" s="11"/>
       <c r="C2271" s="3"/>
       <c r="D2271" s="3"/>
-      <c r="E2271" s="46"/>
+      <c r="E2271" s="45"/>
       <c r="F2271" s="7"/>
     </row>
     <row r="2272" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2272" s="11"/>
       <c r="C2272" s="3"/>
       <c r="D2272" s="3"/>
-      <c r="E2272" s="46"/>
+      <c r="E2272" s="45"/>
       <c r="F2272" s="7"/>
     </row>
     <row r="2273" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2273" s="11"/>
       <c r="C2273" s="3"/>
       <c r="D2273" s="3"/>
-      <c r="E2273" s="46"/>
+      <c r="E2273" s="45"/>
       <c r="F2273" s="7"/>
     </row>
     <row r="2274" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2274" s="11"/>
       <c r="C2274" s="3"/>
       <c r="D2274" s="3"/>
-      <c r="E2274" s="46"/>
+      <c r="E2274" s="45"/>
       <c r="F2274" s="7"/>
     </row>
     <row r="2275" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2275" s="11"/>
       <c r="C2275" s="3"/>
       <c r="D2275" s="3"/>
-      <c r="E2275" s="46"/>
+      <c r="E2275" s="45"/>
       <c r="F2275" s="7"/>
     </row>
     <row r="2276" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2276" s="11"/>
       <c r="C2276" s="3"/>
       <c r="D2276" s="3"/>
-      <c r="E2276" s="46"/>
+      <c r="E2276" s="45"/>
       <c r="F2276" s="7"/>
     </row>
     <row r="2277" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2277" s="11"/>
       <c r="C2277" s="3"/>
       <c r="D2277" s="3"/>
-      <c r="E2277" s="46"/>
+      <c r="E2277" s="45"/>
       <c r="F2277" s="7"/>
     </row>
     <row r="2278" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2278" s="11"/>
       <c r="C2278" s="3"/>
       <c r="D2278" s="3"/>
-      <c r="E2278" s="46"/>
+      <c r="E2278" s="45"/>
       <c r="F2278" s="7"/>
     </row>
     <row r="2279" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2279" s="11"/>
       <c r="C2279" s="3"/>
       <c r="D2279" s="3"/>
-      <c r="E2279" s="46"/>
+      <c r="E2279" s="45"/>
       <c r="F2279" s="7"/>
     </row>
     <row r="2280" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2280" s="11"/>
       <c r="C2280" s="3"/>
       <c r="D2280" s="3"/>
-      <c r="E2280" s="46"/>
+      <c r="E2280" s="45"/>
       <c r="F2280" s="7"/>
     </row>
     <row r="2281" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2281" s="11"/>
       <c r="C2281" s="3"/>
       <c r="D2281" s="3"/>
-      <c r="E2281" s="46"/>
+      <c r="E2281" s="45"/>
       <c r="F2281" s="7"/>
     </row>
     <row r="2282" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2282" s="11"/>
       <c r="C2282" s="3"/>
       <c r="D2282" s="3"/>
-      <c r="E2282" s="46"/>
+      <c r="E2282" s="45"/>
       <c r="F2282" s="7"/>
     </row>
     <row r="2283" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2283" s="11"/>
       <c r="C2283" s="3"/>
       <c r="D2283" s="3"/>
-      <c r="E2283" s="46"/>
+      <c r="E2283" s="45"/>
       <c r="F2283" s="7"/>
     </row>
     <row r="2284" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2284" s="11"/>
       <c r="C2284" s="3"/>
       <c r="D2284" s="3"/>
-      <c r="E2284" s="46"/>
+      <c r="E2284" s="45"/>
       <c r="F2284" s="7"/>
     </row>
     <row r="2285" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2285" s="11"/>
       <c r="C2285" s="3"/>
       <c r="D2285" s="3"/>
-      <c r="E2285" s="46"/>
+      <c r="E2285" s="45"/>
       <c r="F2285" s="7"/>
     </row>
     <row r="2286" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2286" s="11"/>
       <c r="C2286" s="3"/>
       <c r="D2286" s="3"/>
-      <c r="E2286" s="46"/>
+      <c r="E2286" s="45"/>
       <c r="F2286" s="7"/>
     </row>
     <row r="2287" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2287" s="11"/>
       <c r="C2287" s="3"/>
       <c r="D2287" s="3"/>
-      <c r="E2287" s="46"/>
+      <c r="E2287" s="45"/>
       <c r="F2287" s="7"/>
     </row>
     <row r="2288" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2288" s="11"/>
       <c r="C2288" s="3"/>
       <c r="D2288" s="3"/>
-      <c r="E2288" s="46"/>
+      <c r="E2288" s="45"/>
       <c r="F2288" s="7"/>
     </row>
     <row r="2289" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2289" s="11"/>
       <c r="C2289" s="3"/>
       <c r="D2289" s="3"/>
-      <c r="E2289" s="46"/>
+      <c r="E2289" s="45"/>
       <c r="F2289" s="7"/>
     </row>
     <row r="2290" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2290" s="11"/>
       <c r="C2290" s="3"/>
       <c r="D2290" s="3"/>
-      <c r="E2290" s="46"/>
+      <c r="E2290" s="45"/>
       <c r="F2290" s="7"/>
     </row>
     <row r="2291" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2291" s="11"/>
       <c r="C2291" s="3"/>
       <c r="D2291" s="3"/>
-      <c r="E2291" s="46"/>
+      <c r="E2291" s="45"/>
       <c r="F2291" s="7"/>
     </row>
     <row r="2292" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2292" s="11"/>
       <c r="C2292" s="3"/>
       <c r="D2292" s="3"/>
-      <c r="E2292" s="46"/>
+      <c r="E2292" s="45"/>
       <c r="F2292" s="7"/>
     </row>
     <row r="2293" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2293" s="11"/>
       <c r="C2293" s="3"/>
       <c r="D2293" s="3"/>
-      <c r="E2293" s="46"/>
+      <c r="E2293" s="45"/>
       <c r="F2293" s="7"/>
     </row>
     <row r="2294" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2294" s="11"/>
       <c r="C2294" s="3"/>
       <c r="D2294" s="3"/>
-      <c r="E2294" s="46"/>
+      <c r="E2294" s="45"/>
       <c r="F2294" s="7"/>
     </row>
     <row r="2295" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2295" s="11"/>
       <c r="C2295" s="3"/>
       <c r="D2295" s="3"/>
-      <c r="E2295" s="46"/>
+      <c r="E2295" s="45"/>
       <c r="F2295" s="7"/>
     </row>
     <row r="2296" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2296" s="11"/>
       <c r="C2296" s="3"/>
       <c r="D2296" s="3"/>
-      <c r="E2296" s="46"/>
+      <c r="E2296" s="45"/>
       <c r="F2296" s="7"/>
     </row>
     <row r="2297" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2297" s="11"/>
       <c r="C2297" s="3"/>
       <c r="D2297" s="3"/>
-      <c r="E2297" s="46"/>
+      <c r="E2297" s="45"/>
       <c r="F2297" s="7"/>
     </row>
     <row r="2298" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2298" s="11"/>
       <c r="C2298" s="3"/>
       <c r="D2298" s="3"/>
-      <c r="E2298" s="46"/>
+      <c r="E2298" s="45"/>
       <c r="F2298" s="7"/>
     </row>
     <row r="2299" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2299" s="11"/>
       <c r="C2299" s="3"/>
       <c r="D2299" s="3"/>
-      <c r="E2299" s="46"/>
+      <c r="E2299" s="45"/>
       <c r="F2299" s="7"/>
     </row>
     <row r="2300" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2300" s="11"/>
       <c r="C2300" s="3"/>
       <c r="D2300" s="3"/>
-      <c r="E2300" s="46"/>
+      <c r="E2300" s="45"/>
       <c r="F2300" s="7"/>
     </row>
     <row r="2301" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2301" s="11"/>
       <c r="C2301" s="3"/>
       <c r="D2301" s="3"/>
-      <c r="E2301" s="46"/>
+      <c r="E2301" s="45"/>
       <c r="F2301" s="7"/>
     </row>
     <row r="2302" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2302" s="11"/>
       <c r="C2302" s="3"/>
       <c r="D2302" s="3"/>
-      <c r="E2302" s="46"/>
+      <c r="E2302" s="45"/>
       <c r="F2302" s="7"/>
     </row>
     <row r="2303" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2303" s="11"/>
       <c r="C2303" s="3"/>
       <c r="D2303" s="3"/>
-      <c r="E2303" s="46"/>
+      <c r="E2303" s="45"/>
       <c r="F2303" s="7"/>
     </row>
     <row r="2304" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2304" s="11"/>
       <c r="C2304" s="3"/>
       <c r="D2304" s="3"/>
-      <c r="E2304" s="46"/>
+      <c r="E2304" s="45"/>
       <c r="F2304" s="7"/>
     </row>
     <row r="2305" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2305" s="11"/>
       <c r="C2305" s="3"/>
       <c r="D2305" s="3"/>
-      <c r="E2305" s="46"/>
+      <c r="E2305" s="45"/>
       <c r="F2305" s="7"/>
     </row>
     <row r="2306" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2306" s="11"/>
       <c r="C2306" s="3"/>
       <c r="D2306" s="3"/>
-      <c r="E2306" s="46"/>
+      <c r="E2306" s="45"/>
       <c r="F2306" s="7"/>
     </row>
     <row r="2307" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2307" s="11"/>
       <c r="C2307" s="3"/>
       <c r="D2307" s="3"/>
-      <c r="E2307" s="46"/>
+      <c r="E2307" s="45"/>
       <c r="F2307" s="7"/>
     </row>
     <row r="2308" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2308" s="11"/>
       <c r="C2308" s="3"/>
       <c r="D2308" s="3"/>
-      <c r="E2308" s="46"/>
+      <c r="E2308" s="45"/>
       <c r="F2308" s="7"/>
     </row>
     <row r="2309" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2309" s="11"/>
       <c r="C2309" s="3"/>
       <c r="D2309" s="3"/>
-      <c r="E2309" s="46"/>
+      <c r="E2309" s="45"/>
       <c r="F2309" s="7"/>
     </row>
     <row r="2310" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2310" s="11"/>
       <c r="C2310" s="3"/>
       <c r="D2310" s="3"/>
-      <c r="E2310" s="46"/>
+      <c r="E2310" s="45"/>
       <c r="F2310" s="7"/>
     </row>
     <row r="2311" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2311" s="11"/>
       <c r="C2311" s="3"/>
       <c r="D2311" s="3"/>
-      <c r="E2311" s="46"/>
+      <c r="E2311" s="45"/>
       <c r="F2311" s="7"/>
     </row>
     <row r="2312" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2312" s="11"/>
       <c r="C2312" s="3"/>
       <c r="D2312" s="3"/>
-      <c r="E2312" s="46"/>
+      <c r="E2312" s="45"/>
       <c r="F2312" s="7"/>
     </row>
     <row r="2313" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2313" s="11"/>
       <c r="C2313" s="3"/>
       <c r="D2313" s="3"/>
-      <c r="E2313" s="46"/>
+      <c r="E2313" s="45"/>
       <c r="F2313" s="7"/>
     </row>
     <row r="2314" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2314" s="11"/>
       <c r="C2314" s="3"/>
       <c r="D2314" s="3"/>
-      <c r="E2314" s="46"/>
+      <c r="E2314" s="45"/>
       <c r="F2314" s="7"/>
     </row>
     <row r="2315" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2315" s="11"/>
       <c r="C2315" s="3"/>
       <c r="D2315" s="3"/>
-      <c r="E2315" s="46"/>
+      <c r="E2315" s="45"/>
       <c r="F2315" s="7"/>
     </row>
     <row r="2316" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2316" s="11"/>
       <c r="C2316" s="3"/>
       <c r="D2316" s="3"/>
-      <c r="E2316" s="46"/>
+      <c r="E2316" s="45"/>
       <c r="F2316" s="7"/>
     </row>
     <row r="2317" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2317" s="11"/>
       <c r="C2317" s="3"/>
       <c r="D2317" s="3"/>
-      <c r="E2317" s="46"/>
+      <c r="E2317" s="45"/>
       <c r="F2317" s="7"/>
     </row>
     <row r="2318" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2318" s="11"/>
       <c r="C2318" s="3"/>
       <c r="D2318" s="3"/>
-      <c r="E2318" s="46"/>
+      <c r="E2318" s="45"/>
       <c r="F2318" s="7"/>
     </row>
     <row r="2319" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2319" s="11"/>
       <c r="C2319" s="3"/>
       <c r="D2319" s="3"/>
-      <c r="E2319" s="46"/>
+      <c r="E2319" s="45"/>
       <c r="F2319" s="7"/>
     </row>
     <row r="2320" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2320" s="11"/>
       <c r="C2320" s="3"/>
       <c r="D2320" s="3"/>
-      <c r="E2320" s="46"/>
+      <c r="E2320" s="45"/>
       <c r="F2320" s="7"/>
     </row>
     <row r="2321" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2321" s="11"/>
       <c r="C2321" s="3"/>
       <c r="D2321" s="3"/>
-      <c r="E2321" s="46"/>
+      <c r="E2321" s="45"/>
       <c r="F2321" s="7"/>
     </row>
     <row r="2322" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2322" s="11"/>
       <c r="C2322" s="3"/>
       <c r="D2322" s="3"/>
-      <c r="E2322" s="46"/>
+      <c r="E2322" s="45"/>
       <c r="F2322" s="7"/>
     </row>
     <row r="2323" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2323" s="11"/>
       <c r="C2323" s="3"/>
       <c r="D2323" s="3"/>
-      <c r="E2323" s="46"/>
+      <c r="E2323" s="45"/>
       <c r="F2323" s="7"/>
     </row>
     <row r="2324" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2324" s="11"/>
       <c r="C2324" s="3"/>
       <c r="D2324" s="3"/>
-      <c r="E2324" s="46"/>
+      <c r="E2324" s="45"/>
       <c r="F2324" s="7"/>
     </row>
     <row r="2325" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2325" s="11"/>
       <c r="C2325" s="3"/>
       <c r="D2325" s="3"/>
-      <c r="E2325" s="46"/>
+      <c r="E2325" s="45"/>
       <c r="F2325" s="7"/>
     </row>
     <row r="2326" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2326" s="11"/>
       <c r="C2326" s="3"/>
       <c r="D2326" s="3"/>
-      <c r="E2326" s="46"/>
+      <c r="E2326" s="45"/>
       <c r="F2326" s="7"/>
     </row>
     <row r="2327" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2327" s="11"/>
       <c r="C2327" s="3"/>
       <c r="D2327" s="3"/>
-      <c r="E2327" s="46"/>
+      <c r="E2327" s="45"/>
       <c r="F2327" s="7"/>
     </row>
     <row r="2328" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2328" s="11"/>
       <c r="C2328" s="3"/>
       <c r="D2328" s="3"/>
-      <c r="E2328" s="46"/>
+      <c r="E2328" s="45"/>
       <c r="F2328" s="7"/>
     </row>
     <row r="2329" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2329" s="11"/>
       <c r="C2329" s="3"/>
       <c r="D2329" s="3"/>
-      <c r="E2329" s="46"/>
+      <c r="E2329" s="45"/>
       <c r="F2329" s="7"/>
     </row>
     <row r="2330" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2330" s="11"/>
       <c r="C2330" s="3"/>
       <c r="D2330" s="3"/>
-      <c r="E2330" s="46"/>
+      <c r="E2330" s="45"/>
       <c r="F2330" s="7"/>
     </row>
     <row r="2331" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2331" s="11"/>
       <c r="C2331" s="3"/>
       <c r="D2331" s="3"/>
-      <c r="E2331" s="46"/>
+      <c r="E2331" s="45"/>
       <c r="F2331" s="7"/>
     </row>
     <row r="2332" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2332" s="11"/>
       <c r="C2332" s="3"/>
       <c r="D2332" s="3"/>
-      <c r="E2332" s="46"/>
+      <c r="E2332" s="45"/>
       <c r="F2332" s="7"/>
     </row>
     <row r="2333" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2333" s="11"/>
       <c r="C2333" s="3"/>
       <c r="D2333" s="3"/>
-      <c r="E2333" s="46"/>
+      <c r="E2333" s="45"/>
       <c r="F2333" s="7"/>
     </row>
     <row r="2334" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2334" s="11"/>
       <c r="C2334" s="3"/>
       <c r="D2334" s="3"/>
-      <c r="E2334" s="46"/>
+      <c r="E2334" s="45"/>
       <c r="F2334" s="7"/>
     </row>
     <row r="2335" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2335" s="11"/>
       <c r="C2335" s="3"/>
       <c r="D2335" s="3"/>
-      <c r="E2335" s="46"/>
+      <c r="E2335" s="45"/>
       <c r="F2335" s="7"/>
     </row>
     <row r="2336" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2336" s="11"/>
       <c r="C2336" s="3"/>
       <c r="D2336" s="3"/>
-      <c r="E2336" s="46"/>
+      <c r="E2336" s="45"/>
       <c r="F2336" s="7"/>
     </row>
     <row r="2337" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2337" s="11"/>
       <c r="C2337" s="3"/>
       <c r="D2337" s="3"/>
-      <c r="E2337" s="46"/>
+      <c r="E2337" s="45"/>
       <c r="F2337" s="7"/>
     </row>
     <row r="2338" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2338" s="11"/>
       <c r="C2338" s="3"/>
       <c r="D2338" s="3"/>
-      <c r="E2338" s="46"/>
+      <c r="E2338" s="45"/>
       <c r="F2338" s="7"/>
     </row>
     <row r="2339" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2339" s="11"/>
       <c r="C2339" s="3"/>
       <c r="D2339" s="3"/>
-      <c r="E2339" s="46"/>
+      <c r="E2339" s="45"/>
       <c r="F2339" s="7"/>
     </row>
     <row r="2340" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2340" s="11"/>
       <c r="C2340" s="3"/>
       <c r="D2340" s="3"/>
-      <c r="E2340" s="46"/>
+      <c r="E2340" s="45"/>
       <c r="F2340" s="7"/>
     </row>
     <row r="2341" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2341" s="11"/>
       <c r="C2341" s="3"/>
       <c r="D2341" s="3"/>
-      <c r="E2341" s="46"/>
+      <c r="E2341" s="45"/>
       <c r="F2341" s="7"/>
     </row>
     <row r="2342" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2342" s="11"/>
       <c r="C2342" s="3"/>
       <c r="D2342" s="3"/>
-      <c r="E2342" s="46"/>
+      <c r="E2342" s="45"/>
       <c r="F2342" s="7"/>
     </row>
     <row r="2343" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2343" s="11"/>
       <c r="C2343" s="3"/>
       <c r="D2343" s="3"/>
-      <c r="E2343" s="46"/>
+      <c r="E2343" s="45"/>
       <c r="F2343" s="7"/>
     </row>
     <row r="2344" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2344" s="11"/>
       <c r="C2344" s="3"/>
       <c r="D2344" s="3"/>
-      <c r="E2344" s="46"/>
+      <c r="E2344" s="45"/>
       <c r="F2344" s="7"/>
     </row>
     <row r="2345" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2345" s="11"/>
       <c r="C2345" s="3"/>
       <c r="D2345" s="3"/>
-      <c r="E2345" s="46"/>
+      <c r="E2345" s="45"/>
       <c r="F2345" s="7"/>
     </row>
     <row r="2346" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2346" s="11"/>
       <c r="C2346" s="3"/>
       <c r="D2346" s="3"/>
-      <c r="E2346" s="46"/>
+      <c r="E2346" s="45"/>
       <c r="F2346" s="7"/>
     </row>
     <row r="2347" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2347" s="11"/>
       <c r="C2347" s="3"/>
       <c r="D2347" s="3"/>
-      <c r="E2347" s="46"/>
+      <c r="E2347" s="45"/>
       <c r="F2347" s="7"/>
     </row>
     <row r="2348" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2348" s="11"/>
       <c r="C2348" s="3"/>
       <c r="D2348" s="3"/>
-      <c r="E2348" s="46"/>
+      <c r="E2348" s="45"/>
       <c r="F2348" s="7"/>
     </row>
     <row r="2349" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2349" s="11"/>
       <c r="C2349" s="3"/>
       <c r="D2349" s="3"/>
-      <c r="E2349" s="46"/>
+      <c r="E2349" s="45"/>
       <c r="F2349" s="7"/>
     </row>
     <row r="2350" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2350" s="11"/>
       <c r="C2350" s="3"/>
       <c r="D2350" s="3"/>
-      <c r="E2350" s="46"/>
+      <c r="E2350" s="45"/>
       <c r="F2350" s="7"/>
     </row>
     <row r="2351" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2351" s="11"/>
       <c r="C2351" s="3"/>
       <c r="D2351" s="3"/>
-      <c r="E2351" s="46"/>
+      <c r="E2351" s="45"/>
       <c r="F2351" s="7"/>
     </row>
     <row r="2352" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2352" s="11"/>
       <c r="C2352" s="3"/>
       <c r="D2352" s="3"/>
-      <c r="E2352" s="46"/>
+      <c r="E2352" s="45"/>
       <c r="F2352" s="7"/>
     </row>
     <row r="2353" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2353" s="11"/>
       <c r="C2353" s="3"/>
       <c r="D2353" s="3"/>
-      <c r="E2353" s="46"/>
+      <c r="E2353" s="45"/>
       <c r="F2353" s="7"/>
     </row>
     <row r="2354" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2354" s="11"/>
       <c r="C2354" s="3"/>
       <c r="D2354" s="3"/>
-      <c r="E2354" s="46"/>
+      <c r="E2354" s="45"/>
       <c r="F2354" s="7"/>
     </row>
     <row r="2355" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2355" s="11"/>
       <c r="C2355" s="3"/>
       <c r="D2355" s="3"/>
-      <c r="E2355" s="46"/>
+      <c r="E2355" s="45"/>
       <c r="F2355" s="7"/>
     </row>
     <row r="2356" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2356" s="11"/>
       <c r="C2356" s="3"/>
       <c r="D2356" s="3"/>
-      <c r="E2356" s="46"/>
+      <c r="E2356" s="45"/>
       <c r="F2356" s="7"/>
     </row>
     <row r="2357" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2357" s="11"/>
       <c r="C2357" s="3"/>
       <c r="D2357" s="3"/>
-      <c r="E2357" s="46"/>
+      <c r="E2357" s="45"/>
       <c r="F2357" s="7"/>
     </row>
     <row r="2358" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2358" s="11"/>
       <c r="C2358" s="3"/>
       <c r="D2358" s="3"/>
-      <c r="E2358" s="46"/>
+      <c r="E2358" s="45"/>
       <c r="F2358" s="7"/>
     </row>
     <row r="2359" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2359" s="11"/>
       <c r="C2359" s="3"/>
       <c r="D2359" s="3"/>
-      <c r="E2359" s="46"/>
+      <c r="E2359" s="45"/>
       <c r="F2359" s="7"/>
     </row>
     <row r="2360" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2360" s="11"/>
       <c r="C2360" s="3"/>
       <c r="D2360" s="3"/>
-      <c r="E2360" s="46"/>
+      <c r="E2360" s="45"/>
       <c r="F2360" s="7"/>
     </row>
     <row r="2361" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2361" s="11"/>
       <c r="C2361" s="3"/>
       <c r="D2361" s="3"/>
-      <c r="E2361" s="46"/>
+      <c r="E2361" s="45"/>
       <c r="F2361" s="7"/>
     </row>
     <row r="2362" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2362" s="11"/>
       <c r="C2362" s="3"/>
       <c r="D2362" s="3"/>
-      <c r="E2362" s="46"/>
+      <c r="E2362" s="45"/>
       <c r="F2362" s="7"/>
     </row>
     <row r="2363" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2363" s="11"/>
       <c r="C2363" s="3"/>
       <c r="D2363" s="3"/>
-      <c r="E2363" s="46"/>
+      <c r="E2363" s="45"/>
       <c r="F2363" s="7"/>
     </row>
     <row r="2364" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2364" s="11"/>
       <c r="C2364" s="3"/>
       <c r="D2364" s="3"/>
-      <c r="E2364" s="46"/>
+      <c r="E2364" s="45"/>
       <c r="F2364" s="7"/>
     </row>
     <row r="2365" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2365" s="11"/>
       <c r="C2365" s="3"/>
       <c r="D2365" s="3"/>
-      <c r="E2365" s="46"/>
+      <c r="E2365" s="45"/>
       <c r="F2365" s="7"/>
     </row>
     <row r="2366" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2366" s="11"/>
       <c r="C2366" s="3"/>
       <c r="D2366" s="3"/>
-      <c r="E2366" s="46"/>
+      <c r="E2366" s="45"/>
       <c r="F2366" s="7"/>
     </row>
     <row r="2367" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2367" s="11"/>
       <c r="C2367" s="3"/>
       <c r="D2367" s="3"/>
-      <c r="E2367" s="46"/>
+      <c r="E2367" s="45"/>
       <c r="F2367" s="7"/>
     </row>
     <row r="2368" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2368" s="11"/>
       <c r="C2368" s="3"/>
       <c r="D2368" s="3"/>
-      <c r="E2368" s="46"/>
+      <c r="E2368" s="45"/>
       <c r="F2368" s="7"/>
     </row>
     <row r="2369" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2369" s="11"/>
       <c r="C2369" s="3"/>
       <c r="D2369" s="3"/>
-      <c r="E2369" s="46"/>
+      <c r="E2369" s="45"/>
       <c r="F2369" s="7"/>
     </row>
     <row r="2370" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2370" s="11"/>
       <c r="C2370" s="3"/>
       <c r="D2370" s="3"/>
-      <c r="E2370" s="46"/>
+      <c r="E2370" s="45"/>
       <c r="F2370" s="7"/>
     </row>
     <row r="2371" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2371" s="11"/>
       <c r="C2371" s="3"/>
       <c r="D2371" s="3"/>
-      <c r="E2371" s="46"/>
+      <c r="E2371" s="45"/>
       <c r="F2371" s="7"/>
     </row>
     <row r="2372" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2372" s="11"/>
       <c r="C2372" s="3"/>
       <c r="D2372" s="3"/>
-      <c r="E2372" s="46"/>
+      <c r="E2372" s="45"/>
       <c r="F2372" s="7"/>
     </row>
     <row r="2373" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2373" s="11"/>
       <c r="C2373" s="3"/>
       <c r="D2373" s="3"/>
-      <c r="E2373" s="46"/>
+      <c r="E2373" s="45"/>
       <c r="F2373" s="7"/>
     </row>
     <row r="2374" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2374" s="11"/>
       <c r="C2374" s="3"/>
       <c r="D2374" s="3"/>
-      <c r="E2374" s="46"/>
+      <c r="E2374" s="45"/>
       <c r="F2374" s="7"/>
     </row>
     <row r="2375" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2375" s="11"/>
       <c r="C2375" s="3"/>
       <c r="D2375" s="3"/>
-      <c r="E2375" s="46"/>
+      <c r="E2375" s="45"/>
       <c r="F2375" s="7"/>
     </row>
     <row r="2376" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2376" s="11"/>
       <c r="C2376" s="3"/>
       <c r="D2376" s="3"/>
-      <c r="E2376" s="46"/>
+      <c r="E2376" s="45"/>
       <c r="F2376" s="7"/>
     </row>
     <row r="2377" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2377" s="11"/>
       <c r="C2377" s="3"/>
       <c r="D2377" s="3"/>
-      <c r="E2377" s="46"/>
+      <c r="E2377" s="45"/>
       <c r="F2377" s="7"/>
     </row>
     <row r="2378" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2378" s="11"/>
       <c r="C2378" s="3"/>
       <c r="D2378" s="3"/>
-      <c r="E2378" s="46"/>
+      <c r="E2378" s="45"/>
       <c r="F2378" s="7"/>
     </row>
     <row r="2379" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2379" s="11"/>
       <c r="C2379" s="3"/>
       <c r="D2379" s="3"/>
-      <c r="E2379" s="46"/>
+      <c r="E2379" s="45"/>
       <c r="F2379" s="7"/>
     </row>
     <row r="2380" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2380" s="11"/>
       <c r="C2380" s="3"/>
       <c r="D2380" s="3"/>
-      <c r="E2380" s="46"/>
+      <c r="E2380" s="45"/>
       <c r="F2380" s="7"/>
     </row>
     <row r="2381" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2381" s="11"/>
       <c r="C2381" s="3"/>
       <c r="D2381" s="3"/>
-      <c r="E2381" s="46"/>
+      <c r="E2381" s="45"/>
       <c r="F2381" s="7"/>
     </row>
     <row r="2382" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2382" s="11"/>
       <c r="C2382" s="3"/>
       <c r="D2382" s="3"/>
-      <c r="E2382" s="46"/>
+      <c r="E2382" s="45"/>
       <c r="F2382" s="7"/>
     </row>
     <row r="2383" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2383" s="11"/>
       <c r="C2383" s="3"/>
       <c r="D2383" s="3"/>
-      <c r="E2383" s="46"/>
+      <c r="E2383" s="45"/>
       <c r="F2383" s="7"/>
     </row>
     <row r="2384" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2384" s="11"/>
       <c r="C2384" s="3"/>
       <c r="D2384" s="3"/>
-      <c r="E2384" s="46"/>
+      <c r="E2384" s="45"/>
       <c r="F2384" s="7"/>
     </row>
     <row r="2385" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2385" s="11"/>
       <c r="C2385" s="3"/>
       <c r="D2385" s="3"/>
-      <c r="E2385" s="46"/>
+      <c r="E2385" s="45"/>
       <c r="F2385" s="7"/>
     </row>
     <row r="2386" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2386" s="11"/>
       <c r="C2386" s="3"/>
       <c r="D2386" s="3"/>
-      <c r="E2386" s="46"/>
+      <c r="E2386" s="45"/>
       <c r="F2386" s="7"/>
     </row>
     <row r="2387" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2387" s="11"/>
       <c r="C2387" s="3"/>
       <c r="D2387" s="3"/>
-      <c r="E2387" s="46"/>
+      <c r="E2387" s="45"/>
       <c r="F2387" s="7"/>
     </row>
     <row r="2388" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2388" s="11"/>
       <c r="C2388" s="3"/>
       <c r="D2388" s="3"/>
-      <c r="E2388" s="46"/>
+      <c r="E2388" s="45"/>
       <c r="F2388" s="7"/>
     </row>
     <row r="2389" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2389" s="11"/>
       <c r="C2389" s="3"/>
       <c r="D2389" s="3"/>
-      <c r="E2389" s="46"/>
+      <c r="E2389" s="45"/>
       <c r="F2389" s="7"/>
     </row>
     <row r="2390" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2390" s="11"/>
       <c r="C2390" s="3"/>
       <c r="D2390" s="3"/>
-      <c r="E2390" s="46"/>
+      <c r="E2390" s="45"/>
       <c r="F2390" s="7"/>
     </row>
     <row r="2391" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2391" s="11"/>
       <c r="C2391" s="3"/>
       <c r="D2391" s="3"/>
-      <c r="E2391" s="46"/>
+      <c r="E2391" s="45"/>
       <c r="F2391" s="7"/>
     </row>
     <row r="2392" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2392" s="11"/>
       <c r="C2392" s="3"/>
       <c r="D2392" s="3"/>
-      <c r="E2392" s="46"/>
+      <c r="E2392" s="45"/>
       <c r="F2392" s="7"/>
     </row>
     <row r="2393" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2393" s="11"/>
       <c r="C2393" s="3"/>
       <c r="D2393" s="3"/>
-      <c r="E2393" s="46"/>
+      <c r="E2393" s="45"/>
       <c r="F2393" s="7"/>
     </row>
     <row r="2394" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2394" s="11"/>
       <c r="C2394" s="3"/>
       <c r="D2394" s="3"/>
-      <c r="E2394" s="46"/>
+      <c r="E2394" s="45"/>
       <c r="F2394" s="7"/>
     </row>
     <row r="2395" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2395" s="11"/>
       <c r="C2395" s="3"/>
       <c r="D2395" s="3"/>
-      <c r="E2395" s="46"/>
+      <c r="E2395" s="45"/>
       <c r="F2395" s="7"/>
     </row>
     <row r="2396" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2396" s="11"/>
       <c r="C2396" s="3"/>
       <c r="D2396" s="3"/>
-      <c r="E2396" s="46"/>
+      <c r="E2396" s="45"/>
       <c r="F2396" s="7"/>
     </row>
     <row r="2397" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2397" s="11"/>
       <c r="C2397" s="3"/>
       <c r="D2397" s="3"/>
-      <c r="E2397" s="46"/>
+      <c r="E2397" s="45"/>
       <c r="F2397" s="7"/>
     </row>
     <row r="2398" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2398" s="11"/>
       <c r="C2398" s="3"/>
       <c r="D2398" s="3"/>
-      <c r="E2398" s="46"/>
+      <c r="E2398" s="45"/>
       <c r="F2398" s="7"/>
     </row>
     <row r="2399" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2399" s="11"/>
       <c r="C2399" s="3"/>
       <c r="D2399" s="3"/>
-      <c r="E2399" s="46"/>
+      <c r="E2399" s="45"/>
       <c r="F2399" s="7"/>
     </row>
     <row r="2400" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2400" s="11"/>
       <c r="C2400" s="3"/>
       <c r="D2400" s="3"/>
-      <c r="E2400" s="46"/>
+      <c r="E2400" s="45"/>
       <c r="F2400" s="7"/>
     </row>
     <row r="2401" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2401" s="11"/>
       <c r="C2401" s="3"/>
       <c r="D2401" s="3"/>
-      <c r="E2401" s="46"/>
+      <c r="E2401" s="45"/>
       <c r="F2401" s="7"/>
     </row>
     <row r="2402" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2402" s="11"/>
       <c r="C2402" s="3"/>
       <c r="D2402" s="3"/>
-      <c r="E2402" s="46"/>
+      <c r="E2402" s="45"/>
       <c r="F2402" s="7"/>
     </row>
     <row r="2403" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2403" s="11"/>
       <c r="C2403" s="3"/>
       <c r="D2403" s="3"/>
-      <c r="E2403" s="46"/>
+      <c r="E2403" s="45"/>
       <c r="F2403" s="7"/>
     </row>
     <row r="2404" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2404" s="11"/>
       <c r="C2404" s="3"/>
       <c r="D2404" s="3"/>
-      <c r="E2404" s="46"/>
+      <c r="E2404" s="45"/>
       <c r="F2404" s="7"/>
     </row>
     <row r="2405" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2405" s="11"/>
       <c r="C2405" s="3"/>
       <c r="D2405" s="3"/>
-      <c r="E2405" s="46"/>
+      <c r="E2405" s="45"/>
       <c r="F2405" s="7"/>
     </row>
     <row r="2406" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2406" s="11"/>
       <c r="C2406" s="3"/>
       <c r="D2406" s="3"/>
-      <c r="E2406" s="46"/>
+      <c r="E2406" s="45"/>
       <c r="F2406" s="7"/>
     </row>
     <row r="2407" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2407" s="11"/>
       <c r="C2407" s="3"/>
       <c r="D2407" s="3"/>
-      <c r="E2407" s="46"/>
+      <c r="E2407" s="45"/>
       <c r="F2407" s="7"/>
     </row>
     <row r="2408" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2408" s="11"/>
       <c r="C2408" s="3"/>
       <c r="D2408" s="3"/>
-      <c r="E2408" s="46"/>
+      <c r="E2408" s="45"/>
       <c r="F2408" s="7"/>
     </row>
     <row r="2409" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2409" s="11"/>
       <c r="C2409" s="3"/>
       <c r="D2409" s="3"/>
-      <c r="E2409" s="46"/>
+      <c r="E2409" s="45"/>
       <c r="F2409" s="7"/>
     </row>
     <row r="2410" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2410" s="11"/>
       <c r="C2410" s="3"/>
       <c r="D2410" s="3"/>
-      <c r="E2410" s="46"/>
+      <c r="E2410" s="45"/>
       <c r="F2410" s="7"/>
     </row>
     <row r="2411" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2411" s="11"/>
       <c r="C2411" s="3"/>
       <c r="D2411" s="3"/>
-      <c r="E2411" s="46"/>
+      <c r="E2411" s="45"/>
       <c r="F2411" s="7"/>
     </row>
     <row r="2412" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2412" s="11"/>
       <c r="C2412" s="3"/>
       <c r="D2412" s="3"/>
-      <c r="E2412" s="46"/>
+      <c r="E2412" s="45"/>
       <c r="F2412" s="7"/>
     </row>
     <row r="2413" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2413" s="11"/>
       <c r="C2413" s="3"/>
       <c r="D2413" s="3"/>
-      <c r="E2413" s="46"/>
+      <c r="E2413" s="45"/>
       <c r="F2413" s="7"/>
     </row>
     <row r="2414" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2414" s="11"/>
       <c r="C2414" s="3"/>
       <c r="D2414" s="3"/>
-      <c r="E2414" s="46"/>
+      <c r="E2414" s="45"/>
       <c r="F2414" s="7"/>
     </row>
     <row r="2415" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2415" s="11"/>
       <c r="C2415" s="3"/>
       <c r="D2415" s="3"/>
-      <c r="E2415" s="46"/>
+      <c r="E2415" s="45"/>
       <c r="F2415" s="7"/>
     </row>
     <row r="2416" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2416" s="11"/>
       <c r="C2416" s="3"/>
       <c r="D2416" s="3"/>
-      <c r="E2416" s="46"/>
+      <c r="E2416" s="45"/>
       <c r="F2416" s="7"/>
     </row>
     <row r="2417" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2417" s="11"/>
       <c r="C2417" s="3"/>
       <c r="D2417" s="3"/>
-      <c r="E2417" s="46"/>
+      <c r="E2417" s="45"/>
       <c r="F2417" s="7"/>
     </row>
     <row r="2418" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2418" s="11"/>
       <c r="C2418" s="3"/>
       <c r="D2418" s="3"/>
-      <c r="E2418" s="46"/>
+      <c r="E2418" s="45"/>
       <c r="F2418" s="7"/>
     </row>
     <row r="2419" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2419" s="11"/>
       <c r="C2419" s="3"/>
       <c r="D2419" s="3"/>
-      <c r="E2419" s="46"/>
+      <c r="E2419" s="45"/>
       <c r="F2419" s="7"/>
     </row>
     <row r="2420" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2420" s="11"/>
       <c r="C2420" s="3"/>
       <c r="D2420" s="3"/>
-      <c r="E2420" s="46"/>
+      <c r="E2420" s="45"/>
       <c r="F2420" s="7"/>
     </row>
     <row r="2421" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2421" s="11"/>
       <c r="C2421" s="3"/>
       <c r="D2421" s="3"/>
-      <c r="E2421" s="46"/>
+      <c r="E2421" s="45"/>
       <c r="F2421" s="7"/>
     </row>
     <row r="2422" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2422" s="11"/>
       <c r="C2422" s="3"/>
       <c r="D2422" s="3"/>
-      <c r="E2422" s="46"/>
+      <c r="E2422" s="45"/>
       <c r="F2422" s="7"/>
     </row>
     <row r="2423" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2423" s="11"/>
       <c r="C2423" s="3"/>
       <c r="D2423" s="3"/>
-      <c r="E2423" s="46"/>
+      <c r="E2423" s="45"/>
       <c r="F2423" s="7"/>
     </row>
     <row r="2424" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2424" s="11"/>
       <c r="C2424" s="3"/>
       <c r="D2424" s="3"/>
-      <c r="E2424" s="46"/>
+      <c r="E2424" s="45"/>
       <c r="F2424" s="7"/>
     </row>
     <row r="2425" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2425" s="11"/>
       <c r="C2425" s="3"/>
       <c r="D2425" s="3"/>
-      <c r="E2425" s="46"/>
+      <c r="E2425" s="45"/>
       <c r="F2425" s="7"/>
     </row>
     <row r="2426" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2426" s="11"/>
       <c r="C2426" s="3"/>
       <c r="D2426" s="3"/>
-      <c r="E2426" s="46"/>
+      <c r="E2426" s="45"/>
       <c r="F2426" s="7"/>
     </row>
     <row r="2427" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2427" s="11"/>
       <c r="C2427" s="3"/>
       <c r="D2427" s="3"/>
-      <c r="E2427" s="46"/>
+      <c r="E2427" s="45"/>
       <c r="F2427" s="7"/>
     </row>
     <row r="2428" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2428" s="11"/>
       <c r="C2428" s="3"/>
       <c r="D2428" s="3"/>
-      <c r="E2428" s="46"/>
+      <c r="E2428" s="45"/>
       <c r="F2428" s="7"/>
     </row>
     <row r="2429" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2429" s="11"/>
       <c r="C2429" s="3"/>
       <c r="D2429" s="3"/>
-      <c r="E2429" s="46"/>
+      <c r="E2429" s="45"/>
       <c r="F2429" s="7"/>
     </row>
     <row r="2430" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2430" s="11"/>
       <c r="C2430" s="3"/>
       <c r="D2430" s="3"/>
-      <c r="E2430" s="46"/>
+      <c r="E2430" s="45"/>
       <c r="F2430" s="7"/>
     </row>
     <row r="2431" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2431" s="11"/>
       <c r="C2431" s="3"/>
       <c r="D2431" s="3"/>
-      <c r="E2431" s="46"/>
+      <c r="E2431" s="45"/>
       <c r="F2431" s="7"/>
     </row>
     <row r="2432" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2432" s="11"/>
       <c r="C2432" s="3"/>
       <c r="D2432" s="3"/>
-      <c r="E2432" s="46"/>
+      <c r="E2432" s="45"/>
       <c r="F2432" s="7"/>
     </row>
     <row r="2433" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2433" s="11"/>
       <c r="C2433" s="3"/>
       <c r="D2433" s="3"/>
-      <c r="E2433" s="46"/>
+      <c r="E2433" s="45"/>
       <c r="F2433" s="7"/>
     </row>
     <row r="2434" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2434" s="11"/>
       <c r="C2434" s="3"/>
       <c r="D2434" s="3"/>
-      <c r="E2434" s="46"/>
+      <c r="E2434" s="45"/>
       <c r="F2434" s="7"/>
     </row>
     <row r="2435" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2435" s="11"/>
       <c r="C2435" s="3"/>
       <c r="D2435" s="3"/>
-      <c r="E2435" s="46"/>
+      <c r="E2435" s="45"/>
       <c r="F2435" s="7"/>
     </row>
     <row r="2436" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2436" s="11"/>
       <c r="C2436" s="3"/>
       <c r="D2436" s="3"/>
-      <c r="E2436" s="46"/>
+      <c r="E2436" s="45"/>
       <c r="F2436" s="7"/>
     </row>
     <row r="2437" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2437" s="11"/>
       <c r="C2437" s="3"/>
       <c r="D2437" s="3"/>
-      <c r="E2437" s="46"/>
+      <c r="E2437" s="45"/>
       <c r="F2437" s="7"/>
     </row>
     <row r="2438" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2438" s="11"/>
       <c r="C2438" s="3"/>
       <c r="D2438" s="3"/>
-      <c r="E2438" s="46"/>
+      <c r="E2438" s="45"/>
       <c r="F2438" s="7"/>
     </row>
     <row r="2439" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2439" s="11"/>
       <c r="C2439" s="3"/>
       <c r="D2439" s="3"/>
-      <c r="E2439" s="46"/>
+      <c r="E2439" s="45"/>
       <c r="F2439" s="7"/>
     </row>
     <row r="2440" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2440" s="11"/>
       <c r="C2440" s="3"/>
       <c r="D2440" s="3"/>
-      <c r="E2440" s="46"/>
+      <c r="E2440" s="45"/>
       <c r="F2440" s="7"/>
     </row>
     <row r="2441" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2441" s="11"/>
       <c r="C2441" s="3"/>
       <c r="D2441" s="3"/>
-      <c r="E2441" s="46"/>
+      <c r="E2441" s="45"/>
       <c r="F2441" s="7"/>
     </row>
     <row r="2442" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2442" s="11"/>
       <c r="C2442" s="3"/>
       <c r="D2442" s="3"/>
-      <c r="E2442" s="46"/>
+      <c r="E2442" s="45"/>
       <c r="F2442" s="7"/>
     </row>
     <row r="2443" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2443" s="11"/>
       <c r="C2443" s="3"/>
       <c r="D2443" s="3"/>
-      <c r="E2443" s="46"/>
+      <c r="E2443" s="45"/>
       <c r="F2443" s="7"/>
     </row>
     <row r="2444" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2444" s="11"/>
       <c r="C2444" s="3"/>
       <c r="D2444" s="3"/>
-      <c r="E2444" s="46"/>
+      <c r="E2444" s="45"/>
       <c r="F2444" s="7"/>
     </row>
     <row r="2445" spans="2:6" x14ac:dyDescent="0.25">
@@ -57460,1386 +57535,1386 @@
       <c r="B2446" s="11"/>
       <c r="C2446" s="3"/>
       <c r="D2446" s="3"/>
-      <c r="E2446" s="46"/>
+      <c r="E2446" s="45"/>
       <c r="F2446" s="7"/>
     </row>
     <row r="2447" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2447" s="11"/>
       <c r="C2447" s="3"/>
       <c r="D2447" s="3"/>
-      <c r="E2447" s="46"/>
+      <c r="E2447" s="45"/>
       <c r="F2447" s="7"/>
     </row>
     <row r="2448" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2448" s="11"/>
       <c r="C2448" s="3"/>
       <c r="D2448" s="3"/>
-      <c r="E2448" s="46"/>
+      <c r="E2448" s="45"/>
       <c r="F2448" s="7"/>
     </row>
     <row r="2449" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2449" s="11"/>
       <c r="C2449" s="3"/>
       <c r="D2449" s="3"/>
-      <c r="E2449" s="46"/>
+      <c r="E2449" s="45"/>
       <c r="F2449" s="7"/>
     </row>
     <row r="2450" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2450" s="11"/>
       <c r="C2450" s="3"/>
       <c r="D2450" s="3"/>
-      <c r="E2450" s="46"/>
+      <c r="E2450" s="45"/>
       <c r="F2450" s="7"/>
     </row>
     <row r="2451" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2451" s="11"/>
       <c r="C2451" s="3"/>
       <c r="D2451" s="3"/>
-      <c r="E2451" s="46"/>
+      <c r="E2451" s="45"/>
       <c r="F2451" s="7"/>
     </row>
     <row r="2452" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2452" s="11"/>
       <c r="C2452" s="3"/>
       <c r="D2452" s="3"/>
-      <c r="E2452" s="46"/>
+      <c r="E2452" s="45"/>
       <c r="F2452" s="7"/>
     </row>
     <row r="2453" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2453" s="11"/>
       <c r="C2453" s="3"/>
       <c r="D2453" s="3"/>
-      <c r="E2453" s="46"/>
+      <c r="E2453" s="45"/>
       <c r="F2453" s="7"/>
     </row>
     <row r="2454" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2454" s="11"/>
       <c r="C2454" s="3"/>
       <c r="D2454" s="3"/>
-      <c r="E2454" s="46"/>
+      <c r="E2454" s="45"/>
       <c r="F2454" s="7"/>
     </row>
     <row r="2455" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2455" s="11"/>
       <c r="C2455" s="3"/>
       <c r="D2455" s="3"/>
-      <c r="E2455" s="46"/>
+      <c r="E2455" s="45"/>
       <c r="F2455" s="7"/>
     </row>
     <row r="2456" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2456" s="11"/>
       <c r="C2456" s="3"/>
       <c r="D2456" s="3"/>
-      <c r="E2456" s="46"/>
+      <c r="E2456" s="45"/>
       <c r="F2456" s="7"/>
     </row>
     <row r="2457" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2457" s="11"/>
       <c r="C2457" s="3"/>
       <c r="D2457" s="3"/>
-      <c r="E2457" s="46"/>
+      <c r="E2457" s="45"/>
       <c r="F2457" s="7"/>
     </row>
     <row r="2458" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2458" s="11"/>
       <c r="C2458" s="3"/>
       <c r="D2458" s="3"/>
-      <c r="E2458" s="46"/>
+      <c r="E2458" s="45"/>
       <c r="F2458" s="7"/>
     </row>
     <row r="2459" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2459" s="11"/>
       <c r="C2459" s="3"/>
       <c r="D2459" s="3"/>
-      <c r="E2459" s="46"/>
+      <c r="E2459" s="45"/>
       <c r="F2459" s="7"/>
     </row>
     <row r="2460" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2460" s="11"/>
       <c r="C2460" s="3"/>
       <c r="D2460" s="3"/>
-      <c r="E2460" s="46"/>
+      <c r="E2460" s="45"/>
       <c r="F2460" s="7"/>
     </row>
     <row r="2461" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2461" s="11"/>
       <c r="C2461" s="3"/>
       <c r="D2461" s="3"/>
-      <c r="E2461" s="46"/>
+      <c r="E2461" s="45"/>
       <c r="F2461" s="7"/>
     </row>
     <row r="2462" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2462" s="11"/>
       <c r="C2462" s="3"/>
       <c r="D2462" s="3"/>
-      <c r="E2462" s="46"/>
+      <c r="E2462" s="45"/>
       <c r="F2462" s="7"/>
     </row>
     <row r="2463" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2463" s="11"/>
       <c r="C2463" s="3"/>
       <c r="D2463" s="3"/>
-      <c r="E2463" s="46"/>
+      <c r="E2463" s="45"/>
       <c r="F2463" s="7"/>
     </row>
     <row r="2464" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2464" s="11"/>
       <c r="C2464" s="3"/>
       <c r="D2464" s="3"/>
-      <c r="E2464" s="46"/>
+      <c r="E2464" s="45"/>
       <c r="F2464" s="7"/>
     </row>
     <row r="2465" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2465" s="11"/>
       <c r="C2465" s="3"/>
       <c r="D2465" s="3"/>
-      <c r="E2465" s="46"/>
+      <c r="E2465" s="45"/>
       <c r="F2465" s="7"/>
     </row>
     <row r="2466" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2466" s="11"/>
       <c r="C2466" s="3"/>
       <c r="D2466" s="3"/>
-      <c r="E2466" s="46"/>
+      <c r="E2466" s="45"/>
       <c r="F2466" s="7"/>
     </row>
     <row r="2467" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2467" s="11"/>
       <c r="C2467" s="3"/>
       <c r="D2467" s="3"/>
-      <c r="E2467" s="46"/>
+      <c r="E2467" s="45"/>
       <c r="F2467" s="7"/>
     </row>
     <row r="2468" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2468" s="11"/>
       <c r="C2468" s="3"/>
       <c r="D2468" s="3"/>
-      <c r="E2468" s="46"/>
+      <c r="E2468" s="45"/>
       <c r="F2468" s="7"/>
     </row>
     <row r="2469" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2469" s="11"/>
       <c r="C2469" s="3"/>
       <c r="D2469" s="3"/>
-      <c r="E2469" s="46"/>
+      <c r="E2469" s="45"/>
       <c r="F2469" s="7"/>
     </row>
     <row r="2470" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2470" s="11"/>
       <c r="C2470" s="3"/>
       <c r="D2470" s="3"/>
-      <c r="E2470" s="46"/>
+      <c r="E2470" s="45"/>
       <c r="F2470" s="7"/>
     </row>
     <row r="2471" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2471" s="11"/>
       <c r="C2471" s="3"/>
       <c r="D2471" s="3"/>
-      <c r="E2471" s="46"/>
+      <c r="E2471" s="45"/>
       <c r="F2471" s="7"/>
     </row>
     <row r="2472" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2472" s="11"/>
       <c r="C2472" s="3"/>
       <c r="D2472" s="3"/>
-      <c r="E2472" s="46"/>
+      <c r="E2472" s="45"/>
       <c r="F2472" s="7"/>
     </row>
     <row r="2473" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2473" s="11"/>
       <c r="C2473" s="3"/>
       <c r="D2473" s="3"/>
-      <c r="E2473" s="46"/>
+      <c r="E2473" s="45"/>
       <c r="F2473" s="7"/>
     </row>
     <row r="2474" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2474" s="11"/>
       <c r="C2474" s="3"/>
       <c r="D2474" s="3"/>
-      <c r="E2474" s="46"/>
+      <c r="E2474" s="45"/>
       <c r="F2474" s="7"/>
     </row>
     <row r="2475" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2475" s="11"/>
       <c r="C2475" s="3"/>
       <c r="D2475" s="3"/>
-      <c r="E2475" s="46"/>
+      <c r="E2475" s="45"/>
       <c r="F2475" s="7"/>
     </row>
     <row r="2476" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2476" s="11"/>
       <c r="C2476" s="3"/>
       <c r="D2476" s="3"/>
-      <c r="E2476" s="46"/>
+      <c r="E2476" s="45"/>
       <c r="F2476" s="7"/>
     </row>
     <row r="2477" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2477" s="11"/>
       <c r="C2477" s="3"/>
       <c r="D2477" s="3"/>
-      <c r="E2477" s="46"/>
+      <c r="E2477" s="45"/>
       <c r="F2477" s="7"/>
     </row>
     <row r="2478" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2478" s="11"/>
       <c r="C2478" s="3"/>
       <c r="D2478" s="3"/>
-      <c r="E2478" s="46"/>
+      <c r="E2478" s="45"/>
       <c r="F2478" s="7"/>
     </row>
     <row r="2479" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2479" s="11"/>
       <c r="C2479" s="3"/>
       <c r="D2479" s="3"/>
-      <c r="E2479" s="46"/>
+      <c r="E2479" s="45"/>
       <c r="F2479" s="7"/>
     </row>
     <row r="2480" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2480" s="11"/>
       <c r="C2480" s="3"/>
       <c r="D2480" s="3"/>
-      <c r="E2480" s="46"/>
+      <c r="E2480" s="45"/>
       <c r="F2480" s="7"/>
     </row>
     <row r="2481" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2481" s="11"/>
       <c r="C2481" s="3"/>
       <c r="D2481" s="3"/>
-      <c r="E2481" s="46"/>
+      <c r="E2481" s="45"/>
       <c r="F2481" s="7"/>
     </row>
     <row r="2482" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2482" s="11"/>
       <c r="C2482" s="3"/>
       <c r="D2482" s="3"/>
-      <c r="E2482" s="46"/>
+      <c r="E2482" s="45"/>
       <c r="F2482" s="7"/>
     </row>
     <row r="2483" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2483" s="11"/>
       <c r="C2483" s="3"/>
       <c r="D2483" s="3"/>
-      <c r="E2483" s="46"/>
+      <c r="E2483" s="45"/>
       <c r="F2483" s="7"/>
     </row>
     <row r="2484" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2484" s="11"/>
       <c r="C2484" s="3"/>
       <c r="D2484" s="3"/>
-      <c r="E2484" s="46"/>
+      <c r="E2484" s="45"/>
       <c r="F2484" s="7"/>
     </row>
     <row r="2485" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2485" s="11"/>
       <c r="C2485" s="3"/>
       <c r="D2485" s="3"/>
-      <c r="E2485" s="46"/>
+      <c r="E2485" s="45"/>
       <c r="F2485" s="7"/>
     </row>
     <row r="2486" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2486" s="11"/>
       <c r="C2486" s="3"/>
       <c r="D2486" s="3"/>
-      <c r="E2486" s="46"/>
+      <c r="E2486" s="45"/>
       <c r="F2486" s="7"/>
     </row>
     <row r="2487" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2487" s="11"/>
       <c r="C2487" s="3"/>
       <c r="D2487" s="3"/>
-      <c r="E2487" s="46"/>
+      <c r="E2487" s="45"/>
       <c r="F2487" s="7"/>
     </row>
     <row r="2488" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2488" s="11"/>
       <c r="C2488" s="3"/>
       <c r="D2488" s="3"/>
-      <c r="E2488" s="46"/>
+      <c r="E2488" s="45"/>
       <c r="F2488" s="7"/>
     </row>
     <row r="2489" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2489" s="11"/>
       <c r="C2489" s="3"/>
       <c r="D2489" s="3"/>
-      <c r="E2489" s="46"/>
+      <c r="E2489" s="45"/>
       <c r="F2489" s="7"/>
     </row>
     <row r="2490" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2490" s="11"/>
       <c r="C2490" s="3"/>
       <c r="D2490" s="3"/>
-      <c r="E2490" s="46"/>
+      <c r="E2490" s="45"/>
       <c r="F2490" s="7"/>
     </row>
     <row r="2491" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2491" s="11"/>
       <c r="C2491" s="3"/>
       <c r="D2491" s="3"/>
-      <c r="E2491" s="46"/>
+      <c r="E2491" s="45"/>
       <c r="F2491" s="7"/>
     </row>
     <row r="2492" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2492" s="11"/>
       <c r="C2492" s="3"/>
       <c r="D2492" s="3"/>
-      <c r="E2492" s="46"/>
+      <c r="E2492" s="45"/>
       <c r="F2492" s="7"/>
     </row>
     <row r="2493" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2493" s="11"/>
       <c r="C2493" s="3"/>
       <c r="D2493" s="3"/>
-      <c r="E2493" s="46"/>
+      <c r="E2493" s="45"/>
       <c r="F2493" s="7"/>
     </row>
     <row r="2494" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2494" s="11"/>
       <c r="C2494" s="3"/>
       <c r="D2494" s="3"/>
-      <c r="E2494" s="46"/>
+      <c r="E2494" s="45"/>
       <c r="F2494" s="7"/>
     </row>
     <row r="2495" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2495" s="11"/>
       <c r="C2495" s="3"/>
       <c r="D2495" s="3"/>
-      <c r="E2495" s="46"/>
+      <c r="E2495" s="45"/>
       <c r="F2495" s="7"/>
     </row>
     <row r="2496" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2496" s="11"/>
       <c r="C2496" s="3"/>
       <c r="D2496" s="3"/>
-      <c r="E2496" s="46"/>
+      <c r="E2496" s="45"/>
       <c r="F2496" s="7"/>
     </row>
     <row r="2497" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2497" s="11"/>
       <c r="C2497" s="3"/>
       <c r="D2497" s="3"/>
-      <c r="E2497" s="46"/>
+      <c r="E2497" s="45"/>
       <c r="F2497" s="7"/>
     </row>
     <row r="2498" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2498" s="11"/>
       <c r="C2498" s="3"/>
       <c r="D2498" s="3"/>
-      <c r="E2498" s="46"/>
+      <c r="E2498" s="45"/>
       <c r="F2498" s="7"/>
     </row>
     <row r="2499" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2499" s="11"/>
       <c r="C2499" s="3"/>
       <c r="D2499" s="3"/>
-      <c r="E2499" s="46"/>
+      <c r="E2499" s="45"/>
       <c r="F2499" s="7"/>
     </row>
     <row r="2500" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2500" s="11"/>
       <c r="C2500" s="3"/>
       <c r="D2500" s="3"/>
-      <c r="E2500" s="46"/>
+      <c r="E2500" s="45"/>
       <c r="F2500" s="7"/>
     </row>
     <row r="2501" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2501" s="11"/>
       <c r="C2501" s="3"/>
       <c r="D2501" s="3"/>
-      <c r="E2501" s="46"/>
+      <c r="E2501" s="45"/>
       <c r="F2501" s="7"/>
     </row>
     <row r="2502" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2502" s="11"/>
       <c r="C2502" s="3"/>
       <c r="D2502" s="3"/>
-      <c r="E2502" s="46"/>
+      <c r="E2502" s="45"/>
       <c r="F2502" s="7"/>
     </row>
     <row r="2503" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2503" s="11"/>
       <c r="C2503" s="3"/>
       <c r="D2503" s="3"/>
-      <c r="E2503" s="46"/>
+      <c r="E2503" s="45"/>
       <c r="F2503" s="7"/>
     </row>
     <row r="2504" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2504" s="11"/>
       <c r="C2504" s="3"/>
       <c r="D2504" s="3"/>
-      <c r="E2504" s="46"/>
+      <c r="E2504" s="45"/>
       <c r="F2504" s="7"/>
     </row>
     <row r="2505" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2505" s="11"/>
       <c r="C2505" s="3"/>
       <c r="D2505" s="3"/>
-      <c r="E2505" s="46"/>
+      <c r="E2505" s="45"/>
       <c r="F2505" s="7"/>
     </row>
     <row r="2506" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2506" s="11"/>
       <c r="C2506" s="3"/>
       <c r="D2506" s="3"/>
-      <c r="E2506" s="46"/>
+      <c r="E2506" s="45"/>
       <c r="F2506" s="7"/>
     </row>
     <row r="2507" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2507" s="11"/>
       <c r="C2507" s="3"/>
       <c r="D2507" s="3"/>
-      <c r="E2507" s="46"/>
+      <c r="E2507" s="45"/>
       <c r="F2507" s="7"/>
     </row>
     <row r="2508" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2508" s="11"/>
       <c r="C2508" s="3"/>
       <c r="D2508" s="3"/>
-      <c r="E2508" s="46"/>
+      <c r="E2508" s="45"/>
       <c r="F2508" s="7"/>
     </row>
     <row r="2509" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2509" s="11"/>
       <c r="C2509" s="3"/>
       <c r="D2509" s="3"/>
-      <c r="E2509" s="46"/>
+      <c r="E2509" s="45"/>
       <c r="F2509" s="7"/>
     </row>
     <row r="2510" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2510" s="11"/>
       <c r="C2510" s="3"/>
       <c r="D2510" s="3"/>
-      <c r="E2510" s="46"/>
+      <c r="E2510" s="45"/>
       <c r="F2510" s="7"/>
     </row>
     <row r="2511" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2511" s="11"/>
       <c r="C2511" s="3"/>
       <c r="D2511" s="3"/>
-      <c r="E2511" s="46"/>
+      <c r="E2511" s="45"/>
       <c r="F2511" s="7"/>
     </row>
     <row r="2512" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2512" s="11"/>
       <c r="C2512" s="3"/>
       <c r="D2512" s="3"/>
-      <c r="E2512" s="46"/>
+      <c r="E2512" s="45"/>
       <c r="F2512" s="7"/>
     </row>
     <row r="2513" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2513" s="11"/>
       <c r="C2513" s="3"/>
       <c r="D2513" s="3"/>
-      <c r="E2513" s="46"/>
+      <c r="E2513" s="45"/>
       <c r="F2513" s="7"/>
     </row>
     <row r="2514" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2514" s="11"/>
       <c r="C2514" s="3"/>
       <c r="D2514" s="3"/>
-      <c r="E2514" s="46"/>
+      <c r="E2514" s="45"/>
       <c r="F2514" s="7"/>
     </row>
     <row r="2515" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2515" s="11"/>
       <c r="C2515" s="3"/>
       <c r="D2515" s="3"/>
-      <c r="E2515" s="46"/>
+      <c r="E2515" s="45"/>
       <c r="F2515" s="7"/>
     </row>
     <row r="2516" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2516" s="11"/>
       <c r="C2516" s="3"/>
       <c r="D2516" s="3"/>
-      <c r="E2516" s="46"/>
+      <c r="E2516" s="45"/>
       <c r="F2516" s="7"/>
     </row>
     <row r="2517" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2517" s="11"/>
       <c r="C2517" s="3"/>
       <c r="D2517" s="3"/>
-      <c r="E2517" s="46"/>
+      <c r="E2517" s="45"/>
       <c r="F2517" s="7"/>
     </row>
     <row r="2518" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2518" s="11"/>
       <c r="C2518" s="3"/>
       <c r="D2518" s="3"/>
-      <c r="E2518" s="46"/>
+      <c r="E2518" s="45"/>
       <c r="F2518" s="7"/>
     </row>
     <row r="2519" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2519" s="11"/>
       <c r="C2519" s="3"/>
       <c r="D2519" s="3"/>
-      <c r="E2519" s="46"/>
+      <c r="E2519" s="45"/>
       <c r="F2519" s="7"/>
     </row>
     <row r="2520" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2520" s="11"/>
       <c r="C2520" s="3"/>
       <c r="D2520" s="3"/>
-      <c r="E2520" s="46"/>
+      <c r="E2520" s="45"/>
       <c r="F2520" s="7"/>
     </row>
     <row r="2521" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2521" s="11"/>
       <c r="C2521" s="3"/>
       <c r="D2521" s="3"/>
-      <c r="E2521" s="46"/>
+      <c r="E2521" s="45"/>
       <c r="F2521" s="7"/>
     </row>
     <row r="2522" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2522" s="11"/>
       <c r="C2522" s="3"/>
       <c r="D2522" s="3"/>
-      <c r="E2522" s="46"/>
+      <c r="E2522" s="45"/>
       <c r="F2522" s="7"/>
     </row>
     <row r="2523" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2523" s="11"/>
       <c r="C2523" s="3"/>
       <c r="D2523" s="3"/>
-      <c r="E2523" s="46"/>
+      <c r="E2523" s="45"/>
       <c r="F2523" s="7"/>
     </row>
     <row r="2524" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2524" s="11"/>
       <c r="C2524" s="3"/>
       <c r="D2524" s="3"/>
-      <c r="E2524" s="46"/>
+      <c r="E2524" s="45"/>
       <c r="F2524" s="7"/>
     </row>
     <row r="2525" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2525" s="11"/>
       <c r="C2525" s="3"/>
       <c r="D2525" s="3"/>
-      <c r="E2525" s="46"/>
+      <c r="E2525" s="45"/>
       <c r="F2525" s="7"/>
     </row>
     <row r="2526" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2526" s="11"/>
       <c r="C2526" s="3"/>
       <c r="D2526" s="3"/>
-      <c r="E2526" s="46"/>
+      <c r="E2526" s="45"/>
       <c r="F2526" s="7"/>
     </row>
     <row r="2527" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2527" s="11"/>
       <c r="C2527" s="3"/>
       <c r="D2527" s="3"/>
-      <c r="E2527" s="46"/>
+      <c r="E2527" s="45"/>
       <c r="F2527" s="7"/>
     </row>
     <row r="2528" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2528" s="11"/>
       <c r="C2528" s="3"/>
       <c r="D2528" s="3"/>
-      <c r="E2528" s="46"/>
+      <c r="E2528" s="45"/>
       <c r="F2528" s="7"/>
     </row>
     <row r="2529" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2529" s="11"/>
       <c r="C2529" s="3"/>
       <c r="D2529" s="3"/>
-      <c r="E2529" s="46"/>
+      <c r="E2529" s="45"/>
       <c r="F2529" s="7"/>
     </row>
     <row r="2530" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2530" s="11"/>
       <c r="C2530" s="3"/>
       <c r="D2530" s="3"/>
-      <c r="E2530" s="46"/>
+      <c r="E2530" s="45"/>
       <c r="F2530" s="7"/>
     </row>
     <row r="2531" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2531" s="11"/>
       <c r="C2531" s="3"/>
       <c r="D2531" s="3"/>
-      <c r="E2531" s="46"/>
+      <c r="E2531" s="45"/>
       <c r="F2531" s="7"/>
     </row>
     <row r="2532" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2532" s="11"/>
       <c r="C2532" s="3"/>
       <c r="D2532" s="3"/>
-      <c r="E2532" s="46"/>
+      <c r="E2532" s="45"/>
       <c r="F2532" s="7"/>
     </row>
     <row r="2533" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2533" s="11"/>
       <c r="C2533" s="3"/>
       <c r="D2533" s="3"/>
-      <c r="E2533" s="46"/>
+      <c r="E2533" s="45"/>
       <c r="F2533" s="7"/>
     </row>
     <row r="2534" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2534" s="11"/>
       <c r="C2534" s="3"/>
       <c r="D2534" s="3"/>
-      <c r="E2534" s="46"/>
+      <c r="E2534" s="45"/>
       <c r="F2534" s="7"/>
     </row>
     <row r="2535" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2535" s="11"/>
       <c r="C2535" s="3"/>
       <c r="D2535" s="3"/>
-      <c r="E2535" s="46"/>
+      <c r="E2535" s="45"/>
       <c r="F2535" s="7"/>
     </row>
     <row r="2536" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2536" s="11"/>
       <c r="C2536" s="3"/>
       <c r="D2536" s="3"/>
-      <c r="E2536" s="46"/>
+      <c r="E2536" s="45"/>
       <c r="F2536" s="7"/>
     </row>
     <row r="2537" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2537" s="11"/>
       <c r="C2537" s="3"/>
       <c r="D2537" s="3"/>
-      <c r="E2537" s="46"/>
+      <c r="E2537" s="45"/>
       <c r="F2537" s="7"/>
     </row>
     <row r="2538" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2538" s="11"/>
       <c r="C2538" s="3"/>
       <c r="D2538" s="3"/>
-      <c r="E2538" s="46"/>
+      <c r="E2538" s="45"/>
       <c r="F2538" s="7"/>
     </row>
     <row r="2539" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2539" s="11"/>
       <c r="C2539" s="3"/>
       <c r="D2539" s="3"/>
-      <c r="E2539" s="46"/>
+      <c r="E2539" s="45"/>
       <c r="F2539" s="7"/>
     </row>
     <row r="2540" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2540" s="11"/>
       <c r="C2540" s="3"/>
       <c r="D2540" s="3"/>
-      <c r="E2540" s="46"/>
+      <c r="E2540" s="45"/>
       <c r="F2540" s="7"/>
     </row>
     <row r="2541" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2541" s="11"/>
       <c r="C2541" s="3"/>
       <c r="D2541" s="3"/>
-      <c r="E2541" s="46"/>
+      <c r="E2541" s="45"/>
       <c r="F2541" s="7"/>
     </row>
     <row r="2542" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2542" s="11"/>
       <c r="C2542" s="3"/>
       <c r="D2542" s="3"/>
-      <c r="E2542" s="46"/>
+      <c r="E2542" s="45"/>
       <c r="F2542" s="7"/>
     </row>
     <row r="2543" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2543" s="11"/>
       <c r="C2543" s="3"/>
       <c r="D2543" s="3"/>
-      <c r="E2543" s="46"/>
+      <c r="E2543" s="45"/>
       <c r="F2543" s="7"/>
     </row>
     <row r="2544" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2544" s="11"/>
       <c r="C2544" s="3"/>
       <c r="D2544" s="3"/>
-      <c r="E2544" s="46"/>
+      <c r="E2544" s="45"/>
       <c r="F2544" s="7"/>
     </row>
     <row r="2545" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2545" s="11"/>
       <c r="C2545" s="3"/>
       <c r="D2545" s="3"/>
-      <c r="E2545" s="46"/>
+      <c r="E2545" s="45"/>
       <c r="F2545" s="7"/>
     </row>
     <row r="2546" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2546" s="11"/>
       <c r="C2546" s="3"/>
       <c r="D2546" s="3"/>
-      <c r="E2546" s="46"/>
+      <c r="E2546" s="45"/>
       <c r="F2546" s="7"/>
     </row>
     <row r="2547" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2547" s="11"/>
       <c r="C2547" s="3"/>
       <c r="D2547" s="3"/>
-      <c r="E2547" s="46"/>
+      <c r="E2547" s="45"/>
       <c r="F2547" s="7"/>
     </row>
     <row r="2548" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2548" s="11"/>
       <c r="C2548" s="3"/>
       <c r="D2548" s="3"/>
-      <c r="E2548" s="46"/>
+      <c r="E2548" s="45"/>
       <c r="F2548" s="7"/>
     </row>
     <row r="2549" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2549" s="11"/>
       <c r="C2549" s="3"/>
       <c r="D2549" s="3"/>
-      <c r="E2549" s="46"/>
+      <c r="E2549" s="45"/>
       <c r="F2549" s="7"/>
     </row>
     <row r="2550" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2550" s="11"/>
       <c r="C2550" s="3"/>
       <c r="D2550" s="3"/>
-      <c r="E2550" s="46"/>
+      <c r="E2550" s="45"/>
       <c r="F2550" s="7"/>
     </row>
     <row r="2551" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2551" s="11"/>
       <c r="C2551" s="3"/>
       <c r="D2551" s="3"/>
-      <c r="E2551" s="46"/>
+      <c r="E2551" s="45"/>
       <c r="F2551" s="7"/>
     </row>
     <row r="2552" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2552" s="11"/>
       <c r="C2552" s="3"/>
       <c r="D2552" s="3"/>
-      <c r="E2552" s="46"/>
+      <c r="E2552" s="45"/>
       <c r="F2552" s="7"/>
     </row>
     <row r="2553" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2553" s="11"/>
       <c r="C2553" s="3"/>
       <c r="D2553" s="3"/>
-      <c r="E2553" s="46"/>
+      <c r="E2553" s="45"/>
       <c r="F2553" s="7"/>
     </row>
     <row r="2554" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2554" s="11"/>
       <c r="C2554" s="3"/>
       <c r="D2554" s="3"/>
-      <c r="E2554" s="46"/>
+      <c r="E2554" s="45"/>
       <c r="F2554" s="7"/>
     </row>
     <row r="2555" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2555" s="11"/>
       <c r="C2555" s="3"/>
       <c r="D2555" s="3"/>
-      <c r="E2555" s="46"/>
+      <c r="E2555" s="45"/>
       <c r="F2555" s="7"/>
     </row>
     <row r="2556" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2556" s="11"/>
       <c r="C2556" s="3"/>
       <c r="D2556" s="3"/>
-      <c r="E2556" s="46"/>
+      <c r="E2556" s="45"/>
       <c r="F2556" s="7"/>
     </row>
     <row r="2557" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2557" s="11"/>
       <c r="C2557" s="3"/>
       <c r="D2557" s="3"/>
-      <c r="E2557" s="46"/>
+      <c r="E2557" s="45"/>
       <c r="F2557" s="7"/>
     </row>
     <row r="2558" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2558" s="11"/>
       <c r="C2558" s="3"/>
       <c r="D2558" s="3"/>
-      <c r="E2558" s="46"/>
+      <c r="E2558" s="45"/>
       <c r="F2558" s="7"/>
     </row>
     <row r="2559" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2559" s="11"/>
       <c r="C2559" s="3"/>
       <c r="D2559" s="3"/>
-      <c r="E2559" s="46"/>
+      <c r="E2559" s="45"/>
       <c r="F2559" s="7"/>
     </row>
     <row r="2560" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2560" s="11"/>
       <c r="C2560" s="3"/>
       <c r="D2560" s="3"/>
-      <c r="E2560" s="46"/>
+      <c r="E2560" s="45"/>
       <c r="F2560" s="7"/>
     </row>
     <row r="2561" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2561" s="11"/>
       <c r="C2561" s="3"/>
       <c r="D2561" s="3"/>
-      <c r="E2561" s="46"/>
+      <c r="E2561" s="45"/>
       <c r="F2561" s="7"/>
     </row>
     <row r="2562" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2562" s="11"/>
       <c r="C2562" s="3"/>
       <c r="D2562" s="3"/>
-      <c r="E2562" s="46"/>
+      <c r="E2562" s="45"/>
       <c r="F2562" s="7"/>
     </row>
     <row r="2563" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2563" s="11"/>
       <c r="C2563" s="3"/>
       <c r="D2563" s="3"/>
-      <c r="E2563" s="46"/>
+      <c r="E2563" s="45"/>
       <c r="F2563" s="7"/>
     </row>
     <row r="2564" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2564" s="11"/>
       <c r="C2564" s="3"/>
       <c r="D2564" s="3"/>
-      <c r="E2564" s="46"/>
+      <c r="E2564" s="45"/>
       <c r="F2564" s="7"/>
     </row>
     <row r="2565" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2565" s="11"/>
       <c r="C2565" s="3"/>
       <c r="D2565" s="3"/>
-      <c r="E2565" s="46"/>
+      <c r="E2565" s="45"/>
       <c r="F2565" s="7"/>
     </row>
     <row r="2566" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2566" s="11"/>
       <c r="C2566" s="3"/>
       <c r="D2566" s="3"/>
-      <c r="E2566" s="46"/>
+      <c r="E2566" s="45"/>
       <c r="F2566" s="7"/>
     </row>
     <row r="2567" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2567" s="11"/>
       <c r="C2567" s="3"/>
       <c r="D2567" s="3"/>
-      <c r="E2567" s="46"/>
+      <c r="E2567" s="45"/>
       <c r="F2567" s="7"/>
     </row>
     <row r="2568" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2568" s="11"/>
       <c r="C2568" s="3"/>
       <c r="D2568" s="3"/>
-      <c r="E2568" s="46"/>
+      <c r="E2568" s="45"/>
       <c r="F2568" s="7"/>
     </row>
     <row r="2569" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2569" s="11"/>
       <c r="C2569" s="3"/>
       <c r="D2569" s="3"/>
-      <c r="E2569" s="46"/>
+      <c r="E2569" s="45"/>
       <c r="F2569" s="7"/>
     </row>
     <row r="2570" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2570" s="11"/>
       <c r="C2570" s="3"/>
       <c r="D2570" s="3"/>
-      <c r="E2570" s="46"/>
+      <c r="E2570" s="45"/>
       <c r="F2570" s="7"/>
     </row>
     <row r="2571" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2571" s="11"/>
       <c r="C2571" s="3"/>
       <c r="D2571" s="3"/>
-      <c r="E2571" s="46"/>
+      <c r="E2571" s="45"/>
       <c r="F2571" s="7"/>
     </row>
     <row r="2572" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2572" s="11"/>
       <c r="C2572" s="3"/>
       <c r="D2572" s="3"/>
-      <c r="E2572" s="46"/>
+      <c r="E2572" s="45"/>
       <c r="F2572" s="7"/>
     </row>
     <row r="2573" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2573" s="11"/>
       <c r="C2573" s="3"/>
       <c r="D2573" s="3"/>
-      <c r="E2573" s="46"/>
+      <c r="E2573" s="45"/>
       <c r="F2573" s="7"/>
     </row>
     <row r="2574" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2574" s="11"/>
       <c r="C2574" s="3"/>
       <c r="D2574" s="3"/>
-      <c r="E2574" s="46"/>
+      <c r="E2574" s="45"/>
       <c r="F2574" s="7"/>
     </row>
     <row r="2575" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2575" s="11"/>
       <c r="C2575" s="3"/>
       <c r="D2575" s="3"/>
-      <c r="E2575" s="46"/>
+      <c r="E2575" s="45"/>
       <c r="F2575" s="7"/>
     </row>
     <row r="2576" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2576" s="11"/>
       <c r="C2576" s="3"/>
       <c r="D2576" s="3"/>
-      <c r="E2576" s="46"/>
+      <c r="E2576" s="45"/>
       <c r="F2576" s="7"/>
     </row>
     <row r="2577" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2577" s="11"/>
       <c r="C2577" s="3"/>
       <c r="D2577" s="3"/>
-      <c r="E2577" s="46"/>
+      <c r="E2577" s="45"/>
       <c r="F2577" s="7"/>
     </row>
     <row r="2578" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2578" s="11"/>
       <c r="C2578" s="3"/>
       <c r="D2578" s="3"/>
-      <c r="E2578" s="46"/>
+      <c r="E2578" s="45"/>
       <c r="F2578" s="7"/>
     </row>
     <row r="2579" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2579" s="11"/>
       <c r="C2579" s="3"/>
       <c r="D2579" s="3"/>
-      <c r="E2579" s="46"/>
+      <c r="E2579" s="45"/>
       <c r="F2579" s="7"/>
     </row>
     <row r="2580" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2580" s="11"/>
       <c r="C2580" s="3"/>
       <c r="D2580" s="3"/>
-      <c r="E2580" s="46"/>
+      <c r="E2580" s="45"/>
       <c r="F2580" s="7"/>
     </row>
     <row r="2581" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2581" s="11"/>
       <c r="C2581" s="3"/>
       <c r="D2581" s="3"/>
-      <c r="E2581" s="46"/>
+      <c r="E2581" s="45"/>
       <c r="F2581" s="7"/>
     </row>
     <row r="2582" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2582" s="11"/>
       <c r="C2582" s="3"/>
       <c r="D2582" s="3"/>
-      <c r="E2582" s="46"/>
+      <c r="E2582" s="45"/>
       <c r="F2582" s="7"/>
     </row>
     <row r="2583" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2583" s="11"/>
       <c r="C2583" s="3"/>
       <c r="D2583" s="3"/>
-      <c r="E2583" s="46"/>
+      <c r="E2583" s="45"/>
       <c r="F2583" s="7"/>
     </row>
     <row r="2584" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2584" s="11"/>
       <c r="C2584" s="3"/>
       <c r="D2584" s="3"/>
-      <c r="E2584" s="46"/>
+      <c r="E2584" s="45"/>
       <c r="F2584" s="7"/>
     </row>
     <row r="2585" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2585" s="11"/>
       <c r="C2585" s="3"/>
       <c r="D2585" s="3"/>
-      <c r="E2585" s="46"/>
+      <c r="E2585" s="45"/>
       <c r="F2585" s="7"/>
     </row>
     <row r="2586" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2586" s="11"/>
       <c r="C2586" s="3"/>
       <c r="D2586" s="3"/>
-      <c r="E2586" s="46"/>
+      <c r="E2586" s="45"/>
       <c r="F2586" s="7"/>
     </row>
     <row r="2587" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2587" s="16"/>
       <c r="C2587" s="3"/>
       <c r="D2587" s="3"/>
-      <c r="E2587" s="46"/>
+      <c r="E2587" s="45"/>
       <c r="F2587" s="7"/>
     </row>
     <row r="2588" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2588" s="16"/>
       <c r="C2588" s="3"/>
       <c r="D2588" s="3"/>
-      <c r="E2588" s="46"/>
+      <c r="E2588" s="45"/>
       <c r="F2588" s="7"/>
     </row>
     <row r="2589" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2589" s="16"/>
       <c r="C2589" s="3"/>
       <c r="D2589" s="3"/>
-      <c r="E2589" s="46"/>
+      <c r="E2589" s="45"/>
       <c r="F2589" s="7"/>
     </row>
     <row r="2590" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2590" s="16"/>
       <c r="C2590" s="3"/>
       <c r="D2590" s="3"/>
-      <c r="E2590" s="46"/>
+      <c r="E2590" s="45"/>
       <c r="F2590" s="7"/>
     </row>
     <row r="2591" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2591" s="16"/>
       <c r="C2591" s="3"/>
       <c r="D2591" s="3"/>
-      <c r="E2591" s="46"/>
+      <c r="E2591" s="45"/>
       <c r="F2591" s="7"/>
     </row>
     <row r="2592" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2592" s="16"/>
       <c r="C2592" s="3"/>
       <c r="D2592" s="3"/>
-      <c r="E2592" s="46"/>
+      <c r="E2592" s="45"/>
       <c r="F2592" s="7"/>
     </row>
     <row r="2593" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2593" s="16"/>
       <c r="C2593" s="3"/>
       <c r="D2593" s="3"/>
-      <c r="E2593" s="46"/>
+      <c r="E2593" s="45"/>
       <c r="F2593" s="7"/>
     </row>
     <row r="2594" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2594" s="16"/>
       <c r="C2594" s="3"/>
       <c r="D2594" s="3"/>
-      <c r="E2594" s="46"/>
+      <c r="E2594" s="45"/>
       <c r="F2594" s="7"/>
     </row>
     <row r="2595" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2595" s="16"/>
       <c r="C2595" s="3"/>
       <c r="D2595" s="3"/>
-      <c r="E2595" s="46"/>
+      <c r="E2595" s="45"/>
       <c r="F2595" s="7"/>
     </row>
     <row r="2596" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2596" s="16"/>
       <c r="C2596" s="3"/>
       <c r="D2596" s="3"/>
-      <c r="E2596" s="46"/>
+      <c r="E2596" s="45"/>
       <c r="F2596" s="7"/>
     </row>
     <row r="2597" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2597" s="16"/>
       <c r="C2597" s="3"/>
       <c r="D2597" s="3"/>
-      <c r="E2597" s="46"/>
+      <c r="E2597" s="45"/>
       <c r="F2597" s="7"/>
     </row>
     <row r="2598" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2598" s="16"/>
       <c r="C2598" s="3"/>
       <c r="D2598" s="3"/>
-      <c r="E2598" s="46"/>
+      <c r="E2598" s="45"/>
       <c r="F2598" s="7"/>
     </row>
     <row r="2599" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2599" s="11"/>
       <c r="C2599" s="3"/>
       <c r="D2599" s="3"/>
-      <c r="E2599" s="46"/>
+      <c r="E2599" s="45"/>
       <c r="F2599" s="7"/>
     </row>
     <row r="2600" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2600" s="11"/>
       <c r="C2600" s="3"/>
       <c r="D2600" s="3"/>
-      <c r="E2600" s="46"/>
+      <c r="E2600" s="45"/>
       <c r="F2600" s="7"/>
     </row>
     <row r="2601" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2601" s="16"/>
       <c r="C2601" s="3"/>
       <c r="D2601" s="3"/>
-      <c r="E2601" s="46"/>
+      <c r="E2601" s="45"/>
       <c r="F2601" s="7"/>
     </row>
     <row r="2602" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2602" s="16"/>
       <c r="C2602" s="3"/>
       <c r="D2602" s="3"/>
-      <c r="E2602" s="46"/>
+      <c r="E2602" s="45"/>
       <c r="F2602" s="7"/>
     </row>
     <row r="2603" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2603" s="16"/>
       <c r="C2603" s="3"/>
       <c r="D2603" s="3"/>
-      <c r="E2603" s="46"/>
+      <c r="E2603" s="45"/>
       <c r="F2603" s="7"/>
     </row>
     <row r="2604" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2604" s="16"/>
       <c r="C2604" s="3"/>
       <c r="D2604" s="3"/>
-      <c r="E2604" s="46"/>
+      <c r="E2604" s="45"/>
       <c r="F2604" s="7"/>
     </row>
     <row r="2605" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2605" s="16"/>
       <c r="C2605" s="3"/>
       <c r="D2605" s="3"/>
-      <c r="E2605" s="46"/>
+      <c r="E2605" s="45"/>
       <c r="F2605" s="7"/>
     </row>
     <row r="2606" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2606" s="16"/>
       <c r="C2606" s="3"/>
       <c r="D2606" s="3"/>
-      <c r="E2606" s="46"/>
+      <c r="E2606" s="45"/>
       <c r="F2606" s="7"/>
     </row>
     <row r="2607" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2607" s="16"/>
       <c r="C2607" s="3"/>
       <c r="D2607" s="3"/>
-      <c r="E2607" s="46"/>
+      <c r="E2607" s="45"/>
       <c r="F2607" s="7"/>
     </row>
     <row r="2608" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2608" s="16"/>
       <c r="C2608" s="3"/>
       <c r="D2608" s="3"/>
-      <c r="E2608" s="46"/>
+      <c r="E2608" s="45"/>
       <c r="F2608" s="7"/>
     </row>
     <row r="2609" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2609" s="16"/>
       <c r="C2609" s="3"/>
       <c r="D2609" s="3"/>
-      <c r="E2609" s="46"/>
+      <c r="E2609" s="45"/>
       <c r="F2609" s="7"/>
     </row>
     <row r="2610" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2610" s="16"/>
       <c r="C2610" s="3"/>
       <c r="D2610" s="3"/>
-      <c r="E2610" s="46"/>
+      <c r="E2610" s="45"/>
       <c r="F2610" s="7"/>
     </row>
     <row r="2611" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2611" s="16"/>
       <c r="C2611" s="3"/>
       <c r="D2611" s="3"/>
-      <c r="E2611" s="46"/>
+      <c r="E2611" s="45"/>
       <c r="F2611" s="7"/>
     </row>
     <row r="2612" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2612" s="16"/>
       <c r="C2612" s="3"/>
       <c r="D2612" s="3"/>
-      <c r="E2612" s="46"/>
+      <c r="E2612" s="45"/>
       <c r="F2612" s="7"/>
     </row>
     <row r="2613" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2613" s="16"/>
       <c r="C2613" s="3"/>
       <c r="D2613" s="3"/>
-      <c r="E2613" s="46"/>
+      <c r="E2613" s="45"/>
       <c r="F2613" s="7"/>
     </row>
     <row r="2614" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2614" s="16"/>
       <c r="C2614" s="3"/>
       <c r="D2614" s="3"/>
-      <c r="E2614" s="46"/>
+      <c r="E2614" s="45"/>
       <c r="F2614" s="7"/>
     </row>
     <row r="2615" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2615" s="16"/>
       <c r="C2615" s="3"/>
       <c r="D2615" s="3"/>
-      <c r="E2615" s="46"/>
+      <c r="E2615" s="45"/>
       <c r="F2615" s="7"/>
     </row>
     <row r="2616" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2616" s="16"/>
       <c r="C2616" s="3"/>
       <c r="D2616" s="3"/>
-      <c r="E2616" s="46"/>
+      <c r="E2616" s="45"/>
       <c r="F2616" s="7"/>
     </row>
     <row r="2617" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2617" s="16"/>
       <c r="C2617" s="3"/>
       <c r="D2617" s="3"/>
-      <c r="E2617" s="46"/>
+      <c r="E2617" s="45"/>
       <c r="F2617" s="7"/>
     </row>
     <row r="2618" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2618" s="16"/>
       <c r="C2618" s="3"/>
       <c r="D2618" s="3"/>
-      <c r="E2618" s="46"/>
+      <c r="E2618" s="45"/>
       <c r="F2618" s="7"/>
     </row>
     <row r="2619" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2619" s="16"/>
       <c r="C2619" s="3"/>
       <c r="D2619" s="3"/>
-      <c r="E2619" s="46"/>
+      <c r="E2619" s="45"/>
       <c r="F2619" s="7"/>
     </row>
     <row r="2620" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2620" s="16"/>
       <c r="C2620" s="3"/>
       <c r="D2620" s="3"/>
-      <c r="E2620" s="46"/>
+      <c r="E2620" s="45"/>
       <c r="F2620" s="7"/>
     </row>
     <row r="2621" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2621" s="16"/>
       <c r="C2621" s="3"/>
       <c r="D2621" s="3"/>
-      <c r="E2621" s="46"/>
+      <c r="E2621" s="45"/>
       <c r="F2621" s="7"/>
     </row>
     <row r="2622" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2622" s="16"/>
       <c r="C2622" s="3"/>
       <c r="D2622" s="3"/>
-      <c r="E2622" s="46"/>
+      <c r="E2622" s="45"/>
       <c r="F2622" s="7"/>
     </row>
     <row r="2623" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2623" s="16"/>
       <c r="C2623" s="3"/>
       <c r="D2623" s="3"/>
-      <c r="E2623" s="46"/>
+      <c r="E2623" s="45"/>
       <c r="F2623" s="7"/>
     </row>
     <row r="2624" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2624" s="16"/>
       <c r="C2624" s="3"/>
       <c r="D2624" s="3"/>
-      <c r="E2624" s="46"/>
+      <c r="E2624" s="45"/>
       <c r="F2624" s="7"/>
     </row>
     <row r="2625" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2625" s="16"/>
       <c r="C2625" s="3"/>
       <c r="D2625" s="3"/>
-      <c r="E2625" s="46"/>
+      <c r="E2625" s="45"/>
       <c r="F2625" s="7"/>
     </row>
     <row r="2626" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2626" s="16"/>
       <c r="C2626" s="3"/>
       <c r="D2626" s="3"/>
-      <c r="E2626" s="46"/>
+      <c r="E2626" s="45"/>
       <c r="F2626" s="7"/>
     </row>
     <row r="2627" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2627" s="16"/>
       <c r="C2627" s="3"/>
       <c r="D2627" s="3"/>
-      <c r="E2627" s="46"/>
+      <c r="E2627" s="45"/>
       <c r="F2627" s="7"/>
     </row>
     <row r="2628" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2628" s="16"/>
       <c r="C2628" s="3"/>
       <c r="D2628" s="3"/>
-      <c r="E2628" s="46"/>
+      <c r="E2628" s="45"/>
       <c r="F2628" s="7"/>
     </row>
     <row r="2629" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2629" s="16"/>
       <c r="C2629" s="3"/>
       <c r="D2629" s="3"/>
-      <c r="E2629" s="46"/>
+      <c r="E2629" s="45"/>
       <c r="F2629" s="7"/>
     </row>
     <row r="2630" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2630" s="16"/>
       <c r="C2630" s="3"/>
       <c r="D2630" s="3"/>
-      <c r="E2630" s="46"/>
+      <c r="E2630" s="45"/>
       <c r="F2630" s="7"/>
     </row>
     <row r="2631" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2631" s="16"/>
       <c r="C2631" s="3"/>
       <c r="D2631" s="3"/>
-      <c r="E2631" s="46"/>
+      <c r="E2631" s="45"/>
       <c r="F2631" s="7"/>
     </row>
     <row r="2632" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2632" s="16"/>
       <c r="C2632" s="3"/>
       <c r="D2632" s="3"/>
-      <c r="E2632" s="46"/>
+      <c r="E2632" s="45"/>
       <c r="F2632" s="7"/>
     </row>
     <row r="2633" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2633" s="16"/>
       <c r="C2633" s="3"/>
       <c r="D2633" s="3"/>
-      <c r="E2633" s="46"/>
+      <c r="E2633" s="45"/>
       <c r="F2633" s="7"/>
     </row>
     <row r="2634" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2634" s="16"/>
       <c r="C2634" s="3"/>
       <c r="D2634" s="3"/>
-      <c r="E2634" s="46"/>
+      <c r="E2634" s="45"/>
       <c r="F2634" s="7"/>
     </row>
     <row r="2635" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2635" s="16"/>
       <c r="C2635" s="3"/>
       <c r="D2635" s="3"/>
-      <c r="E2635" s="46"/>
+      <c r="E2635" s="45"/>
       <c r="F2635" s="7"/>
     </row>
     <row r="2636" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2636" s="16"/>
       <c r="C2636" s="3"/>
       <c r="D2636" s="3"/>
-      <c r="E2636" s="46"/>
+      <c r="E2636" s="45"/>
       <c r="F2636" s="7"/>
     </row>
     <row r="2637" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2637" s="16"/>
       <c r="C2637" s="3"/>
       <c r="D2637" s="3"/>
-      <c r="E2637" s="46"/>
+      <c r="E2637" s="45"/>
       <c r="F2637" s="7"/>
     </row>
     <row r="2638" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2638" s="16"/>
       <c r="C2638" s="3"/>
       <c r="D2638" s="3"/>
-      <c r="E2638" s="46"/>
+      <c r="E2638" s="45"/>
       <c r="F2638" s="7"/>
     </row>
     <row r="2639" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2639" s="16"/>
       <c r="C2639" s="3"/>
       <c r="D2639" s="3"/>
-      <c r="E2639" s="46"/>
+      <c r="E2639" s="45"/>
       <c r="F2639" s="7"/>
     </row>
     <row r="2640" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2640" s="16"/>
       <c r="C2640" s="3"/>
       <c r="D2640" s="3"/>
-      <c r="E2640" s="46"/>
+      <c r="E2640" s="45"/>
       <c r="F2640" s="7"/>
     </row>
     <row r="2641" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2641" s="16"/>
       <c r="C2641" s="3"/>
       <c r="D2641" s="3"/>
-      <c r="E2641" s="46"/>
+      <c r="E2641" s="45"/>
       <c r="F2641" s="7"/>
     </row>
     <row r="2642" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2642" s="16"/>
       <c r="C2642" s="3"/>
       <c r="D2642" s="3"/>
-      <c r="E2642" s="46"/>
+      <c r="E2642" s="45"/>
       <c r="F2642" s="7"/>
     </row>
     <row r="2643" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2643" s="16"/>
       <c r="C2643" s="3"/>
       <c r="D2643" s="3"/>
-      <c r="E2643" s="46"/>
+      <c r="E2643" s="45"/>
       <c r="F2643" s="7"/>
     </row>
     <row r="2644" spans="2:6" x14ac:dyDescent="0.25">
@@ -58853,1806 +58928,1806 @@
       <c r="B2645" s="16"/>
       <c r="C2645" s="3"/>
       <c r="D2645" s="3"/>
-      <c r="E2645" s="46"/>
+      <c r="E2645" s="45"/>
       <c r="F2645" s="7"/>
     </row>
     <row r="2646" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2646" s="16"/>
       <c r="C2646" s="3"/>
       <c r="D2646" s="3"/>
-      <c r="E2646" s="46"/>
+      <c r="E2646" s="45"/>
       <c r="F2646" s="7"/>
     </row>
     <row r="2647" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2647" s="16"/>
       <c r="C2647" s="3"/>
       <c r="D2647" s="3"/>
-      <c r="E2647" s="46"/>
+      <c r="E2647" s="45"/>
       <c r="F2647" s="7"/>
     </row>
     <row r="2648" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2648" s="16"/>
       <c r="C2648" s="3"/>
       <c r="D2648" s="3"/>
-      <c r="E2648" s="46"/>
+      <c r="E2648" s="45"/>
       <c r="F2648" s="7"/>
     </row>
     <row r="2649" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2649" s="16"/>
       <c r="C2649" s="3"/>
       <c r="D2649" s="3"/>
-      <c r="E2649" s="46"/>
+      <c r="E2649" s="45"/>
       <c r="F2649" s="7"/>
     </row>
     <row r="2650" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2650" s="16"/>
       <c r="C2650" s="3"/>
       <c r="D2650" s="3"/>
-      <c r="E2650" s="46"/>
+      <c r="E2650" s="45"/>
       <c r="F2650" s="7"/>
     </row>
     <row r="2651" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2651" s="16"/>
       <c r="C2651" s="3"/>
       <c r="D2651" s="3"/>
-      <c r="E2651" s="46"/>
+      <c r="E2651" s="45"/>
       <c r="F2651" s="7"/>
     </row>
     <row r="2652" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2652" s="16"/>
       <c r="C2652" s="3"/>
       <c r="D2652" s="3"/>
-      <c r="E2652" s="46"/>
+      <c r="E2652" s="45"/>
       <c r="F2652" s="7"/>
     </row>
     <row r="2653" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2653" s="16"/>
       <c r="C2653" s="3"/>
       <c r="D2653" s="3"/>
-      <c r="E2653" s="46"/>
+      <c r="E2653" s="45"/>
       <c r="F2653" s="7"/>
     </row>
     <row r="2654" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2654" s="16"/>
       <c r="C2654" s="3"/>
       <c r="D2654" s="3"/>
-      <c r="E2654" s="46"/>
+      <c r="E2654" s="45"/>
       <c r="F2654" s="7"/>
     </row>
     <row r="2655" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2655" s="16"/>
       <c r="C2655" s="3"/>
       <c r="D2655" s="3"/>
-      <c r="E2655" s="46"/>
+      <c r="E2655" s="45"/>
       <c r="F2655" s="7"/>
     </row>
     <row r="2656" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2656" s="16"/>
       <c r="C2656" s="3"/>
       <c r="D2656" s="3"/>
-      <c r="E2656" s="46"/>
+      <c r="E2656" s="45"/>
       <c r="F2656" s="7"/>
     </row>
     <row r="2657" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2657" s="16"/>
       <c r="C2657" s="3"/>
       <c r="D2657" s="3"/>
-      <c r="E2657" s="46"/>
+      <c r="E2657" s="45"/>
       <c r="F2657" s="7"/>
     </row>
     <row r="2658" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2658" s="16"/>
       <c r="C2658" s="3"/>
       <c r="D2658" s="3"/>
-      <c r="E2658" s="46"/>
+      <c r="E2658" s="45"/>
       <c r="F2658" s="7"/>
     </row>
     <row r="2659" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2659" s="16"/>
       <c r="C2659" s="3"/>
       <c r="D2659" s="3"/>
-      <c r="E2659" s="46"/>
+      <c r="E2659" s="45"/>
       <c r="F2659" s="7"/>
     </row>
     <row r="2660" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2660" s="16"/>
       <c r="C2660" s="3"/>
       <c r="D2660" s="3"/>
-      <c r="E2660" s="46"/>
+      <c r="E2660" s="45"/>
       <c r="F2660" s="7"/>
     </row>
     <row r="2661" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2661" s="16"/>
       <c r="C2661" s="3"/>
       <c r="D2661" s="3"/>
-      <c r="E2661" s="46"/>
+      <c r="E2661" s="45"/>
       <c r="F2661" s="7"/>
     </row>
     <row r="2662" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2662" s="16"/>
       <c r="C2662" s="3"/>
       <c r="D2662" s="3"/>
-      <c r="E2662" s="46"/>
+      <c r="E2662" s="45"/>
       <c r="F2662" s="7"/>
     </row>
     <row r="2663" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2663" s="16"/>
       <c r="C2663" s="3"/>
       <c r="D2663" s="3"/>
-      <c r="E2663" s="46"/>
+      <c r="E2663" s="45"/>
       <c r="F2663" s="7"/>
     </row>
     <row r="2664" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2664" s="16"/>
       <c r="C2664" s="3"/>
       <c r="D2664" s="3"/>
-      <c r="E2664" s="46"/>
+      <c r="E2664" s="45"/>
       <c r="F2664" s="7"/>
     </row>
     <row r="2665" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2665" s="16"/>
       <c r="C2665" s="3"/>
       <c r="D2665" s="3"/>
-      <c r="E2665" s="46"/>
+      <c r="E2665" s="45"/>
       <c r="F2665" s="7"/>
     </row>
     <row r="2666" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2666" s="16"/>
       <c r="C2666" s="3"/>
       <c r="D2666" s="3"/>
-      <c r="E2666" s="46"/>
+      <c r="E2666" s="45"/>
       <c r="F2666" s="7"/>
     </row>
     <row r="2667" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2667" s="16"/>
       <c r="C2667" s="3"/>
       <c r="D2667" s="3"/>
-      <c r="E2667" s="46"/>
+      <c r="E2667" s="45"/>
       <c r="F2667" s="7"/>
     </row>
     <row r="2668" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2668" s="16"/>
       <c r="C2668" s="3"/>
       <c r="D2668" s="3"/>
-      <c r="E2668" s="46"/>
+      <c r="E2668" s="45"/>
       <c r="F2668" s="7"/>
     </row>
     <row r="2669" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2669" s="16"/>
       <c r="C2669" s="3"/>
       <c r="D2669" s="3"/>
-      <c r="E2669" s="46"/>
+      <c r="E2669" s="45"/>
       <c r="F2669" s="7"/>
     </row>
     <row r="2670" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2670" s="16"/>
       <c r="C2670" s="3"/>
       <c r="D2670" s="3"/>
-      <c r="E2670" s="46"/>
+      <c r="E2670" s="45"/>
       <c r="F2670" s="7"/>
     </row>
     <row r="2671" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2671" s="16"/>
       <c r="C2671" s="3"/>
       <c r="D2671" s="3"/>
-      <c r="E2671" s="46"/>
+      <c r="E2671" s="45"/>
       <c r="F2671" s="7"/>
     </row>
     <row r="2672" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2672" s="16"/>
       <c r="C2672" s="3"/>
       <c r="D2672" s="3"/>
-      <c r="E2672" s="46"/>
+      <c r="E2672" s="45"/>
       <c r="F2672" s="7"/>
     </row>
     <row r="2673" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2673" s="16"/>
       <c r="C2673" s="3"/>
       <c r="D2673" s="3"/>
-      <c r="E2673" s="46"/>
+      <c r="E2673" s="45"/>
       <c r="F2673" s="7"/>
     </row>
     <row r="2674" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2674" s="16"/>
       <c r="C2674" s="3"/>
       <c r="D2674" s="3"/>
-      <c r="E2674" s="46"/>
+      <c r="E2674" s="45"/>
       <c r="F2674" s="7"/>
     </row>
     <row r="2675" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2675" s="16"/>
       <c r="C2675" s="3"/>
       <c r="D2675" s="3"/>
-      <c r="E2675" s="46"/>
+      <c r="E2675" s="45"/>
       <c r="F2675" s="7"/>
     </row>
     <row r="2676" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2676" s="16"/>
       <c r="C2676" s="3"/>
       <c r="D2676" s="3"/>
-      <c r="E2676" s="46"/>
+      <c r="E2676" s="45"/>
       <c r="F2676" s="7"/>
     </row>
     <row r="2677" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2677" s="16"/>
       <c r="C2677" s="3"/>
       <c r="D2677" s="3"/>
-      <c r="E2677" s="46"/>
+      <c r="E2677" s="45"/>
       <c r="F2677" s="7"/>
     </row>
     <row r="2678" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2678" s="16"/>
       <c r="C2678" s="3"/>
       <c r="D2678" s="3"/>
-      <c r="E2678" s="46"/>
+      <c r="E2678" s="45"/>
       <c r="F2678" s="7"/>
     </row>
     <row r="2679" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2679" s="16"/>
       <c r="C2679" s="3"/>
       <c r="D2679" s="3"/>
-      <c r="E2679" s="46"/>
+      <c r="E2679" s="45"/>
       <c r="F2679" s="7"/>
     </row>
     <row r="2680" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2680" s="16"/>
       <c r="C2680" s="3"/>
       <c r="D2680" s="3"/>
-      <c r="E2680" s="46"/>
+      <c r="E2680" s="45"/>
       <c r="F2680" s="7"/>
     </row>
     <row r="2681" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2681" s="16"/>
       <c r="C2681" s="3"/>
       <c r="D2681" s="3"/>
-      <c r="E2681" s="46"/>
+      <c r="E2681" s="45"/>
       <c r="F2681" s="7"/>
     </row>
     <row r="2682" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2682" s="16"/>
       <c r="C2682" s="3"/>
       <c r="D2682" s="3"/>
-      <c r="E2682" s="46"/>
+      <c r="E2682" s="45"/>
       <c r="F2682" s="7"/>
     </row>
     <row r="2683" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2683" s="16"/>
       <c r="C2683" s="3"/>
       <c r="D2683" s="3"/>
-      <c r="E2683" s="46"/>
+      <c r="E2683" s="45"/>
       <c r="F2683" s="7"/>
     </row>
     <row r="2684" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2684" s="16"/>
       <c r="C2684" s="3"/>
       <c r="D2684" s="3"/>
-      <c r="E2684" s="46"/>
+      <c r="E2684" s="45"/>
       <c r="F2684" s="7"/>
     </row>
     <row r="2685" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2685" s="16"/>
       <c r="C2685" s="3"/>
       <c r="D2685" s="3"/>
-      <c r="E2685" s="46"/>
+      <c r="E2685" s="45"/>
       <c r="F2685" s="7"/>
     </row>
     <row r="2686" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2686" s="16"/>
       <c r="C2686" s="3"/>
       <c r="D2686" s="3"/>
-      <c r="E2686" s="46"/>
+      <c r="E2686" s="45"/>
       <c r="F2686" s="7"/>
     </row>
     <row r="2687" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2687" s="16"/>
       <c r="C2687" s="3"/>
       <c r="D2687" s="3"/>
-      <c r="E2687" s="46"/>
+      <c r="E2687" s="45"/>
       <c r="F2687" s="7"/>
     </row>
     <row r="2688" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2688" s="16"/>
       <c r="C2688" s="3"/>
       <c r="D2688" s="3"/>
-      <c r="E2688" s="46"/>
+      <c r="E2688" s="45"/>
       <c r="F2688" s="7"/>
     </row>
     <row r="2689" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2689" s="16"/>
       <c r="C2689" s="3"/>
       <c r="D2689" s="3"/>
-      <c r="E2689" s="46"/>
+      <c r="E2689" s="45"/>
       <c r="F2689" s="7"/>
     </row>
     <row r="2690" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2690" s="16"/>
       <c r="C2690" s="3"/>
       <c r="D2690" s="3"/>
-      <c r="E2690" s="46"/>
+      <c r="E2690" s="45"/>
       <c r="F2690" s="7"/>
     </row>
     <row r="2691" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2691" s="16"/>
       <c r="C2691" s="3"/>
       <c r="D2691" s="3"/>
-      <c r="E2691" s="46"/>
+      <c r="E2691" s="45"/>
       <c r="F2691" s="7"/>
     </row>
     <row r="2692" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2692" s="16"/>
       <c r="C2692" s="3"/>
       <c r="D2692" s="3"/>
-      <c r="E2692" s="46"/>
+      <c r="E2692" s="45"/>
       <c r="F2692" s="7"/>
     </row>
     <row r="2693" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2693" s="16"/>
       <c r="C2693" s="3"/>
       <c r="D2693" s="3"/>
-      <c r="E2693" s="46"/>
+      <c r="E2693" s="45"/>
       <c r="F2693" s="7"/>
     </row>
     <row r="2694" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2694" s="16"/>
       <c r="C2694" s="3"/>
       <c r="D2694" s="3"/>
-      <c r="E2694" s="46"/>
+      <c r="E2694" s="45"/>
       <c r="F2694" s="7"/>
     </row>
     <row r="2695" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2695" s="16"/>
       <c r="C2695" s="3"/>
       <c r="D2695" s="3"/>
-      <c r="E2695" s="46"/>
+      <c r="E2695" s="45"/>
       <c r="F2695" s="7"/>
     </row>
     <row r="2696" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2696" s="16"/>
       <c r="C2696" s="3"/>
       <c r="D2696" s="3"/>
-      <c r="E2696" s="46"/>
+      <c r="E2696" s="45"/>
       <c r="F2696" s="7"/>
     </row>
     <row r="2697" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2697" s="16"/>
       <c r="C2697" s="3"/>
       <c r="D2697" s="3"/>
-      <c r="E2697" s="46"/>
+      <c r="E2697" s="45"/>
       <c r="F2697" s="7"/>
     </row>
     <row r="2698" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2698" s="16"/>
       <c r="C2698" s="3"/>
       <c r="D2698" s="3"/>
-      <c r="E2698" s="46"/>
+      <c r="E2698" s="45"/>
       <c r="F2698" s="7"/>
     </row>
     <row r="2699" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2699" s="16"/>
       <c r="C2699" s="3"/>
       <c r="D2699" s="3"/>
-      <c r="E2699" s="46"/>
+      <c r="E2699" s="45"/>
       <c r="F2699" s="7"/>
     </row>
     <row r="2700" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2700" s="16"/>
       <c r="C2700" s="3"/>
       <c r="D2700" s="3"/>
-      <c r="E2700" s="46"/>
+      <c r="E2700" s="45"/>
       <c r="F2700" s="7"/>
     </row>
     <row r="2701" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2701" s="16"/>
       <c r="C2701" s="3"/>
       <c r="D2701" s="3"/>
-      <c r="E2701" s="46"/>
+      <c r="E2701" s="45"/>
       <c r="F2701" s="7"/>
     </row>
     <row r="2702" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2702" s="16"/>
       <c r="C2702" s="3"/>
       <c r="D2702" s="3"/>
-      <c r="E2702" s="46"/>
+      <c r="E2702" s="45"/>
       <c r="F2702" s="7"/>
     </row>
     <row r="2703" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2703" s="16"/>
       <c r="C2703" s="3"/>
       <c r="D2703" s="3"/>
-      <c r="E2703" s="46"/>
+      <c r="E2703" s="45"/>
       <c r="F2703" s="7"/>
     </row>
     <row r="2704" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2704" s="16"/>
       <c r="C2704" s="3"/>
       <c r="D2704" s="3"/>
-      <c r="E2704" s="46"/>
+      <c r="E2704" s="45"/>
       <c r="F2704" s="7"/>
     </row>
     <row r="2705" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2705" s="16"/>
       <c r="C2705" s="3"/>
       <c r="D2705" s="3"/>
-      <c r="E2705" s="46"/>
+      <c r="E2705" s="45"/>
       <c r="F2705" s="7"/>
     </row>
     <row r="2706" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2706" s="16"/>
       <c r="C2706" s="3"/>
       <c r="D2706" s="3"/>
-      <c r="E2706" s="46"/>
+      <c r="E2706" s="45"/>
       <c r="F2706" s="7"/>
     </row>
     <row r="2707" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2707" s="16"/>
       <c r="C2707" s="3"/>
       <c r="D2707" s="3"/>
-      <c r="E2707" s="46"/>
+      <c r="E2707" s="45"/>
       <c r="F2707" s="7"/>
     </row>
     <row r="2708" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2708" s="16"/>
       <c r="C2708" s="3"/>
       <c r="D2708" s="3"/>
-      <c r="E2708" s="46"/>
+      <c r="E2708" s="45"/>
       <c r="F2708" s="7"/>
     </row>
     <row r="2709" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2709" s="16"/>
       <c r="C2709" s="3"/>
       <c r="D2709" s="3"/>
-      <c r="E2709" s="46"/>
+      <c r="E2709" s="45"/>
       <c r="F2709" s="7"/>
     </row>
     <row r="2710" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2710" s="16"/>
       <c r="C2710" s="3"/>
       <c r="D2710" s="3"/>
-      <c r="E2710" s="46"/>
+      <c r="E2710" s="45"/>
       <c r="F2710" s="7"/>
     </row>
     <row r="2711" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2711" s="16"/>
       <c r="C2711" s="3"/>
       <c r="D2711" s="3"/>
-      <c r="E2711" s="46"/>
+      <c r="E2711" s="45"/>
       <c r="F2711" s="7"/>
     </row>
     <row r="2712" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2712" s="16"/>
       <c r="C2712" s="3"/>
       <c r="D2712" s="3"/>
-      <c r="E2712" s="46"/>
+      <c r="E2712" s="45"/>
       <c r="F2712" s="7"/>
     </row>
     <row r="2713" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2713" s="16"/>
       <c r="C2713" s="3"/>
       <c r="D2713" s="3"/>
-      <c r="E2713" s="46"/>
+      <c r="E2713" s="45"/>
       <c r="F2713" s="7"/>
     </row>
     <row r="2714" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2714" s="16"/>
       <c r="C2714" s="3"/>
       <c r="D2714" s="3"/>
-      <c r="E2714" s="46"/>
+      <c r="E2714" s="45"/>
       <c r="F2714" s="7"/>
     </row>
     <row r="2715" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2715" s="16"/>
       <c r="C2715" s="3"/>
       <c r="D2715" s="3"/>
-      <c r="E2715" s="46"/>
+      <c r="E2715" s="45"/>
       <c r="F2715" s="7"/>
     </row>
     <row r="2716" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2716" s="16"/>
       <c r="C2716" s="3"/>
       <c r="D2716" s="3"/>
-      <c r="E2716" s="46"/>
+      <c r="E2716" s="45"/>
       <c r="F2716" s="7"/>
     </row>
     <row r="2717" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2717" s="16"/>
       <c r="C2717" s="3"/>
       <c r="D2717" s="3"/>
-      <c r="E2717" s="46"/>
+      <c r="E2717" s="45"/>
       <c r="F2717" s="7"/>
     </row>
     <row r="2718" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2718" s="16"/>
       <c r="C2718" s="3"/>
       <c r="D2718" s="3"/>
-      <c r="E2718" s="46"/>
+      <c r="E2718" s="45"/>
       <c r="F2718" s="7"/>
     </row>
     <row r="2719" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2719" s="16"/>
       <c r="C2719" s="3"/>
       <c r="D2719" s="3"/>
-      <c r="E2719" s="46"/>
+      <c r="E2719" s="45"/>
       <c r="F2719" s="7"/>
     </row>
     <row r="2720" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2720" s="16"/>
       <c r="C2720" s="3"/>
       <c r="D2720" s="3"/>
-      <c r="E2720" s="46"/>
+      <c r="E2720" s="45"/>
       <c r="F2720" s="7"/>
     </row>
     <row r="2721" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2721" s="16"/>
       <c r="C2721" s="3"/>
       <c r="D2721" s="3"/>
-      <c r="E2721" s="46"/>
+      <c r="E2721" s="45"/>
       <c r="F2721" s="7"/>
     </row>
     <row r="2722" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2722" s="16"/>
       <c r="C2722" s="3"/>
       <c r="D2722" s="3"/>
-      <c r="E2722" s="46"/>
+      <c r="E2722" s="45"/>
       <c r="F2722" s="7"/>
     </row>
     <row r="2723" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2723" s="16"/>
       <c r="C2723" s="3"/>
       <c r="D2723" s="3"/>
-      <c r="E2723" s="46"/>
+      <c r="E2723" s="45"/>
       <c r="F2723" s="7"/>
     </row>
     <row r="2724" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2724" s="16"/>
       <c r="C2724" s="3"/>
       <c r="D2724" s="3"/>
-      <c r="E2724" s="46"/>
+      <c r="E2724" s="45"/>
       <c r="F2724" s="7"/>
     </row>
     <row r="2725" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2725" s="16"/>
       <c r="C2725" s="3"/>
       <c r="D2725" s="3"/>
-      <c r="E2725" s="46"/>
+      <c r="E2725" s="45"/>
       <c r="F2725" s="7"/>
     </row>
     <row r="2726" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2726" s="16"/>
       <c r="C2726" s="3"/>
       <c r="D2726" s="3"/>
-      <c r="E2726" s="46"/>
+      <c r="E2726" s="45"/>
       <c r="F2726" s="7"/>
     </row>
     <row r="2727" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2727" s="16"/>
       <c r="C2727" s="3"/>
       <c r="D2727" s="3"/>
-      <c r="E2727" s="46"/>
+      <c r="E2727" s="45"/>
       <c r="F2727" s="7"/>
     </row>
     <row r="2728" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2728" s="16"/>
       <c r="C2728" s="3"/>
       <c r="D2728" s="3"/>
-      <c r="E2728" s="46"/>
+      <c r="E2728" s="45"/>
       <c r="F2728" s="7"/>
     </row>
     <row r="2729" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2729" s="16"/>
       <c r="C2729" s="3"/>
       <c r="D2729" s="3"/>
-      <c r="E2729" s="46"/>
+      <c r="E2729" s="45"/>
       <c r="F2729" s="7"/>
     </row>
     <row r="2730" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2730" s="16"/>
       <c r="C2730" s="3"/>
       <c r="D2730" s="3"/>
-      <c r="E2730" s="46"/>
+      <c r="E2730" s="45"/>
       <c r="F2730" s="7"/>
     </row>
     <row r="2731" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2731" s="16"/>
       <c r="C2731" s="3"/>
       <c r="D2731" s="3"/>
-      <c r="E2731" s="46"/>
+      <c r="E2731" s="45"/>
       <c r="F2731" s="7"/>
     </row>
     <row r="2732" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2732" s="16"/>
       <c r="C2732" s="3"/>
       <c r="D2732" s="3"/>
-      <c r="E2732" s="46"/>
+      <c r="E2732" s="45"/>
       <c r="F2732" s="7"/>
     </row>
     <row r="2733" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2733" s="16"/>
       <c r="C2733" s="3"/>
       <c r="D2733" s="3"/>
-      <c r="E2733" s="46"/>
+      <c r="E2733" s="45"/>
       <c r="F2733" s="7"/>
     </row>
     <row r="2734" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2734" s="16"/>
       <c r="C2734" s="3"/>
       <c r="D2734" s="3"/>
-      <c r="E2734" s="46"/>
+      <c r="E2734" s="45"/>
       <c r="F2734" s="7"/>
     </row>
     <row r="2735" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2735" s="16"/>
       <c r="C2735" s="3"/>
       <c r="D2735" s="3"/>
-      <c r="E2735" s="46"/>
+      <c r="E2735" s="45"/>
       <c r="F2735" s="7"/>
     </row>
     <row r="2736" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2736" s="16"/>
       <c r="C2736" s="3"/>
       <c r="D2736" s="3"/>
-      <c r="E2736" s="46"/>
+      <c r="E2736" s="45"/>
       <c r="F2736" s="7"/>
     </row>
     <row r="2737" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2737" s="16"/>
       <c r="C2737" s="3"/>
       <c r="D2737" s="3"/>
-      <c r="E2737" s="46"/>
+      <c r="E2737" s="45"/>
       <c r="F2737" s="7"/>
     </row>
     <row r="2738" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2738" s="16"/>
       <c r="C2738" s="3"/>
       <c r="D2738" s="3"/>
-      <c r="E2738" s="46"/>
+      <c r="E2738" s="45"/>
       <c r="F2738" s="7"/>
     </row>
     <row r="2739" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2739" s="16"/>
       <c r="C2739" s="3"/>
       <c r="D2739" s="3"/>
-      <c r="E2739" s="46"/>
+      <c r="E2739" s="45"/>
       <c r="F2739" s="7"/>
     </row>
     <row r="2740" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2740" s="16"/>
       <c r="C2740" s="3"/>
       <c r="D2740" s="3"/>
-      <c r="E2740" s="46"/>
+      <c r="E2740" s="45"/>
       <c r="F2740" s="7"/>
     </row>
     <row r="2741" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2741" s="16"/>
       <c r="C2741" s="3"/>
       <c r="D2741" s="3"/>
-      <c r="E2741" s="46"/>
+      <c r="E2741" s="45"/>
       <c r="F2741" s="7"/>
     </row>
     <row r="2742" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2742" s="16"/>
       <c r="C2742" s="3"/>
       <c r="D2742" s="3"/>
-      <c r="E2742" s="46"/>
+      <c r="E2742" s="45"/>
       <c r="F2742" s="7"/>
     </row>
     <row r="2743" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2743" s="16"/>
       <c r="C2743" s="3"/>
       <c r="D2743" s="3"/>
-      <c r="E2743" s="46"/>
+      <c r="E2743" s="45"/>
       <c r="F2743" s="7"/>
     </row>
     <row r="2744" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2744" s="16"/>
       <c r="C2744" s="3"/>
       <c r="D2744" s="3"/>
-      <c r="E2744" s="46"/>
+      <c r="E2744" s="45"/>
       <c r="F2744" s="7"/>
     </row>
     <row r="2745" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2745" s="16"/>
       <c r="C2745" s="3"/>
       <c r="D2745" s="3"/>
-      <c r="E2745" s="46"/>
+      <c r="E2745" s="45"/>
       <c r="F2745" s="7"/>
     </row>
     <row r="2746" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2746" s="16"/>
       <c r="C2746" s="3"/>
       <c r="D2746" s="3"/>
-      <c r="E2746" s="46"/>
+      <c r="E2746" s="45"/>
       <c r="F2746" s="7"/>
     </row>
     <row r="2747" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2747" s="16"/>
       <c r="C2747" s="3"/>
       <c r="D2747" s="3"/>
-      <c r="E2747" s="46"/>
+      <c r="E2747" s="45"/>
       <c r="F2747" s="7"/>
     </row>
     <row r="2748" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2748" s="16"/>
       <c r="C2748" s="3"/>
       <c r="D2748" s="3"/>
-      <c r="E2748" s="46"/>
+      <c r="E2748" s="45"/>
       <c r="F2748" s="7"/>
     </row>
     <row r="2749" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2749" s="16"/>
       <c r="C2749" s="3"/>
       <c r="D2749" s="3"/>
-      <c r="E2749" s="46"/>
+      <c r="E2749" s="45"/>
       <c r="F2749" s="7"/>
     </row>
     <row r="2750" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2750" s="16"/>
       <c r="C2750" s="3"/>
       <c r="D2750" s="3"/>
-      <c r="E2750" s="46"/>
+      <c r="E2750" s="45"/>
       <c r="F2750" s="7"/>
     </row>
     <row r="2751" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2751" s="16"/>
       <c r="C2751" s="3"/>
       <c r="D2751" s="3"/>
-      <c r="E2751" s="46"/>
+      <c r="E2751" s="45"/>
       <c r="F2751" s="7"/>
     </row>
     <row r="2752" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2752" s="16"/>
       <c r="C2752" s="3"/>
       <c r="D2752" s="3"/>
-      <c r="E2752" s="46"/>
+      <c r="E2752" s="45"/>
       <c r="F2752" s="7"/>
     </row>
     <row r="2753" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2753" s="16"/>
       <c r="C2753" s="3"/>
       <c r="D2753" s="3"/>
-      <c r="E2753" s="46"/>
+      <c r="E2753" s="45"/>
       <c r="F2753" s="7"/>
     </row>
     <row r="2754" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2754" s="16"/>
       <c r="C2754" s="3"/>
       <c r="D2754" s="3"/>
-      <c r="E2754" s="46"/>
+      <c r="E2754" s="45"/>
       <c r="F2754" s="7"/>
     </row>
     <row r="2755" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2755" s="16"/>
       <c r="C2755" s="3"/>
       <c r="D2755" s="3"/>
-      <c r="E2755" s="46"/>
+      <c r="E2755" s="45"/>
       <c r="F2755" s="7"/>
     </row>
     <row r="2756" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2756" s="16"/>
       <c r="C2756" s="3"/>
       <c r="D2756" s="3"/>
-      <c r="E2756" s="46"/>
+      <c r="E2756" s="45"/>
       <c r="F2756" s="7"/>
     </row>
     <row r="2757" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2757" s="16"/>
       <c r="C2757" s="3"/>
       <c r="D2757" s="3"/>
-      <c r="E2757" s="46"/>
+      <c r="E2757" s="45"/>
       <c r="F2757" s="7"/>
     </row>
     <row r="2758" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2758" s="16"/>
       <c r="C2758" s="3"/>
       <c r="D2758" s="3"/>
-      <c r="E2758" s="46"/>
+      <c r="E2758" s="45"/>
       <c r="F2758" s="7"/>
     </row>
     <row r="2759" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2759" s="16"/>
       <c r="C2759" s="3"/>
       <c r="D2759" s="3"/>
-      <c r="E2759" s="46"/>
+      <c r="E2759" s="45"/>
       <c r="F2759" s="7"/>
     </row>
     <row r="2760" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2760" s="16"/>
       <c r="C2760" s="3"/>
       <c r="D2760" s="3"/>
-      <c r="E2760" s="46"/>
+      <c r="E2760" s="45"/>
       <c r="F2760" s="7"/>
     </row>
     <row r="2761" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2761" s="16"/>
       <c r="C2761" s="3"/>
       <c r="D2761" s="3"/>
-      <c r="E2761" s="46"/>
+      <c r="E2761" s="45"/>
       <c r="F2761" s="7"/>
     </row>
     <row r="2762" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2762" s="16"/>
       <c r="C2762" s="3"/>
       <c r="D2762" s="3"/>
-      <c r="E2762" s="46"/>
+      <c r="E2762" s="45"/>
       <c r="F2762" s="7"/>
     </row>
     <row r="2763" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2763" s="16"/>
       <c r="C2763" s="3"/>
       <c r="D2763" s="3"/>
-      <c r="E2763" s="46"/>
+      <c r="E2763" s="45"/>
       <c r="F2763" s="7"/>
     </row>
     <row r="2764" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2764" s="16"/>
       <c r="C2764" s="3"/>
       <c r="D2764" s="3"/>
-      <c r="E2764" s="46"/>
+      <c r="E2764" s="45"/>
       <c r="F2764" s="7"/>
     </row>
     <row r="2765" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2765" s="16"/>
       <c r="C2765" s="3"/>
       <c r="D2765" s="3"/>
-      <c r="E2765" s="46"/>
+      <c r="E2765" s="45"/>
       <c r="F2765" s="7"/>
     </row>
     <row r="2766" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2766" s="16"/>
       <c r="C2766" s="3"/>
       <c r="D2766" s="3"/>
-      <c r="E2766" s="46"/>
+      <c r="E2766" s="45"/>
       <c r="F2766" s="7"/>
     </row>
     <row r="2767" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2767" s="16"/>
       <c r="C2767" s="3"/>
       <c r="D2767" s="3"/>
-      <c r="E2767" s="46"/>
+      <c r="E2767" s="45"/>
       <c r="F2767" s="7"/>
     </row>
     <row r="2768" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2768" s="16"/>
       <c r="C2768" s="3"/>
       <c r="D2768" s="3"/>
-      <c r="E2768" s="46"/>
+      <c r="E2768" s="45"/>
       <c r="F2768" s="7"/>
     </row>
     <row r="2769" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2769" s="16"/>
       <c r="C2769" s="3"/>
       <c r="D2769" s="3"/>
-      <c r="E2769" s="46"/>
+      <c r="E2769" s="45"/>
       <c r="F2769" s="7"/>
     </row>
     <row r="2770" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2770" s="16"/>
       <c r="C2770" s="3"/>
       <c r="D2770" s="3"/>
-      <c r="E2770" s="46"/>
+      <c r="E2770" s="45"/>
       <c r="F2770" s="7"/>
     </row>
     <row r="2771" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2771" s="16"/>
       <c r="C2771" s="3"/>
       <c r="D2771" s="3"/>
-      <c r="E2771" s="46"/>
+      <c r="E2771" s="45"/>
       <c r="F2771" s="7"/>
     </row>
     <row r="2772" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2772" s="16"/>
       <c r="C2772" s="3"/>
       <c r="D2772" s="3"/>
-      <c r="E2772" s="46"/>
+      <c r="E2772" s="45"/>
       <c r="F2772" s="7"/>
     </row>
     <row r="2773" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2773" s="16"/>
       <c r="C2773" s="3"/>
       <c r="D2773" s="3"/>
-      <c r="E2773" s="46"/>
+      <c r="E2773" s="45"/>
       <c r="F2773" s="7"/>
     </row>
     <row r="2774" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2774" s="16"/>
       <c r="C2774" s="3"/>
       <c r="D2774" s="3"/>
-      <c r="E2774" s="46"/>
+      <c r="E2774" s="45"/>
       <c r="F2774" s="7"/>
     </row>
     <row r="2775" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2775" s="16"/>
       <c r="C2775" s="3"/>
       <c r="D2775" s="3"/>
-      <c r="E2775" s="46"/>
+      <c r="E2775" s="45"/>
       <c r="F2775" s="7"/>
     </row>
     <row r="2776" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2776" s="16"/>
       <c r="C2776" s="3"/>
       <c r="D2776" s="3"/>
-      <c r="E2776" s="46"/>
+      <c r="E2776" s="45"/>
       <c r="F2776" s="7"/>
     </row>
     <row r="2777" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2777" s="16"/>
       <c r="C2777" s="3"/>
       <c r="D2777" s="3"/>
-      <c r="E2777" s="46"/>
+      <c r="E2777" s="45"/>
       <c r="F2777" s="7"/>
     </row>
     <row r="2778" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2778" s="16"/>
       <c r="C2778" s="3"/>
       <c r="D2778" s="3"/>
-      <c r="E2778" s="46"/>
+      <c r="E2778" s="45"/>
       <c r="F2778" s="7"/>
     </row>
     <row r="2779" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2779" s="16"/>
       <c r="C2779" s="3"/>
       <c r="D2779" s="3"/>
-      <c r="E2779" s="46"/>
+      <c r="E2779" s="45"/>
       <c r="F2779" s="7"/>
     </row>
     <row r="2780" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2780" s="16"/>
       <c r="C2780" s="3"/>
       <c r="D2780" s="3"/>
-      <c r="E2780" s="46"/>
+      <c r="E2780" s="45"/>
       <c r="F2780" s="7"/>
     </row>
     <row r="2781" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2781" s="16"/>
       <c r="C2781" s="3"/>
       <c r="D2781" s="3"/>
-      <c r="E2781" s="46"/>
+      <c r="E2781" s="45"/>
       <c r="F2781" s="7"/>
     </row>
     <row r="2782" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2782" s="16"/>
       <c r="C2782" s="3"/>
       <c r="D2782" s="3"/>
-      <c r="E2782" s="46"/>
+      <c r="E2782" s="45"/>
       <c r="F2782" s="7"/>
     </row>
     <row r="2783" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2783" s="16"/>
       <c r="C2783" s="3"/>
       <c r="D2783" s="3"/>
-      <c r="E2783" s="46"/>
+      <c r="E2783" s="45"/>
       <c r="F2783" s="7"/>
     </row>
     <row r="2784" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2784" s="16"/>
       <c r="C2784" s="3"/>
       <c r="D2784" s="3"/>
-      <c r="E2784" s="46"/>
+      <c r="E2784" s="45"/>
       <c r="F2784" s="7"/>
     </row>
     <row r="2785" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2785" s="16"/>
       <c r="C2785" s="3"/>
       <c r="D2785" s="3"/>
-      <c r="E2785" s="46"/>
+      <c r="E2785" s="45"/>
       <c r="F2785" s="7"/>
     </row>
     <row r="2786" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2786" s="16"/>
       <c r="C2786" s="3"/>
       <c r="D2786" s="3"/>
-      <c r="E2786" s="46"/>
+      <c r="E2786" s="45"/>
       <c r="F2786" s="7"/>
     </row>
     <row r="2787" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2787" s="16"/>
       <c r="C2787" s="3"/>
       <c r="D2787" s="3"/>
-      <c r="E2787" s="46"/>
+      <c r="E2787" s="45"/>
       <c r="F2787" s="7"/>
     </row>
     <row r="2788" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2788" s="16"/>
       <c r="C2788" s="3"/>
       <c r="D2788" s="3"/>
-      <c r="E2788" s="46"/>
+      <c r="E2788" s="45"/>
       <c r="F2788" s="7"/>
     </row>
     <row r="2789" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2789" s="16"/>
       <c r="C2789" s="3"/>
       <c r="D2789" s="3"/>
-      <c r="E2789" s="46"/>
+      <c r="E2789" s="45"/>
       <c r="F2789" s="7"/>
     </row>
     <row r="2790" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2790" s="16"/>
       <c r="C2790" s="3"/>
       <c r="D2790" s="3"/>
-      <c r="E2790" s="46"/>
+      <c r="E2790" s="45"/>
       <c r="F2790" s="7"/>
     </row>
     <row r="2791" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2791" s="16"/>
       <c r="C2791" s="3"/>
       <c r="D2791" s="3"/>
-      <c r="E2791" s="46"/>
+      <c r="E2791" s="45"/>
       <c r="F2791" s="7"/>
     </row>
     <row r="2792" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2792" s="16"/>
       <c r="C2792" s="3"/>
       <c r="D2792" s="3"/>
-      <c r="E2792" s="46"/>
+      <c r="E2792" s="45"/>
       <c r="F2792" s="7"/>
     </row>
     <row r="2793" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2793" s="16"/>
       <c r="C2793" s="3"/>
       <c r="D2793" s="3"/>
-      <c r="E2793" s="46"/>
+      <c r="E2793" s="45"/>
       <c r="F2793" s="7"/>
     </row>
     <row r="2794" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2794" s="16"/>
       <c r="C2794" s="3"/>
       <c r="D2794" s="3"/>
-      <c r="E2794" s="46"/>
+      <c r="E2794" s="45"/>
       <c r="F2794" s="7"/>
     </row>
     <row r="2795" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2795" s="16"/>
       <c r="C2795" s="3"/>
       <c r="D2795" s="3"/>
-      <c r="E2795" s="46"/>
+      <c r="E2795" s="45"/>
       <c r="F2795" s="7"/>
     </row>
     <row r="2796" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2796" s="16"/>
       <c r="C2796" s="3"/>
       <c r="D2796" s="3"/>
-      <c r="E2796" s="46"/>
+      <c r="E2796" s="45"/>
       <c r="F2796" s="7"/>
     </row>
     <row r="2797" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2797" s="16"/>
       <c r="C2797" s="3"/>
       <c r="D2797" s="3"/>
-      <c r="E2797" s="46"/>
+      <c r="E2797" s="45"/>
       <c r="F2797" s="7"/>
     </row>
     <row r="2798" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2798" s="16"/>
       <c r="C2798" s="3"/>
       <c r="D2798" s="3"/>
-      <c r="E2798" s="46"/>
+      <c r="E2798" s="45"/>
       <c r="F2798" s="7"/>
     </row>
     <row r="2799" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2799" s="16"/>
       <c r="C2799" s="3"/>
       <c r="D2799" s="3"/>
-      <c r="E2799" s="46"/>
+      <c r="E2799" s="45"/>
       <c r="F2799" s="7"/>
     </row>
     <row r="2800" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2800" s="16"/>
       <c r="C2800" s="3"/>
       <c r="D2800" s="3"/>
-      <c r="E2800" s="46"/>
+      <c r="E2800" s="45"/>
       <c r="F2800" s="7"/>
     </row>
     <row r="2801" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2801" s="16"/>
       <c r="C2801" s="3"/>
       <c r="D2801" s="3"/>
-      <c r="E2801" s="46"/>
+      <c r="E2801" s="45"/>
       <c r="F2801" s="7"/>
     </row>
     <row r="2802" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2802" s="16"/>
       <c r="C2802" s="3"/>
       <c r="D2802" s="3"/>
-      <c r="E2802" s="46"/>
+      <c r="E2802" s="45"/>
       <c r="F2802" s="7"/>
     </row>
     <row r="2803" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2803" s="16"/>
       <c r="C2803" s="3"/>
       <c r="D2803" s="3"/>
-      <c r="E2803" s="46"/>
+      <c r="E2803" s="45"/>
       <c r="F2803" s="7"/>
     </row>
     <row r="2804" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2804" s="16"/>
       <c r="C2804" s="3"/>
       <c r="D2804" s="3"/>
-      <c r="E2804" s="46"/>
+      <c r="E2804" s="45"/>
       <c r="F2804" s="7"/>
     </row>
     <row r="2805" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2805" s="16"/>
       <c r="C2805" s="3"/>
       <c r="D2805" s="3"/>
-      <c r="E2805" s="46"/>
+      <c r="E2805" s="45"/>
       <c r="F2805" s="7"/>
     </row>
     <row r="2806" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2806" s="16"/>
       <c r="C2806" s="3"/>
       <c r="D2806" s="3"/>
-      <c r="E2806" s="46"/>
+      <c r="E2806" s="45"/>
       <c r="F2806" s="7"/>
     </row>
     <row r="2807" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2807" s="16"/>
       <c r="C2807" s="3"/>
       <c r="D2807" s="3"/>
-      <c r="E2807" s="46"/>
+      <c r="E2807" s="45"/>
       <c r="F2807" s="7"/>
     </row>
     <row r="2808" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2808" s="16"/>
       <c r="C2808" s="3"/>
       <c r="D2808" s="3"/>
-      <c r="E2808" s="46"/>
+      <c r="E2808" s="45"/>
       <c r="F2808" s="7"/>
     </row>
     <row r="2809" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2809" s="16"/>
       <c r="C2809" s="3"/>
       <c r="D2809" s="3"/>
-      <c r="E2809" s="46"/>
+      <c r="E2809" s="45"/>
       <c r="F2809" s="7"/>
     </row>
     <row r="2810" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2810" s="16"/>
       <c r="C2810" s="3"/>
       <c r="D2810" s="3"/>
-      <c r="E2810" s="46"/>
+      <c r="E2810" s="45"/>
       <c r="F2810" s="7"/>
     </row>
     <row r="2811" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2811" s="16"/>
       <c r="C2811" s="3"/>
       <c r="D2811" s="3"/>
-      <c r="E2811" s="46"/>
+      <c r="E2811" s="45"/>
       <c r="F2811" s="7"/>
     </row>
     <row r="2812" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2812" s="16"/>
       <c r="C2812" s="3"/>
       <c r="D2812" s="3"/>
-      <c r="E2812" s="46"/>
+      <c r="E2812" s="45"/>
       <c r="F2812" s="7"/>
     </row>
     <row r="2813" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2813" s="16"/>
       <c r="C2813" s="3"/>
       <c r="D2813" s="3"/>
-      <c r="E2813" s="46"/>
+      <c r="E2813" s="45"/>
       <c r="F2813" s="7"/>
     </row>
     <row r="2814" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2814" s="16"/>
       <c r="C2814" s="3"/>
       <c r="D2814" s="3"/>
-      <c r="E2814" s="46"/>
+      <c r="E2814" s="45"/>
       <c r="F2814" s="7"/>
     </row>
     <row r="2815" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2815" s="16"/>
       <c r="C2815" s="3"/>
       <c r="D2815" s="3"/>
-      <c r="E2815" s="46"/>
+      <c r="E2815" s="45"/>
       <c r="F2815" s="7"/>
     </row>
     <row r="2816" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2816" s="16"/>
       <c r="C2816" s="3"/>
       <c r="D2816" s="3"/>
-      <c r="E2816" s="46"/>
+      <c r="E2816" s="45"/>
       <c r="F2816" s="7"/>
     </row>
     <row r="2817" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2817" s="16"/>
       <c r="C2817" s="3"/>
       <c r="D2817" s="3"/>
-      <c r="E2817" s="46"/>
+      <c r="E2817" s="45"/>
       <c r="F2817" s="7"/>
     </row>
     <row r="2818" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2818" s="16"/>
       <c r="C2818" s="3"/>
       <c r="D2818" s="3"/>
-      <c r="E2818" s="46"/>
+      <c r="E2818" s="45"/>
       <c r="F2818" s="7"/>
     </row>
     <row r="2819" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2819" s="16"/>
       <c r="C2819" s="3"/>
       <c r="D2819" s="3"/>
-      <c r="E2819" s="46"/>
+      <c r="E2819" s="45"/>
       <c r="F2819" s="7"/>
     </row>
     <row r="2820" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2820" s="16"/>
       <c r="C2820" s="3"/>
       <c r="D2820" s="3"/>
-      <c r="E2820" s="46"/>
+      <c r="E2820" s="45"/>
       <c r="F2820" s="7"/>
     </row>
     <row r="2821" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2821" s="16"/>
       <c r="C2821" s="3"/>
       <c r="D2821" s="3"/>
-      <c r="E2821" s="46"/>
+      <c r="E2821" s="45"/>
       <c r="F2821" s="7"/>
     </row>
     <row r="2822" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2822" s="16"/>
       <c r="C2822" s="3"/>
       <c r="D2822" s="3"/>
-      <c r="E2822" s="46"/>
+      <c r="E2822" s="45"/>
       <c r="F2822" s="7"/>
     </row>
     <row r="2823" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2823" s="16"/>
       <c r="C2823" s="3"/>
       <c r="D2823" s="3"/>
-      <c r="E2823" s="46"/>
+      <c r="E2823" s="45"/>
       <c r="F2823" s="7"/>
     </row>
     <row r="2824" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2824" s="16"/>
       <c r="C2824" s="3"/>
       <c r="D2824" s="3"/>
-      <c r="E2824" s="46"/>
+      <c r="E2824" s="45"/>
       <c r="F2824" s="7"/>
     </row>
     <row r="2825" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2825" s="16"/>
       <c r="C2825" s="3"/>
       <c r="D2825" s="3"/>
-      <c r="E2825" s="46"/>
+      <c r="E2825" s="45"/>
       <c r="F2825" s="7"/>
     </row>
     <row r="2826" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2826" s="16"/>
       <c r="C2826" s="3"/>
       <c r="D2826" s="3"/>
-      <c r="E2826" s="46"/>
+      <c r="E2826" s="45"/>
       <c r="F2826" s="7"/>
     </row>
     <row r="2827" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2827" s="16"/>
       <c r="C2827" s="3"/>
       <c r="D2827" s="3"/>
-      <c r="E2827" s="46"/>
+      <c r="E2827" s="45"/>
       <c r="F2827" s="7"/>
     </row>
     <row r="2828" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2828" s="16"/>
       <c r="C2828" s="3"/>
       <c r="D2828" s="3"/>
-      <c r="E2828" s="46"/>
+      <c r="E2828" s="45"/>
       <c r="F2828" s="7"/>
     </row>
     <row r="2829" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2829" s="16"/>
       <c r="C2829" s="3"/>
       <c r="D2829" s="3"/>
-      <c r="E2829" s="46"/>
+      <c r="E2829" s="45"/>
       <c r="F2829" s="7"/>
     </row>
     <row r="2830" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2830" s="16"/>
       <c r="C2830" s="3"/>
       <c r="D2830" s="3"/>
-      <c r="E2830" s="46"/>
+      <c r="E2830" s="45"/>
       <c r="F2830" s="7"/>
     </row>
     <row r="2831" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2831" s="16"/>
       <c r="C2831" s="3"/>
       <c r="D2831" s="3"/>
-      <c r="E2831" s="46"/>
+      <c r="E2831" s="45"/>
       <c r="F2831" s="7"/>
     </row>
     <row r="2832" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2832" s="16"/>
       <c r="C2832" s="3"/>
       <c r="D2832" s="3"/>
-      <c r="E2832" s="46"/>
+      <c r="E2832" s="45"/>
       <c r="F2832" s="7"/>
     </row>
     <row r="2833" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2833" s="16"/>
       <c r="C2833" s="3"/>
       <c r="D2833" s="3"/>
-      <c r="E2833" s="46"/>
+      <c r="E2833" s="45"/>
       <c r="F2833" s="7"/>
     </row>
     <row r="2834" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2834" s="16"/>
       <c r="C2834" s="3"/>
       <c r="D2834" s="3"/>
-      <c r="E2834" s="46"/>
+      <c r="E2834" s="45"/>
       <c r="F2834" s="7"/>
     </row>
     <row r="2835" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2835" s="16"/>
       <c r="C2835" s="3"/>
       <c r="D2835" s="3"/>
-      <c r="E2835" s="46"/>
+      <c r="E2835" s="45"/>
       <c r="F2835" s="7"/>
     </row>
     <row r="2836" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2836" s="16"/>
       <c r="C2836" s="3"/>
       <c r="D2836" s="3"/>
-      <c r="E2836" s="46"/>
+      <c r="E2836" s="45"/>
       <c r="F2836" s="7"/>
     </row>
     <row r="2837" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2837" s="16"/>
       <c r="C2837" s="3"/>
       <c r="D2837" s="3"/>
-      <c r="E2837" s="46"/>
+      <c r="E2837" s="45"/>
       <c r="F2837" s="7"/>
     </row>
     <row r="2838" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2838" s="16"/>
       <c r="C2838" s="3"/>
       <c r="D2838" s="3"/>
-      <c r="E2838" s="46"/>
+      <c r="E2838" s="45"/>
       <c r="F2838" s="7"/>
     </row>
     <row r="2839" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2839" s="16"/>
       <c r="C2839" s="3"/>
       <c r="D2839" s="3"/>
-      <c r="E2839" s="46"/>
+      <c r="E2839" s="45"/>
       <c r="F2839" s="7"/>
     </row>
     <row r="2840" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2840" s="16"/>
       <c r="C2840" s="3"/>
       <c r="D2840" s="3"/>
-      <c r="E2840" s="46"/>
+      <c r="E2840" s="45"/>
       <c r="F2840" s="7"/>
     </row>
     <row r="2841" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2841" s="16"/>
       <c r="C2841" s="3"/>
       <c r="D2841" s="3"/>
-      <c r="E2841" s="46"/>
+      <c r="E2841" s="45"/>
       <c r="F2841" s="7"/>
     </row>
     <row r="2842" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2842" s="16"/>
       <c r="C2842" s="3"/>
       <c r="D2842" s="3"/>
-      <c r="E2842" s="46"/>
+      <c r="E2842" s="45"/>
       <c r="F2842" s="7"/>
     </row>
     <row r="2843" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2843" s="16"/>
       <c r="C2843" s="3"/>
       <c r="D2843" s="3"/>
-      <c r="E2843" s="46"/>
+      <c r="E2843" s="45"/>
       <c r="F2843" s="7"/>
     </row>
     <row r="2844" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2844" s="16"/>
       <c r="C2844" s="3"/>
       <c r="D2844" s="3"/>
-      <c r="E2844" s="46"/>
+      <c r="E2844" s="45"/>
       <c r="F2844" s="7"/>
     </row>
     <row r="2845" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2845" s="16"/>
       <c r="C2845" s="3"/>
       <c r="D2845" s="3"/>
-      <c r="E2845" s="46"/>
+      <c r="E2845" s="45"/>
       <c r="F2845" s="7"/>
     </row>
     <row r="2846" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2846" s="16"/>
       <c r="C2846" s="3"/>
       <c r="D2846" s="3"/>
-      <c r="E2846" s="46"/>
+      <c r="E2846" s="45"/>
       <c r="F2846" s="7"/>
     </row>
     <row r="2847" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2847" s="16"/>
       <c r="C2847" s="3"/>
       <c r="D2847" s="3"/>
-      <c r="E2847" s="46"/>
+      <c r="E2847" s="45"/>
       <c r="F2847" s="7"/>
     </row>
     <row r="2848" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2848" s="16"/>
       <c r="C2848" s="3"/>
       <c r="D2848" s="3"/>
-      <c r="E2848" s="46"/>
+      <c r="E2848" s="45"/>
       <c r="F2848" s="7"/>
     </row>
     <row r="2849" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2849" s="16"/>
       <c r="C2849" s="3"/>
       <c r="D2849" s="3"/>
-      <c r="E2849" s="46"/>
+      <c r="E2849" s="45"/>
       <c r="F2849" s="7"/>
     </row>
     <row r="2850" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2850" s="16"/>
       <c r="C2850" s="3"/>
       <c r="D2850" s="3"/>
-      <c r="E2850" s="46"/>
+      <c r="E2850" s="45"/>
       <c r="F2850" s="7"/>
     </row>
     <row r="2851" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2851" s="16"/>
       <c r="C2851" s="3"/>
       <c r="D2851" s="3"/>
-      <c r="E2851" s="46"/>
+      <c r="E2851" s="45"/>
       <c r="F2851" s="7"/>
     </row>
     <row r="2852" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2852" s="16"/>
       <c r="C2852" s="3"/>
       <c r="D2852" s="3"/>
-      <c r="E2852" s="46"/>
+      <c r="E2852" s="45"/>
       <c r="F2852" s="7"/>
     </row>
     <row r="2853" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2853" s="16"/>
       <c r="C2853" s="3"/>
       <c r="D2853" s="3"/>
-      <c r="E2853" s="46"/>
+      <c r="E2853" s="45"/>
       <c r="F2853" s="7"/>
     </row>
     <row r="2854" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2854" s="16"/>
       <c r="C2854" s="3"/>
       <c r="D2854" s="3"/>
-      <c r="E2854" s="46"/>
+      <c r="E2854" s="45"/>
       <c r="F2854" s="7"/>
     </row>
     <row r="2855" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2855" s="16"/>
       <c r="C2855" s="3"/>
       <c r="D2855" s="3"/>
-      <c r="E2855" s="46"/>
+      <c r="E2855" s="45"/>
       <c r="F2855" s="7"/>
     </row>
     <row r="2856" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2856" s="16"/>
       <c r="C2856" s="3"/>
       <c r="D2856" s="3"/>
-      <c r="E2856" s="46"/>
+      <c r="E2856" s="45"/>
       <c r="F2856" s="7"/>
     </row>
     <row r="2857" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2857" s="16"/>
       <c r="C2857" s="3"/>
       <c r="D2857" s="3"/>
-      <c r="E2857" s="46"/>
+      <c r="E2857" s="45"/>
       <c r="F2857" s="7"/>
     </row>
     <row r="2858" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2858" s="16"/>
       <c r="C2858" s="3"/>
       <c r="D2858" s="3"/>
-      <c r="E2858" s="46"/>
+      <c r="E2858" s="45"/>
       <c r="F2858" s="7"/>
     </row>
     <row r="2859" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2859" s="16"/>
       <c r="C2859" s="3"/>
       <c r="D2859" s="3"/>
-      <c r="E2859" s="46"/>
+      <c r="E2859" s="45"/>
       <c r="F2859" s="7"/>
     </row>
     <row r="2860" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2860" s="16"/>
       <c r="C2860" s="3"/>
       <c r="D2860" s="3"/>
-      <c r="E2860" s="46"/>
+      <c r="E2860" s="45"/>
       <c r="F2860" s="7"/>
     </row>
     <row r="2861" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2861" s="16"/>
       <c r="C2861" s="3"/>
       <c r="D2861" s="3"/>
-      <c r="E2861" s="46"/>
+      <c r="E2861" s="45"/>
       <c r="F2861" s="7"/>
     </row>
     <row r="2862" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2862" s="16"/>
       <c r="C2862" s="3"/>
       <c r="D2862" s="3"/>
-      <c r="E2862" s="46"/>
+      <c r="E2862" s="45"/>
       <c r="F2862" s="7"/>
     </row>
     <row r="2863" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2863" s="16"/>
       <c r="C2863" s="3"/>
       <c r="D2863" s="3"/>
-      <c r="E2863" s="46"/>
+      <c r="E2863" s="45"/>
       <c r="F2863" s="7"/>
     </row>
     <row r="2864" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2864" s="16"/>
       <c r="C2864" s="3"/>
       <c r="D2864" s="3"/>
-      <c r="E2864" s="46"/>
+      <c r="E2864" s="45"/>
       <c r="F2864" s="7"/>
     </row>
     <row r="2865" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2865" s="16"/>
       <c r="C2865" s="3"/>
       <c r="D2865" s="3"/>
-      <c r="E2865" s="46"/>
+      <c r="E2865" s="45"/>
       <c r="F2865" s="7"/>
     </row>
     <row r="2866" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2866" s="16"/>
       <c r="C2866" s="3"/>
       <c r="D2866" s="3"/>
-      <c r="E2866" s="46"/>
+      <c r="E2866" s="45"/>
       <c r="F2866" s="7"/>
     </row>
     <row r="2867" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2867" s="16"/>
       <c r="C2867" s="3"/>
       <c r="D2867" s="3"/>
-      <c r="E2867" s="46"/>
+      <c r="E2867" s="45"/>
       <c r="F2867" s="7"/>
     </row>
     <row r="2868" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2868" s="16"/>
       <c r="C2868" s="3"/>
       <c r="D2868" s="3"/>
-      <c r="E2868" s="46"/>
+      <c r="E2868" s="45"/>
       <c r="F2868" s="7"/>
     </row>
     <row r="2869" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2869" s="16"/>
       <c r="C2869" s="3"/>
       <c r="D2869" s="3"/>
-      <c r="E2869" s="46"/>
+      <c r="E2869" s="45"/>
       <c r="F2869" s="7"/>
     </row>
     <row r="2870" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2870" s="16"/>
       <c r="C2870" s="3"/>
       <c r="D2870" s="3"/>
-      <c r="E2870" s="46"/>
+      <c r="E2870" s="45"/>
       <c r="F2870" s="7"/>
     </row>
     <row r="2871" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2871" s="16"/>
       <c r="C2871" s="3"/>
       <c r="D2871" s="3"/>
-      <c r="E2871" s="46"/>
+      <c r="E2871" s="45"/>
       <c r="F2871" s="7"/>
     </row>
     <row r="2872" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2872" s="16"/>
       <c r="C2872" s="3"/>
       <c r="D2872" s="3"/>
-      <c r="E2872" s="46"/>
+      <c r="E2872" s="45"/>
       <c r="F2872" s="7"/>
     </row>
     <row r="2873" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2873" s="16"/>
       <c r="C2873" s="3"/>
       <c r="D2873" s="3"/>
-      <c r="E2873" s="46"/>
+      <c r="E2873" s="45"/>
       <c r="F2873" s="7"/>
     </row>
     <row r="2874" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2874" s="16"/>
       <c r="C2874" s="3"/>
       <c r="D2874" s="3"/>
-      <c r="E2874" s="46"/>
+      <c r="E2874" s="45"/>
       <c r="F2874" s="7"/>
     </row>
     <row r="2875" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2875" s="16"/>
       <c r="C2875" s="3"/>
       <c r="D2875" s="3"/>
-      <c r="E2875" s="46"/>
+      <c r="E2875" s="45"/>
       <c r="F2875" s="7"/>
     </row>
     <row r="2876" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2876" s="16"/>
       <c r="C2876" s="3"/>
       <c r="D2876" s="3"/>
-      <c r="E2876" s="46"/>
+      <c r="E2876" s="45"/>
       <c r="F2876" s="7"/>
     </row>
     <row r="2877" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2877" s="16"/>
       <c r="C2877" s="3"/>
       <c r="D2877" s="3"/>
-      <c r="E2877" s="46"/>
+      <c r="E2877" s="45"/>
       <c r="F2877" s="7"/>
     </row>
     <row r="2878" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2878" s="16"/>
       <c r="C2878" s="3"/>
       <c r="D2878" s="3"/>
-      <c r="E2878" s="46"/>
+      <c r="E2878" s="45"/>
       <c r="F2878" s="7"/>
     </row>
     <row r="2879" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2879" s="16"/>
       <c r="C2879" s="3"/>
       <c r="D2879" s="3"/>
-      <c r="E2879" s="46"/>
+      <c r="E2879" s="45"/>
       <c r="F2879" s="7"/>
     </row>
     <row r="2880" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2880" s="16"/>
       <c r="C2880" s="3"/>
       <c r="D2880" s="3"/>
-      <c r="E2880" s="46"/>
+      <c r="E2880" s="45"/>
       <c r="F2880" s="7"/>
     </row>
     <row r="2881" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2881" s="16"/>
       <c r="C2881" s="3"/>
       <c r="D2881" s="3"/>
-      <c r="E2881" s="46"/>
+      <c r="E2881" s="45"/>
       <c r="F2881" s="7"/>
     </row>
     <row r="2882" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2882" s="16"/>
       <c r="C2882" s="3"/>
       <c r="D2882" s="3"/>
-      <c r="E2882" s="46"/>
+      <c r="E2882" s="45"/>
       <c r="F2882" s="7"/>
     </row>
     <row r="2883" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2883" s="16"/>
       <c r="C2883" s="3"/>
       <c r="D2883" s="3"/>
-      <c r="E2883" s="46"/>
+      <c r="E2883" s="45"/>
       <c r="F2883" s="7"/>
     </row>
     <row r="2884" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2884" s="16"/>
       <c r="C2884" s="3"/>
       <c r="D2884" s="3"/>
-      <c r="E2884" s="46"/>
+      <c r="E2884" s="45"/>
       <c r="F2884" s="7"/>
     </row>
     <row r="2885" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2885" s="16"/>
       <c r="C2885" s="3"/>
       <c r="D2885" s="3"/>
-      <c r="E2885" s="46"/>
+      <c r="E2885" s="45"/>
       <c r="F2885" s="7"/>
     </row>
     <row r="2886" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2886" s="16"/>
       <c r="C2886" s="3"/>
       <c r="D2886" s="3"/>
-      <c r="E2886" s="46"/>
+      <c r="E2886" s="45"/>
       <c r="F2886" s="7"/>
     </row>
     <row r="2887" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2887" s="16"/>
       <c r="C2887" s="3"/>
       <c r="D2887" s="3"/>
-      <c r="E2887" s="46"/>
+      <c r="E2887" s="45"/>
       <c r="F2887" s="7"/>
     </row>
     <row r="2888" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2888" s="16"/>
       <c r="C2888" s="3"/>
       <c r="D2888" s="3"/>
-      <c r="E2888" s="46"/>
+      <c r="E2888" s="45"/>
       <c r="F2888" s="7"/>
     </row>
     <row r="2889" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2889" s="16"/>
       <c r="C2889" s="3"/>
       <c r="D2889" s="3"/>
-      <c r="E2889" s="46"/>
+      <c r="E2889" s="45"/>
       <c r="F2889" s="7"/>
     </row>
     <row r="2890" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2890" s="16"/>
       <c r="C2890" s="3"/>
       <c r="D2890" s="3"/>
-      <c r="E2890" s="46"/>
+      <c r="E2890" s="45"/>
       <c r="F2890" s="7"/>
     </row>
     <row r="2891" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2891" s="16"/>
       <c r="C2891" s="3"/>
       <c r="D2891" s="3"/>
-      <c r="E2891" s="46"/>
+      <c r="E2891" s="45"/>
       <c r="F2891" s="7"/>
     </row>
     <row r="2892" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2892" s="16"/>
       <c r="C2892" s="3"/>
       <c r="D2892" s="3"/>
-      <c r="E2892" s="46"/>
+      <c r="E2892" s="45"/>
       <c r="F2892" s="7"/>
     </row>
     <row r="2893" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2893" s="16"/>
       <c r="C2893" s="3"/>
       <c r="D2893" s="3"/>
-      <c r="E2893" s="46"/>
+      <c r="E2893" s="45"/>
       <c r="F2893" s="7"/>
     </row>
     <row r="2894" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2894" s="16"/>
       <c r="C2894" s="3"/>
       <c r="D2894" s="3"/>
-      <c r="E2894" s="46"/>
+      <c r="E2894" s="45"/>
       <c r="F2894" s="7"/>
     </row>
     <row r="2895" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2895" s="16"/>
       <c r="C2895" s="3"/>
       <c r="D2895" s="3"/>
-      <c r="E2895" s="46"/>
+      <c r="E2895" s="45"/>
       <c r="F2895" s="7"/>
     </row>
     <row r="2896" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2896" s="16"/>
       <c r="C2896" s="3"/>
       <c r="D2896" s="3"/>
-      <c r="E2896" s="46"/>
+      <c r="E2896" s="45"/>
       <c r="F2896" s="7"/>
     </row>
     <row r="2897" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2897" s="16"/>
       <c r="C2897" s="3"/>
       <c r="D2897" s="3"/>
-      <c r="E2897" s="46"/>
+      <c r="E2897" s="45"/>
       <c r="F2897" s="7"/>
     </row>
     <row r="2898" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2898" s="16"/>
       <c r="C2898" s="3"/>
       <c r="D2898" s="3"/>
-      <c r="E2898" s="46"/>
+      <c r="E2898" s="45"/>
       <c r="F2898" s="7"/>
     </row>
     <row r="2899" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2899" s="16"/>
       <c r="C2899" s="3"/>
       <c r="D2899" s="3"/>
-      <c r="E2899" s="46"/>
+      <c r="E2899" s="45"/>
       <c r="F2899" s="7"/>
     </row>
     <row r="2900" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2900" s="16"/>
       <c r="C2900" s="3"/>
       <c r="D2900" s="3"/>
-      <c r="E2900" s="46"/>
+      <c r="E2900" s="45"/>
       <c r="F2900" s="7"/>
     </row>
     <row r="2901" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2901" s="16"/>
       <c r="C2901" s="3"/>
       <c r="D2901" s="3"/>
-      <c r="E2901" s="46"/>
+      <c r="E2901" s="45"/>
       <c r="F2901" s="7"/>
     </row>
     <row r="2902" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2902" s="16"/>
       <c r="C2902" s="3"/>
       <c r="D2902" s="3"/>
-      <c r="E2902" s="46"/>
+      <c r="E2902" s="45"/>
       <c r="F2902" s="7"/>
     </row>
     <row r="2903" spans="2:6" x14ac:dyDescent="0.25">
@@ -60666,616 +60741,616 @@
       <c r="B2904" s="24"/>
       <c r="C2904" s="24"/>
       <c r="D2904" s="24"/>
-      <c r="E2904" s="48"/>
+      <c r="E2904" s="46"/>
       <c r="F2904" s="35"/>
     </row>
     <row r="2905" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2905" s="24"/>
       <c r="C2905" s="24"/>
       <c r="D2905" s="24"/>
-      <c r="E2905" s="48"/>
+      <c r="E2905" s="46"/>
       <c r="F2905" s="35"/>
     </row>
     <row r="2906" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2906" s="24"/>
       <c r="C2906" s="24"/>
       <c r="D2906" s="24"/>
-      <c r="E2906" s="48"/>
+      <c r="E2906" s="46"/>
       <c r="F2906" s="35"/>
     </row>
     <row r="2907" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2907" s="24"/>
       <c r="C2907" s="24"/>
       <c r="D2907" s="24"/>
-      <c r="E2907" s="48"/>
+      <c r="E2907" s="46"/>
       <c r="F2907" s="35"/>
     </row>
     <row r="2908" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2908" s="24"/>
       <c r="C2908" s="24"/>
       <c r="D2908" s="24"/>
-      <c r="E2908" s="48"/>
+      <c r="E2908" s="46"/>
       <c r="F2908" s="35"/>
     </row>
     <row r="2909" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2909" s="24"/>
       <c r="C2909" s="24"/>
       <c r="D2909" s="24"/>
-      <c r="E2909" s="48"/>
+      <c r="E2909" s="46"/>
       <c r="F2909" s="35"/>
     </row>
     <row r="2910" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2910" s="24"/>
       <c r="C2910" s="24"/>
       <c r="D2910" s="24"/>
-      <c r="E2910" s="48"/>
+      <c r="E2910" s="46"/>
       <c r="F2910" s="35"/>
     </row>
     <row r="2911" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2911" s="24"/>
       <c r="C2911" s="24"/>
       <c r="D2911" s="24"/>
-      <c r="E2911" s="48"/>
+      <c r="E2911" s="46"/>
       <c r="F2911" s="35"/>
     </row>
     <row r="2912" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2912" s="24"/>
       <c r="C2912" s="24"/>
       <c r="D2912" s="24"/>
-      <c r="E2912" s="48"/>
+      <c r="E2912" s="46"/>
       <c r="F2912" s="35"/>
     </row>
     <row r="2913" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2913" s="24"/>
       <c r="C2913" s="24"/>
       <c r="D2913" s="24"/>
-      <c r="E2913" s="48"/>
+      <c r="E2913" s="46"/>
       <c r="F2913" s="35"/>
     </row>
     <row r="2914" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2914" s="24"/>
       <c r="C2914" s="24"/>
       <c r="D2914" s="24"/>
-      <c r="E2914" s="48"/>
+      <c r="E2914" s="46"/>
       <c r="F2914" s="35"/>
     </row>
     <row r="2915" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2915" s="24"/>
       <c r="C2915" s="24"/>
       <c r="D2915" s="24"/>
-      <c r="E2915" s="48"/>
+      <c r="E2915" s="46"/>
       <c r="F2915" s="35"/>
     </row>
     <row r="2916" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2916" s="24"/>
       <c r="C2916" s="24"/>
       <c r="D2916" s="24"/>
-      <c r="E2916" s="48"/>
+      <c r="E2916" s="46"/>
       <c r="F2916" s="35"/>
     </row>
     <row r="2917" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2917" s="24"/>
       <c r="C2917" s="24"/>
       <c r="D2917" s="24"/>
-      <c r="E2917" s="48"/>
+      <c r="E2917" s="46"/>
       <c r="F2917" s="35"/>
     </row>
     <row r="2918" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2918" s="24"/>
       <c r="C2918" s="24"/>
       <c r="D2918" s="24"/>
-      <c r="E2918" s="48"/>
+      <c r="E2918" s="46"/>
       <c r="F2918" s="35"/>
     </row>
     <row r="2919" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2919" s="24"/>
       <c r="C2919" s="24"/>
       <c r="D2919" s="24"/>
-      <c r="E2919" s="48"/>
+      <c r="E2919" s="46"/>
       <c r="F2919" s="35"/>
     </row>
     <row r="2920" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2920" s="24"/>
       <c r="C2920" s="24"/>
       <c r="D2920" s="24"/>
-      <c r="E2920" s="48"/>
+      <c r="E2920" s="46"/>
       <c r="F2920" s="35"/>
     </row>
     <row r="2921" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2921" s="24"/>
       <c r="C2921" s="24"/>
       <c r="D2921" s="24"/>
-      <c r="E2921" s="48"/>
+      <c r="E2921" s="46"/>
       <c r="F2921" s="35"/>
     </row>
     <row r="2922" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2922" s="24"/>
       <c r="C2922" s="24"/>
       <c r="D2922" s="24"/>
-      <c r="E2922" s="48"/>
+      <c r="E2922" s="46"/>
       <c r="F2922" s="35"/>
     </row>
     <row r="2923" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2923" s="24"/>
       <c r="C2923" s="24"/>
       <c r="D2923" s="24"/>
-      <c r="E2923" s="48"/>
+      <c r="E2923" s="46"/>
       <c r="F2923" s="35"/>
     </row>
     <row r="2924" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2924" s="24"/>
       <c r="C2924" s="24"/>
       <c r="D2924" s="24"/>
-      <c r="E2924" s="48"/>
+      <c r="E2924" s="46"/>
       <c r="F2924" s="35"/>
     </row>
     <row r="2925" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2925" s="24"/>
       <c r="C2925" s="24"/>
       <c r="D2925" s="24"/>
-      <c r="E2925" s="48"/>
+      <c r="E2925" s="46"/>
       <c r="F2925" s="35"/>
     </row>
     <row r="2926" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2926" s="24"/>
       <c r="C2926" s="24"/>
       <c r="D2926" s="24"/>
-      <c r="E2926" s="48"/>
+      <c r="E2926" s="46"/>
       <c r="F2926" s="35"/>
     </row>
     <row r="2927" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2927" s="24"/>
       <c r="C2927" s="24"/>
       <c r="D2927" s="24"/>
-      <c r="E2927" s="48"/>
+      <c r="E2927" s="46"/>
       <c r="F2927" s="35"/>
     </row>
     <row r="2928" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2928" s="24"/>
       <c r="C2928" s="24"/>
       <c r="D2928" s="24"/>
-      <c r="E2928" s="48"/>
+      <c r="E2928" s="46"/>
       <c r="F2928" s="35"/>
     </row>
     <row r="2929" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2929" s="24"/>
       <c r="C2929" s="24"/>
       <c r="D2929" s="24"/>
-      <c r="E2929" s="48"/>
+      <c r="E2929" s="46"/>
       <c r="F2929" s="35"/>
     </row>
     <row r="2930" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2930" s="24"/>
       <c r="C2930" s="24"/>
       <c r="D2930" s="24"/>
-      <c r="E2930" s="48"/>
+      <c r="E2930" s="46"/>
       <c r="F2930" s="35"/>
     </row>
     <row r="2931" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2931" s="24"/>
       <c r="C2931" s="24"/>
       <c r="D2931" s="24"/>
-      <c r="E2931" s="48"/>
+      <c r="E2931" s="46"/>
       <c r="F2931" s="35"/>
     </row>
     <row r="2932" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2932" s="24"/>
       <c r="C2932" s="24"/>
       <c r="D2932" s="24"/>
-      <c r="E2932" s="48"/>
+      <c r="E2932" s="46"/>
       <c r="F2932" s="35"/>
     </row>
     <row r="2933" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2933" s="24"/>
       <c r="C2933" s="24"/>
       <c r="D2933" s="24"/>
-      <c r="E2933" s="48"/>
+      <c r="E2933" s="46"/>
       <c r="F2933" s="35"/>
     </row>
     <row r="2934" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2934" s="24"/>
       <c r="C2934" s="24"/>
       <c r="D2934" s="24"/>
-      <c r="E2934" s="48"/>
+      <c r="E2934" s="46"/>
       <c r="F2934" s="35"/>
     </row>
     <row r="2935" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2935" s="24"/>
       <c r="C2935" s="24"/>
       <c r="D2935" s="24"/>
-      <c r="E2935" s="48"/>
+      <c r="E2935" s="46"/>
       <c r="F2935" s="35"/>
     </row>
     <row r="2936" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2936" s="24"/>
       <c r="C2936" s="24"/>
       <c r="D2936" s="24"/>
-      <c r="E2936" s="48"/>
+      <c r="E2936" s="46"/>
       <c r="F2936" s="35"/>
     </row>
     <row r="2937" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2937" s="24"/>
       <c r="C2937" s="24"/>
       <c r="D2937" s="24"/>
-      <c r="E2937" s="48"/>
+      <c r="E2937" s="46"/>
       <c r="F2937" s="35"/>
     </row>
     <row r="2938" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2938" s="24"/>
       <c r="C2938" s="24"/>
       <c r="D2938" s="24"/>
-      <c r="E2938" s="48"/>
+      <c r="E2938" s="46"/>
       <c r="F2938" s="35"/>
     </row>
     <row r="2939" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2939" s="24"/>
       <c r="C2939" s="24"/>
       <c r="D2939" s="24"/>
-      <c r="E2939" s="48"/>
+      <c r="E2939" s="46"/>
       <c r="F2939" s="35"/>
     </row>
     <row r="2940" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2940" s="24"/>
       <c r="C2940" s="24"/>
       <c r="D2940" s="24"/>
-      <c r="E2940" s="48"/>
+      <c r="E2940" s="46"/>
       <c r="F2940" s="35"/>
     </row>
     <row r="2941" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2941" s="24"/>
       <c r="C2941" s="24"/>
       <c r="D2941" s="24"/>
-      <c r="E2941" s="48"/>
+      <c r="E2941" s="46"/>
       <c r="F2941" s="35"/>
     </row>
     <row r="2942" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2942" s="24"/>
       <c r="C2942" s="24"/>
       <c r="D2942" s="24"/>
-      <c r="E2942" s="48"/>
+      <c r="E2942" s="46"/>
       <c r="F2942" s="38"/>
     </row>
     <row r="2943" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2943" s="11"/>
       <c r="C2943" s="24"/>
       <c r="D2943" s="3"/>
-      <c r="E2943" s="48"/>
+      <c r="E2943" s="46"/>
       <c r="F2943" s="7"/>
     </row>
     <row r="2945" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2945" s="24"/>
       <c r="C2945" s="24"/>
       <c r="D2945" s="24"/>
-      <c r="E2945" s="48"/>
+      <c r="E2945" s="46"/>
       <c r="F2945" s="38"/>
     </row>
     <row r="2946" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2946" s="24"/>
       <c r="C2946" s="24"/>
       <c r="D2946" s="24"/>
-      <c r="E2946" s="48"/>
+      <c r="E2946" s="46"/>
       <c r="F2946" s="38"/>
     </row>
     <row r="2947" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2947" s="24"/>
       <c r="C2947" s="24"/>
       <c r="D2947" s="24"/>
-      <c r="E2947" s="48"/>
+      <c r="E2947" s="46"/>
       <c r="F2947" s="38"/>
     </row>
     <row r="2948" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2948" s="24"/>
       <c r="C2948" s="24"/>
       <c r="D2948" s="24"/>
-      <c r="E2948" s="48"/>
+      <c r="E2948" s="46"/>
       <c r="F2948" s="38"/>
     </row>
     <row r="2949" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2949" s="24"/>
       <c r="C2949" s="24"/>
       <c r="D2949" s="24"/>
-      <c r="E2949" s="48"/>
+      <c r="E2949" s="46"/>
       <c r="F2949" s="38"/>
     </row>
     <row r="2950" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2950" s="24"/>
       <c r="C2950" s="24"/>
       <c r="D2950" s="24"/>
-      <c r="E2950" s="48"/>
+      <c r="E2950" s="46"/>
       <c r="F2950" s="38"/>
     </row>
     <row r="2951" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2951" s="24"/>
       <c r="C2951" s="24"/>
       <c r="D2951" s="24"/>
-      <c r="E2951" s="48"/>
+      <c r="E2951" s="46"/>
       <c r="F2951" s="38"/>
     </row>
     <row r="2952" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2952" s="24"/>
       <c r="C2952" s="24"/>
       <c r="D2952" s="24"/>
-      <c r="E2952" s="48"/>
+      <c r="E2952" s="46"/>
       <c r="F2952" s="38"/>
     </row>
     <row r="2953" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2953" s="24"/>
       <c r="C2953" s="24"/>
       <c r="D2953" s="24"/>
-      <c r="E2953" s="48"/>
+      <c r="E2953" s="46"/>
       <c r="F2953" s="38"/>
     </row>
     <row r="2954" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2954" s="24"/>
       <c r="C2954" s="24"/>
       <c r="D2954" s="24"/>
-      <c r="E2954" s="48"/>
+      <c r="E2954" s="46"/>
       <c r="F2954" s="38"/>
     </row>
     <row r="2955" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2955" s="24"/>
       <c r="C2955" s="24"/>
       <c r="D2955" s="24"/>
-      <c r="E2955" s="48"/>
+      <c r="E2955" s="46"/>
       <c r="F2955" s="38"/>
     </row>
     <row r="2956" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2956" s="24"/>
       <c r="C2956" s="24"/>
       <c r="D2956" s="24"/>
-      <c r="E2956" s="48"/>
+      <c r="E2956" s="46"/>
       <c r="F2956" s="38"/>
     </row>
     <row r="2957" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2957" s="24"/>
       <c r="C2957" s="24"/>
       <c r="D2957" s="24"/>
-      <c r="E2957" s="48"/>
+      <c r="E2957" s="46"/>
       <c r="F2957" s="38"/>
     </row>
     <row r="2958" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2958" s="24"/>
       <c r="C2958" s="24"/>
       <c r="D2958" s="24"/>
-      <c r="E2958" s="48"/>
+      <c r="E2958" s="46"/>
       <c r="F2958" s="38"/>
     </row>
     <row r="2959" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2959" s="24"/>
       <c r="C2959" s="24"/>
       <c r="D2959" s="24"/>
-      <c r="E2959" s="48"/>
+      <c r="E2959" s="46"/>
       <c r="F2959" s="38"/>
     </row>
     <row r="2960" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2960" s="24"/>
       <c r="C2960" s="24"/>
       <c r="D2960" s="24"/>
-      <c r="E2960" s="48"/>
+      <c r="E2960" s="46"/>
       <c r="F2960" s="38"/>
     </row>
     <row r="2961" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2961" s="24"/>
       <c r="C2961" s="24"/>
       <c r="D2961" s="24"/>
-      <c r="E2961" s="48"/>
+      <c r="E2961" s="46"/>
       <c r="F2961" s="38"/>
     </row>
     <row r="2962" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2962" s="24"/>
       <c r="C2962" s="24"/>
       <c r="D2962" s="24"/>
-      <c r="E2962" s="48"/>
+      <c r="E2962" s="46"/>
       <c r="F2962" s="38"/>
     </row>
     <row r="2963" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2963" s="24"/>
       <c r="C2963" s="24"/>
       <c r="D2963" s="24"/>
-      <c r="E2963" s="48"/>
+      <c r="E2963" s="46"/>
       <c r="F2963" s="38"/>
     </row>
     <row r="2964" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2964" s="24"/>
       <c r="C2964" s="24"/>
       <c r="D2964" s="24"/>
-      <c r="E2964" s="48"/>
+      <c r="E2964" s="46"/>
       <c r="F2964" s="38"/>
     </row>
     <row r="2965" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2965" s="24"/>
       <c r="C2965" s="24"/>
       <c r="D2965" s="24"/>
-      <c r="E2965" s="48"/>
+      <c r="E2965" s="46"/>
       <c r="F2965" s="38"/>
     </row>
     <row r="2966" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2966" s="24"/>
       <c r="C2966" s="24"/>
       <c r="D2966" s="24"/>
-      <c r="E2966" s="48"/>
+      <c r="E2966" s="46"/>
       <c r="F2966" s="38"/>
     </row>
     <row r="2967" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2967" s="24"/>
       <c r="C2967" s="24"/>
       <c r="D2967" s="24"/>
-      <c r="E2967" s="48"/>
+      <c r="E2967" s="46"/>
       <c r="F2967" s="38"/>
     </row>
     <row r="2968" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2968" s="24"/>
       <c r="C2968" s="24"/>
       <c r="D2968" s="24"/>
-      <c r="E2968" s="48"/>
+      <c r="E2968" s="46"/>
       <c r="F2968" s="38"/>
     </row>
     <row r="2969" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2969" s="24"/>
       <c r="C2969" s="24"/>
       <c r="D2969" s="24"/>
-      <c r="E2969" s="48"/>
+      <c r="E2969" s="46"/>
       <c r="F2969" s="38"/>
     </row>
     <row r="2970" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2970" s="24"/>
       <c r="C2970" s="24"/>
       <c r="D2970" s="24"/>
-      <c r="E2970" s="48"/>
+      <c r="E2970" s="46"/>
       <c r="F2970" s="38"/>
     </row>
     <row r="2971" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2971" s="24"/>
       <c r="C2971" s="24"/>
       <c r="D2971" s="24"/>
-      <c r="E2971" s="48"/>
+      <c r="E2971" s="46"/>
       <c r="F2971" s="38"/>
     </row>
     <row r="2972" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2972" s="24"/>
       <c r="C2972" s="24"/>
       <c r="D2972" s="24"/>
-      <c r="E2972" s="48"/>
+      <c r="E2972" s="46"/>
       <c r="F2972" s="38"/>
     </row>
     <row r="2973" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2973" s="24"/>
       <c r="C2973" s="24"/>
       <c r="D2973" s="24"/>
-      <c r="E2973" s="48"/>
+      <c r="E2973" s="46"/>
       <c r="F2973" s="38"/>
     </row>
     <row r="2974" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2974" s="24"/>
       <c r="C2974" s="24"/>
       <c r="D2974" s="24"/>
-      <c r="E2974" s="48"/>
+      <c r="E2974" s="46"/>
       <c r="F2974" s="38"/>
     </row>
     <row r="2975" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2975" s="24"/>
       <c r="C2975" s="24"/>
       <c r="D2975" s="24"/>
-      <c r="E2975" s="48"/>
+      <c r="E2975" s="46"/>
       <c r="F2975" s="38"/>
     </row>
     <row r="2976" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2976" s="24"/>
       <c r="C2976" s="24"/>
       <c r="D2976" s="24"/>
-      <c r="E2976" s="48"/>
+      <c r="E2976" s="46"/>
       <c r="F2976" s="38"/>
     </row>
     <row r="2977" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2977" s="24"/>
       <c r="C2977" s="24"/>
       <c r="D2977" s="24"/>
-      <c r="E2977" s="48"/>
+      <c r="E2977" s="46"/>
       <c r="F2977" s="38"/>
     </row>
     <row r="2978" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2978" s="24"/>
       <c r="C2978" s="24"/>
       <c r="D2978" s="24"/>
-      <c r="E2978" s="48"/>
+      <c r="E2978" s="46"/>
       <c r="F2978" s="38"/>
     </row>
     <row r="2979" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2979" s="24"/>
       <c r="C2979" s="24"/>
       <c r="D2979" s="24"/>
-      <c r="E2979" s="48"/>
+      <c r="E2979" s="46"/>
       <c r="F2979" s="38"/>
     </row>
     <row r="2980" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2980" s="24"/>
       <c r="C2980" s="24"/>
       <c r="D2980" s="24"/>
-      <c r="E2980" s="48"/>
+      <c r="E2980" s="46"/>
       <c r="F2980" s="38"/>
     </row>
     <row r="2981" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2981" s="24"/>
       <c r="C2981" s="24"/>
       <c r="D2981" s="24"/>
-      <c r="E2981" s="48"/>
+      <c r="E2981" s="46"/>
       <c r="F2981" s="38"/>
     </row>
     <row r="2982" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2982" s="24"/>
       <c r="C2982" s="24"/>
       <c r="D2982" s="24"/>
-      <c r="E2982" s="48"/>
+      <c r="E2982" s="46"/>
       <c r="F2982" s="38"/>
     </row>
     <row r="2983" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2983" s="24"/>
       <c r="C2983" s="24"/>
       <c r="D2983" s="24"/>
-      <c r="E2983" s="48"/>
+      <c r="E2983" s="46"/>
       <c r="F2983" s="38"/>
     </row>
     <row r="2984" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2984" s="24"/>
       <c r="C2984" s="24"/>
       <c r="D2984" s="24"/>
-      <c r="E2984" s="48"/>
+      <c r="E2984" s="46"/>
       <c r="F2984" s="38"/>
     </row>
     <row r="2985" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2985" s="24"/>
       <c r="C2985" s="24"/>
       <c r="D2985" s="24"/>
-      <c r="E2985" s="48"/>
+      <c r="E2985" s="46"/>
       <c r="F2985" s="38"/>
     </row>
     <row r="2986" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2986" s="24"/>
       <c r="C2986" s="24"/>
       <c r="D2986" s="24"/>
-      <c r="E2986" s="48"/>
+      <c r="E2986" s="46"/>
       <c r="F2986" s="38"/>
     </row>
     <row r="2987" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2987" s="24"/>
       <c r="C2987" s="24"/>
       <c r="D2987" s="24"/>
-      <c r="E2987" s="48"/>
+      <c r="E2987" s="46"/>
       <c r="F2987" s="38"/>
     </row>
     <row r="2988" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2988" s="24"/>
       <c r="C2988" s="24"/>
       <c r="D2988" s="24"/>
-      <c r="E2988" s="48"/>
+      <c r="E2988" s="46"/>
       <c r="F2988" s="38"/>
     </row>
     <row r="2989" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2989" s="24"/>
       <c r="C2989" s="24"/>
       <c r="D2989" s="24"/>
-      <c r="E2989" s="48"/>
+      <c r="E2989" s="46"/>
       <c r="F2989" s="38"/>
     </row>
     <row r="2990" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2990" s="24"/>
       <c r="C2990" s="24"/>
       <c r="D2990" s="24"/>
-      <c r="E2990" s="48"/>
+      <c r="E2990" s="46"/>
       <c r="F2990" s="38"/>
     </row>
     <row r="2991" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2991" s="24"/>
       <c r="C2991" s="24"/>
       <c r="D2991" s="24"/>
-      <c r="E2991" s="48"/>
+      <c r="E2991" s="46"/>
       <c r="F2991" s="38"/>
     </row>
     <row r="2992" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2992" s="24"/>
       <c r="C2992" s="24"/>
       <c r="D2992" s="24"/>
-      <c r="E2992" s="48"/>
+      <c r="E2992" s="46"/>
       <c r="F2992" s="38"/>
     </row>
   </sheetData>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1637" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{241F45C3-221F-4D1C-BC8D-5A9199C92226}"/>
+  <xr:revisionPtr revIDLastSave="1732" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2033DD5B-D805-4547-A370-A9FCA34F733D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2420" uniqueCount="154">
   <si>
     <t>Custo</t>
   </si>
@@ -500,6 +500,9 @@
   </si>
   <si>
     <t>DALMEIDA</t>
+  </si>
+  <si>
+    <t>DAF SANCAR</t>
   </si>
 </sst>
 </file>
@@ -41166,165 +41169,349 @@
       </c>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B108" s="11"/>
+      <c r="B108" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C108" s="5"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="43"/>
-      <c r="F108" s="7"/>
+      <c r="D108" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E108" s="43">
+        <v>400</v>
+      </c>
+      <c r="F108" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B109" s="11"/>
+      <c r="B109" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C109" s="5"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="43"/>
-      <c r="F109" s="7"/>
+      <c r="D109" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E109" s="43">
+        <v>30</v>
+      </c>
+      <c r="F109" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B110" s="11"/>
+      <c r="B110" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C110" s="5"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="43"/>
-      <c r="F110" s="7"/>
+      <c r="D110" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E110" s="43">
+        <v>2735.31</v>
+      </c>
+      <c r="F110" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B111" s="11"/>
+      <c r="B111" s="11" t="s">
+        <v>14</v>
+      </c>
       <c r="C111" s="5"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="43"/>
-      <c r="F111" s="7"/>
+      <c r="D111" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E111" s="43">
+        <v>100</v>
+      </c>
+      <c r="F111" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B112" s="11"/>
+      <c r="B112" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C112" s="5"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="43"/>
-      <c r="F112" s="7"/>
+      <c r="D112" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E112" s="43">
+        <v>1805</v>
+      </c>
+      <c r="F112" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B113" s="11"/>
+      <c r="B113" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C113" s="5"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="43"/>
-      <c r="F113" s="7"/>
+      <c r="D113" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E113" s="43">
+        <v>200</v>
+      </c>
+      <c r="F113" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B114" s="11"/>
+      <c r="B114" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C114" s="5"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="43"/>
-      <c r="F114" s="7"/>
+      <c r="D114" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E114" s="43">
+        <v>90</v>
+      </c>
+      <c r="F114" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B115" s="11"/>
+      <c r="B115" s="11" t="s">
+        <v>14</v>
+      </c>
       <c r="C115" s="5"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="43"/>
-      <c r="F115" s="7"/>
+      <c r="D115" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E115" s="43">
+        <v>642.5</v>
+      </c>
+      <c r="F115" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B116" s="11"/>
+      <c r="B116" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="C116" s="5"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="43"/>
-      <c r="F116" s="7"/>
+      <c r="D116" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E116" s="43">
+        <v>930</v>
+      </c>
+      <c r="F116" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B117" s="11"/>
+      <c r="B117" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C117" s="5"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="43"/>
-      <c r="F117" s="7"/>
+      <c r="D117" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E117" s="43">
+        <v>1285</v>
+      </c>
+      <c r="F117" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B118" s="11"/>
+      <c r="B118" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C118" s="5"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="43"/>
-      <c r="F118" s="7"/>
+      <c r="D118" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E118" s="43">
+        <v>430</v>
+      </c>
+      <c r="F118" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B119" s="11"/>
+      <c r="B119" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C119" s="5"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="43"/>
-      <c r="F119" s="7"/>
+      <c r="D119" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E119" s="43">
+        <v>2458.4</v>
+      </c>
+      <c r="F119" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B120" s="11"/>
+      <c r="B120" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C120" s="5"/>
-      <c r="D120" s="3"/>
-      <c r="E120" s="43"/>
-      <c r="F120" s="7"/>
+      <c r="D120" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E120" s="43">
+        <v>500</v>
+      </c>
+      <c r="F120" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B121" s="11"/>
+      <c r="B121" s="11" t="s">
+        <v>124</v>
+      </c>
       <c r="C121" s="5"/>
-      <c r="D121" s="3"/>
-      <c r="E121" s="43"/>
-      <c r="F121" s="7"/>
+      <c r="D121" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E121" s="43">
+        <v>425</v>
+      </c>
+      <c r="F121" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B122" s="11"/>
+      <c r="B122" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C122" s="5"/>
-      <c r="D122" s="3"/>
-      <c r="E122" s="43"/>
-      <c r="F122" s="7"/>
+      <c r="D122" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E122" s="43">
+        <v>2930</v>
+      </c>
+      <c r="F122" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B123" s="11"/>
+      <c r="B123" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C123" s="5"/>
-      <c r="D123" s="3"/>
-      <c r="E123" s="43"/>
-      <c r="F123" s="7"/>
+      <c r="D123" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E123" s="43">
+        <v>70</v>
+      </c>
+      <c r="F123" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B124" s="11"/>
+      <c r="B124" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C124" s="5"/>
-      <c r="D124" s="3"/>
-      <c r="E124" s="43"/>
-      <c r="F124" s="7"/>
+      <c r="D124" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E124" s="43">
+        <v>200</v>
+      </c>
+      <c r="F124" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B125" s="11"/>
+      <c r="B125" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C125" s="5"/>
-      <c r="D125" s="3"/>
-      <c r="E125" s="43"/>
-      <c r="F125" s="7"/>
+      <c r="D125" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E125" s="43">
+        <v>700</v>
+      </c>
+      <c r="F125" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B126" s="11"/>
+      <c r="B126" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C126" s="5"/>
-      <c r="D126" s="3"/>
-      <c r="E126" s="43"/>
-      <c r="F126" s="7"/>
+      <c r="D126" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E126" s="43">
+        <v>1300</v>
+      </c>
+      <c r="F126" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B127" s="11"/>
+      <c r="B127" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C127" s="5"/>
-      <c r="D127" s="3"/>
-      <c r="E127" s="43"/>
-      <c r="F127" s="7"/>
+      <c r="D127" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E127" s="43">
+        <v>1100</v>
+      </c>
+      <c r="F127" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B128" s="11"/>
+      <c r="B128" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="C128" s="5"/>
-      <c r="D128" s="3"/>
-      <c r="E128" s="43"/>
-      <c r="F128" s="7"/>
+      <c r="D128" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E128" s="43">
+        <v>1287</v>
+      </c>
+      <c r="F128" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B129" s="11"/>
+      <c r="B129" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="C129" s="5"/>
-      <c r="D129" s="3"/>
-      <c r="E129" s="43"/>
-      <c r="F129" s="7"/>
+      <c r="D129" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E129" s="43">
+        <v>805.5</v>
+      </c>
+      <c r="F129" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B130" s="11"/>
+      <c r="B130" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C130" s="5"/>
-      <c r="D130" s="3"/>
-      <c r="E130" s="43"/>
-      <c r="F130" s="7"/>
+      <c r="D130" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E130" s="43">
+        <v>43</v>
+      </c>
+      <c r="F130" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B131" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1732" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2033DD5B-D805-4547-A370-A9FCA34F733D}"/>
+  <xr:revisionPtr revIDLastSave="1737" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{029E7EF9-91B9-43C9-A4CC-A3B6E9C2622C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2420" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="154">
   <si>
     <t>Custo</t>
   </si>
@@ -41514,11 +41514,19 @@
       </c>
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B131" s="11"/>
+      <c r="B131" s="11" t="s">
+        <v>12</v>
+      </c>
       <c r="C131" s="5"/>
-      <c r="D131" s="3"/>
-      <c r="E131" s="43"/>
-      <c r="F131" s="7"/>
+      <c r="D131" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E131" s="43">
+        <v>214</v>
+      </c>
+      <c r="F131" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B132" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1737" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{029E7EF9-91B9-43C9-A4CC-A3B6E9C2622C}"/>
+  <xr:revisionPtr revIDLastSave="1840" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BB0A405-1C76-4FE2-A563-9E698248BE50}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="155">
   <si>
     <t>Custo</t>
   </si>
@@ -503,6 +503,9 @@
   </si>
   <si>
     <t>DAF SANCAR</t>
+  </si>
+  <si>
+    <t>SILVA CARROCERIA</t>
   </si>
 </sst>
 </file>
@@ -41529,186 +41532,394 @@
       </c>
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B132" s="11"/>
+      <c r="B132" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C132" s="5"/>
-      <c r="D132" s="3"/>
-      <c r="E132" s="43"/>
-      <c r="F132" s="7"/>
+      <c r="D132" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E132" s="43">
+        <v>95</v>
+      </c>
+      <c r="F132" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B133" s="11"/>
+      <c r="B133" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C133" s="5"/>
-      <c r="D133" s="3"/>
-      <c r="E133" s="43"/>
-      <c r="F133" s="7"/>
+      <c r="D133" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E133" s="43">
+        <v>360</v>
+      </c>
+      <c r="F133" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B134" s="11"/>
+      <c r="B134" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C134" s="5"/>
-      <c r="D134" s="3"/>
-      <c r="E134" s="43"/>
-      <c r="F134" s="7"/>
+      <c r="D134" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E134" s="43">
+        <v>310</v>
+      </c>
+      <c r="F134" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B135" s="11"/>
+      <c r="B135" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C135" s="5"/>
-      <c r="D135" s="3"/>
-      <c r="E135" s="43"/>
-      <c r="F135" s="7"/>
+      <c r="D135" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E135" s="43">
+        <v>1350</v>
+      </c>
+      <c r="F135" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B136" s="11"/>
+      <c r="B136" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C136" s="5"/>
-      <c r="D136" s="3"/>
-      <c r="E136" s="43"/>
-      <c r="F136" s="7"/>
+      <c r="D136" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E136" s="43">
+        <v>190</v>
+      </c>
+      <c r="F136" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B137" s="11"/>
+      <c r="B137" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="C137" s="5"/>
-      <c r="D137" s="3"/>
-      <c r="E137" s="43"/>
-      <c r="F137" s="7"/>
+      <c r="D137" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E137" s="43">
+        <v>720</v>
+      </c>
+      <c r="F137" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B138" s="11"/>
+      <c r="B138" s="11" t="s">
+        <v>142</v>
+      </c>
       <c r="C138" s="5"/>
-      <c r="D138" s="3"/>
-      <c r="E138" s="43"/>
-      <c r="F138" s="7"/>
+      <c r="D138" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E138" s="43">
+        <v>160</v>
+      </c>
+      <c r="F138" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B139" s="11"/>
+      <c r="B139" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C139" s="5"/>
-      <c r="D139" s="3"/>
-      <c r="E139" s="43"/>
-      <c r="F139" s="7"/>
+      <c r="D139" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E139" s="43">
+        <v>180</v>
+      </c>
+      <c r="F139" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B140" s="11"/>
+      <c r="B140" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C140" s="5"/>
-      <c r="D140" s="3"/>
-      <c r="E140" s="43"/>
-      <c r="F140" s="7"/>
+      <c r="D140" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E140" s="43">
+        <v>2710</v>
+      </c>
+      <c r="F140" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B141" s="11"/>
+      <c r="B141" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C141" s="5"/>
-      <c r="D141" s="3"/>
-      <c r="E141" s="43"/>
-      <c r="F141" s="7"/>
+      <c r="D141" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E141" s="43">
+        <v>920</v>
+      </c>
+      <c r="F141" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B142" s="11"/>
+      <c r="B142" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C142" s="5"/>
-      <c r="D142" s="3"/>
-      <c r="E142" s="43"/>
-      <c r="F142" s="7"/>
+      <c r="D142" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E142" s="43">
+        <v>40</v>
+      </c>
+      <c r="F142" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B143" s="11"/>
+      <c r="B143" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C143" s="5"/>
-      <c r="D143" s="3"/>
-      <c r="E143" s="43"/>
-      <c r="F143" s="7"/>
+      <c r="D143" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E143" s="43">
+        <v>390</v>
+      </c>
+      <c r="F143" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B144" s="11"/>
+      <c r="B144" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C144" s="5"/>
-      <c r="D144" s="3"/>
-      <c r="E144" s="43"/>
-      <c r="F144" s="7"/>
+      <c r="D144" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E144" s="43">
+        <v>70</v>
+      </c>
+      <c r="F144" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B145" s="11"/>
+      <c r="B145" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C145" s="5"/>
-      <c r="D145" s="3"/>
-      <c r="E145" s="43"/>
-      <c r="F145" s="7"/>
+      <c r="D145" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E145" s="43">
+        <v>200</v>
+      </c>
+      <c r="F145" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B146" s="11"/>
+      <c r="B146" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C146" s="5"/>
-      <c r="D146" s="3"/>
-      <c r="E146" s="43"/>
-      <c r="F146" s="7"/>
+      <c r="D146" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E146" s="43">
+        <v>1083.3</v>
+      </c>
+      <c r="F146" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B147" s="11"/>
+      <c r="B147" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C147" s="5"/>
-      <c r="D147" s="3"/>
-      <c r="E147" s="43"/>
-      <c r="F147" s="7"/>
+      <c r="D147" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E147" s="43">
+        <v>100</v>
+      </c>
+      <c r="F147" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="148" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B148" s="11"/>
+      <c r="B148" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C148" s="5"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="43"/>
-      <c r="F148" s="7"/>
+      <c r="D148" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E148" s="43">
+        <v>1500</v>
+      </c>
+      <c r="F148" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B149" s="11"/>
+      <c r="B149" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C149" s="5"/>
-      <c r="D149" s="3"/>
-      <c r="E149" s="43"/>
-      <c r="F149" s="7"/>
+      <c r="D149" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E149" s="43">
+        <v>35</v>
+      </c>
+      <c r="F149" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B150" s="11"/>
+      <c r="B150" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C150" s="5"/>
-      <c r="D150" s="3"/>
-      <c r="E150" s="43"/>
-      <c r="F150" s="7"/>
+      <c r="D150" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E150" s="43">
+        <v>120</v>
+      </c>
+      <c r="F150" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B151" s="11"/>
+      <c r="B151" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C151" s="5"/>
-      <c r="D151" s="3"/>
-      <c r="E151" s="43"/>
-      <c r="F151" s="7"/>
+      <c r="D151" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E151" s="43">
+        <v>65</v>
+      </c>
+      <c r="F151" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B152" s="11"/>
+      <c r="B152" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C152" s="5"/>
-      <c r="D152" s="3"/>
-      <c r="E152" s="43"/>
-      <c r="F152" s="7"/>
+      <c r="D152" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E152" s="43">
+        <v>50</v>
+      </c>
+      <c r="F152" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="153" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B153" s="11"/>
+      <c r="B153" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C153" s="5"/>
-      <c r="D153" s="3"/>
-      <c r="E153" s="43"/>
-      <c r="F153" s="7"/>
+      <c r="D153" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E153" s="43">
+        <v>343</v>
+      </c>
+      <c r="F153" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="154" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B154" s="11"/>
+      <c r="B154" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C154" s="5"/>
-      <c r="D154" s="3"/>
-      <c r="E154" s="43"/>
-      <c r="F154" s="7"/>
+      <c r="D154" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E154" s="43">
+        <v>1339</v>
+      </c>
+      <c r="F154" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B155" s="11"/>
+      <c r="B155" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C155" s="5"/>
-      <c r="D155" s="3"/>
-      <c r="E155" s="43"/>
-      <c r="F155" s="7"/>
+      <c r="D155" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E155" s="43">
+        <v>150</v>
+      </c>
+      <c r="F155" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="156" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B156" s="11"/>
+      <c r="B156" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C156" s="5"/>
-      <c r="D156" s="3"/>
-      <c r="E156" s="43"/>
-      <c r="F156" s="7"/>
+      <c r="D156" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E156" s="43">
+        <v>606</v>
+      </c>
+      <c r="F156" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="157" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B157" s="11"/>
+      <c r="B157" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C157" s="5"/>
-      <c r="D157" s="3"/>
-      <c r="E157" s="43"/>
-      <c r="F157" s="7"/>
+      <c r="D157" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E157" s="43">
+        <v>100</v>
+      </c>
+      <c r="F157" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B158" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1840" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BB0A405-1C76-4FE2-A563-9E698248BE50}"/>
+  <xr:revisionPtr revIDLastSave="1867" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98D2DBEE-BCCF-4A7A-AE23-F8D92B52D14D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="157">
   <si>
     <t>Custo</t>
   </si>
@@ -506,6 +506,12 @@
   </si>
   <si>
     <t>SILVA CARROCERIA</t>
+  </si>
+  <si>
+    <t>PNEU MAX</t>
+  </si>
+  <si>
+    <t>BORRACHARIA NITEROI</t>
   </si>
 </sst>
 </file>
@@ -41922,60 +41928,124 @@
       </c>
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B158" s="11"/>
+      <c r="B158" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="C158" s="5"/>
-      <c r="D158" s="3"/>
-      <c r="E158" s="43"/>
-      <c r="F158" s="7"/>
+      <c r="D158" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E158" s="43">
+        <v>280</v>
+      </c>
+      <c r="F158" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="159" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B159" s="11"/>
+      <c r="B159" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C159" s="5"/>
-      <c r="D159" s="3"/>
-      <c r="E159" s="43"/>
-      <c r="F159" s="7"/>
+      <c r="D159" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E159" s="43">
+        <v>1508</v>
+      </c>
+      <c r="F159" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="160" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B160" s="11"/>
+      <c r="B160" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="C160" s="5"/>
-      <c r="D160" s="3"/>
-      <c r="E160" s="43"/>
-      <c r="F160" s="7"/>
+      <c r="D160" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E160" s="43">
+        <v>67</v>
+      </c>
+      <c r="F160" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B161" s="11"/>
+      <c r="B161" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="C161" s="5"/>
-      <c r="D161" s="3"/>
-      <c r="E161" s="43"/>
-      <c r="F161" s="7"/>
+      <c r="D161" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E161" s="43">
+        <v>30</v>
+      </c>
+      <c r="F161" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B162" s="11"/>
+      <c r="B162" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C162" s="5"/>
-      <c r="D162" s="3"/>
-      <c r="E162" s="43"/>
-      <c r="F162" s="7"/>
+      <c r="D162" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E162" s="43">
+        <v>3635</v>
+      </c>
+      <c r="F162" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B163" s="11"/>
+      <c r="B163" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C163" s="5"/>
-      <c r="D163" s="3"/>
-      <c r="E163" s="43"/>
-      <c r="F163" s="7"/>
+      <c r="D163" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E163" s="43">
+        <v>4200</v>
+      </c>
+      <c r="F163" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B164" s="11"/>
+      <c r="B164" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C164" s="5"/>
-      <c r="D164" s="3"/>
-      <c r="E164" s="43"/>
-      <c r="F164" s="7"/>
+      <c r="D164" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E164" s="43">
+        <v>1497</v>
+      </c>
+      <c r="F164" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B165" s="11"/>
+      <c r="B165" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C165" s="5"/>
-      <c r="D165" s="3"/>
-      <c r="E165" s="43"/>
-      <c r="F165" s="7"/>
+      <c r="D165" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E165" s="43">
+        <v>2944</v>
+      </c>
+      <c r="F165" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B166" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1867" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98D2DBEE-BCCF-4A7A-AE23-F8D92B52D14D}"/>
+  <xr:revisionPtr revIDLastSave="1897" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A0F3D02-81E1-4ECD-8884-A9490C15A990}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="158">
   <si>
     <t>Custo</t>
   </si>
@@ -512,6 +512,9 @@
   </si>
   <si>
     <t>BORRACHARIA NITEROI</t>
+  </si>
+  <si>
+    <t>TEQ5C84</t>
   </si>
 </sst>
 </file>
@@ -42048,53 +42051,109 @@
       </c>
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B166" s="11"/>
+      <c r="B166" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C166" s="5"/>
-      <c r="D166" s="3"/>
-      <c r="E166" s="43"/>
-      <c r="F166" s="7"/>
+      <c r="D166" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E166" s="43">
+        <v>122</v>
+      </c>
+      <c r="F166" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B167" s="11"/>
+      <c r="B167" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C167" s="5"/>
-      <c r="D167" s="3"/>
-      <c r="E167" s="43"/>
-      <c r="F167" s="7"/>
+      <c r="D167" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E167" s="43">
+        <v>40</v>
+      </c>
+      <c r="F167" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B168" s="11"/>
+      <c r="B168" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C168" s="5"/>
-      <c r="D168" s="3"/>
-      <c r="E168" s="43"/>
-      <c r="F168" s="7"/>
+      <c r="D168" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E168" s="43">
+        <v>100</v>
+      </c>
+      <c r="F168" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B169" s="11"/>
+      <c r="B169" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C169" s="5"/>
-      <c r="D169" s="3"/>
-      <c r="E169" s="43"/>
-      <c r="F169" s="7"/>
+      <c r="D169" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E169" s="43">
+        <v>50</v>
+      </c>
+      <c r="F169" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B170" s="11"/>
+      <c r="B170" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C170" s="5"/>
-      <c r="D170" s="3"/>
-      <c r="E170" s="43"/>
-      <c r="F170" s="7"/>
+      <c r="D170" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E170" s="43">
+        <v>12</v>
+      </c>
+      <c r="F170" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B171" s="11"/>
+      <c r="B171" s="11" t="s">
+        <v>26</v>
+      </c>
       <c r="C171" s="5"/>
-      <c r="D171" s="3"/>
-      <c r="E171" s="43"/>
-      <c r="F171" s="7"/>
+      <c r="D171" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E171" s="43">
+        <v>210</v>
+      </c>
+      <c r="F171" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B172" s="11"/>
+      <c r="B172" s="11" t="s">
+        <v>157</v>
+      </c>
       <c r="C172" s="5"/>
-      <c r="D172" s="3"/>
-      <c r="E172" s="43"/>
-      <c r="F172" s="7"/>
+      <c r="D172" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E172" s="43">
+        <v>55</v>
+      </c>
+      <c r="F172" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B173" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1897" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A0F3D02-81E1-4ECD-8884-A9490C15A990}"/>
+  <xr:revisionPtr revIDLastSave="1905" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34BE65B4-AA1B-446F-A968-3FC4FC7D3240}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="158">
   <si>
     <t>Custo</t>
   </si>
@@ -42156,18 +42156,34 @@
       </c>
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B173" s="11"/>
+      <c r="B173" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C173" s="5"/>
-      <c r="D173" s="3"/>
-      <c r="E173" s="43"/>
-      <c r="F173" s="7"/>
+      <c r="D173" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E173" s="43">
+        <v>100</v>
+      </c>
+      <c r="F173" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B174" s="11"/>
+      <c r="B174" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C174" s="5"/>
-      <c r="D174" s="3"/>
-      <c r="E174" s="43"/>
-      <c r="F174" s="7"/>
+      <c r="D174" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E174" s="43">
+        <v>70</v>
+      </c>
+      <c r="F174" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B175" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1905" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34BE65B4-AA1B-446F-A968-3FC4FC7D3240}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1785F16A-F5B8-4E25-831A-CCA32E76DB98}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2552" uniqueCount="162">
   <si>
     <t>Custo</t>
   </si>
@@ -515,6 +515,18 @@
   </si>
   <si>
     <t>TEQ5C84</t>
+  </si>
+  <si>
+    <t>OFICINA CATALÃO DIESEL</t>
+  </si>
+  <si>
+    <t>AUTO ESCAPAMENTO FREITAS</t>
+  </si>
+  <si>
+    <t>AUTO PEÇAS DALDEGAN</t>
+  </si>
+  <si>
+    <t>CT DIESEL</t>
   </si>
 </sst>
 </file>
@@ -42186,158 +42198,334 @@
       </c>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B175" s="11"/>
+      <c r="B175" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C175" s="5"/>
-      <c r="D175" s="3"/>
-      <c r="E175" s="43"/>
-      <c r="F175" s="7"/>
+      <c r="D175" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E175" s="43">
+        <v>1102</v>
+      </c>
+      <c r="F175" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B176" s="11"/>
+      <c r="B176" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C176" s="5"/>
-      <c r="D176" s="3"/>
-      <c r="E176" s="43"/>
-      <c r="F176" s="7"/>
+      <c r="D176" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E176" s="43">
+        <v>1200</v>
+      </c>
+      <c r="F176" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B177" s="11"/>
+      <c r="B177" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C177" s="5"/>
-      <c r="D177" s="3"/>
-      <c r="E177" s="43"/>
-      <c r="F177" s="7"/>
+      <c r="D177" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E177" s="43">
+        <v>280</v>
+      </c>
+      <c r="F177" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B178" s="11"/>
+      <c r="B178" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C178" s="5"/>
-      <c r="D178" s="3"/>
-      <c r="E178" s="43"/>
-      <c r="F178" s="7"/>
+      <c r="D178" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E178" s="43">
+        <v>46</v>
+      </c>
+      <c r="F178" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="179" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B179" s="11"/>
+      <c r="B179" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C179" s="5"/>
-      <c r="D179" s="3"/>
-      <c r="E179" s="43"/>
-      <c r="F179" s="7"/>
+      <c r="D179" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E179" s="43">
+        <v>136.9</v>
+      </c>
+      <c r="F179" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="180" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B180" s="11"/>
+      <c r="B180" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C180" s="5"/>
-      <c r="D180" s="3"/>
-      <c r="E180" s="43"/>
-      <c r="F180" s="7"/>
+      <c r="D180" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E180" s="43">
+        <v>965</v>
+      </c>
+      <c r="F180" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="181" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B181" s="11"/>
+      <c r="B181" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C181" s="5"/>
-      <c r="D181" s="3"/>
-      <c r="E181" s="43"/>
-      <c r="F181" s="7"/>
+      <c r="D181" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E181" s="43">
+        <v>1623.4</v>
+      </c>
+      <c r="F181" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="182" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B182" s="11"/>
+      <c r="B182" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C182" s="5"/>
-      <c r="D182" s="3"/>
-      <c r="E182" s="43"/>
-      <c r="F182" s="7"/>
+      <c r="D182" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E182" s="43">
+        <v>130</v>
+      </c>
+      <c r="F182" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="183" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B183" s="11"/>
+      <c r="B183" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C183" s="5"/>
-      <c r="D183" s="3"/>
-      <c r="E183" s="43"/>
-      <c r="F183" s="7"/>
+      <c r="D183" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E183" s="43">
+        <v>1908</v>
+      </c>
+      <c r="F183" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="184" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B184" s="11"/>
+      <c r="B184" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C184" s="5"/>
-      <c r="D184" s="3"/>
-      <c r="E184" s="43"/>
-      <c r="F184" s="7"/>
+      <c r="D184" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E184" s="43">
+        <v>1435</v>
+      </c>
+      <c r="F184" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B185" s="11"/>
+      <c r="B185" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C185" s="5"/>
-      <c r="D185" s="3"/>
-      <c r="E185" s="43"/>
-      <c r="F185" s="7"/>
+      <c r="D185" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E185" s="43">
+        <v>224.18</v>
+      </c>
+      <c r="F185" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="186" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B186" s="11"/>
+      <c r="B186" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C186" s="5"/>
-      <c r="D186" s="3"/>
-      <c r="E186" s="43"/>
-      <c r="F186" s="7"/>
+      <c r="D186" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E186" s="43">
+        <v>100</v>
+      </c>
+      <c r="F186" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="187" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B187" s="11"/>
+      <c r="B187" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C187" s="5"/>
-      <c r="D187" s="3"/>
-      <c r="E187" s="43"/>
-      <c r="F187" s="7"/>
+      <c r="D187" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E187" s="43">
+        <v>250</v>
+      </c>
+      <c r="F187" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="188" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B188" s="11"/>
+      <c r="B188" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C188" s="5"/>
-      <c r="D188" s="3"/>
-      <c r="E188" s="43"/>
-      <c r="F188" s="7"/>
+      <c r="D188" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E188" s="43">
+        <v>135</v>
+      </c>
+      <c r="F188" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B189" s="11"/>
+      <c r="B189" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C189" s="5"/>
-      <c r="D189" s="3"/>
-      <c r="E189" s="43"/>
-      <c r="F189" s="7"/>
+      <c r="D189" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E189" s="43">
+        <v>855</v>
+      </c>
+      <c r="F189" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="190" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B190" s="11"/>
+      <c r="B190" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C190" s="5"/>
-      <c r="D190" s="3"/>
-      <c r="E190" s="43"/>
-      <c r="F190" s="7"/>
+      <c r="D190" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E190" s="43">
+        <v>280</v>
+      </c>
+      <c r="F190" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="191" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B191" s="11"/>
+      <c r="B191" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C191" s="5"/>
-      <c r="D191" s="3"/>
-      <c r="E191" s="43"/>
-      <c r="F191" s="7"/>
+      <c r="D191" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E191" s="43">
+        <v>1700</v>
+      </c>
+      <c r="F191" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="192" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B192" s="11"/>
+      <c r="B192" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C192" s="5"/>
-      <c r="D192" s="3"/>
-      <c r="E192" s="43"/>
-      <c r="F192" s="7"/>
+      <c r="D192" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E192" s="43">
+        <v>5576.47</v>
+      </c>
+      <c r="F192" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="193" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B193" s="11"/>
+      <c r="B193" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C193" s="5"/>
-      <c r="D193" s="3"/>
-      <c r="E193" s="43"/>
-      <c r="F193" s="7"/>
+      <c r="D193" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E193" s="43">
+        <v>185.5</v>
+      </c>
+      <c r="F193" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="194" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B194" s="11"/>
+      <c r="B194" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C194" s="5"/>
-      <c r="D194" s="3"/>
-      <c r="E194" s="43"/>
-      <c r="F194" s="7"/>
+      <c r="D194" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E194" s="43">
+        <v>80</v>
+      </c>
+      <c r="F194" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B195" s="11"/>
+      <c r="B195" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C195" s="5"/>
-      <c r="D195" s="3"/>
-      <c r="E195" s="43"/>
-      <c r="F195" s="7"/>
+      <c r="D195" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E195" s="43">
+        <v>134</v>
+      </c>
+      <c r="F195" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="196" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B196" s="11"/>
+      <c r="B196" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C196" s="5"/>
-      <c r="D196" s="3"/>
-      <c r="E196" s="43"/>
-      <c r="F196" s="7"/>
+      <c r="D196" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E196" s="43">
+        <v>200</v>
+      </c>
+      <c r="F196" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B197" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1785F16A-F5B8-4E25-831A-CCA32E76DB98}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C57B275A-21D9-4049-9D63-8AB7635DA7AC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2552" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2574" uniqueCount="165">
   <si>
     <t>Custo</t>
   </si>
@@ -527,6 +527,15 @@
   </si>
   <si>
     <t>CT DIESEL</t>
+  </si>
+  <si>
+    <t>OFICINA DO RODINHO</t>
+  </si>
+  <si>
+    <t>KLM TRANSPORTES</t>
+  </si>
+  <si>
+    <t>HMR9D08</t>
   </si>
 </sst>
 </file>
@@ -42528,81 +42537,169 @@
       </c>
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B197" s="11"/>
+      <c r="B197" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C197" s="5"/>
-      <c r="D197" s="3"/>
-      <c r="E197" s="43"/>
-      <c r="F197" s="7"/>
+      <c r="D197" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E197" s="43">
+        <v>153</v>
+      </c>
+      <c r="F197" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B198" s="11"/>
+      <c r="B198" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C198" s="5"/>
-      <c r="D198" s="3"/>
-      <c r="E198" s="43"/>
-      <c r="F198" s="7"/>
+      <c r="D198" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E198" s="43">
+        <v>200</v>
+      </c>
+      <c r="F198" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B199" s="11"/>
+      <c r="B199" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C199" s="5"/>
-      <c r="D199" s="3"/>
-      <c r="E199" s="43"/>
-      <c r="F199" s="7"/>
+      <c r="D199" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E199" s="43">
+        <v>150</v>
+      </c>
+      <c r="F199" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B200" s="11"/>
+      <c r="B200" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C200" s="5"/>
-      <c r="D200" s="3"/>
-      <c r="E200" s="43"/>
-      <c r="F200" s="7"/>
+      <c r="D200" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E200" s="43">
+        <v>1300</v>
+      </c>
+      <c r="F200" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="201" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B201" s="11"/>
+      <c r="B201" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C201" s="5"/>
-      <c r="D201" s="3"/>
-      <c r="E201" s="43"/>
-      <c r="F201" s="7"/>
+      <c r="D201" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E201" s="43">
+        <v>240</v>
+      </c>
+      <c r="F201" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="202" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B202" s="11"/>
+      <c r="B202" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C202" s="5"/>
-      <c r="D202" s="3"/>
-      <c r="E202" s="43"/>
-      <c r="F202" s="7"/>
+      <c r="D202" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E202" s="43">
+        <v>2026.6</v>
+      </c>
+      <c r="F202" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="203" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B203" s="11"/>
+      <c r="B203" s="11" t="s">
+        <v>10</v>
+      </c>
       <c r="C203" s="5"/>
-      <c r="D203" s="3"/>
-      <c r="E203" s="43"/>
-      <c r="F203" s="7"/>
+      <c r="D203" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E203" s="43">
+        <v>1465.8</v>
+      </c>
+      <c r="F203" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="204" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B204" s="11"/>
+      <c r="B204" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C204" s="5"/>
-      <c r="D204" s="3"/>
-      <c r="E204" s="43"/>
-      <c r="F204" s="7"/>
+      <c r="D204" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E204" s="43">
+        <v>100</v>
+      </c>
+      <c r="F204" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="205" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B205" s="11"/>
+      <c r="B205" s="11" t="s">
+        <v>142</v>
+      </c>
       <c r="C205" s="5"/>
-      <c r="D205" s="3"/>
-      <c r="E205" s="43"/>
-      <c r="F205" s="7"/>
+      <c r="D205" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E205" s="43">
+        <v>612.5</v>
+      </c>
+      <c r="F205" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="206" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B206" s="11"/>
+      <c r="B206" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C206" s="5"/>
-      <c r="D206" s="3"/>
-      <c r="E206" s="43"/>
-      <c r="F206" s="7"/>
+      <c r="D206" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E206" s="43">
+        <v>80</v>
+      </c>
+      <c r="F206" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="207" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B207" s="11"/>
+      <c r="B207" s="11" t="s">
+        <v>164</v>
+      </c>
       <c r="C207" s="5"/>
-      <c r="D207" s="3"/>
-      <c r="E207" s="43"/>
-      <c r="F207" s="7"/>
+      <c r="D207" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E207" s="43">
+        <v>35</v>
+      </c>
+      <c r="F207" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="208" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B208" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C57B275A-21D9-4049-9D63-8AB7635DA7AC}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02FF2DBB-C695-46F2-B7D3-B2EECCA0E8C3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2025'!$B$2:$G$4196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$2:$G$2944</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2026'!$B$2:$G$2946</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2574" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2590" uniqueCount="167">
   <si>
     <t>Custo</t>
   </si>
@@ -536,6 +536,12 @@
   </si>
   <si>
     <t>HMR9D08</t>
+  </si>
+  <si>
+    <t>JOK PNEUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORRACHARIA  </t>
   </si>
 </sst>
 </file>
@@ -42702,46 +42708,94 @@
       </c>
     </row>
     <row r="208" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B208" s="11"/>
+      <c r="B208" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C208" s="5"/>
-      <c r="D208" s="3"/>
-      <c r="E208" s="43"/>
-      <c r="F208" s="7"/>
+      <c r="D208" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E208" s="43">
+        <v>50</v>
+      </c>
+      <c r="F208" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B209" s="11"/>
+      <c r="B209" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C209" s="5"/>
-      <c r="D209" s="3"/>
-      <c r="E209" s="43"/>
-      <c r="F209" s="7"/>
+      <c r="D209" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E209" s="43">
+        <v>726.9</v>
+      </c>
+      <c r="F209" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="210" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B210" s="11"/>
+      <c r="B210" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C210" s="5"/>
-      <c r="D210" s="3"/>
-      <c r="E210" s="43"/>
-      <c r="F210" s="7"/>
+      <c r="D210" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E210" s="43">
+        <v>50</v>
+      </c>
+      <c r="F210" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="211" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B211" s="11"/>
+      <c r="B211" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C211" s="5"/>
-      <c r="D211" s="3"/>
-      <c r="E211" s="43"/>
-      <c r="F211" s="7"/>
+      <c r="D211" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E211" s="43">
+        <v>140</v>
+      </c>
+      <c r="F211" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="212" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B212" s="11"/>
+      <c r="B212" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C212" s="5"/>
-      <c r="D212" s="3"/>
-      <c r="E212" s="43"/>
-      <c r="F212" s="7"/>
+      <c r="D212" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E212" s="43">
+        <v>100</v>
+      </c>
+      <c r="F212" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B213" s="11"/>
+      <c r="B213" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C213" s="5"/>
-      <c r="D213" s="3"/>
-      <c r="E213" s="43"/>
-      <c r="F213" s="7"/>
+      <c r="D213" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E213" s="43">
+        <v>3980</v>
+      </c>
+      <c r="F213" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B214" s="11"/>
@@ -61854,18 +61908,34 @@
       <c r="F2943" s="7"/>
     </row>
     <row r="2945" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2945" s="24"/>
+      <c r="B2945" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="C2945" s="24"/>
-      <c r="D2945" s="24"/>
-      <c r="E2945" s="46"/>
-      <c r="F2945" s="38"/>
+      <c r="D2945" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2945" s="46">
+        <v>40</v>
+      </c>
+      <c r="F2945" s="7">
+        <v>46023</v>
+      </c>
     </row>
     <row r="2946" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2946" s="24"/>
+      <c r="B2946" s="24" t="s">
+        <v>3</v>
+      </c>
       <c r="C2946" s="24"/>
-      <c r="D2946" s="24"/>
-      <c r="E2946" s="46"/>
-      <c r="F2946" s="38"/>
+      <c r="D2946" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2946" s="46">
+        <v>70</v>
+      </c>
+      <c r="F2946" s="38">
+        <v>46054</v>
+      </c>
     </row>
     <row r="2947" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2947" s="24"/>
@@ -62190,7 +62260,7 @@
       <c r="F2992" s="38"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G2944" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
+  <autoFilter ref="B2:G2946" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02FF2DBB-C695-46F2-B7D3-B2EECCA0E8C3}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ADB41D6-95F4-4504-86AD-18FB3434A5E0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2590" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2593" uniqueCount="167">
   <si>
     <t>Custo</t>
   </si>
@@ -42798,18 +42798,32 @@
       </c>
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B214" s="11"/>
+      <c r="B214" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="C214" s="5"/>
-      <c r="D214" s="3"/>
-      <c r="E214" s="43"/>
-      <c r="F214" s="7"/>
+      <c r="D214" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E214" s="43">
+        <v>32</v>
+      </c>
+      <c r="F214" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B215" s="11"/>
       <c r="C215" s="5"/>
-      <c r="D215" s="3"/>
-      <c r="E215" s="43"/>
-      <c r="F215" s="7"/>
+      <c r="D215" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E215" s="43">
+        <v>550</v>
+      </c>
+      <c r="F215" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="216" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B216" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ADB41D6-95F4-4504-86AD-18FB3434A5E0}"/>
+  <xr:revisionPtr revIDLastSave="363" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6340FEDA-37CA-457D-B2E0-A5895F5A1E2A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2593" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2718" uniqueCount="172">
   <si>
     <t>Custo</t>
   </si>
@@ -542,6 +542,21 @@
   </si>
   <si>
     <t xml:space="preserve">BORRACHARIA  </t>
+  </si>
+  <si>
+    <t>SEM</t>
+  </si>
+  <si>
+    <t>CARLITO PNEUS</t>
+  </si>
+  <si>
+    <t>TEB9E97</t>
+  </si>
+  <si>
+    <t>VOLKS BEM AUTO PEÇAS</t>
+  </si>
+  <si>
+    <t>MANG DIVI</t>
   </si>
 </sst>
 </file>
@@ -42813,7 +42828,9 @@
       </c>
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B215" s="11"/>
+      <c r="B215" s="11" t="s">
+        <v>167</v>
+      </c>
       <c r="C215" s="5"/>
       <c r="D215" s="3" t="s">
         <v>135</v>
@@ -42826,438 +42843,934 @@
       </c>
     </row>
     <row r="216" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B216" s="11"/>
+      <c r="B216" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C216" s="5"/>
-      <c r="D216" s="3"/>
-      <c r="E216" s="43"/>
-      <c r="F216" s="7"/>
+      <c r="D216" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E216" s="43">
+        <v>420</v>
+      </c>
+      <c r="F216" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B217" s="11"/>
+      <c r="B217" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C217" s="5"/>
-      <c r="D217" s="3"/>
-      <c r="E217" s="43"/>
-      <c r="F217" s="7"/>
+      <c r="D217" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E217" s="43">
+        <v>2746.74</v>
+      </c>
+      <c r="F217" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B218" s="11"/>
+      <c r="B218" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C218" s="5"/>
-      <c r="D218" s="3"/>
-      <c r="E218" s="43"/>
-      <c r="F218" s="7"/>
+      <c r="D218" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E218" s="43">
+        <v>72.260000000000005</v>
+      </c>
+      <c r="F218" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="219" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B219" s="11"/>
+      <c r="B219" s="11" t="s">
+        <v>164</v>
+      </c>
       <c r="C219" s="5"/>
-      <c r="D219" s="3"/>
-      <c r="E219" s="43"/>
-      <c r="F219" s="7"/>
+      <c r="D219" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E219" s="43">
+        <v>30</v>
+      </c>
+      <c r="F219" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B220" s="11"/>
+      <c r="B220" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C220" s="5"/>
-      <c r="D220" s="3"/>
-      <c r="E220" s="43"/>
-      <c r="F220" s="7"/>
+      <c r="D220" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E220" s="43">
+        <v>2600</v>
+      </c>
+      <c r="F220" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="221" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B221" s="11"/>
+      <c r="B221" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="C221" s="5"/>
-      <c r="D221" s="3"/>
-      <c r="E221" s="43"/>
-      <c r="F221" s="7"/>
+      <c r="D221" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E221" s="43">
+        <v>1440</v>
+      </c>
+      <c r="F221" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="222" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B222" s="11"/>
+      <c r="B222" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C222" s="5"/>
-      <c r="D222" s="3"/>
-      <c r="E222" s="43"/>
-      <c r="F222" s="7"/>
+      <c r="D222" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E222" s="43">
+        <v>89.84</v>
+      </c>
+      <c r="F222" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="223" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B223" s="11"/>
+      <c r="B223" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="C223" s="5"/>
-      <c r="D223" s="3"/>
-      <c r="E223" s="43"/>
-      <c r="F223" s="7"/>
+      <c r="D223" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E223" s="43">
+        <v>635</v>
+      </c>
+      <c r="F223" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="224" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B224" s="11"/>
+      <c r="B224" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C224" s="5"/>
-      <c r="D224" s="3"/>
-      <c r="E224" s="43"/>
-      <c r="F224" s="7"/>
+      <c r="D224" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E224" s="43">
+        <v>44</v>
+      </c>
+      <c r="F224" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="225" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B225" s="11"/>
+      <c r="B225" s="11" t="s">
+        <v>169</v>
+      </c>
       <c r="C225" s="5"/>
-      <c r="D225" s="3"/>
-      <c r="E225" s="43"/>
-      <c r="F225" s="7"/>
+      <c r="D225" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E225" s="43">
+        <v>55</v>
+      </c>
+      <c r="F225" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="226" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B226" s="11"/>
+      <c r="B226" s="11" t="s">
+        <v>112</v>
+      </c>
       <c r="C226" s="5"/>
-      <c r="D226" s="3"/>
-      <c r="E226" s="43"/>
-      <c r="F226" s="7"/>
+      <c r="D226" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E226" s="43">
+        <v>120</v>
+      </c>
+      <c r="F226" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="227" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B227" s="11"/>
+      <c r="B227" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C227" s="5"/>
-      <c r="D227" s="3"/>
-      <c r="E227" s="43"/>
-      <c r="F227" s="7"/>
+      <c r="D227" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E227" s="43">
+        <v>200</v>
+      </c>
+      <c r="F227" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="228" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B228" s="11"/>
+      <c r="B228" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C228" s="5"/>
-      <c r="D228" s="3"/>
-      <c r="E228" s="43"/>
-      <c r="F228" s="7"/>
+      <c r="D228" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E228" s="43">
+        <v>175</v>
+      </c>
+      <c r="F228" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="229" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B229" s="11"/>
+      <c r="B229" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C229" s="5"/>
-      <c r="D229" s="3"/>
-      <c r="E229" s="43"/>
-      <c r="F229" s="7"/>
+      <c r="D229" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E229" s="43">
+        <v>205</v>
+      </c>
+      <c r="F229" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="230" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B230" s="11"/>
+      <c r="B230" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="C230" s="5"/>
-      <c r="D230" s="3"/>
-      <c r="E230" s="43"/>
-      <c r="F230" s="7"/>
+      <c r="D230" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E230" s="43">
+        <v>200</v>
+      </c>
+      <c r="F230" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="231" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B231" s="11"/>
+      <c r="B231" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C231" s="5"/>
-      <c r="D231" s="3"/>
-      <c r="E231" s="43"/>
-      <c r="F231" s="7"/>
+      <c r="D231" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E231" s="43">
+        <v>3500</v>
+      </c>
+      <c r="F231" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="232" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B232" s="11"/>
+      <c r="B232" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C232" s="5"/>
-      <c r="D232" s="3"/>
-      <c r="E232" s="43"/>
-      <c r="F232" s="7"/>
+      <c r="D232" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E232" s="43">
+        <v>60</v>
+      </c>
+      <c r="F232" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B233" s="11"/>
+      <c r="B233" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C233" s="5"/>
-      <c r="D233" s="3"/>
-      <c r="E233" s="43"/>
-      <c r="F233" s="7"/>
+      <c r="D233" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E233" s="43">
+        <v>219</v>
+      </c>
+      <c r="F233" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B234" s="11"/>
+      <c r="B234" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C234" s="5"/>
-      <c r="D234" s="3"/>
-      <c r="E234" s="43"/>
-      <c r="F234" s="7"/>
+      <c r="D234" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E234" s="43">
+        <v>105</v>
+      </c>
+      <c r="F234" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B235" s="11"/>
+      <c r="B235" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C235" s="5"/>
-      <c r="D235" s="3"/>
-      <c r="E235" s="43"/>
-      <c r="F235" s="7"/>
+      <c r="D235" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E235" s="43">
+        <v>1950</v>
+      </c>
+      <c r="F235" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B236" s="11"/>
+      <c r="B236" s="11" t="s">
+        <v>167</v>
+      </c>
       <c r="C236" s="5"/>
-      <c r="D236" s="3"/>
-      <c r="E236" s="43"/>
-      <c r="F236" s="7"/>
+      <c r="D236" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E236" s="43">
+        <v>70</v>
+      </c>
+      <c r="F236" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B237" s="11"/>
+      <c r="B237" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C237" s="5"/>
-      <c r="D237" s="3"/>
-      <c r="E237" s="43"/>
-      <c r="F237" s="7"/>
+      <c r="D237" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E237" s="43">
+        <v>70</v>
+      </c>
+      <c r="F237" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B238" s="11"/>
+      <c r="B238" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C238" s="5"/>
-      <c r="D238" s="3"/>
-      <c r="E238" s="43"/>
-      <c r="F238" s="7"/>
+      <c r="D238" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E238" s="43">
+        <v>35</v>
+      </c>
+      <c r="F238" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B239" s="11"/>
+      <c r="B239" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C239" s="5"/>
-      <c r="D239" s="3"/>
-      <c r="E239" s="43"/>
-      <c r="F239" s="7"/>
+      <c r="D239" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E239" s="43">
+        <v>7320</v>
+      </c>
+      <c r="F239" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B240" s="11"/>
+      <c r="B240" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C240" s="5"/>
-      <c r="D240" s="3"/>
-      <c r="E240" s="43"/>
-      <c r="F240" s="7"/>
+      <c r="D240" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E240" s="43">
+        <v>346</v>
+      </c>
+      <c r="F240" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B241" s="11"/>
+      <c r="B241" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C241" s="5"/>
-      <c r="D241" s="3"/>
-      <c r="E241" s="43"/>
-      <c r="F241" s="7"/>
+      <c r="D241" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E241" s="43">
+        <v>50</v>
+      </c>
+      <c r="F241" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B242" s="11"/>
+      <c r="B242" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C242" s="5"/>
-      <c r="D242" s="3"/>
-      <c r="E242" s="43"/>
-      <c r="F242" s="7"/>
+      <c r="D242" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E242" s="43">
+        <v>100</v>
+      </c>
+      <c r="F242" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B243" s="11"/>
+      <c r="B243" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C243" s="5"/>
-      <c r="D243" s="3"/>
-      <c r="E243" s="43"/>
-      <c r="F243" s="7"/>
+      <c r="D243" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E243" s="43">
+        <v>394.38</v>
+      </c>
+      <c r="F243" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B244" s="11"/>
+      <c r="B244" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C244" s="5"/>
-      <c r="D244" s="3"/>
-      <c r="E244" s="43"/>
-      <c r="F244" s="7"/>
+      <c r="D244" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E244" s="43">
+        <v>78</v>
+      </c>
+      <c r="F244" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B245" s="11"/>
+      <c r="B245" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C245" s="5"/>
-      <c r="D245" s="3"/>
-      <c r="E245" s="43"/>
-      <c r="F245" s="7"/>
+      <c r="D245" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E245" s="43">
+        <v>190</v>
+      </c>
+      <c r="F245" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B246" s="11"/>
+      <c r="B246" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C246" s="5"/>
-      <c r="D246" s="3"/>
-      <c r="E246" s="43"/>
-      <c r="F246" s="7"/>
+      <c r="D246" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E246" s="43">
+        <v>50</v>
+      </c>
+      <c r="F246" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B247" s="11"/>
+      <c r="B247" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C247" s="5"/>
-      <c r="D247" s="3"/>
-      <c r="E247" s="43"/>
-      <c r="F247" s="7"/>
+      <c r="D247" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E247" s="43">
+        <v>630</v>
+      </c>
+      <c r="F247" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B248" s="11"/>
+      <c r="B248" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C248" s="5"/>
-      <c r="D248" s="3"/>
-      <c r="E248" s="43"/>
-      <c r="F248" s="7"/>
+      <c r="D248" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E248" s="43">
+        <v>2778</v>
+      </c>
+      <c r="F248" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B249" s="11"/>
+      <c r="B249" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C249" s="5"/>
-      <c r="D249" s="3"/>
-      <c r="E249" s="43"/>
-      <c r="F249" s="7"/>
+      <c r="D249" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E249" s="43">
+        <v>592</v>
+      </c>
+      <c r="F249" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B250" s="11"/>
+      <c r="B250" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C250" s="5"/>
-      <c r="D250" s="3"/>
-      <c r="E250" s="43"/>
-      <c r="F250" s="7"/>
+      <c r="D250" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E250" s="43">
+        <v>1012.35</v>
+      </c>
+      <c r="F250" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B251" s="11"/>
+      <c r="B251" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C251" s="5"/>
-      <c r="D251" s="3"/>
-      <c r="E251" s="43"/>
-      <c r="F251" s="7"/>
+      <c r="D251" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E251" s="43">
+        <v>580</v>
+      </c>
+      <c r="F251" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B252" s="11"/>
+      <c r="B252" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C252" s="5"/>
-      <c r="D252" s="3"/>
-      <c r="E252" s="43"/>
-      <c r="F252" s="7"/>
+      <c r="D252" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E252" s="43">
+        <v>185</v>
+      </c>
+      <c r="F252" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="253" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B253" s="11"/>
+      <c r="B253" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C253" s="5"/>
-      <c r="D253" s="3"/>
-      <c r="E253" s="43"/>
-      <c r="F253" s="7"/>
+      <c r="D253" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E253" s="43">
+        <v>60</v>
+      </c>
+      <c r="F253" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B254" s="11"/>
+      <c r="B254" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C254" s="5"/>
-      <c r="D254" s="3"/>
-      <c r="E254" s="43"/>
-      <c r="F254" s="7"/>
+      <c r="D254" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E254" s="43">
+        <v>12156</v>
+      </c>
+      <c r="F254" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B255" s="11"/>
+      <c r="B255" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C255" s="5"/>
-      <c r="D255" s="3"/>
-      <c r="E255" s="43"/>
-      <c r="F255" s="7"/>
+      <c r="D255" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E255" s="43">
+        <v>16800</v>
+      </c>
+      <c r="F255" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B256" s="11"/>
+      <c r="B256" s="11" t="s">
+        <v>167</v>
+      </c>
       <c r="C256" s="5"/>
-      <c r="D256" s="3"/>
-      <c r="E256" s="43"/>
-      <c r="F256" s="7"/>
+      <c r="D256" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E256" s="43">
+        <v>97</v>
+      </c>
+      <c r="F256" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="257" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B257" s="11"/>
+      <c r="B257" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C257" s="5"/>
-      <c r="D257" s="3"/>
-      <c r="E257" s="43"/>
-      <c r="F257" s="7"/>
+      <c r="D257" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E257" s="43">
+        <v>1392</v>
+      </c>
+      <c r="F257" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B258" s="11"/>
+      <c r="B258" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C258" s="5"/>
-      <c r="D258" s="3"/>
-      <c r="E258" s="43"/>
-      <c r="F258" s="7"/>
+      <c r="D258" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E258" s="43">
+        <v>1245</v>
+      </c>
+      <c r="F258" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B259" s="11"/>
+      <c r="B259" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C259" s="5"/>
-      <c r="D259" s="3"/>
-      <c r="E259" s="43"/>
-      <c r="F259" s="7"/>
+      <c r="D259" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E259" s="43">
+        <v>712</v>
+      </c>
+      <c r="F259" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B260" s="11"/>
+      <c r="B260" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C260" s="5"/>
-      <c r="D260" s="3"/>
-      <c r="E260" s="43"/>
-      <c r="F260" s="7"/>
+      <c r="D260" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E260" s="43">
+        <v>1420</v>
+      </c>
+      <c r="F260" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B261" s="11"/>
+      <c r="B261" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C261" s="5"/>
-      <c r="D261" s="3"/>
-      <c r="E261" s="43"/>
-      <c r="F261" s="7"/>
+      <c r="D261" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E261" s="43">
+        <v>696</v>
+      </c>
+      <c r="F261" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B262" s="11"/>
+      <c r="B262" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C262" s="5"/>
-      <c r="D262" s="3"/>
-      <c r="E262" s="43"/>
-      <c r="F262" s="7"/>
+      <c r="D262" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E262" s="43">
+        <v>100</v>
+      </c>
+      <c r="F262" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B263" s="11"/>
+      <c r="B263" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C263" s="5"/>
-      <c r="D263" s="3"/>
-      <c r="E263" s="43"/>
-      <c r="F263" s="7"/>
+      <c r="D263" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E263" s="43">
+        <v>40</v>
+      </c>
+      <c r="F263" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B264" s="11"/>
+      <c r="B264" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C264" s="5"/>
-      <c r="D264" s="3"/>
-      <c r="E264" s="43"/>
-      <c r="F264" s="7"/>
+      <c r="D264" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E264" s="43">
+        <v>108</v>
+      </c>
+      <c r="F264" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B265" s="11"/>
+      <c r="B265" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C265" s="5"/>
-      <c r="D265" s="3"/>
-      <c r="E265" s="43"/>
-      <c r="F265" s="7"/>
+      <c r="D265" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E265" s="43">
+        <v>66</v>
+      </c>
+      <c r="F265" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="266" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B266" s="11"/>
+      <c r="B266" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C266" s="5"/>
-      <c r="D266" s="3"/>
-      <c r="E266" s="43"/>
-      <c r="F266" s="7"/>
+      <c r="D266" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E266" s="43">
+        <v>200</v>
+      </c>
+      <c r="F266" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="267" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B267" s="11"/>
+      <c r="B267" s="11" t="s">
+        <v>12</v>
+      </c>
       <c r="C267" s="5"/>
-      <c r="D267" s="3"/>
-      <c r="E267" s="43"/>
-      <c r="F267" s="7"/>
+      <c r="D267" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E267" s="43">
+        <v>1200</v>
+      </c>
+      <c r="F267" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="268" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B268" s="11"/>
+      <c r="B268" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C268" s="5"/>
-      <c r="D268" s="3"/>
-      <c r="E268" s="43"/>
-      <c r="F268" s="7"/>
+      <c r="D268" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E268" s="43">
+        <v>10</v>
+      </c>
+      <c r="F268" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B269" s="11"/>
+      <c r="B269" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C269" s="5"/>
-      <c r="D269" s="3"/>
-      <c r="E269" s="43"/>
-      <c r="F269" s="7"/>
+      <c r="D269" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E269" s="43">
+        <v>180</v>
+      </c>
+      <c r="F269" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="270" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B270" s="11"/>
+      <c r="B270" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C270" s="5"/>
-      <c r="D270" s="3"/>
-      <c r="E270" s="43"/>
-      <c r="F270" s="7"/>
+      <c r="D270" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E270" s="43">
+        <v>280</v>
+      </c>
+      <c r="F270" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="271" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B271" s="11"/>
+      <c r="B271" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C271" s="5"/>
-      <c r="D271" s="3"/>
-      <c r="E271" s="43"/>
-      <c r="F271" s="7"/>
+      <c r="D271" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E271" s="43">
+        <v>210</v>
+      </c>
+      <c r="F271" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="272" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B272" s="11"/>
+      <c r="B272" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C272" s="5"/>
-      <c r="D272" s="3"/>
-      <c r="E272" s="43"/>
-      <c r="F272" s="7"/>
+      <c r="D272" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E272" s="43">
+        <v>250</v>
+      </c>
+      <c r="F272" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="273" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B273" s="11"/>
+      <c r="B273" s="11" t="s">
+        <v>167</v>
+      </c>
       <c r="C273" s="5"/>
-      <c r="D273" s="3"/>
-      <c r="E273" s="43"/>
-      <c r="F273" s="7"/>
+      <c r="D273" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E273" s="43">
+        <v>309.72000000000003</v>
+      </c>
+      <c r="F273" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="274" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B274" s="11"/>
+      <c r="B274" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C274" s="5"/>
-      <c r="D274" s="3"/>
-      <c r="E274" s="43"/>
-      <c r="F274" s="7"/>
+      <c r="D274" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E274" s="43">
+        <v>265.60000000000002</v>
+      </c>
+      <c r="F274" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="275" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B275" s="11"/>
+      <c r="B275" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C275" s="5"/>
-      <c r="D275" s="3"/>
-      <c r="E275" s="43"/>
-      <c r="F275" s="7"/>
+      <c r="D275" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E275" s="43">
+        <v>263</v>
+      </c>
+      <c r="F275" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="276" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B276" s="11"/>
+      <c r="B276" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C276" s="5"/>
-      <c r="D276" s="3"/>
-      <c r="E276" s="43"/>
-      <c r="F276" s="7"/>
+      <c r="D276" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E276" s="43">
+        <v>150</v>
+      </c>
+      <c r="F276" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="277" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B277" s="11"/>
+      <c r="B277" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C277" s="5"/>
-      <c r="D277" s="3"/>
-      <c r="E277" s="43"/>
-      <c r="F277" s="7"/>
+      <c r="D277" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E277" s="43">
+        <v>100</v>
+      </c>
+      <c r="F277" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B278" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="363" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6340FEDA-37CA-457D-B2E0-A5895F5A1E2A}"/>
+  <xr:revisionPtr revIDLastSave="386" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{461B6FF1-0012-4F9F-9BCA-A49BBC422EC9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2718" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2729" uniqueCount="172">
   <si>
     <t>Custo</t>
   </si>
@@ -43773,46 +43773,92 @@
       </c>
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B278" s="11"/>
+      <c r="B278" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="C278" s="5"/>
-      <c r="D278" s="3"/>
-      <c r="E278" s="43"/>
-      <c r="F278" s="7"/>
+      <c r="D278" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E278" s="43">
+        <v>33</v>
+      </c>
+      <c r="F278" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="279" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B279" s="11"/>
+      <c r="B279" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C279" s="5"/>
       <c r="D279" s="3"/>
-      <c r="E279" s="43"/>
-      <c r="F279" s="7"/>
+      <c r="E279" s="43">
+        <v>410</v>
+      </c>
+      <c r="F279" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B280" s="11"/>
+      <c r="B280" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C280" s="5"/>
-      <c r="D280" s="3"/>
-      <c r="E280" s="43"/>
-      <c r="F280" s="7"/>
+      <c r="D280" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E280" s="43">
+        <v>450</v>
+      </c>
+      <c r="F280" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B281" s="11"/>
+      <c r="B281" s="11" t="s">
+        <v>142</v>
+      </c>
       <c r="C281" s="5"/>
-      <c r="D281" s="3"/>
-      <c r="E281" s="43"/>
-      <c r="F281" s="7"/>
+      <c r="D281" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E281" s="43">
+        <v>50</v>
+      </c>
+      <c r="F281" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="282" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B282" s="11"/>
+      <c r="B282" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C282" s="5"/>
-      <c r="D282" s="3"/>
-      <c r="E282" s="43"/>
-      <c r="F282" s="7"/>
+      <c r="D282" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E282" s="43">
+        <v>150</v>
+      </c>
+      <c r="F282" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="283" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B283" s="11"/>
+      <c r="B283" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C283" s="5"/>
-      <c r="D283" s="3"/>
-      <c r="E283" s="43"/>
-      <c r="F283" s="7"/>
+      <c r="D283" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E283" s="43">
+        <v>690</v>
+      </c>
+      <c r="F283" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="284" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B284" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="386" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{461B6FF1-0012-4F9F-9BCA-A49BBC422EC9}"/>
+  <xr:revisionPtr revIDLastSave="528" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFE480CF-7CE6-44C1-B2EE-93EAF9F9936A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2729" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2795" uniqueCount="175">
   <si>
     <t>Custo</t>
   </si>
@@ -557,6 +557,15 @@
   </si>
   <si>
     <t>MANG DIVI</t>
+  </si>
+  <si>
+    <t>GW LANTERNAGEM</t>
+  </si>
+  <si>
+    <t>GBAPNEUS</t>
+  </si>
+  <si>
+    <t>NORTE FREIOS</t>
   </si>
 </sst>
 </file>
@@ -43861,235 +43870,499 @@
       </c>
     </row>
     <row r="284" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B284" s="11"/>
+      <c r="B284" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="C284" s="5"/>
-      <c r="D284" s="3"/>
-      <c r="E284" s="43"/>
-      <c r="F284" s="7"/>
+      <c r="D284" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E284" s="43">
+        <v>7000</v>
+      </c>
+      <c r="F284" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="285" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B285" s="11"/>
+      <c r="B285" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C285" s="5"/>
-      <c r="D285" s="3"/>
-      <c r="E285" s="43"/>
-      <c r="F285" s="7"/>
+      <c r="D285" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E285" s="43">
+        <v>190</v>
+      </c>
+      <c r="F285" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="286" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B286" s="11"/>
+      <c r="B286" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C286" s="5"/>
-      <c r="D286" s="3"/>
-      <c r="E286" s="43"/>
-      <c r="F286" s="7"/>
+      <c r="D286" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E286" s="43">
+        <v>193</v>
+      </c>
+      <c r="F286" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="287" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B287" s="11"/>
+      <c r="B287" s="11" t="s">
+        <v>142</v>
+      </c>
       <c r="C287" s="5"/>
-      <c r="D287" s="3"/>
-      <c r="E287" s="43"/>
-      <c r="F287" s="7"/>
+      <c r="D287" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E287" s="43">
+        <v>80</v>
+      </c>
+      <c r="F287" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="288" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B288" s="11"/>
+      <c r="B288" s="11" t="s">
+        <v>142</v>
+      </c>
       <c r="C288" s="5"/>
-      <c r="D288" s="3"/>
-      <c r="E288" s="43"/>
-      <c r="F288" s="7"/>
+      <c r="D288" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E288" s="43">
+        <v>432</v>
+      </c>
+      <c r="F288" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="289" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B289" s="11"/>
+      <c r="B289" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C289" s="5"/>
-      <c r="D289" s="3"/>
-      <c r="E289" s="43"/>
-      <c r="F289" s="7"/>
+      <c r="D289" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E289" s="43">
+        <v>833.5</v>
+      </c>
+      <c r="F289" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="290" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B290" s="11"/>
+      <c r="B290" s="11" t="s">
+        <v>26</v>
+      </c>
       <c r="C290" s="5"/>
-      <c r="D290" s="3"/>
-      <c r="E290" s="43"/>
-      <c r="F290" s="7"/>
+      <c r="D290" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E290" s="43">
+        <v>269</v>
+      </c>
+      <c r="F290" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="291" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B291" s="11"/>
+      <c r="B291" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C291" s="5"/>
-      <c r="D291" s="3"/>
-      <c r="E291" s="43"/>
-      <c r="F291" s="7"/>
+      <c r="D291" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E291" s="43">
+        <v>2861</v>
+      </c>
+      <c r="F291" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="292" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B292" s="11"/>
+      <c r="B292" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C292" s="5"/>
-      <c r="D292" s="3"/>
-      <c r="E292" s="43"/>
-      <c r="F292" s="7"/>
+      <c r="D292" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E292" s="43">
+        <v>100</v>
+      </c>
+      <c r="F292" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="293" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B293" s="11"/>
+      <c r="B293" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C293" s="5"/>
-      <c r="D293" s="3"/>
-      <c r="E293" s="43"/>
-      <c r="F293" s="7"/>
+      <c r="D293" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E293" s="43">
+        <v>40</v>
+      </c>
+      <c r="F293" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="294" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B294" s="11"/>
+      <c r="B294" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C294" s="5"/>
-      <c r="D294" s="3"/>
-      <c r="E294" s="43"/>
-      <c r="F294" s="7"/>
+      <c r="D294" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E294" s="43">
+        <v>60</v>
+      </c>
+      <c r="F294" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="295" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B295" s="11"/>
+      <c r="B295" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C295" s="5"/>
-      <c r="D295" s="3"/>
-      <c r="E295" s="43"/>
-      <c r="F295" s="7"/>
+      <c r="D295" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E295" s="43">
+        <v>251.1</v>
+      </c>
+      <c r="F295" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="296" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B296" s="11"/>
+      <c r="B296" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C296" s="5"/>
-      <c r="D296" s="3"/>
-      <c r="E296" s="43"/>
-      <c r="F296" s="7"/>
+      <c r="D296" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E296" s="43">
+        <v>600</v>
+      </c>
+      <c r="F296" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="297" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B297" s="11"/>
+      <c r="B297" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C297" s="5"/>
-      <c r="D297" s="3"/>
-      <c r="E297" s="43"/>
-      <c r="F297" s="7"/>
+      <c r="D297" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E297" s="43">
+        <v>902.1</v>
+      </c>
+      <c r="F297" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="298" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B298" s="11"/>
+      <c r="B298" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C298" s="5"/>
-      <c r="D298" s="3"/>
-      <c r="E298" s="43"/>
-      <c r="F298" s="7"/>
+      <c r="D298" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E298" s="43">
+        <v>200</v>
+      </c>
+      <c r="F298" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="299" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B299" s="11"/>
+      <c r="B299" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C299" s="5"/>
-      <c r="D299" s="3"/>
-      <c r="E299" s="43"/>
-      <c r="F299" s="7"/>
+      <c r="D299" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E299" s="43">
+        <v>50</v>
+      </c>
+      <c r="F299" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="300" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B300" s="11"/>
+      <c r="B300" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C300" s="5"/>
-      <c r="D300" s="3"/>
-      <c r="E300" s="43"/>
-      <c r="F300" s="7"/>
+      <c r="D300" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E300" s="43">
+        <v>65</v>
+      </c>
+      <c r="F300" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="301" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B301" s="11"/>
+      <c r="B301" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C301" s="5"/>
-      <c r="D301" s="3"/>
-      <c r="E301" s="43"/>
-      <c r="F301" s="7"/>
+      <c r="D301" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E301" s="43">
+        <v>200</v>
+      </c>
+      <c r="F301" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="302" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B302" s="11"/>
+      <c r="B302" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C302" s="5"/>
-      <c r="D302" s="3"/>
-      <c r="E302" s="43"/>
-      <c r="F302" s="7"/>
+      <c r="D302" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E302" s="43">
+        <v>185</v>
+      </c>
+      <c r="F302" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="303" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B303" s="11"/>
+      <c r="B303" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C303" s="5"/>
-      <c r="D303" s="3"/>
-      <c r="E303" s="43"/>
-      <c r="F303" s="7"/>
+      <c r="D303" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E303" s="43">
+        <v>128.25</v>
+      </c>
+      <c r="F303" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="304" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B304" s="11"/>
+      <c r="B304" s="11" t="s">
+        <v>142</v>
+      </c>
       <c r="C304" s="5"/>
-      <c r="D304" s="3"/>
-      <c r="E304" s="43"/>
-      <c r="F304" s="7"/>
+      <c r="D304" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E304" s="43">
+        <v>410.5</v>
+      </c>
+      <c r="F304" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="305" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B305" s="11"/>
+      <c r="B305" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C305" s="5"/>
-      <c r="D305" s="3"/>
-      <c r="E305" s="43"/>
-      <c r="F305" s="7"/>
+      <c r="D305" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E305" s="43">
+        <v>1113.3</v>
+      </c>
+      <c r="F305" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="306" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B306" s="11"/>
+      <c r="B306" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C306" s="5"/>
-      <c r="D306" s="3"/>
-      <c r="E306" s="43"/>
-      <c r="F306" s="7"/>
+      <c r="D306" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E306" s="43">
+        <v>350</v>
+      </c>
+      <c r="F306" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="307" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B307" s="11"/>
+      <c r="B307" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C307" s="5"/>
-      <c r="D307" s="3"/>
-      <c r="E307" s="43"/>
-      <c r="F307" s="7"/>
+      <c r="D307" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E307" s="43">
+        <v>1509.86</v>
+      </c>
+      <c r="F307" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="308" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B308" s="11"/>
+      <c r="B308" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C308" s="5"/>
-      <c r="D308" s="3"/>
-      <c r="E308" s="43"/>
-      <c r="F308" s="7"/>
+      <c r="D308" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E308" s="43">
+        <v>2110</v>
+      </c>
+      <c r="F308" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="309" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B309" s="11"/>
+      <c r="B309" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C309" s="5"/>
-      <c r="D309" s="3"/>
-      <c r="E309" s="43"/>
-      <c r="F309" s="7"/>
+      <c r="D309" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E309" s="43">
+        <v>802</v>
+      </c>
+      <c r="F309" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="310" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B310" s="11"/>
+      <c r="B310" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C310" s="5"/>
-      <c r="D310" s="3"/>
-      <c r="E310" s="43"/>
-      <c r="F310" s="7"/>
+      <c r="D310" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E310" s="43">
+        <v>200</v>
+      </c>
+      <c r="F310" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="311" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B311" s="11"/>
+      <c r="B311" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C311" s="5"/>
-      <c r="D311" s="3"/>
-      <c r="E311" s="43"/>
-      <c r="F311" s="7"/>
+      <c r="D311" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E311" s="43">
+        <v>934</v>
+      </c>
+      <c r="F311" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="312" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B312" s="11"/>
+      <c r="B312" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C312" s="5"/>
-      <c r="D312" s="3"/>
-      <c r="E312" s="43"/>
-      <c r="F312" s="7"/>
+      <c r="D312" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E312" s="43">
+        <v>1460</v>
+      </c>
+      <c r="F312" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="313" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B313" s="11"/>
+      <c r="B313" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C313" s="5"/>
-      <c r="D313" s="3"/>
-      <c r="E313" s="43"/>
-      <c r="F313" s="7"/>
+      <c r="D313" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E313" s="43">
+        <v>3250</v>
+      </c>
+      <c r="F313" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="314" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B314" s="11"/>
+      <c r="B314" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C314" s="5"/>
-      <c r="D314" s="3"/>
-      <c r="E314" s="43"/>
-      <c r="F314" s="7"/>
+      <c r="D314" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E314" s="43">
+        <v>100</v>
+      </c>
+      <c r="F314" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="315" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B315" s="11"/>
+      <c r="B315" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C315" s="5"/>
-      <c r="D315" s="3"/>
-      <c r="E315" s="43"/>
-      <c r="F315" s="7"/>
+      <c r="D315" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E315" s="43">
+        <v>250</v>
+      </c>
+      <c r="F315" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="316" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B316" s="11"/>
+      <c r="B316" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C316" s="5"/>
-      <c r="D316" s="3"/>
-      <c r="E316" s="43"/>
-      <c r="F316" s="7"/>
+      <c r="D316" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E316" s="43">
+        <v>2096</v>
+      </c>
+      <c r="F316" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B317" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="528" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFE480CF-7CE6-44C1-B2EE-93EAF9F9936A}"/>
+  <xr:revisionPtr revIDLastSave="581" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFDF2FBC-8492-4091-98B2-99EDC29E3E6A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
+    <workbookView xWindow="28680" yWindow="2025" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2795" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2821" uniqueCount="175">
   <si>
     <t>Custo</t>
   </si>
@@ -44365,95 +44365,199 @@
       </c>
     </row>
     <row r="317" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B317" s="11"/>
+      <c r="B317" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C317" s="5"/>
-      <c r="D317" s="3"/>
-      <c r="E317" s="43"/>
-      <c r="F317" s="7"/>
+      <c r="D317" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E317" s="43">
+        <v>671</v>
+      </c>
+      <c r="F317" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="318" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B318" s="11"/>
+      <c r="B318" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C318" s="5"/>
-      <c r="D318" s="3"/>
-      <c r="E318" s="43"/>
-      <c r="F318" s="7"/>
+      <c r="D318" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E318" s="43">
+        <v>530</v>
+      </c>
+      <c r="F318" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="319" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B319" s="11"/>
+      <c r="B319" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C319" s="5"/>
-      <c r="D319" s="3"/>
-      <c r="E319" s="43"/>
-      <c r="F319" s="7"/>
+      <c r="D319" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E319" s="43">
+        <v>70</v>
+      </c>
+      <c r="F319" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="320" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B320" s="11"/>
+      <c r="B320" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C320" s="5"/>
-      <c r="D320" s="3"/>
-      <c r="E320" s="43"/>
-      <c r="F320" s="7"/>
+      <c r="D320" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E320" s="43">
+        <v>200</v>
+      </c>
+      <c r="F320" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="321" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B321" s="11"/>
+      <c r="B321" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="C321" s="5"/>
-      <c r="D321" s="3"/>
-      <c r="E321" s="43"/>
-      <c r="F321" s="7"/>
+      <c r="D321" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E321" s="43">
+        <v>1101</v>
+      </c>
+      <c r="F321" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="322" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B322" s="11"/>
+      <c r="B322" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C322" s="5"/>
-      <c r="D322" s="3"/>
-      <c r="E322" s="43"/>
-      <c r="F322" s="7"/>
+      <c r="D322" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E322" s="43">
+        <v>213.6</v>
+      </c>
+      <c r="F322" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="323" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B323" s="11"/>
+      <c r="B323" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C323" s="5"/>
-      <c r="D323" s="3"/>
-      <c r="E323" s="43"/>
-      <c r="F323" s="7"/>
+      <c r="D323" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E323" s="43">
+        <v>280</v>
+      </c>
+      <c r="F323" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="324" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B324" s="11"/>
+      <c r="B324" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C324" s="5"/>
-      <c r="D324" s="3"/>
-      <c r="E324" s="43"/>
-      <c r="F324" s="7"/>
+      <c r="D324" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E324" s="43">
+        <v>345</v>
+      </c>
+      <c r="F324" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="325" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B325" s="11"/>
+      <c r="B325" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="C325" s="5"/>
-      <c r="D325" s="3"/>
-      <c r="E325" s="43"/>
-      <c r="F325" s="7"/>
+      <c r="D325" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E325" s="43">
+        <v>288</v>
+      </c>
+      <c r="F325" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="326" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B326" s="11"/>
+      <c r="B326" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="C326" s="5"/>
-      <c r="D326" s="3"/>
-      <c r="E326" s="43"/>
-      <c r="F326" s="7"/>
+      <c r="D326" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E326" s="43">
+        <v>1335</v>
+      </c>
+      <c r="F326" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="327" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B327" s="11"/>
+      <c r="B327" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C327" s="5"/>
-      <c r="D327" s="3"/>
-      <c r="E327" s="43"/>
-      <c r="F327" s="7"/>
+      <c r="D327" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E327" s="43">
+        <v>3500</v>
+      </c>
+      <c r="F327" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="328" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B328" s="11"/>
+      <c r="B328" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C328" s="5"/>
-      <c r="D328" s="3"/>
-      <c r="E328" s="43"/>
-      <c r="F328" s="7"/>
+      <c r="D328" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E328" s="43">
+        <v>175</v>
+      </c>
+      <c r="F328" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="329" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B329" s="11"/>
+      <c r="B329" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C329" s="5"/>
-      <c r="D329" s="3"/>
-      <c r="E329" s="43"/>
-      <c r="F329" s="7"/>
+      <c r="D329" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E329" s="43">
+        <v>960</v>
+      </c>
+      <c r="F329" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="330" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B330" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="581" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFDF2FBC-8492-4091-98B2-99EDC29E3E6A}"/>
+  <xr:revisionPtr revIDLastSave="613" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{371E4FA9-A655-47FA-A8BF-0C060F3CEF65}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="2025" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2821" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2837" uniqueCount="180">
   <si>
     <t>Custo</t>
   </si>
@@ -566,6 +566,21 @@
   </si>
   <si>
     <t>NORTE FREIOS</t>
+  </si>
+  <si>
+    <t>AUTO CENTRO TUDO CAR</t>
+  </si>
+  <si>
+    <t>AO ELETRICA DO LEO</t>
+  </si>
+  <si>
+    <t>BORRACHARIA  CARGA PESADA</t>
+  </si>
+  <si>
+    <t>BORRACHARIA DO DEVIS</t>
+  </si>
+  <si>
+    <t>HIDRAUMANG</t>
   </si>
 </sst>
 </file>
@@ -44560,60 +44575,124 @@
       </c>
     </row>
     <row r="330" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B330" s="11"/>
+      <c r="B330" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C330" s="5"/>
-      <c r="D330" s="3"/>
-      <c r="E330" s="43"/>
-      <c r="F330" s="7"/>
+      <c r="D330" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E330" s="43">
+        <v>50</v>
+      </c>
+      <c r="F330" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="331" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B331" s="11"/>
+      <c r="B331" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C331" s="5"/>
-      <c r="D331" s="3"/>
-      <c r="E331" s="43"/>
-      <c r="F331" s="7"/>
+      <c r="D331" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E331" s="43">
+        <v>200</v>
+      </c>
+      <c r="F331" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="332" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B332" s="11"/>
+      <c r="B332" s="11" t="s">
+        <v>26</v>
+      </c>
       <c r="C332" s="5"/>
-      <c r="D332" s="3"/>
-      <c r="E332" s="43"/>
-      <c r="F332" s="7"/>
+      <c r="D332" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E332" s="43">
+        <v>200</v>
+      </c>
+      <c r="F332" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="333" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B333" s="11"/>
+      <c r="B333" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C333" s="5"/>
-      <c r="D333" s="3"/>
-      <c r="E333" s="43"/>
-      <c r="F333" s="7"/>
+      <c r="D333" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E333" s="43">
+        <v>161.30000000000001</v>
+      </c>
+      <c r="F333" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="334" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B334" s="11"/>
+      <c r="B334" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C334" s="5"/>
-      <c r="D334" s="3"/>
-      <c r="E334" s="43"/>
-      <c r="F334" s="7"/>
+      <c r="D334" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E334" s="43">
+        <v>110</v>
+      </c>
+      <c r="F334" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="335" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B335" s="11"/>
+      <c r="B335" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C335" s="5"/>
-      <c r="D335" s="3"/>
-      <c r="E335" s="43"/>
-      <c r="F335" s="7"/>
+      <c r="D335" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E335" s="43">
+        <v>192.2</v>
+      </c>
+      <c r="F335" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="336" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B336" s="11"/>
+      <c r="B336" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C336" s="5"/>
-      <c r="D336" s="3"/>
-      <c r="E336" s="43"/>
-      <c r="F336" s="7"/>
+      <c r="D336" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E336" s="43">
+        <v>80</v>
+      </c>
+      <c r="F336" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="337" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B337" s="11"/>
+      <c r="B337" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C337" s="5"/>
-      <c r="D337" s="3"/>
-      <c r="E337" s="43"/>
-      <c r="F337" s="7"/>
+      <c r="D337" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E337" s="43">
+        <v>30</v>
+      </c>
+      <c r="F337" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="338" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B338" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="613" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{371E4FA9-A655-47FA-A8BF-0C060F3CEF65}"/>
+  <xr:revisionPtr revIDLastSave="1109" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B71718C-E7FA-4FF4-8117-07FD318F6E2C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="2025" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2837" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3078" uniqueCount="185">
   <si>
     <t>Custo</t>
   </si>
@@ -581,6 +581,21 @@
   </si>
   <si>
     <t>HIDRAUMANG</t>
+  </si>
+  <si>
+    <t>TEJ3A51</t>
+  </si>
+  <si>
+    <t>TOTAL PARTS ACESSORIOS</t>
+  </si>
+  <si>
+    <t>TDT2D85</t>
+  </si>
+  <si>
+    <t>ELI PNEUS</t>
+  </si>
+  <si>
+    <t>bombas injetoras</t>
   </si>
 </sst>
 </file>
@@ -44695,851 +44710,1817 @@
       </c>
     </row>
     <row r="338" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B338" s="11"/>
+      <c r="B338" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C338" s="5"/>
-      <c r="D338" s="3"/>
-      <c r="E338" s="43"/>
-      <c r="F338" s="7"/>
+      <c r="D338" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E338" s="43">
+        <v>1334</v>
+      </c>
+      <c r="F338" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="339" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B339" s="11"/>
+      <c r="B339" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C339" s="5"/>
-      <c r="D339" s="3"/>
-      <c r="E339" s="43"/>
-      <c r="F339" s="7"/>
+      <c r="D339" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E339" s="43">
+        <v>2967</v>
+      </c>
+      <c r="F339" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="340" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B340" s="11"/>
+      <c r="B340" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C340" s="5"/>
-      <c r="D340" s="3"/>
-      <c r="E340" s="43"/>
-      <c r="F340" s="7"/>
+      <c r="D340" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E340" s="43">
+        <v>110</v>
+      </c>
+      <c r="F340" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="341" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B341" s="11"/>
+      <c r="B341" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C341" s="5"/>
-      <c r="D341" s="3"/>
-      <c r="E341" s="43"/>
-      <c r="F341" s="7"/>
+      <c r="D341" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E341" s="43">
+        <v>160</v>
+      </c>
+      <c r="F341" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="342" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B342" s="11"/>
+      <c r="B342" s="11" t="s">
+        <v>39</v>
+      </c>
       <c r="C342" s="5"/>
-      <c r="D342" s="3"/>
-      <c r="E342" s="43"/>
-      <c r="F342" s="7"/>
+      <c r="D342" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E342" s="43">
+        <v>80</v>
+      </c>
+      <c r="F342" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="343" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B343" s="11"/>
+      <c r="B343" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C343" s="5"/>
-      <c r="D343" s="3"/>
-      <c r="E343" s="43"/>
-      <c r="F343" s="7"/>
+      <c r="D343" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E343" s="43">
+        <v>510</v>
+      </c>
+      <c r="F343" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="344" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B344" s="11"/>
+      <c r="B344" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C344" s="5"/>
-      <c r="D344" s="3"/>
-      <c r="E344" s="43"/>
-      <c r="F344" s="7"/>
+      <c r="D344" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E344" s="43">
+        <v>520</v>
+      </c>
+      <c r="F344" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="345" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B345" s="11"/>
+      <c r="B345" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C345" s="5"/>
-      <c r="D345" s="3"/>
-      <c r="E345" s="43"/>
-      <c r="F345" s="7"/>
+      <c r="D345" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E345" s="43">
+        <v>122.94</v>
+      </c>
+      <c r="F345" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="346" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B346" s="11"/>
+      <c r="B346" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C346" s="5"/>
-      <c r="D346" s="3"/>
-      <c r="E346" s="43"/>
-      <c r="F346" s="7"/>
+      <c r="D346" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E346" s="43">
+        <v>10002</v>
+      </c>
+      <c r="F346" s="7">
+        <v>46143</v>
+      </c>
     </row>
     <row r="347" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B347" s="11"/>
+      <c r="B347" s="11" t="s">
+        <v>180</v>
+      </c>
       <c r="C347" s="5"/>
       <c r="D347" s="3"/>
-      <c r="E347" s="43"/>
-      <c r="F347" s="7"/>
+      <c r="E347" s="43">
+        <v>90</v>
+      </c>
+      <c r="F347" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="348" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B348" s="11"/>
+      <c r="B348" s="11" t="s">
+        <v>26</v>
+      </c>
       <c r="C348" s="5"/>
-      <c r="D348" s="3"/>
-      <c r="E348" s="43"/>
-      <c r="F348" s="7"/>
+      <c r="D348" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E348" s="43">
+        <v>95</v>
+      </c>
+      <c r="F348" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="349" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B349" s="11"/>
+      <c r="B349" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C349" s="5"/>
-      <c r="D349" s="3"/>
-      <c r="E349" s="43"/>
-      <c r="F349" s="7"/>
+      <c r="D349" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E349" s="43">
+        <v>100</v>
+      </c>
+      <c r="F349" s="7">
+        <v>46143</v>
+      </c>
     </row>
     <row r="350" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B350" s="11"/>
+      <c r="B350" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C350" s="5"/>
-      <c r="D350" s="3"/>
-      <c r="E350" s="43"/>
-      <c r="F350" s="7"/>
+      <c r="D350" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E350" s="43">
+        <v>200</v>
+      </c>
+      <c r="F350" s="7">
+        <v>46143</v>
+      </c>
     </row>
     <row r="351" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B351" s="11"/>
+      <c r="B351" s="11" t="s">
+        <v>10</v>
+      </c>
       <c r="C351" s="5"/>
-      <c r="D351" s="3"/>
-      <c r="E351" s="43"/>
-      <c r="F351" s="7"/>
+      <c r="D351" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E351" s="43">
+        <v>240</v>
+      </c>
+      <c r="F351" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="352" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B352" s="11"/>
+      <c r="B352" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C352" s="5"/>
-      <c r="D352" s="3"/>
-      <c r="E352" s="43"/>
-      <c r="F352" s="7"/>
+      <c r="D352" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E352" s="43">
+        <v>1010</v>
+      </c>
+      <c r="F352" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="353" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B353" s="11"/>
+      <c r="B353" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C353" s="5"/>
-      <c r="D353" s="3"/>
-      <c r="E353" s="43"/>
-      <c r="F353" s="7"/>
+      <c r="D353" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E353" s="43">
+        <v>556.6</v>
+      </c>
+      <c r="F353" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="354" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B354" s="11"/>
+      <c r="B354" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C354" s="5"/>
-      <c r="D354" s="3"/>
-      <c r="E354" s="43"/>
-      <c r="F354" s="7"/>
+      <c r="D354" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E354" s="43">
+        <v>185</v>
+      </c>
+      <c r="F354" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="355" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B355" s="11"/>
+      <c r="B355" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C355" s="5"/>
-      <c r="D355" s="3"/>
-      <c r="E355" s="43"/>
-      <c r="F355" s="7"/>
+      <c r="D355" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E355" s="43">
+        <v>140</v>
+      </c>
+      <c r="F355" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="356" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B356" s="11"/>
+      <c r="B356" s="11" t="s">
+        <v>182</v>
+      </c>
       <c r="C356" s="5"/>
-      <c r="D356" s="3"/>
-      <c r="E356" s="43"/>
-      <c r="F356" s="7"/>
+      <c r="D356" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E356" s="43">
+        <v>30</v>
+      </c>
+      <c r="F356" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="357" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B357" s="11"/>
+      <c r="B357" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="C357" s="5"/>
-      <c r="D357" s="3"/>
-      <c r="E357" s="43"/>
-      <c r="F357" s="7"/>
+      <c r="D357" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E357" s="43">
+        <v>1020</v>
+      </c>
+      <c r="F357" s="7">
+        <v>46143</v>
+      </c>
     </row>
     <row r="358" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B358" s="11"/>
+      <c r="B358" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="C358" s="5"/>
-      <c r="D358" s="3"/>
-      <c r="E358" s="43"/>
-      <c r="F358" s="7"/>
+      <c r="D358" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E358" s="43">
+        <v>1123</v>
+      </c>
+      <c r="F358" s="7">
+        <v>46143</v>
+      </c>
     </row>
     <row r="359" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B359" s="11"/>
+      <c r="B359" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C359" s="5"/>
-      <c r="D359" s="3"/>
-      <c r="E359" s="43"/>
-      <c r="F359" s="7"/>
+      <c r="D359" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E359" s="43">
+        <v>971</v>
+      </c>
+      <c r="F359" s="7">
+        <v>46143</v>
+      </c>
     </row>
     <row r="360" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B360" s="11"/>
+      <c r="B360" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C360" s="5"/>
-      <c r="D360" s="3"/>
-      <c r="E360" s="43"/>
-      <c r="F360" s="7"/>
+      <c r="D360" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E360" s="43">
+        <v>295</v>
+      </c>
+      <c r="F360" s="7">
+        <v>46143</v>
+      </c>
     </row>
     <row r="361" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B361" s="11"/>
+      <c r="B361" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C361" s="5"/>
-      <c r="D361" s="3"/>
-      <c r="E361" s="43"/>
-      <c r="F361" s="7"/>
+      <c r="D361" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E361" s="43">
+        <v>2858</v>
+      </c>
+      <c r="F361" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="362" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B362" s="11"/>
+      <c r="B362" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C362" s="5"/>
-      <c r="D362" s="3"/>
-      <c r="E362" s="43"/>
-      <c r="F362" s="7"/>
+      <c r="D362" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E362" s="43">
+        <v>2150</v>
+      </c>
+      <c r="F362" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="363" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B363" s="11"/>
+      <c r="B363" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C363" s="5"/>
-      <c r="D363" s="3"/>
-      <c r="E363" s="43"/>
-      <c r="F363" s="7"/>
+      <c r="D363" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E363" s="43">
+        <v>100</v>
+      </c>
+      <c r="F363" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="364" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B364" s="11"/>
+      <c r="B364" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C364" s="5"/>
-      <c r="D364" s="3"/>
-      <c r="E364" s="43"/>
-      <c r="F364" s="7"/>
+      <c r="D364" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E364" s="43">
+        <v>370</v>
+      </c>
+      <c r="F364" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="365" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B365" s="11"/>
+      <c r="B365" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C365" s="5"/>
-      <c r="D365" s="3"/>
-      <c r="E365" s="43"/>
-      <c r="F365" s="7"/>
+      <c r="D365" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E365" s="43">
+        <v>1870</v>
+      </c>
+      <c r="F365" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="366" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B366" s="11"/>
+      <c r="B366" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C366" s="5"/>
-      <c r="D366" s="3"/>
-      <c r="E366" s="43"/>
-      <c r="F366" s="7"/>
+      <c r="D366" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E366" s="43">
+        <v>870</v>
+      </c>
+      <c r="F366" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="367" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B367" s="11"/>
+      <c r="B367" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C367" s="5"/>
-      <c r="D367" s="3"/>
-      <c r="E367" s="43"/>
-      <c r="F367" s="7"/>
+      <c r="D367" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E367" s="43">
+        <v>303</v>
+      </c>
+      <c r="F367" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="368" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B368" s="11"/>
+      <c r="B368" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C368" s="5"/>
-      <c r="D368" s="3"/>
-      <c r="E368" s="43"/>
-      <c r="F368" s="7"/>
+      <c r="D368" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E368" s="43">
+        <v>250</v>
+      </c>
+      <c r="F368" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="369" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B369" s="11"/>
+      <c r="B369" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C369" s="5"/>
-      <c r="D369" s="3"/>
-      <c r="E369" s="43"/>
-      <c r="F369" s="7"/>
+      <c r="D369" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E369" s="43">
+        <v>308.7</v>
+      </c>
+      <c r="F369" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="370" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B370" s="11"/>
+      <c r="B370" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C370" s="5"/>
-      <c r="D370" s="3"/>
-      <c r="E370" s="43"/>
-      <c r="F370" s="7"/>
+      <c r="D370" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E370" s="43">
+        <v>460</v>
+      </c>
+      <c r="F370" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="371" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B371" s="11"/>
+      <c r="B371" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C371" s="5"/>
-      <c r="D371" s="3"/>
-      <c r="E371" s="43"/>
-      <c r="F371" s="7"/>
+      <c r="D371" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E371" s="43">
+        <v>938.9</v>
+      </c>
+      <c r="F371" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="372" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B372" s="11"/>
+      <c r="B372" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C372" s="5"/>
-      <c r="D372" s="3"/>
-      <c r="E372" s="43"/>
-      <c r="F372" s="7"/>
+      <c r="D372" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E372" s="43">
+        <v>638.25</v>
+      </c>
+      <c r="F372" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="373" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B373" s="11"/>
+      <c r="B373" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C373" s="5"/>
-      <c r="D373" s="3"/>
-      <c r="E373" s="43"/>
-      <c r="F373" s="7"/>
+      <c r="D373" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E373" s="43">
+        <v>185</v>
+      </c>
+      <c r="F373" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="374" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B374" s="11"/>
+      <c r="B374" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C374" s="5"/>
-      <c r="D374" s="3"/>
-      <c r="E374" s="43"/>
-      <c r="F374" s="7"/>
+      <c r="D374" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E374" s="43">
+        <v>1863.5</v>
+      </c>
+      <c r="F374" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="375" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B375" s="11"/>
+      <c r="B375" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C375" s="5"/>
-      <c r="D375" s="3"/>
-      <c r="E375" s="43"/>
-      <c r="F375" s="7"/>
+      <c r="D375" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E375" s="43">
+        <v>65</v>
+      </c>
+      <c r="F375" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="376" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B376" s="11"/>
+      <c r="B376" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C376" s="5"/>
-      <c r="D376" s="3"/>
-      <c r="E376" s="43"/>
-      <c r="F376" s="7"/>
+      <c r="D376" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E376" s="43">
+        <v>238.8</v>
+      </c>
+      <c r="F376" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="377" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B377" s="11"/>
+      <c r="B377" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C377" s="5"/>
-      <c r="D377" s="3"/>
-      <c r="E377" s="43"/>
-      <c r="F377" s="7"/>
+      <c r="D377" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E377" s="43">
+        <v>580</v>
+      </c>
+      <c r="F377" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="378" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B378" s="11"/>
+      <c r="B378" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C378" s="5"/>
-      <c r="D378" s="3"/>
-      <c r="E378" s="43"/>
-      <c r="F378" s="7"/>
+      <c r="D378" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E378" s="43">
+        <v>16</v>
+      </c>
+      <c r="F378" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="379" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B379" s="11"/>
+      <c r="B379" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C379" s="5"/>
-      <c r="D379" s="3"/>
-      <c r="E379" s="43"/>
-      <c r="F379" s="7"/>
+      <c r="D379" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E379" s="43">
+        <v>16</v>
+      </c>
+      <c r="F379" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="380" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B380" s="11"/>
+      <c r="B380" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C380" s="5"/>
-      <c r="D380" s="3"/>
-      <c r="E380" s="43"/>
-      <c r="F380" s="7"/>
+      <c r="D380" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E380" s="43">
+        <v>971</v>
+      </c>
+      <c r="F380" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="381" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B381" s="11"/>
+      <c r="B381" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C381" s="5"/>
-      <c r="D381" s="3"/>
-      <c r="E381" s="43"/>
-      <c r="F381" s="7"/>
+      <c r="D381" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E381" s="43">
+        <v>28</v>
+      </c>
+      <c r="F381" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="382" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B382" s="11"/>
+      <c r="B382" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C382" s="5"/>
-      <c r="D382" s="3"/>
-      <c r="E382" s="43"/>
-      <c r="F382" s="7"/>
+      <c r="D382" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E382" s="43">
+        <v>140</v>
+      </c>
+      <c r="F382" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="383" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B383" s="11"/>
+      <c r="B383" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="C383" s="5"/>
-      <c r="D383" s="3"/>
-      <c r="E383" s="43"/>
-      <c r="F383" s="7"/>
+      <c r="D383" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E383" s="43">
+        <v>203</v>
+      </c>
+      <c r="F383" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="384" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B384" s="11"/>
+      <c r="B384" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="C384" s="5"/>
-      <c r="D384" s="3"/>
-      <c r="E384" s="43"/>
-      <c r="F384" s="7"/>
+      <c r="D384" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E384" s="43">
+        <v>487</v>
+      </c>
+      <c r="F384" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="385" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B385" s="11"/>
+      <c r="B385" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C385" s="5"/>
-      <c r="D385" s="3"/>
-      <c r="E385" s="43"/>
-      <c r="F385" s="7"/>
+      <c r="D385" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E385" s="43">
+        <v>651.54999999999995</v>
+      </c>
+      <c r="F385" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="386" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B386" s="11"/>
+      <c r="B386" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C386" s="5"/>
-      <c r="D386" s="3"/>
-      <c r="E386" s="43"/>
-      <c r="F386" s="7"/>
+      <c r="D386" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E386" s="43">
+        <v>100</v>
+      </c>
+      <c r="F386" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="387" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B387" s="11"/>
+      <c r="B387" s="11" t="s">
+        <v>14</v>
+      </c>
       <c r="C387" s="5"/>
-      <c r="D387" s="3"/>
-      <c r="E387" s="43"/>
-      <c r="F387" s="7"/>
+      <c r="D387" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E387" s="43">
+        <v>40</v>
+      </c>
+      <c r="F387" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="388" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B388" s="11"/>
+      <c r="B388" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="C388" s="5"/>
-      <c r="D388" s="3"/>
-      <c r="E388" s="43"/>
-      <c r="F388" s="7"/>
+      <c r="D388" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E388" s="43">
+        <v>643</v>
+      </c>
+      <c r="F388" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="389" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B389" s="11"/>
+      <c r="B389" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="C389" s="5"/>
-      <c r="D389" s="3"/>
-      <c r="E389" s="43"/>
-      <c r="F389" s="7"/>
+      <c r="D389" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E389" s="43">
+        <v>881</v>
+      </c>
+      <c r="F389" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="390" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B390" s="11"/>
+      <c r="B390" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C390" s="5"/>
-      <c r="D390" s="3"/>
-      <c r="E390" s="43"/>
-      <c r="F390" s="7"/>
+      <c r="D390" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E390" s="43">
+        <v>387</v>
+      </c>
+      <c r="F390" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="391" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B391" s="11"/>
+      <c r="B391" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C391" s="5"/>
-      <c r="D391" s="3"/>
-      <c r="E391" s="43"/>
-      <c r="F391" s="7"/>
+      <c r="D391" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E391" s="43">
+        <v>483.6</v>
+      </c>
+      <c r="F391" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="392" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B392" s="11"/>
+      <c r="B392" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C392" s="5"/>
-      <c r="D392" s="3"/>
-      <c r="E392" s="43"/>
-      <c r="F392" s="7"/>
+      <c r="D392" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E392" s="43">
+        <v>80</v>
+      </c>
+      <c r="F392" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="393" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B393" s="11"/>
+      <c r="B393" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C393" s="5"/>
-      <c r="D393" s="3"/>
-      <c r="E393" s="43"/>
-      <c r="F393" s="7"/>
+      <c r="D393" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E393" s="43">
+        <v>148</v>
+      </c>
+      <c r="F393" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="394" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B394" s="11"/>
+      <c r="B394" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C394" s="5"/>
-      <c r="D394" s="3"/>
-      <c r="E394" s="43"/>
-      <c r="F394" s="7"/>
+      <c r="D394" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E394" s="43">
+        <v>248</v>
+      </c>
+      <c r="F394" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="395" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B395" s="11"/>
+      <c r="B395" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C395" s="5"/>
-      <c r="D395" s="3"/>
-      <c r="E395" s="43"/>
-      <c r="F395" s="7"/>
+      <c r="D395" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E395" s="43">
+        <v>38</v>
+      </c>
+      <c r="F395" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="396" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B396" s="11"/>
+      <c r="B396" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C396" s="5"/>
-      <c r="D396" s="3"/>
-      <c r="E396" s="43"/>
-      <c r="F396" s="7"/>
+      <c r="D396" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E396" s="43">
+        <v>1355</v>
+      </c>
+      <c r="F396" s="7">
+        <v>46143</v>
+      </c>
     </row>
     <row r="397" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B397" s="11"/>
+      <c r="B397" s="11" t="s">
+        <v>7</v>
+      </c>
       <c r="C397" s="5"/>
-      <c r="D397" s="3"/>
-      <c r="E397" s="43"/>
-      <c r="F397" s="7"/>
+      <c r="D397" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E397" s="43">
+        <v>250</v>
+      </c>
+      <c r="F397" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="398" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B398" s="11"/>
+      <c r="B398" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C398" s="5"/>
-      <c r="D398" s="3"/>
-      <c r="E398" s="43"/>
-      <c r="F398" s="7"/>
+      <c r="D398" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E398" s="43">
+        <v>1393</v>
+      </c>
+      <c r="F398" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="399" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B399" s="11"/>
+      <c r="B399" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C399" s="5"/>
-      <c r="D399" s="3"/>
-      <c r="E399" s="43"/>
-      <c r="F399" s="7"/>
+      <c r="D399" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E399" s="43">
+        <v>4</v>
+      </c>
+      <c r="F399" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="400" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B400" s="11"/>
+      <c r="B400" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C400" s="5"/>
-      <c r="D400" s="3"/>
-      <c r="E400" s="43"/>
-      <c r="F400" s="7"/>
+      <c r="D400" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E400" s="43">
+        <v>690</v>
+      </c>
+      <c r="F400" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="401" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B401" s="11"/>
+      <c r="B401" s="11" t="s">
+        <v>10</v>
+      </c>
       <c r="C401" s="5"/>
-      <c r="D401" s="3"/>
-      <c r="E401" s="43"/>
-      <c r="F401" s="7"/>
+      <c r="D401" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E401" s="43">
+        <v>1620</v>
+      </c>
+      <c r="F401" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="402" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B402" s="11"/>
+      <c r="B402" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C402" s="5"/>
-      <c r="D402" s="3"/>
-      <c r="E402" s="43"/>
-      <c r="F402" s="7"/>
+      <c r="D402" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E402" s="43">
+        <v>145</v>
+      </c>
+      <c r="F402" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="403" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B403" s="11"/>
+      <c r="B403" s="11" t="s">
+        <v>23</v>
+      </c>
       <c r="C403" s="5"/>
-      <c r="D403" s="3"/>
-      <c r="E403" s="43"/>
-      <c r="F403" s="7"/>
+      <c r="D403" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E403" s="43">
+        <v>120</v>
+      </c>
+      <c r="F403" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="404" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B404" s="11"/>
+      <c r="B404" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C404" s="5"/>
-      <c r="D404" s="3"/>
-      <c r="E404" s="43"/>
-      <c r="F404" s="7"/>
+      <c r="D404" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E404" s="43">
+        <v>100</v>
+      </c>
+      <c r="F404" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="405" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B405" s="11"/>
+      <c r="B405" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C405" s="5"/>
-      <c r="D405" s="3"/>
-      <c r="E405" s="43"/>
-      <c r="F405" s="7"/>
+      <c r="D405" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E405" s="43">
+        <v>195</v>
+      </c>
+      <c r="F405" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="406" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B406" s="11"/>
+      <c r="B406" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C406" s="5"/>
-      <c r="D406" s="3"/>
-      <c r="E406" s="43"/>
-      <c r="F406" s="7"/>
+      <c r="D406" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E406" s="43">
+        <v>200</v>
+      </c>
+      <c r="F406" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="407" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B407" s="11"/>
+      <c r="B407" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C407" s="5"/>
-      <c r="D407" s="3"/>
-      <c r="E407" s="43"/>
-      <c r="F407" s="7"/>
+      <c r="D407" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E407" s="43">
+        <v>220.2</v>
+      </c>
+      <c r="F407" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="408" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B408" s="11"/>
+      <c r="B408" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C408" s="5"/>
-      <c r="D408" s="3"/>
-      <c r="E408" s="43"/>
-      <c r="F408" s="7"/>
+      <c r="D408" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E408" s="43">
+        <v>460</v>
+      </c>
+      <c r="F408" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="409" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B409" s="11"/>
+      <c r="B409" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C409" s="5"/>
-      <c r="D409" s="3"/>
-      <c r="E409" s="43"/>
-      <c r="F409" s="7"/>
+      <c r="D409" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E409" s="43">
+        <v>280</v>
+      </c>
+      <c r="F409" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="410" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B410" s="11"/>
+      <c r="B410" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C410" s="5"/>
-      <c r="D410" s="3"/>
-      <c r="E410" s="43"/>
-      <c r="F410" s="7"/>
+      <c r="D410" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E410" s="43">
+        <v>470</v>
+      </c>
+      <c r="F410" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="411" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B411" s="11"/>
+      <c r="B411" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C411" s="5"/>
-      <c r="D411" s="3"/>
-      <c r="E411" s="43"/>
-      <c r="F411" s="7"/>
+      <c r="D411" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E411" s="43">
+        <v>1770</v>
+      </c>
+      <c r="F411" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="412" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B412" s="11"/>
+      <c r="B412" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C412" s="5"/>
-      <c r="D412" s="3"/>
-      <c r="E412" s="43"/>
-      <c r="F412" s="7"/>
+      <c r="D412" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E412" s="43">
+        <v>220</v>
+      </c>
+      <c r="F412" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="413" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B413" s="11"/>
+      <c r="B413" s="11" t="s">
+        <v>13</v>
+      </c>
       <c r="C413" s="5"/>
-      <c r="D413" s="3"/>
-      <c r="E413" s="43"/>
-      <c r="F413" s="7"/>
+      <c r="D413" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E413" s="43">
+        <v>380</v>
+      </c>
+      <c r="F413" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="414" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B414" s="11"/>
+      <c r="B414" s="11" t="s">
+        <v>8</v>
+      </c>
       <c r="C414" s="5"/>
-      <c r="D414" s="3"/>
-      <c r="E414" s="43"/>
-      <c r="F414" s="7"/>
+      <c r="D414" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E414" s="43">
+        <v>150</v>
+      </c>
+      <c r="F414" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="415" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B415" s="11"/>
+      <c r="B415" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C415" s="5"/>
-      <c r="D415" s="3"/>
-      <c r="E415" s="43"/>
-      <c r="F415" s="7"/>
+      <c r="D415" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E415" s="43">
+        <v>189</v>
+      </c>
+      <c r="F415" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="416" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B416" s="11"/>
+      <c r="B416" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C416" s="5"/>
-      <c r="D416" s="3"/>
-      <c r="E416" s="43"/>
-      <c r="F416" s="7"/>
+      <c r="D416" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E416" s="43">
+        <v>75</v>
+      </c>
+      <c r="F416" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="417" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B417" s="11"/>
+      <c r="B417" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C417" s="5"/>
-      <c r="D417" s="3"/>
-      <c r="E417" s="43"/>
-      <c r="F417" s="7"/>
+      <c r="D417" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E417" s="43">
+        <v>50</v>
+      </c>
+      <c r="F417" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="418" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B418" s="11"/>
+      <c r="B418" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C418" s="5"/>
-      <c r="D418" s="3"/>
-      <c r="E418" s="43"/>
-      <c r="F418" s="7"/>
+      <c r="D418" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E418" s="43">
+        <v>154</v>
+      </c>
+      <c r="F418" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="419" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B419" s="11"/>
+      <c r="B419" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C419" s="5"/>
-      <c r="D419" s="3"/>
-      <c r="E419" s="43"/>
-      <c r="F419" s="7"/>
+      <c r="D419" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E419" s="43">
+        <v>1066</v>
+      </c>
+      <c r="F419" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="420" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B420" s="11"/>
+      <c r="B420" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C420" s="5"/>
-      <c r="D420" s="3"/>
-      <c r="E420" s="43"/>
-      <c r="F420" s="7"/>
+      <c r="D420" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E420" s="43">
+        <v>500</v>
+      </c>
+      <c r="F420" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="421" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B421" s="11"/>
+      <c r="B421" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C421" s="5"/>
-      <c r="D421" s="3"/>
-      <c r="E421" s="43"/>
-      <c r="F421" s="7"/>
+      <c r="D421" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E421" s="43">
+        <v>120</v>
+      </c>
+      <c r="F421" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="422" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B422" s="11"/>
+      <c r="B422" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C422" s="5"/>
-      <c r="D422" s="3"/>
-      <c r="E422" s="43"/>
-      <c r="F422" s="7"/>
+      <c r="D422" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E422" s="43">
+        <v>240</v>
+      </c>
+      <c r="F422" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="423" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B423" s="11"/>
+      <c r="B423" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C423" s="5"/>
-      <c r="D423" s="3"/>
-      <c r="E423" s="43"/>
-      <c r="F423" s="7"/>
+      <c r="D423" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E423" s="43">
+        <v>80</v>
+      </c>
+      <c r="F423" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="424" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B424" s="11"/>
+      <c r="B424" s="11" t="s">
+        <v>10</v>
+      </c>
       <c r="C424" s="5"/>
-      <c r="D424" s="3"/>
-      <c r="E424" s="43"/>
-      <c r="F424" s="7"/>
+      <c r="D424" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E424" s="43">
+        <v>70</v>
+      </c>
+      <c r="F424" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="425" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B425" s="11"/>
+      <c r="B425" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C425" s="5"/>
-      <c r="D425" s="3"/>
-      <c r="E425" s="43"/>
-      <c r="F425" s="7"/>
+      <c r="D425" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E425" s="43">
+        <v>73</v>
+      </c>
+      <c r="F425" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="426" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B426" s="11"/>
+      <c r="B426" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="C426" s="5"/>
-      <c r="D426" s="3"/>
-      <c r="E426" s="43"/>
-      <c r="F426" s="7"/>
+      <c r="D426" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E426" s="43">
+        <v>200</v>
+      </c>
+      <c r="F426" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="427" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B427" s="11"/>
+      <c r="B427" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C427" s="5"/>
-      <c r="D427" s="3"/>
-      <c r="E427" s="43"/>
-      <c r="F427" s="7"/>
+      <c r="D427" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E427" s="43">
+        <v>510</v>
+      </c>
+      <c r="F427" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="428" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B428" s="11"/>
+      <c r="B428" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C428" s="5"/>
-      <c r="D428" s="3"/>
-      <c r="E428" s="43"/>
-      <c r="F428" s="7"/>
+      <c r="D428" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E428" s="43">
+        <v>6243.77</v>
+      </c>
+      <c r="F428" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="429" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B429" s="11"/>
+      <c r="B429" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C429" s="5"/>
-      <c r="D429" s="3"/>
-      <c r="E429" s="43"/>
-      <c r="F429" s="7"/>
+      <c r="D429" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E429" s="43">
+        <v>2131.3000000000002</v>
+      </c>
+      <c r="F429" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="430" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B430" s="11"/>
+      <c r="B430" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C430" s="5"/>
-      <c r="D430" s="3"/>
-      <c r="E430" s="43"/>
-      <c r="F430" s="7"/>
+      <c r="D430" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E430" s="43">
+        <v>1510</v>
+      </c>
+      <c r="F430" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="431" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B431" s="11"/>
+      <c r="B431" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C431" s="5"/>
-      <c r="D431" s="3"/>
-      <c r="E431" s="43"/>
-      <c r="F431" s="7"/>
+      <c r="D431" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E431" s="43">
+        <v>80</v>
+      </c>
+      <c r="F431" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="432" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B432" s="11"/>
+      <c r="B432" s="11" t="s">
+        <v>34</v>
+      </c>
       <c r="C432" s="5"/>
-      <c r="D432" s="3"/>
-      <c r="E432" s="43"/>
-      <c r="F432" s="7"/>
+      <c r="D432" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E432" s="43">
+        <v>144</v>
+      </c>
+      <c r="F432" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="433" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B433" s="11"/>
+      <c r="B433" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C433" s="5"/>
-      <c r="D433" s="3"/>
-      <c r="E433" s="43"/>
-      <c r="F433" s="7"/>
+      <c r="D433" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E433" s="43">
+        <v>200</v>
+      </c>
+      <c r="F433" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="434" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B434" s="11"/>
+      <c r="B434" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C434" s="5"/>
-      <c r="D434" s="3"/>
-      <c r="E434" s="43"/>
-      <c r="F434" s="7"/>
+      <c r="D434" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E434" s="43">
+        <v>800</v>
+      </c>
+      <c r="F434" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="435" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B435" s="11"/>
+      <c r="B435" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C435" s="5"/>
-      <c r="D435" s="3"/>
-      <c r="E435" s="43"/>
-      <c r="F435" s="7"/>
+      <c r="D435" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E435" s="43">
+        <v>50</v>
+      </c>
+      <c r="F435" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="436" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B436" s="11"/>
+      <c r="B436" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C436" s="5"/>
-      <c r="D436" s="3"/>
-      <c r="E436" s="43"/>
-      <c r="F436" s="7"/>
+      <c r="D436" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E436" s="43">
+        <v>3500</v>
+      </c>
+      <c r="F436" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="437" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B437" s="11"/>
+      <c r="B437" s="11" t="s">
+        <v>82</v>
+      </c>
       <c r="C437" s="5"/>
-      <c r="D437" s="3"/>
-      <c r="E437" s="43"/>
-      <c r="F437" s="7"/>
+      <c r="D437" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E437" s="43">
+        <v>3250</v>
+      </c>
+      <c r="F437" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="438" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B438" s="11"/>
+      <c r="B438" s="11" t="s">
+        <v>25</v>
+      </c>
       <c r="C438" s="5"/>
-      <c r="D438" s="3"/>
-      <c r="E438" s="43"/>
-      <c r="F438" s="7"/>
+      <c r="D438" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E438" s="43">
+        <v>35</v>
+      </c>
+      <c r="F438" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="439" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B439" s="11"/>
+      <c r="B439" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C439" s="5"/>
-      <c r="D439" s="3"/>
-      <c r="E439" s="43"/>
-      <c r="F439" s="7"/>
+      <c r="D439" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E439" s="43">
+        <v>175</v>
+      </c>
+      <c r="F439" s="7">
+        <v>46082</v>
+      </c>
     </row>
     <row r="440" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B440" s="11"/>
+      <c r="B440" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C440" s="5"/>
-      <c r="D440" s="3"/>
-      <c r="E440" s="43"/>
-      <c r="F440" s="7"/>
+      <c r="D440" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E440" s="43">
+        <v>847</v>
+      </c>
+      <c r="F440" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="441" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B441" s="11"/>
+      <c r="B441" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="C441" s="5"/>
-      <c r="D441" s="3"/>
-      <c r="E441" s="43"/>
-      <c r="F441" s="7"/>
+      <c r="D441" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E441" s="43">
+        <v>302</v>
+      </c>
+      <c r="F441" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="442" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B442" s="11"/>
+      <c r="B442" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="C442" s="5"/>
-      <c r="D442" s="3"/>
-      <c r="E442" s="43"/>
-      <c r="F442" s="7"/>
+      <c r="D442" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E442" s="43">
+        <v>730</v>
+      </c>
+      <c r="F442" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="443" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B443" s="11"/>
+      <c r="B443" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C443" s="5"/>
-      <c r="D443" s="3"/>
-      <c r="E443" s="43"/>
-      <c r="F443" s="7"/>
+      <c r="D443" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E443" s="43">
+        <v>215</v>
+      </c>
+      <c r="F443" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="444" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B444" s="11"/>
+      <c r="B444" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C444" s="5"/>
-      <c r="D444" s="3"/>
-      <c r="E444" s="43"/>
-      <c r="F444" s="7"/>
+      <c r="D444" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E444" s="43">
+        <v>170</v>
+      </c>
+      <c r="F444" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="445" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B445" s="11"/>
+      <c r="B445" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="C445" s="5"/>
-      <c r="D445" s="3"/>
-      <c r="E445" s="43"/>
-      <c r="F445" s="7"/>
+      <c r="D445" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E445" s="43">
+        <v>50</v>
+      </c>
+      <c r="F445" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="446" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B446" s="11"/>
+      <c r="B446" s="11" t="s">
+        <v>117</v>
+      </c>
       <c r="C446" s="5"/>
-      <c r="D446" s="3"/>
-      <c r="E446" s="43"/>
-      <c r="F446" s="7"/>
+      <c r="D446" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E446" s="43">
+        <v>55</v>
+      </c>
+      <c r="F446" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="447" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B447" s="11"/>
+      <c r="B447" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C447" s="5"/>
-      <c r="D447" s="3"/>
-      <c r="E447" s="43"/>
-      <c r="F447" s="7"/>
+      <c r="D447" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E447" s="43">
+        <v>1141</v>
+      </c>
+      <c r="F447" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="448" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B448" s="11"/>
+      <c r="B448" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C448" s="5"/>
-      <c r="D448" s="3"/>
-      <c r="E448" s="43"/>
-      <c r="F448" s="7"/>
+      <c r="D448" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E448" s="43">
+        <v>500</v>
+      </c>
+      <c r="F448" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="449" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B449" s="11"/>
+      <c r="B449" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C449" s="5"/>
-      <c r="D449" s="3"/>
-      <c r="E449" s="43"/>
-      <c r="F449" s="7"/>
+      <c r="D449" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E449" s="43">
+        <v>300</v>
+      </c>
+      <c r="F449" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="450" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B450" s="11"/>
+      <c r="B450" s="11" t="s">
+        <v>29</v>
+      </c>
       <c r="C450" s="5"/>
-      <c r="D450" s="3"/>
-      <c r="E450" s="43"/>
-      <c r="F450" s="7"/>
+      <c r="D450" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E450" s="43">
+        <v>40</v>
+      </c>
+      <c r="F450" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="451" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B451" s="11"/>
+      <c r="B451" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="C451" s="5"/>
-      <c r="D451" s="3"/>
-      <c r="E451" s="43"/>
-      <c r="F451" s="7"/>
+      <c r="D451" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E451" s="43">
+        <v>200</v>
+      </c>
+      <c r="F451" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="452" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B452" s="11"/>
+      <c r="B452" s="11" t="s">
+        <v>5</v>
+      </c>
       <c r="C452" s="5"/>
-      <c r="D452" s="3"/>
-      <c r="E452" s="43"/>
-      <c r="F452" s="7"/>
+      <c r="D452" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E452" s="43">
+        <v>100</v>
+      </c>
+      <c r="F452" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="453" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B453" s="11"/>
+      <c r="B453" s="11" t="s">
+        <v>24</v>
+      </c>
       <c r="C453" s="5"/>
-      <c r="D453" s="3"/>
-      <c r="E453" s="43"/>
-      <c r="F453" s="7"/>
+      <c r="D453" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E453" s="43">
+        <v>1449</v>
+      </c>
+      <c r="F453" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="454" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B454" s="11"/>
+      <c r="B454" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C454" s="5"/>
-      <c r="D454" s="3"/>
-      <c r="E454" s="43"/>
-      <c r="F454" s="7"/>
+      <c r="D454" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E454" s="43">
+        <v>750</v>
+      </c>
+      <c r="F454" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="455" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B455" s="11"/>
+      <c r="B455" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C455" s="5"/>
-      <c r="D455" s="3"/>
-      <c r="E455" s="43"/>
-      <c r="F455" s="7"/>
+      <c r="D455" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E455" s="43">
+        <v>1130</v>
+      </c>
+      <c r="F455" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="456" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B456" s="11"/>
+      <c r="B456" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C456" s="5"/>
-      <c r="D456" s="3"/>
-      <c r="E456" s="43"/>
-      <c r="F456" s="7"/>
+      <c r="D456" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E456" s="43">
+        <v>650</v>
+      </c>
+      <c r="F456" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="457" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B457" s="11"/>
+      <c r="B457" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C457" s="5"/>
-      <c r="D457" s="3"/>
-      <c r="E457" s="43"/>
-      <c r="F457" s="7"/>
+      <c r="D457" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E457" s="43">
+        <v>350</v>
+      </c>
+      <c r="F457" s="7">
+        <v>46143</v>
+      </c>
     </row>
     <row r="458" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B458" s="11"/>
+      <c r="B458" s="11" t="s">
+        <v>3</v>
+      </c>
       <c r="C458" s="5"/>
-      <c r="D458" s="3"/>
-      <c r="E458" s="43"/>
-      <c r="F458" s="7"/>
+      <c r="D458" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E458" s="43">
+        <v>3912</v>
+      </c>
+      <c r="F458" s="7">
+        <v>46143</v>
+      </c>
     </row>
     <row r="459" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B459" s="11"/>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1109" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B71718C-E7FA-4FF4-8117-07FD318F6E2C}"/>
+  <xr:revisionPtr revIDLastSave="1115" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A6139DC-8521-4607-961A-5B98739BE878}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="2025" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3078" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3078" uniqueCount="183">
   <si>
     <t>Custo</t>
   </si>
@@ -487,9 +487,6 @@
     <t>NOVA FREIOS E PEÇAS</t>
   </si>
   <si>
-    <t>PNEUS MAX</t>
-  </si>
-  <si>
     <t>LONAS VINIFORTE</t>
   </si>
   <si>
@@ -506,9 +503,6 @@
   </si>
   <si>
     <t>SILVA CARROCERIA</t>
-  </si>
-  <si>
-    <t>PNEU MAX</t>
   </si>
   <si>
     <t>BORRACHARIA NITEROI</t>
@@ -41132,7 +41126,7 @@
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="E99" s="43">
         <v>505</v>
@@ -41192,7 +41186,7 @@
       </c>
       <c r="C103" s="5"/>
       <c r="D103" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E103" s="43">
         <v>170</v>
@@ -41207,7 +41201,7 @@
       </c>
       <c r="C104" s="5"/>
       <c r="D104" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E104" s="43">
         <v>416</v>
@@ -41222,7 +41216,7 @@
       </c>
       <c r="C105" s="5"/>
       <c r="D105" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E105" s="43">
         <v>1100</v>
@@ -41248,11 +41242,11 @@
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B107" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C107" s="5"/>
       <c r="D107" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E107" s="20">
         <v>1590</v>
@@ -41297,7 +41291,7 @@
       </c>
       <c r="C110" s="5"/>
       <c r="D110" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E110" s="43">
         <v>2735.31</v>
@@ -41657,7 +41651,7 @@
       </c>
       <c r="C134" s="5"/>
       <c r="D134" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E134" s="43">
         <v>310</v>
@@ -41672,7 +41666,7 @@
       </c>
       <c r="C135" s="5"/>
       <c r="D135" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E135" s="43">
         <v>1350</v>
@@ -41687,7 +41681,7 @@
       </c>
       <c r="C136" s="5"/>
       <c r="D136" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E136" s="43">
         <v>190</v>
@@ -41702,7 +41696,7 @@
       </c>
       <c r="C137" s="5"/>
       <c r="D137" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E137" s="43">
         <v>720</v>
@@ -41717,7 +41711,7 @@
       </c>
       <c r="C138" s="5"/>
       <c r="D138" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E138" s="43">
         <v>160</v>
@@ -41732,7 +41726,7 @@
       </c>
       <c r="C139" s="5"/>
       <c r="D139" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E139" s="43">
         <v>180</v>
@@ -41747,7 +41741,7 @@
       </c>
       <c r="C140" s="5"/>
       <c r="D140" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E140" s="43">
         <v>2710</v>
@@ -42032,7 +42026,7 @@
       </c>
       <c r="C159" s="5"/>
       <c r="D159" s="3" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="E159" s="43">
         <v>1508</v>
@@ -42062,7 +42056,7 @@
       </c>
       <c r="C161" s="5"/>
       <c r="D161" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E161" s="43">
         <v>30</v>
@@ -42077,7 +42071,7 @@
       </c>
       <c r="C162" s="5"/>
       <c r="D162" s="3" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="E162" s="43">
         <v>3635</v>
@@ -42092,7 +42086,7 @@
       </c>
       <c r="C163" s="5"/>
       <c r="D163" s="3" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="E163" s="43">
         <v>4200</v>
@@ -42107,7 +42101,7 @@
       </c>
       <c r="C164" s="5"/>
       <c r="D164" s="3" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="E164" s="43">
         <v>1497</v>
@@ -42122,7 +42116,7 @@
       </c>
       <c r="C165" s="5"/>
       <c r="D165" s="3" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="E165" s="43">
         <v>2944</v>
@@ -42223,7 +42217,7 @@
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B172" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C172" s="5"/>
       <c r="D172" s="3" t="s">
@@ -42287,7 +42281,7 @@
       </c>
       <c r="C176" s="5"/>
       <c r="D176" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E176" s="43">
         <v>1200</v>
@@ -42302,7 +42296,7 @@
       </c>
       <c r="C177" s="5"/>
       <c r="D177" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E177" s="43">
         <v>280</v>
@@ -42422,7 +42416,7 @@
       </c>
       <c r="C185" s="5"/>
       <c r="D185" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E185" s="43">
         <v>224.18</v>
@@ -42452,7 +42446,7 @@
       </c>
       <c r="C187" s="5"/>
       <c r="D187" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E187" s="43">
         <v>250</v>
@@ -42557,7 +42551,7 @@
       </c>
       <c r="C194" s="5"/>
       <c r="D194" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E194" s="43">
         <v>80</v>
@@ -42617,7 +42611,7 @@
       </c>
       <c r="C198" s="5"/>
       <c r="D198" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E198" s="43">
         <v>200</v>
@@ -42632,7 +42626,7 @@
       </c>
       <c r="C199" s="5"/>
       <c r="D199" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E199" s="43">
         <v>150</v>
@@ -42748,7 +42742,7 @@
     </row>
     <row r="207" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B207" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C207" s="5"/>
       <c r="D207" s="3" t="s">
@@ -42827,7 +42821,7 @@
       </c>
       <c r="C212" s="5"/>
       <c r="D212" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E212" s="43">
         <v>100</v>
@@ -42868,7 +42862,7 @@
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B215" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C215" s="5"/>
       <c r="D215" s="3" t="s">
@@ -42887,7 +42881,7 @@
       </c>
       <c r="C216" s="5"/>
       <c r="D216" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E216" s="43">
         <v>420</v>
@@ -42928,11 +42922,11 @@
     </row>
     <row r="219" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B219" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C219" s="5"/>
       <c r="D219" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E219" s="43">
         <v>30</v>
@@ -43018,7 +43012,7 @@
     </row>
     <row r="225" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B225" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C225" s="5"/>
       <c r="D225" s="3" t="s">
@@ -43183,7 +43177,7 @@
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B236" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C236" s="5"/>
       <c r="D236" s="3" t="s">
@@ -43307,7 +43301,7 @@
       </c>
       <c r="C244" s="5"/>
       <c r="D244" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E244" s="43">
         <v>78</v>
@@ -43412,7 +43406,7 @@
       </c>
       <c r="C251" s="5"/>
       <c r="D251" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E251" s="43">
         <v>580</v>
@@ -43457,7 +43451,7 @@
       </c>
       <c r="C254" s="5"/>
       <c r="D254" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="E254" s="43">
         <v>12156</v>
@@ -43472,7 +43466,7 @@
       </c>
       <c r="C255" s="5"/>
       <c r="D255" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="E255" s="43">
         <v>16800</v>
@@ -43483,11 +43477,11 @@
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B256" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C256" s="5"/>
       <c r="D256" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E256" s="43">
         <v>97</v>
@@ -43738,7 +43732,7 @@
     </row>
     <row r="273" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B273" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C273" s="5"/>
       <c r="D273" s="3" t="s">
@@ -43905,7 +43899,7 @@
       </c>
       <c r="C284" s="5"/>
       <c r="D284" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E284" s="43">
         <v>7000</v>
@@ -43965,7 +43959,7 @@
       </c>
       <c r="C288" s="5"/>
       <c r="D288" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E288" s="43">
         <v>432</v>
@@ -44130,7 +44124,7 @@
       </c>
       <c r="C299" s="5"/>
       <c r="D299" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E299" s="43">
         <v>50</v>
@@ -44145,7 +44139,7 @@
       </c>
       <c r="C300" s="5"/>
       <c r="D300" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E300" s="43">
         <v>65</v>
@@ -44325,7 +44319,7 @@
       </c>
       <c r="C312" s="5"/>
       <c r="D312" s="3" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="E312" s="43">
         <v>1460</v>
@@ -44385,7 +44379,7 @@
       </c>
       <c r="C316" s="5"/>
       <c r="D316" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="E316" s="43">
         <v>2096</v>
@@ -44475,7 +44469,7 @@
       </c>
       <c r="C322" s="5"/>
       <c r="D322" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E322" s="43">
         <v>213.6</v>
@@ -44625,7 +44619,7 @@
       </c>
       <c r="C332" s="5"/>
       <c r="D332" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E332" s="43">
         <v>200</v>
@@ -44640,7 +44634,7 @@
       </c>
       <c r="C333" s="5"/>
       <c r="D333" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E333" s="43">
         <v>161.30000000000001</v>
@@ -44655,7 +44649,7 @@
       </c>
       <c r="C334" s="5"/>
       <c r="D334" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E334" s="43">
         <v>110</v>
@@ -44685,7 +44679,7 @@
       </c>
       <c r="C336" s="5"/>
       <c r="D336" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E336" s="43">
         <v>80</v>
@@ -44700,7 +44694,7 @@
       </c>
       <c r="C337" s="5"/>
       <c r="D337" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E337" s="43">
         <v>30</v>
@@ -44730,7 +44724,7 @@
       </c>
       <c r="C339" s="5"/>
       <c r="D339" s="3" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="E339" s="43">
         <v>2967</v>
@@ -44790,7 +44784,7 @@
       </c>
       <c r="C343" s="5"/>
       <c r="D343" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E343" s="43">
         <v>510</v>
@@ -44835,7 +44829,7 @@
       </c>
       <c r="C346" s="5"/>
       <c r="D346" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="E346" s="43">
         <v>10002</v>
@@ -44846,7 +44840,7 @@
     </row>
     <row r="347" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B347" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C347" s="5"/>
       <c r="D347" s="3"/>
@@ -44863,7 +44857,7 @@
       </c>
       <c r="C348" s="5"/>
       <c r="D348" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E348" s="43">
         <v>95</v>
@@ -44979,11 +44973,11 @@
     </row>
     <row r="356" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B356" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C356" s="5"/>
       <c r="D356" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E356" s="43">
         <v>30</v>
@@ -45058,7 +45052,7 @@
       </c>
       <c r="C361" s="5"/>
       <c r="D361" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="E361" s="43">
         <v>2858</v>
@@ -45073,7 +45067,7 @@
       </c>
       <c r="C362" s="5"/>
       <c r="D362" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="E362" s="43">
         <v>2150</v>
@@ -45313,7 +45307,7 @@
       </c>
       <c r="C378" s="5"/>
       <c r="D378" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E378" s="43">
         <v>16</v>
@@ -45328,7 +45322,7 @@
       </c>
       <c r="C379" s="5"/>
       <c r="D379" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E379" s="43">
         <v>16</v>
@@ -45598,7 +45592,7 @@
       </c>
       <c r="C397" s="5"/>
       <c r="D397" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E397" s="43">
         <v>250</v>
@@ -45643,7 +45637,7 @@
       </c>
       <c r="C400" s="5"/>
       <c r="D400" s="3" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="E400" s="43">
         <v>690</v>
@@ -45688,7 +45682,7 @@
       </c>
       <c r="C403" s="5"/>
       <c r="D403" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E403" s="43">
         <v>120</v>
@@ -45838,7 +45832,7 @@
       </c>
       <c r="C413" s="5"/>
       <c r="D413" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E413" s="43">
         <v>380</v>
@@ -46093,7 +46087,7 @@
       </c>
       <c r="C430" s="5"/>
       <c r="D430" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E430" s="43">
         <v>1510</v>
@@ -46378,7 +46372,7 @@
       </c>
       <c r="C449" s="5"/>
       <c r="D449" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E449" s="43">
         <v>300</v>
@@ -63923,7 +63917,7 @@
       </c>
       <c r="C2945" s="24"/>
       <c r="D2945" s="24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E2945" s="46">
         <v>40</v>

--- a/data/manutencao.xlsx
+++ b/data/manutencao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/gabriela_costa_jrferragens_com/Documents/Transportes/ARQUIVOS TRANSPORTE/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1115" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A6139DC-8521-4607-961A-5B98739BE878}"/>
+  <xr:revisionPtr revIDLastSave="1189" documentId="13_ncr:1_{1AC0764F-B6E5-4591-8DB7-B0B61D6064FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDD0C52D-5343-4197-8915-DAFF467E1586}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2025" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
+    <workbookView xWindow="28680" yWindow="1050" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3078" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3111" uniqueCount="186">
   <si>
     <t>Custo</t>
   </si>
@@ -590,6 +590,15 @@
   </si>
   <si>
     <t>bombas injetoras</t>
+  </si>
+  <si>
+    <t>HJ PNEUS</t>
+  </si>
+  <si>
+    <t>BORRACHARIA</t>
+  </si>
+  <si>
+    <t>BORRACHARIA BANDEIRANTES</t>
   </si>
 </sst>
 </file>
@@ -17468,10 +17477,19 @@
       </c>
     </row>
     <row r="1080" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1080" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1080" s="7"/>
+      <c r="B1080" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1080" s="5"/>
+      <c r="D1080" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1080" s="43">
+        <v>54</v>
+      </c>
+      <c r="F1080" s="7">
+        <v>45992</v>
+      </c>
     </row>
     <row r="1081" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B1081" s="11"/>
@@ -46517,116 +46535,243 @@
       </c>
     </row>
     <row r="459" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B459" s="11"/>
+      <c r="B459" s="25" t="s">
+        <v>27</v>
+      </c>
       <c r="C459" s="5"/>
-      <c r="D459" s="3"/>
-      <c r="E459" s="43"/>
-      <c r="F459" s="7"/>
+      <c r="D459" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E459" s="43">
+        <v>160</v>
+      </c>
+      <c r="F459" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="460" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B460" s="11"/>
+      <c r="B460" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="C460" s="5"/>
-      <c r="D460" s="3"/>
-      <c r="E460" s="43"/>
-      <c r="F460" s="7"/>
+      <c r="D460" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E460" s="43">
+        <v>755</v>
+      </c>
+      <c r="F460" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="461" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B461" s="11"/>
+      <c r="B461" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="C461" s="5"/>
-      <c r="D461" s="3"/>
-      <c r="E461" s="43"/>
-      <c r="F461" s="7"/>
+      <c r="D461" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E461" s="43">
+        <v>250</v>
+      </c>
+      <c r="F461" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="462" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B462" s="11"/>
+      <c r="B462" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="C462" s="5"/>
-      <c r="D462" s="3"/>
-      <c r="E462" s="43"/>
-      <c r="F462" s="7"/>
+      <c r="D462" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E462" s="43">
+        <v>160</v>
+      </c>
+      <c r="F462" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="463" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B463" s="11"/>
+      <c r="B463" s="11" t="s">
+        <v>6</v>
+      </c>
       <c r="C463" s="5"/>
-      <c r="D463" s="3"/>
-      <c r="E463" s="43"/>
-      <c r="F463" s="7"/>
+      <c r="D463" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E463" s="43">
+        <v>70</v>
+      </c>
+      <c r="F463" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="464" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B464" s="11"/>
+      <c r="B464" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="C464" s="5"/>
-      <c r="D464" s="3"/>
-      <c r="E464" s="43"/>
-      <c r="F464" s="7"/>
+      <c r="D464" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E464" s="43">
+        <v>33</v>
+      </c>
+      <c r="F464" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="465" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B465" s="11"/>
+      <c r="B465" s="11" t="s">
+        <v>26</v>
+      </c>
       <c r="C465" s="5"/>
-      <c r="D465" s="3"/>
-      <c r="E465" s="43"/>
-      <c r="F465" s="7"/>
+      <c r="D465" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E465" s="43">
+        <v>910</v>
+      </c>
+      <c r="F465" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="466" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B466" s="11"/>
+      <c r="B466" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C466" s="5"/>
-      <c r="D466" s="3"/>
-      <c r="E466" s="43"/>
-      <c r="F466" s="7"/>
+      <c r="D466" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E466" s="43">
+        <v>1370</v>
+      </c>
+      <c r="F466" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="467" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B467" s="11"/>
+      <c r="B467" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="C467" s="5"/>
-      <c r="D467" s="3"/>
-      <c r="E467" s="43"/>
-      <c r="F467" s="7"/>
+      <c r="D467" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E467" s="43">
+        <v>720</v>
+      </c>
+      <c r="F467" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="468" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B468" s="11"/>
+      <c r="B468" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="C468" s="5"/>
-      <c r="D468" s="3"/>
-      <c r="E468" s="43"/>
-      <c r="F468" s="7"/>
+      <c r="D468" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E468" s="43">
+        <v>1500</v>
+      </c>
+      <c r="F468" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="469" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B469" s="11"/>
+      <c r="B469" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="C469" s="5"/>
-      <c r="D469" s="3"/>
-      <c r="E469" s="43"/>
-      <c r="F469" s="7"/>
+      <c r="D469" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E469" s="43">
+        <v>460</v>
+      </c>
+      <c r="F469" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="470" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B470" s="11"/>
+      <c r="B470" s="11" t="s">
+        <v>180</v>
+      </c>
       <c r="C470" s="5"/>
-      <c r="D470" s="3"/>
-      <c r="E470" s="43"/>
-      <c r="F470" s="7"/>
+      <c r="D470" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E470" s="43">
+        <v>50</v>
+      </c>
+      <c r="F470" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="471" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B471" s="11"/>
+      <c r="B471" s="11" t="s">
+        <v>180</v>
+      </c>
       <c r="C471" s="5"/>
-      <c r="D471" s="3"/>
-      <c r="E471" s="43"/>
-      <c r="F471" s="7"/>
+      <c r="D471" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E471" s="43">
+        <v>30</v>
+      </c>
+      <c r="F471" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="472" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B472" s="11"/>
-      <c r="C472" s="5"/>
-      <c r="D472" s="3"/>
-      <c r="E472" s="43"/>
-      <c r="F472" s="7"/>
+      <c r="B472" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D472" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E472" s="44">
+        <v>161.30000000000001</v>
+      </c>
+      <c r="F472" s="39">
+        <v>46082</v>
+      </c>
     </row>
     <row r="473" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B473" s="11"/>
+      <c r="B473" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="C473" s="5"/>
-      <c r="D473" s="3"/>
-      <c r="E473" s="43"/>
-      <c r="F473" s="7"/>
+      <c r="D473" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E473" s="43">
+        <v>46</v>
+      </c>
+      <c r="F473" s="7">
+        <v>46054</v>
+      </c>
     </row>
     <row r="474" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B474" s="11"/>
+      <c r="B474" s="11" t="s">
+        <v>34</v>
+      </c>
       <c r="C474" s="5"/>
-      <c r="D474" s="3"/>
-      <c r="E474" s="43"/>
-      <c r="F474" s="7"/>
+      <c r="D474" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E474" s="43">
+        <v>144</v>
+      </c>
+      <c r="F474" s="7">
+        <v>46113</v>
+      </c>
     </row>
     <row r="475" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B475" s="11"/>
